--- a/FPGA_Performance_Comparison_Red_Small.xlsx
+++ b/FPGA_Performance_Comparison_Red_Small.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/DanielBiswas/Desktop/Documents/University/Year 5/Semester 1/AMME4112/Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510008D3-67F3-324A-83A8-76372364EB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C25AD4C-C3B2-BA47-B74B-D9073EF6CA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17760" xr2:uid="{49DEC02E-5D37-064F-A7E8-1E1DC7B5FEA1}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="24100" windowHeight="26980" xr2:uid="{49DEC02E-5D37-064F-A7E8-1E1DC7B5FEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="78">
   <si>
     <t>FPGA Implementation</t>
   </si>
@@ -252,6 +252,24 @@
   </si>
   <si>
     <t>Disparity Exact Match Pixels (Out Of 3136)</t>
+  </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>Dino</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Cotton</t>
+  </si>
+  <si>
+    <t>Town</t>
+  </si>
+  <si>
+    <t>Average</t>
   </si>
 </sst>
 </file>
@@ -320,7 +338,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -356,25 +374,22 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -712,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45085A3-2BCA-FA4F-9A9B-A0D6975F9A68}">
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N156"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="15.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="50.83203125" style="3" customWidth="1"/>
@@ -722,31 +737,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
       <c r="J1" s="6"/>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
       <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="14"/>
+      <c r="A2" s="16"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -785,19 +800,19 @@
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="13">
         <v>80</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
       <c r="E3" s="1">
         <v>200</v>
       </c>
       <c r="F3" s="6"/>
-      <c r="G3" s="15">
-        <v>0</v>
-      </c>
-      <c r="H3" s="15"/>
+      <c r="G3" s="13">
+        <v>0</v>
+      </c>
+      <c r="H3" s="13"/>
       <c r="I3" s="1">
         <f t="shared" ref="I3:I4" si="0">E3-B3</f>
         <v>120</v>
@@ -871,10 +886,10 @@
       <c r="C5" s="1">
         <v>136.59</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="16">
         <v>202.43</v>
       </c>
-      <c r="E5" s="14"/>
+      <c r="E5" s="16"/>
       <c r="F5" s="6"/>
       <c r="G5" s="1">
         <f>C5-B5</f>
@@ -929,10 +944,10 @@
       <c r="C7" s="1">
         <v>9776</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="16">
         <v>10129</v>
       </c>
-      <c r="E7" s="14"/>
+      <c r="E7" s="16"/>
       <c r="F7" s="6"/>
       <c r="G7" s="1">
         <f>C7-B7</f>
@@ -971,10 +986,10 @@
       <c r="C8" s="1">
         <v>24289</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="16">
         <v>27731</v>
       </c>
-      <c r="E8" s="14"/>
+      <c r="E8" s="16"/>
       <c r="F8" s="6"/>
       <c r="G8" s="1">
         <f>C8-B8</f>
@@ -1013,10 +1028,10 @@
       <c r="C9" s="1">
         <v>808736</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="16">
         <v>808736</v>
       </c>
-      <c r="E9" s="14"/>
+      <c r="E9" s="16"/>
       <c r="F9" s="6"/>
       <c r="G9" s="1">
         <f>C9-B9</f>
@@ -1055,10 +1070,10 @@
       <c r="C10" s="2">
         <v>12</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="16">
         <v>12</v>
       </c>
-      <c r="E10" s="14"/>
+      <c r="E10" s="16"/>
       <c r="F10" s="6"/>
       <c r="G10" s="1">
         <f>C10-B10</f>
@@ -1283,16 +1298,16 @@
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="1">
         <v>236.58</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="1">
         <v>215.2</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="11">
         <v>237.19</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="1">
         <v>589.1</v>
       </c>
       <c r="F16" s="6"/>
@@ -1327,16 +1342,16 @@
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="1">
         <v>149.08000000000001</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="1">
         <v>141.09</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="11">
         <v>150.4</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="1">
         <v>376.01</v>
       </c>
       <c r="F17" s="6"/>
@@ -1371,16 +1386,16 @@
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="1">
         <v>10.01</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="1">
         <v>8.35</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="11">
         <v>8.4499999999999993</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="1">
         <v>21.14</v>
       </c>
       <c r="F18" s="6"/>
@@ -1415,16 +1430,16 @@
       <c r="A19" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="1">
         <v>7.32</v>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="1">
         <v>6.68</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="11">
         <v>6.65</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="1">
         <v>16.63</v>
       </c>
       <c r="F19" s="6"/>
@@ -1459,16 +1474,16 @@
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="1">
         <v>43.9</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="1">
         <v>43.46</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="11">
         <v>20.58</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="1">
         <v>51.45</v>
       </c>
       <c r="F20" s="6"/>
@@ -1503,16 +1518,16 @@
       <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="1">
         <v>39.6</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="1">
         <v>39.049999999999997</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="11">
         <v>16.54</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="1">
         <v>41.35</v>
       </c>
       <c r="F21" s="6"/>
@@ -1547,16 +1562,16 @@
       <c r="A22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="18">
+      <c r="B22" s="1">
         <v>14.16</v>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="1">
         <v>13.6</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="11">
         <v>37.5</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="1">
         <v>93.76</v>
       </c>
       <c r="F22" s="6"/>
@@ -1591,16 +1606,16 @@
       <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="18">
+      <c r="B23" s="1">
         <v>12.81</v>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="1">
         <v>12.56</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="11">
         <v>35.74</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="1">
         <v>89.34</v>
       </c>
       <c r="F23" s="6"/>
@@ -1635,16 +1650,16 @@
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="1">
         <v>1.68</v>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="1">
         <v>0.57999999999999996</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="11">
         <v>1.4</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="1">
         <v>3.51</v>
       </c>
       <c r="F24" s="6"/>
@@ -1679,16 +1694,16 @@
       <c r="A25" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="18">
+      <c r="B25" s="1">
         <v>0.63</v>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="1">
         <v>0.28000000000000003</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="11">
         <v>0.56999999999999995</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="1">
         <v>1.41</v>
       </c>
       <c r="F25" s="6"/>
@@ -1723,16 +1738,16 @@
       <c r="A26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="18">
+      <c r="B26" s="1">
         <v>64.56</v>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="1">
         <v>56.71</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="11">
         <v>71.53</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="1">
         <v>178.82</v>
       </c>
       <c r="F26" s="6"/>
@@ -1767,16 +1782,16 @@
       <c r="A27" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="1">
         <v>31.62</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="1">
         <v>26.86</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="11">
         <v>34.15</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="1">
         <v>85.38</v>
       </c>
       <c r="F27" s="6"/>
@@ -1811,16 +1826,16 @@
       <c r="A28" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="18">
+      <c r="B28" s="1">
         <v>5.2</v>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="1">
         <v>4.71</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="11">
         <v>5.89</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="1">
         <v>14.73</v>
       </c>
       <c r="F28" s="6"/>
@@ -1855,16 +1870,16 @@
       <c r="A29" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="18">
+      <c r="B29" s="1">
         <v>4.0199999999999996</v>
       </c>
-      <c r="C29" s="18">
+      <c r="C29" s="1">
         <v>3.51</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="11">
         <v>4.51</v>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="1">
         <v>11.27</v>
       </c>
       <c r="F29" s="6"/>
@@ -1899,16 +1914,16 @@
       <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="1">
         <v>55.4</v>
       </c>
-      <c r="C30" s="18">
+      <c r="C30" s="1">
         <v>54.02</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="11">
         <v>54.25</v>
       </c>
-      <c r="E30" s="18">
+      <c r="E30" s="1">
         <v>135.62</v>
       </c>
       <c r="F30" s="6"/>
@@ -1943,16 +1958,16 @@
       <c r="A31" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="18">
+      <c r="B31" s="1">
         <v>50.91</v>
       </c>
-      <c r="C31" s="18">
+      <c r="C31" s="1">
         <v>49.98</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="11">
         <v>49.99</v>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="1">
         <v>124.98</v>
       </c>
       <c r="F31" s="6"/>
@@ -2001,27 +2016,23 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="1">
-        <v>0.46843099999999999</v>
-      </c>
-      <c r="C33" s="15">
-        <v>2.0848209999999998</v>
-      </c>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
       <c r="F33" s="6"/>
-      <c r="G33" s="15">
-        <f t="shared" ref="G33:G44" si="11">C33-B33</f>
-        <v>1.6163899999999998</v>
-      </c>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
+      <c r="G33" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
       <c r="J33" s="6"/>
-      <c r="K33" s="13">
-        <f>G33/B33</f>
-        <v>3.4506469469356209</v>
+      <c r="K33" s="13" t="s">
+        <v>74</v>
       </c>
       <c r="L33" s="13"/>
       <c r="M33" s="13"/>
@@ -2029,377 +2040,373 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="1">
+        <v>0.46843099999999999</v>
+      </c>
+      <c r="C34" s="13">
+        <v>2.0848209999999998</v>
+      </c>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="13">
+        <f t="shared" ref="G34:G45" si="11">C34-B34</f>
+        <v>1.6163899999999998</v>
+      </c>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="14">
+        <f>G34/B34</f>
+        <v>3.4506469469356209</v>
+      </c>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="6"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B35" s="1">
         <v>0.34279300000000001</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C35" s="13">
         <v>0.91198999999999997</v>
       </c>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="15">
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="13">
         <f t="shared" si="11"/>
         <v>0.56919699999999995</v>
       </c>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="13">
-        <f t="shared" ref="K34:K44" si="12">G34/B34</f>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="14">
+        <f t="shared" ref="K35" si="12">G35/B35</f>
         <v>1.6604685626602642</v>
       </c>
-      <c r="L34" s="13"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="6"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="6"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="1">
-        <v>0</v>
-      </c>
-      <c r="C35" s="15">
+      <c r="B36" s="1">
+        <v>0</v>
+      </c>
+      <c r="C36" s="13">
         <v>1</v>
       </c>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="15">
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="13">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="13" t="s">
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="L35" s="13"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="6"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="6"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="1">
-        <v>0</v>
-      </c>
-      <c r="C36" s="15">
+      <c r="B37" s="1">
+        <v>0</v>
+      </c>
+      <c r="C37" s="13">
         <v>1</v>
       </c>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="15">
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="13">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="13" t="s">
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="L36" s="13"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="6"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="6"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B38" s="1">
         <v>-3</v>
       </c>
-      <c r="C37" s="15">
-        <v>0</v>
-      </c>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="15">
+      <c r="C38" s="13">
+        <v>0</v>
+      </c>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="13">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="13">
-        <f t="shared" si="12"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="14">
+        <f t="shared" ref="K38:K45" si="13">G38/B38</f>
         <v>-1</v>
       </c>
-      <c r="L37" s="13"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="6"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="6"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B39" s="1">
         <v>1</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C39" s="13">
         <v>5</v>
       </c>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="15">
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="13">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="13">
-        <f t="shared" si="12"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="14">
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
-      <c r="L38" s="13"/>
-      <c r="M38" s="13"/>
-      <c r="N38" s="6"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
+      <c r="L39" s="14"/>
+      <c r="M39" s="14"/>
+      <c r="N39" s="6"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B40" s="1">
         <v>7.5959820000000002</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C40" s="13">
         <v>7.1970660000000004</v>
       </c>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="15">
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="13">
         <f t="shared" si="11"/>
         <v>-0.39891599999999983</v>
       </c>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="13">
-        <f t="shared" si="12"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="14">
+        <f t="shared" si="13"/>
         <v>-5.2516712124910221E-2</v>
       </c>
-      <c r="L39" s="13"/>
-      <c r="M39" s="13"/>
-      <c r="N39" s="6"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="6"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A41" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B41" s="1">
         <v>8</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C41" s="13">
         <v>7</v>
       </c>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="15">
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="13">
         <f t="shared" si="11"/>
         <v>-1</v>
       </c>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="13">
-        <f t="shared" si="12"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="14">
+        <f t="shared" si="13"/>
         <v>-0.125</v>
       </c>
-      <c r="L40" s="13"/>
-      <c r="M40" s="13"/>
-      <c r="N40" s="6"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="1">
-        <v>8</v>
-      </c>
-      <c r="C41" s="15">
-        <v>8</v>
-      </c>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="15">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="13">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L41" s="13"/>
-      <c r="M41" s="13"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="14"/>
       <c r="N41" s="6"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="1">
+        <v>8</v>
+      </c>
+      <c r="C42" s="13">
+        <v>8</v>
+      </c>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="13">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="14">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="6"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A43" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B43" s="1">
         <v>5</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C43" s="13">
         <v>4</v>
       </c>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="15">
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="13">
         <f t="shared" si="11"/>
         <v>-1</v>
       </c>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="13">
-        <f t="shared" si="12"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="14">
+        <f t="shared" si="13"/>
         <v>-0.2</v>
       </c>
-      <c r="L42" s="13"/>
-      <c r="M42" s="13"/>
-      <c r="N42" s="6"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
+      <c r="L43" s="14"/>
+      <c r="M43" s="14"/>
+      <c r="N43" s="6"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B44" s="1">
         <v>2234</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C44" s="13">
         <v>1454</v>
       </c>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="15">
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="13">
         <f t="shared" si="11"/>
         <v>-780</v>
       </c>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="13">
-        <f t="shared" si="12"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="14">
+        <f t="shared" si="13"/>
         <v>-0.34914950760966873</v>
       </c>
-      <c r="L43" s="13"/>
-      <c r="M43" s="13"/>
-      <c r="N43" s="6"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
+      <c r="L44" s="14"/>
+      <c r="M44" s="14"/>
+      <c r="N44" s="6"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B45" s="5">
         <v>0.71237245000000005</v>
       </c>
-      <c r="C44" s="16">
+      <c r="C45" s="15">
         <v>0.46364796000000003</v>
       </c>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="15">
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="13">
         <f t="shared" si="11"/>
         <v>-0.24872449000000002</v>
       </c>
-      <c r="H44" s="15"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="13">
-        <f t="shared" si="12"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="14">
+        <f t="shared" si="13"/>
         <v>-0.34914950739602579</v>
       </c>
-      <c r="L44" s="13"/>
-      <c r="M44" s="13"/>
-      <c r="N44" s="6"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A45" s="7"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="8"/>
+      <c r="L45" s="14"/>
+      <c r="M45" s="14"/>
       <c r="N45" s="6"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" s="1">
-        <v>15.246810999999999</v>
-      </c>
-      <c r="C46" s="15">
-        <v>3.3973209999999998</v>
-      </c>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
+      <c r="A46" s="7"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="8"/>
       <c r="F46" s="6"/>
-      <c r="G46" s="15">
-        <f t="shared" ref="G46:G57" si="13">C46-B46</f>
-        <v>-11.849489999999999</v>
-      </c>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
       <c r="J46" s="6"/>
-      <c r="K46" s="13">
-        <f>G46/B46</f>
-        <v>-0.77717825714505151</v>
-      </c>
-      <c r="L46" s="13"/>
-      <c r="M46" s="13"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
       <c r="N46" s="6"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B47" s="1">
-        <v>2.0593110000000001</v>
-      </c>
-      <c r="C47" s="15">
-        <v>1.760842</v>
-      </c>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
       <c r="F47" s="6"/>
-      <c r="G47" s="15">
-        <f t="shared" si="13"/>
-        <v>-0.2984690000000001</v>
-      </c>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
+      <c r="G47" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
       <c r="J47" s="6"/>
-      <c r="K47" s="13">
-        <f t="shared" ref="K47:K57" si="14">G47/B47</f>
-        <v>-0.14493634035849859</v>
+      <c r="K47" s="13" t="s">
+        <v>74</v>
       </c>
       <c r="L47" s="13"/>
       <c r="M47" s="13"/>
@@ -2407,369 +2414,375 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B48" s="1">
-        <v>2</v>
-      </c>
-      <c r="C48" s="15">
-        <v>2</v>
-      </c>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
+        <v>15.246810999999999</v>
+      </c>
+      <c r="C48" s="13">
+        <v>3.3973209999999998</v>
+      </c>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
       <c r="F48" s="6"/>
-      <c r="G48" s="15">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
+      <c r="G48" s="13">
+        <f t="shared" ref="G48:G59" si="14">C48-B48</f>
+        <v>-11.849489999999999</v>
+      </c>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
       <c r="J48" s="6"/>
-      <c r="K48" s="13">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="L48" s="13"/>
-      <c r="M48" s="13"/>
+      <c r="K48" s="14">
+        <f>G48/B48</f>
+        <v>-0.77717825714505151</v>
+      </c>
+      <c r="L48" s="14"/>
+      <c r="M48" s="14"/>
       <c r="N48" s="6"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B49" s="1">
-        <v>-2</v>
-      </c>
-      <c r="C49" s="15">
-        <v>-2</v>
-      </c>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
+        <v>2.0593110000000001</v>
+      </c>
+      <c r="C49" s="13">
+        <v>1.760842</v>
+      </c>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
       <c r="F49" s="6"/>
-      <c r="G49" s="15">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
+      <c r="G49" s="13">
+        <f t="shared" si="14"/>
+        <v>-0.2984690000000001</v>
+      </c>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
       <c r="J49" s="6"/>
-      <c r="K49" s="13">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="L49" s="13"/>
-      <c r="M49" s="13"/>
+      <c r="K49" s="14">
+        <f t="shared" ref="K49:K59" si="15">G49/B49</f>
+        <v>-0.14493634035849859</v>
+      </c>
+      <c r="L49" s="14"/>
+      <c r="M49" s="14"/>
       <c r="N49" s="6"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B50" s="1">
-        <v>-3</v>
-      </c>
-      <c r="C50" s="15">
-        <v>-3</v>
-      </c>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
+        <v>2</v>
+      </c>
+      <c r="C50" s="13">
+        <v>2</v>
+      </c>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
       <c r="F50" s="6"/>
-      <c r="G50" s="15">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H50" s="15"/>
-      <c r="I50" s="15"/>
+      <c r="G50" s="13">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
       <c r="J50" s="6"/>
-      <c r="K50" s="13">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="L50" s="13"/>
-      <c r="M50" s="13"/>
+      <c r="K50" s="14">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="L50" s="14"/>
+      <c r="M50" s="14"/>
       <c r="N50" s="6"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B51" s="1">
-        <v>90</v>
-      </c>
-      <c r="C51" s="15">
-        <v>3</v>
-      </c>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
+        <v>-2</v>
+      </c>
+      <c r="C51" s="13">
+        <v>-2</v>
+      </c>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
       <c r="F51" s="6"/>
-      <c r="G51" s="15">
-        <f t="shared" si="13"/>
-        <v>-87</v>
-      </c>
-      <c r="H51" s="15"/>
-      <c r="I51" s="15"/>
+      <c r="G51" s="13">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
       <c r="J51" s="6"/>
-      <c r="K51" s="13">
-        <f t="shared" si="14"/>
-        <v>-0.96666666666666667</v>
-      </c>
-      <c r="L51" s="13"/>
-      <c r="M51" s="13"/>
+      <c r="K51" s="14">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="L51" s="14"/>
+      <c r="M51" s="14"/>
       <c r="N51" s="6"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B52" s="1">
-        <v>6.7799740000000002</v>
-      </c>
-      <c r="C52" s="15">
-        <v>6.0893110000000004</v>
-      </c>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
+        <v>-3</v>
+      </c>
+      <c r="C52" s="13">
+        <v>-3</v>
+      </c>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
       <c r="F52" s="6"/>
-      <c r="G52" s="15">
-        <f t="shared" si="13"/>
-        <v>-0.6906629999999998</v>
-      </c>
-      <c r="H52" s="15"/>
-      <c r="I52" s="15"/>
+      <c r="G52" s="13">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
       <c r="J52" s="6"/>
-      <c r="K52" s="13">
-        <f t="shared" si="14"/>
-        <v>-0.10186808975963621</v>
-      </c>
-      <c r="L52" s="13"/>
-      <c r="M52" s="13"/>
+      <c r="K52" s="14">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="L52" s="14"/>
+      <c r="M52" s="14"/>
       <c r="N52" s="6"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B53" s="1">
-        <v>7</v>
-      </c>
-      <c r="C53" s="15">
-        <v>7</v>
-      </c>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
+        <v>90</v>
+      </c>
+      <c r="C53" s="13">
+        <v>3</v>
+      </c>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
       <c r="F53" s="6"/>
-      <c r="G53" s="15">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H53" s="15"/>
-      <c r="I53" s="15"/>
+      <c r="G53" s="13">
+        <f t="shared" si="14"/>
+        <v>-87</v>
+      </c>
+      <c r="H53" s="13"/>
+      <c r="I53" s="13"/>
       <c r="J53" s="6"/>
-      <c r="K53" s="13">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="L53" s="13"/>
-      <c r="M53" s="13"/>
+      <c r="K53" s="14">
+        <f t="shared" si="15"/>
+        <v>-0.96666666666666667</v>
+      </c>
+      <c r="L53" s="14"/>
+      <c r="M53" s="14"/>
       <c r="N53" s="6"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B54" s="1">
-        <v>8</v>
-      </c>
-      <c r="C54" s="15">
-        <v>8</v>
-      </c>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
+        <v>6.7799740000000002</v>
+      </c>
+      <c r="C54" s="13">
+        <v>6.0893110000000004</v>
+      </c>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
       <c r="F54" s="6"/>
-      <c r="G54" s="15">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H54" s="15"/>
-      <c r="I54" s="15"/>
+      <c r="G54" s="13">
+        <f t="shared" si="14"/>
+        <v>-0.6906629999999998</v>
+      </c>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
       <c r="J54" s="6"/>
-      <c r="K54" s="13">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="L54" s="13"/>
-      <c r="M54" s="13"/>
+      <c r="K54" s="14">
+        <f t="shared" si="15"/>
+        <v>-0.10186808975963621</v>
+      </c>
+      <c r="L54" s="14"/>
+      <c r="M54" s="14"/>
       <c r="N54" s="6"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B55" s="1">
-        <v>3</v>
-      </c>
-      <c r="C55" s="15">
-        <v>5</v>
-      </c>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
+        <v>7</v>
+      </c>
+      <c r="C55" s="13">
+        <v>7</v>
+      </c>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
       <c r="F55" s="6"/>
-      <c r="G55" s="15">
-        <f t="shared" si="13"/>
-        <v>2</v>
-      </c>
-      <c r="H55" s="15"/>
-      <c r="I55" s="15"/>
+      <c r="G55" s="13">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
       <c r="J55" s="6"/>
-      <c r="K55" s="13">
-        <f t="shared" si="14"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="L55" s="13"/>
-      <c r="M55" s="13"/>
+      <c r="K55" s="14">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="L55" s="14"/>
+      <c r="M55" s="14"/>
       <c r="N55" s="6"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B56" s="1">
-        <v>72</v>
-      </c>
-      <c r="C56" s="15">
-        <v>93</v>
-      </c>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
+        <v>8</v>
+      </c>
+      <c r="C56" s="13">
+        <v>8</v>
+      </c>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
       <c r="F56" s="6"/>
-      <c r="G56" s="15">
-        <f t="shared" si="13"/>
-        <v>21</v>
-      </c>
-      <c r="H56" s="15"/>
-      <c r="I56" s="15"/>
+      <c r="G56" s="13">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
       <c r="J56" s="6"/>
-      <c r="K56" s="13">
-        <f t="shared" si="14"/>
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="L56" s="13"/>
-      <c r="M56" s="13"/>
+      <c r="K56" s="14">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="L56" s="14"/>
+      <c r="M56" s="14"/>
       <c r="N56" s="6"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B57" s="5">
-        <v>2.2959179999999999E-2</v>
+        <v>52</v>
+      </c>
+      <c r="B57" s="1">
+        <v>3</v>
       </c>
       <c r="C57" s="13">
-        <v>2.9655609999999999E-2</v>
+        <v>5</v>
       </c>
       <c r="D57" s="13"/>
       <c r="E57" s="13"/>
       <c r="F57" s="6"/>
-      <c r="G57" s="15">
-        <f t="shared" si="13"/>
-        <v>6.6964299999999997E-3</v>
-      </c>
-      <c r="H57" s="15"/>
-      <c r="I57" s="15"/>
+      <c r="G57" s="13">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
       <c r="J57" s="6"/>
-      <c r="K57" s="13">
+      <c r="K57" s="14">
+        <f t="shared" si="15"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="L57" s="14"/>
+      <c r="M57" s="14"/>
+      <c r="N57" s="6"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A58" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B58" s="1">
+        <v>72</v>
+      </c>
+      <c r="C58" s="13">
+        <v>93</v>
+      </c>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="13">
         <f t="shared" si="14"/>
-        <v>0.29166677555557297</v>
-      </c>
-      <c r="L57" s="13"/>
-      <c r="M57" s="13"/>
-      <c r="N57" s="6"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A58" s="7"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8"/>
+        <v>21</v>
+      </c>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
       <c r="J58" s="6"/>
-      <c r="K58" s="8"/>
-      <c r="L58" s="8"/>
-      <c r="M58" s="8"/>
+      <c r="K58" s="14">
+        <f t="shared" si="15"/>
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L58" s="14"/>
+      <c r="M58" s="14"/>
       <c r="N58" s="6"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B59" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
+        <v>53</v>
+      </c>
+      <c r="B59" s="5">
+        <v>2.2959179999999999E-2</v>
+      </c>
+      <c r="C59" s="14">
+        <v>2.9655609999999999E-2</v>
+      </c>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
       <c r="F59" s="6"/>
-      <c r="G59" s="15">
-        <v>0</v>
-      </c>
-      <c r="H59" s="15"/>
-      <c r="I59" s="15"/>
+      <c r="G59" s="13">
+        <f t="shared" si="14"/>
+        <v>6.6964299999999997E-3</v>
+      </c>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
       <c r="J59" s="6"/>
-      <c r="K59" s="17">
-        <v>0</v>
-      </c>
-      <c r="L59" s="17"/>
-      <c r="M59" s="17"/>
+      <c r="K59" s="14">
+        <f t="shared" si="15"/>
+        <v>0.29166677555557297</v>
+      </c>
+      <c r="L59" s="14"/>
+      <c r="M59" s="14"/>
       <c r="N59" s="6"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A60" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B60" s="15">
-        <v>1</v>
-      </c>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
+      <c r="A60" s="7"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="8"/>
       <c r="F60" s="6"/>
-      <c r="G60" s="15">
-        <v>0</v>
-      </c>
-      <c r="H60" s="15"/>
-      <c r="I60" s="15"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="8"/>
       <c r="J60" s="6"/>
-      <c r="K60" s="13">
-        <f>G60/B60</f>
-        <v>0</v>
-      </c>
-      <c r="L60" s="13"/>
-      <c r="M60" s="13"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="8"/>
+      <c r="M60" s="8"/>
       <c r="N60" s="6"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B61" s="15">
-        <v>69633</v>
-      </c>
-      <c r="C61" s="15"/>
-      <c r="D61" s="15"/>
-      <c r="E61" s="15"/>
+        <v>72</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
       <c r="F61" s="6"/>
-      <c r="G61" s="15">
-        <v>0</v>
-      </c>
-      <c r="H61" s="15"/>
-      <c r="I61" s="15"/>
+      <c r="G61" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
       <c r="J61" s="6"/>
-      <c r="K61" s="13">
-        <f>G61/B61</f>
-        <v>0</v>
+      <c r="K61" s="13" t="s">
+        <v>74</v>
       </c>
       <c r="L61" s="13"/>
       <c r="M61" s="13"/>
@@ -2777,384 +2790,2948 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62" s="15">
-        <v>70350</v>
-      </c>
-      <c r="C62" s="15"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="15"/>
+        <v>32</v>
+      </c>
+      <c r="B62" s="1">
+        <v>0.46843099999999999</v>
+      </c>
+      <c r="C62" s="13">
+        <v>2.6575259999999998</v>
+      </c>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
       <c r="F62" s="6"/>
-      <c r="G62" s="15">
-        <v>0</v>
-      </c>
-      <c r="H62" s="15"/>
-      <c r="I62" s="15"/>
+      <c r="G62" s="13">
+        <f t="shared" ref="G62:G73" si="16">C62-B62</f>
+        <v>2.189095</v>
+      </c>
+      <c r="H62" s="13"/>
+      <c r="I62" s="13"/>
       <c r="J62" s="6"/>
-      <c r="K62" s="13">
+      <c r="K62" s="14">
         <f>G62/B62</f>
-        <v>0</v>
-      </c>
-      <c r="L62" s="13"/>
-      <c r="M62" s="13"/>
+        <v>4.6732496354852691</v>
+      </c>
+      <c r="L62" s="14"/>
+      <c r="M62" s="14"/>
       <c r="N62" s="6"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B63" s="15">
-        <v>74925</v>
-      </c>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
+        <v>33</v>
+      </c>
+      <c r="B63" s="1">
+        <v>0.34279300000000001</v>
+      </c>
+      <c r="C63" s="13">
+        <v>1.2959179999999999</v>
+      </c>
+      <c r="D63" s="13"/>
+      <c r="E63" s="13"/>
       <c r="F63" s="6"/>
-      <c r="G63" s="15">
-        <v>0</v>
-      </c>
-      <c r="H63" s="15"/>
-      <c r="I63" s="15"/>
+      <c r="G63" s="13">
+        <f t="shared" si="16"/>
+        <v>0.95312499999999989</v>
+      </c>
+      <c r="H63" s="13"/>
+      <c r="I63" s="13"/>
       <c r="J63" s="6"/>
-      <c r="K63" s="13">
+      <c r="K63" s="14">
         <f>G63/B63</f>
-        <v>0</v>
-      </c>
-      <c r="L63" s="13"/>
-      <c r="M63" s="13"/>
+        <v>2.7804680959062753</v>
+      </c>
+      <c r="L63" s="14"/>
+      <c r="M63" s="14"/>
       <c r="N63" s="6"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B64" s="15">
-        <f>B63-B60</f>
-        <v>74924</v>
-      </c>
-      <c r="C64" s="15"/>
-      <c r="D64" s="15"/>
-      <c r="E64" s="15"/>
+        <v>34</v>
+      </c>
+      <c r="B64" s="1">
+        <v>0</v>
+      </c>
+      <c r="C64" s="13">
+        <v>1</v>
+      </c>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
       <c r="F64" s="6"/>
-      <c r="G64" s="15">
-        <v>0</v>
-      </c>
-      <c r="H64" s="15"/>
-      <c r="I64" s="15"/>
+      <c r="G64" s="13">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="H64" s="13"/>
+      <c r="I64" s="13"/>
       <c r="J64" s="6"/>
-      <c r="K64" s="13">
-        <f>G64/B64</f>
-        <v>0</v>
-      </c>
-      <c r="L64" s="13"/>
-      <c r="M64" s="13"/>
+      <c r="K64" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="L64" s="14"/>
+      <c r="M64" s="14"/>
       <c r="N64" s="6"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B65" s="15">
-        <f>B64/(B3*10^3)</f>
-        <v>0.93654999999999999</v>
-      </c>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="1">
-        <f>B64/(E3*10^3)</f>
-        <v>0.37462000000000001</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B65" s="1">
+        <v>0</v>
+      </c>
+      <c r="C65" s="13">
+        <v>1</v>
+      </c>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
       <c r="F65" s="6"/>
-      <c r="G65" s="15">
-        <v>0</v>
-      </c>
-      <c r="H65" s="15"/>
-      <c r="I65" s="1">
-        <f>E65-B65</f>
-        <v>-0.56193000000000004</v>
-      </c>
+      <c r="G65" s="13">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="H65" s="13"/>
+      <c r="I65" s="13"/>
       <c r="J65" s="6"/>
-      <c r="K65" s="13">
-        <v>0</v>
-      </c>
-      <c r="L65" s="13"/>
-      <c r="M65" s="5">
-        <f>I65/B65</f>
-        <v>-0.60000000000000009</v>
-      </c>
+      <c r="K65" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="L65" s="14"/>
+      <c r="M65" s="14"/>
       <c r="N65" s="6"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B66" s="15">
-        <f>B63-B61</f>
-        <v>5292</v>
-      </c>
-      <c r="C66" s="15"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="15"/>
+        <v>36</v>
+      </c>
+      <c r="B66" s="1">
+        <v>-3</v>
+      </c>
+      <c r="C66" s="13">
+        <v>-1</v>
+      </c>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
       <c r="F66" s="6"/>
-      <c r="G66" s="15">
-        <v>0</v>
-      </c>
-      <c r="H66" s="15"/>
-      <c r="I66" s="15"/>
+      <c r="G66" s="13">
+        <f t="shared" si="16"/>
+        <v>2</v>
+      </c>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
       <c r="J66" s="6"/>
-      <c r="K66" s="13">
-        <f>G66/B66</f>
-        <v>0</v>
-      </c>
-      <c r="L66" s="13"/>
-      <c r="M66" s="13"/>
+      <c r="K66" s="14">
+        <f t="shared" ref="K66:K73" si="17">G66/B66</f>
+        <v>-0.66666666666666663</v>
+      </c>
+      <c r="L66" s="14"/>
+      <c r="M66" s="14"/>
       <c r="N66" s="6"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B67" s="15">
-        <f>B66/B3</f>
-        <v>66.150000000000006</v>
-      </c>
-      <c r="C67" s="15"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="1">
-        <f>B66/E3</f>
-        <v>26.46</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B67" s="1">
+        <v>1</v>
+      </c>
+      <c r="C67" s="13">
+        <v>6</v>
+      </c>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
       <c r="F67" s="6"/>
-      <c r="G67" s="15">
-        <v>0</v>
-      </c>
-      <c r="H67" s="15"/>
-      <c r="I67" s="1">
-        <f>E67-B67</f>
-        <v>-39.690000000000005</v>
-      </c>
+      <c r="G67" s="13">
+        <f t="shared" si="16"/>
+        <v>5</v>
+      </c>
+      <c r="H67" s="13"/>
+      <c r="I67" s="13"/>
       <c r="J67" s="6"/>
-      <c r="K67" s="13">
-        <v>0</v>
-      </c>
-      <c r="L67" s="13"/>
-      <c r="M67" s="5">
-        <f>I67/B67</f>
-        <v>-0.6</v>
-      </c>
+      <c r="K67" s="14">
+        <f t="shared" si="17"/>
+        <v>5</v>
+      </c>
+      <c r="L67" s="14"/>
+      <c r="M67" s="14"/>
       <c r="N67" s="6"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="B68" s="1">
-        <f>B12*B65</f>
-        <v>617.04596749999996</v>
-      </c>
-      <c r="C68" s="1">
-        <f>C12*B65</f>
-        <v>596.88204600000006</v>
-      </c>
-      <c r="D68" s="11">
-        <f>D12*B65</f>
-        <v>617.60789750000004</v>
-      </c>
-      <c r="E68" s="1">
-        <f t="shared" ref="E68" si="15">E12*E65</f>
-        <v>379.696101</v>
-      </c>
+        <v>7.5959820000000002</v>
+      </c>
+      <c r="C68" s="13">
+        <v>6.7755099999999997</v>
+      </c>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
       <c r="F68" s="6"/>
-      <c r="G68" s="1">
-        <f>C68-B68</f>
-        <v>-20.163921499999901</v>
-      </c>
-      <c r="H68" s="1">
-        <f>D68-B68</f>
-        <v>0.56193000000007487</v>
-      </c>
-      <c r="I68" s="1">
-        <f>E68-B68</f>
-        <v>-237.34986649999996</v>
-      </c>
+      <c r="G68" s="13">
+        <f t="shared" si="16"/>
+        <v>-0.82047200000000053</v>
+      </c>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
       <c r="J68" s="6"/>
-      <c r="K68" s="5">
-        <f>G68/B68</f>
-        <v>-3.267815132427699E-2</v>
-      </c>
-      <c r="L68" s="5">
-        <f>H68/B68</f>
-        <v>9.1067769598555059E-4</v>
-      </c>
-      <c r="M68" s="5"/>
+      <c r="K68" s="14">
+        <f t="shared" si="17"/>
+        <v>-0.10801394737375634</v>
+      </c>
+      <c r="L68" s="14"/>
+      <c r="M68" s="14"/>
       <c r="N68" s="6"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B69" s="1">
+        <v>8</v>
+      </c>
+      <c r="C69" s="13">
+        <v>7</v>
+      </c>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="13">
+        <f t="shared" si="16"/>
+        <v>-1</v>
+      </c>
+      <c r="H69" s="13"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="14">
+        <f t="shared" si="17"/>
+        <v>-0.125</v>
+      </c>
+      <c r="L69" s="14"/>
+      <c r="M69" s="14"/>
+      <c r="N69" s="6"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A70" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B70" s="1">
+        <v>8</v>
+      </c>
+      <c r="C70" s="13">
+        <v>8</v>
+      </c>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="13">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="6"/>
+      <c r="K70" s="14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="L70" s="14"/>
+      <c r="M70" s="14"/>
+      <c r="N70" s="6"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A71" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B71" s="1">
+        <v>5</v>
+      </c>
+      <c r="C71" s="13">
+        <v>4</v>
+      </c>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="13">
+        <f t="shared" si="16"/>
+        <v>-1</v>
+      </c>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="6"/>
+      <c r="K71" s="14">
+        <f t="shared" si="17"/>
+        <v>-0.2</v>
+      </c>
+      <c r="L71" s="14"/>
+      <c r="M71" s="14"/>
+      <c r="N71" s="6"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A72" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B72" s="1">
+        <v>2234</v>
+      </c>
+      <c r="C72" s="13">
+        <v>517</v>
+      </c>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="13">
+        <f t="shared" si="16"/>
+        <v>-1717</v>
+      </c>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="14">
+        <f t="shared" si="17"/>
+        <v>-0.76857654431512978</v>
+      </c>
+      <c r="L72" s="14"/>
+      <c r="M72" s="14"/>
+      <c r="N72" s="6"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A73" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B73" s="5">
+        <v>0.71237245000000005</v>
+      </c>
+      <c r="C73" s="15">
+        <v>0.16485969</v>
+      </c>
+      <c r="D73" s="15"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="13">
+        <f t="shared" si="16"/>
+        <v>-0.54751276000000004</v>
+      </c>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="6"/>
+      <c r="K73" s="14">
+        <f t="shared" si="17"/>
+        <v>-0.76857655008977399</v>
+      </c>
+      <c r="L73" s="14"/>
+      <c r="M73" s="14"/>
+      <c r="N73" s="6"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A74" s="7"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+      <c r="M74" s="8"/>
+      <c r="N74" s="6"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A75" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C75" s="13"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="6"/>
+      <c r="K75" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="L75" s="13"/>
+      <c r="M75" s="13"/>
+      <c r="N75" s="6"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A76" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B76" s="1">
+        <v>15.246810999999999</v>
+      </c>
+      <c r="C76" s="13">
+        <v>0</v>
+      </c>
+      <c r="D76" s="13"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="13">
+        <f t="shared" ref="G76:G87" si="18">C76-B76</f>
+        <v>-15.246810999999999</v>
+      </c>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13"/>
+      <c r="J76" s="6"/>
+      <c r="K76" s="14">
+        <f t="shared" ref="K76:K87" si="19">G76/B76</f>
+        <v>-1</v>
+      </c>
+      <c r="L76" s="14"/>
+      <c r="M76" s="14"/>
+      <c r="N76" s="6"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A77" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B77" s="1">
+        <v>2.0593110000000001</v>
+      </c>
+      <c r="C77" s="13">
+        <v>0</v>
+      </c>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="13">
+        <f t="shared" si="18"/>
+        <v>-2.0593110000000001</v>
+      </c>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="6"/>
+      <c r="K77" s="14">
+        <f t="shared" si="19"/>
+        <v>-1</v>
+      </c>
+      <c r="L77" s="14"/>
+      <c r="M77" s="14"/>
+      <c r="N77" s="6"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A78" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B78" s="1">
+        <v>2</v>
+      </c>
+      <c r="C78" s="13">
+        <v>0</v>
+      </c>
+      <c r="D78" s="13"/>
+      <c r="E78" s="13"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="13">
+        <f t="shared" si="18"/>
+        <v>-2</v>
+      </c>
+      <c r="H78" s="13"/>
+      <c r="I78" s="13"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="14">
+        <f t="shared" si="19"/>
+        <v>-1</v>
+      </c>
+      <c r="L78" s="14"/>
+      <c r="M78" s="14"/>
+      <c r="N78" s="6"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A79" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B79" s="1">
+        <v>-2</v>
+      </c>
+      <c r="C79" s="13">
+        <v>0</v>
+      </c>
+      <c r="D79" s="13"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="13">
+        <f t="shared" si="18"/>
+        <v>2</v>
+      </c>
+      <c r="H79" s="13"/>
+      <c r="I79" s="13"/>
+      <c r="J79" s="6"/>
+      <c r="K79" s="14">
+        <f t="shared" si="19"/>
+        <v>-1</v>
+      </c>
+      <c r="L79" s="14"/>
+      <c r="M79" s="14"/>
+      <c r="N79" s="6"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A80" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B80" s="1">
+        <v>-3</v>
+      </c>
+      <c r="C80" s="13">
+        <v>0</v>
+      </c>
+      <c r="D80" s="13"/>
+      <c r="E80" s="13"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="13">
+        <f t="shared" si="18"/>
+        <v>3</v>
+      </c>
+      <c r="H80" s="13"/>
+      <c r="I80" s="13"/>
+      <c r="J80" s="6"/>
+      <c r="K80" s="14">
+        <f t="shared" si="19"/>
+        <v>-1</v>
+      </c>
+      <c r="L80" s="14"/>
+      <c r="M80" s="14"/>
+      <c r="N80" s="6"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A81" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B81" s="1">
+        <v>90</v>
+      </c>
+      <c r="C81" s="13">
+        <v>8</v>
+      </c>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="13">
+        <f t="shared" si="18"/>
+        <v>-82</v>
+      </c>
+      <c r="H81" s="13"/>
+      <c r="I81" s="13"/>
+      <c r="J81" s="6"/>
+      <c r="K81" s="14">
+        <f t="shared" si="19"/>
+        <v>-0.91111111111111109</v>
+      </c>
+      <c r="L81" s="14"/>
+      <c r="M81" s="14"/>
+      <c r="N81" s="6"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A82" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B82" s="1">
+        <v>6.7799740000000002</v>
+      </c>
+      <c r="C82" s="13">
+        <v>8</v>
+      </c>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="13">
+        <f t="shared" si="18"/>
+        <v>1.2200259999999998</v>
+      </c>
+      <c r="H82" s="13"/>
+      <c r="I82" s="13"/>
+      <c r="J82" s="6"/>
+      <c r="K82" s="14">
+        <f t="shared" si="19"/>
+        <v>0.17994552781470841</v>
+      </c>
+      <c r="L82" s="14"/>
+      <c r="M82" s="14"/>
+      <c r="N82" s="6"/>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A83" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B83" s="1">
+        <v>7</v>
+      </c>
+      <c r="C83" s="13">
+        <v>8</v>
+      </c>
+      <c r="D83" s="13"/>
+      <c r="E83" s="13"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="13">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="H83" s="13"/>
+      <c r="I83" s="13"/>
+      <c r="J83" s="6"/>
+      <c r="K83" s="14">
+        <f t="shared" si="19"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="L83" s="14"/>
+      <c r="M83" s="14"/>
+      <c r="N83" s="6"/>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A84" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B84" s="1">
+        <v>8</v>
+      </c>
+      <c r="C84" s="13">
+        <v>8</v>
+      </c>
+      <c r="D84" s="13"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="13">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="H84" s="13"/>
+      <c r="I84" s="13"/>
+      <c r="J84" s="6"/>
+      <c r="K84" s="14">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="L84" s="14"/>
+      <c r="M84" s="14"/>
+      <c r="N84" s="6"/>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A85" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B85" s="1">
+        <v>3</v>
+      </c>
+      <c r="C85" s="13">
+        <v>8</v>
+      </c>
+      <c r="D85" s="13"/>
+      <c r="E85" s="13"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="13">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="H85" s="13"/>
+      <c r="I85" s="13"/>
+      <c r="J85" s="6"/>
+      <c r="K85" s="14">
+        <f t="shared" si="19"/>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="L85" s="14"/>
+      <c r="M85" s="14"/>
+      <c r="N85" s="6"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A86" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B86" s="1">
+        <v>72</v>
+      </c>
+      <c r="C86" s="13">
+        <v>3136</v>
+      </c>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="13">
+        <f t="shared" si="18"/>
+        <v>3064</v>
+      </c>
+      <c r="H86" s="13"/>
+      <c r="I86" s="13"/>
+      <c r="J86" s="6"/>
+      <c r="K86" s="14">
+        <f t="shared" si="19"/>
+        <v>42.555555555555557</v>
+      </c>
+      <c r="L86" s="14"/>
+      <c r="M86" s="14"/>
+      <c r="N86" s="6"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A87" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B87" s="5">
+        <v>2.2959179999999999E-2</v>
+      </c>
+      <c r="C87" s="14">
+        <v>1</v>
+      </c>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="13">
+        <f t="shared" si="18"/>
+        <v>0.97704082000000003</v>
+      </c>
+      <c r="H87" s="13"/>
+      <c r="I87" s="13"/>
+      <c r="J87" s="6"/>
+      <c r="K87" s="14">
+        <f t="shared" si="19"/>
+        <v>42.555562524445563</v>
+      </c>
+      <c r="L87" s="14"/>
+      <c r="M87" s="14"/>
+      <c r="N87" s="6"/>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A88" s="7"/>
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="12"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="8"/>
+      <c r="J88" s="6"/>
+      <c r="K88" s="8"/>
+      <c r="L88" s="8"/>
+      <c r="M88" s="8"/>
+      <c r="N88" s="6"/>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A89" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C89" s="13"/>
+      <c r="D89" s="13"/>
+      <c r="E89" s="13"/>
+      <c r="F89" s="6"/>
+      <c r="G89" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H89" s="13"/>
+      <c r="I89" s="13"/>
+      <c r="J89" s="6"/>
+      <c r="K89" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="L89" s="13"/>
+      <c r="M89" s="13"/>
+      <c r="N89" s="6"/>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A90" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B90" s="1">
+        <v>0.46843099999999999</v>
+      </c>
+      <c r="C90" s="13">
+        <v>0.93590600000000002</v>
+      </c>
+      <c r="D90" s="13"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="13">
+        <f t="shared" ref="G90:G101" si="20">C90-B90</f>
+        <v>0.46747500000000003</v>
+      </c>
+      <c r="H90" s="13"/>
+      <c r="I90" s="13"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="14">
+        <f>G90/B90</f>
+        <v>0.99795914446311207</v>
+      </c>
+      <c r="L90" s="14"/>
+      <c r="M90" s="14"/>
+      <c r="N90" s="6"/>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A91" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B91" s="1">
+        <v>0.34279300000000001</v>
+      </c>
+      <c r="C91" s="13">
+        <v>0.419962</v>
+      </c>
+      <c r="D91" s="13"/>
+      <c r="E91" s="13"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="13">
+        <f t="shared" si="20"/>
+        <v>7.7168999999999988E-2</v>
+      </c>
+      <c r="H91" s="13"/>
+      <c r="I91" s="13"/>
+      <c r="J91" s="6"/>
+      <c r="K91" s="14">
+        <f t="shared" ref="K91" si="21">G91/B91</f>
+        <v>0.22511836589428602</v>
+      </c>
+      <c r="L91" s="14"/>
+      <c r="M91" s="14"/>
+      <c r="N91" s="6"/>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A92" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B92" s="1">
+        <v>0</v>
+      </c>
+      <c r="C92" s="13">
+        <v>0</v>
+      </c>
+      <c r="D92" s="13"/>
+      <c r="E92" s="13"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H92" s="13"/>
+      <c r="I92" s="13"/>
+      <c r="J92" s="6"/>
+      <c r="K92" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="L92" s="14"/>
+      <c r="M92" s="14"/>
+      <c r="N92" s="6"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A93" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B93" s="1">
+        <v>0</v>
+      </c>
+      <c r="C93" s="13">
+        <v>0</v>
+      </c>
+      <c r="D93" s="13"/>
+      <c r="E93" s="13"/>
+      <c r="F93" s="6"/>
+      <c r="G93" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H93" s="13"/>
+      <c r="I93" s="13"/>
+      <c r="J93" s="6"/>
+      <c r="K93" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="L93" s="14"/>
+      <c r="M93" s="14"/>
+      <c r="N93" s="6"/>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A94" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B94" s="1">
+        <v>-3</v>
+      </c>
+      <c r="C94" s="13">
+        <v>0</v>
+      </c>
+      <c r="D94" s="13"/>
+      <c r="E94" s="13"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="13">
+        <f t="shared" si="20"/>
+        <v>3</v>
+      </c>
+      <c r="H94" s="13"/>
+      <c r="I94" s="13"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="14">
+        <f t="shared" ref="K94:K101" si="22">G94/B94</f>
+        <v>-1</v>
+      </c>
+      <c r="L94" s="14"/>
+      <c r="M94" s="14"/>
+      <c r="N94" s="6"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A95" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B95" s="1">
+        <v>1</v>
+      </c>
+      <c r="C95" s="13">
+        <v>5</v>
+      </c>
+      <c r="D95" s="13"/>
+      <c r="E95" s="13"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="13">
+        <f t="shared" si="20"/>
+        <v>4</v>
+      </c>
+      <c r="H95" s="13"/>
+      <c r="I95" s="13"/>
+      <c r="J95" s="6"/>
+      <c r="K95" s="14">
+        <f t="shared" si="22"/>
+        <v>4</v>
+      </c>
+      <c r="L95" s="14"/>
+      <c r="M95" s="14"/>
+      <c r="N95" s="6"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A96" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B96" s="1">
+        <v>7.5959820000000002</v>
+      </c>
+      <c r="C96" s="13">
+        <v>7.6584820000000002</v>
+      </c>
+      <c r="D96" s="13"/>
+      <c r="E96" s="13"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="13">
+        <f t="shared" si="20"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="H96" s="13"/>
+      <c r="I96" s="13"/>
+      <c r="J96" s="6"/>
+      <c r="K96" s="14">
+        <f t="shared" si="22"/>
+        <v>8.2280342423138968E-3</v>
+      </c>
+      <c r="L96" s="14"/>
+      <c r="M96" s="14"/>
+      <c r="N96" s="6"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A97" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B97" s="1">
+        <v>8</v>
+      </c>
+      <c r="C97" s="13">
+        <v>8</v>
+      </c>
+      <c r="D97" s="13"/>
+      <c r="E97" s="13"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H97" s="13"/>
+      <c r="I97" s="13"/>
+      <c r="J97" s="6"/>
+      <c r="K97" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L97" s="14"/>
+      <c r="M97" s="14"/>
+      <c r="N97" s="6"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A98" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B98" s="1">
+        <v>8</v>
+      </c>
+      <c r="C98" s="13">
+        <v>8</v>
+      </c>
+      <c r="D98" s="13"/>
+      <c r="E98" s="13"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H98" s="13"/>
+      <c r="I98" s="13"/>
+      <c r="J98" s="6"/>
+      <c r="K98" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L98" s="14"/>
+      <c r="M98" s="14"/>
+      <c r="N98" s="6"/>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A99" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B99" s="1">
+        <v>5</v>
+      </c>
+      <c r="C99" s="13">
+        <v>5</v>
+      </c>
+      <c r="D99" s="13"/>
+      <c r="E99" s="13"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H99" s="13"/>
+      <c r="I99" s="13"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L99" s="14"/>
+      <c r="M99" s="14"/>
+      <c r="N99" s="6"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A100" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B100" s="1">
+        <v>2234</v>
+      </c>
+      <c r="C100" s="13">
+        <v>2321</v>
+      </c>
+      <c r="D100" s="13"/>
+      <c r="E100" s="13"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="13">
+        <f t="shared" si="20"/>
+        <v>87</v>
+      </c>
+      <c r="H100" s="13"/>
+      <c r="I100" s="13"/>
+      <c r="J100" s="6"/>
+      <c r="K100" s="14">
+        <f t="shared" si="22"/>
+        <v>3.8943598925693823E-2</v>
+      </c>
+      <c r="L100" s="14"/>
+      <c r="M100" s="14"/>
+      <c r="N100" s="6"/>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A101" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B101" s="5">
+        <v>0.71237245000000005</v>
+      </c>
+      <c r="C101" s="15">
+        <v>0.74011479999999996</v>
+      </c>
+      <c r="D101" s="15"/>
+      <c r="E101" s="15"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="13">
+        <f t="shared" si="20"/>
+        <v>2.7742349999999916E-2</v>
+      </c>
+      <c r="H101" s="13"/>
+      <c r="I101" s="13"/>
+      <c r="J101" s="6"/>
+      <c r="K101" s="14">
+        <f t="shared" si="22"/>
+        <v>3.8943603167135271E-2</v>
+      </c>
+      <c r="L101" s="14"/>
+      <c r="M101" s="14"/>
+      <c r="N101" s="6"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A102" s="7"/>
+      <c r="B102" s="8"/>
+      <c r="C102" s="8"/>
+      <c r="D102" s="12"/>
+      <c r="E102" s="8"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="8"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="8"/>
+      <c r="J102" s="6"/>
+      <c r="K102" s="8"/>
+      <c r="L102" s="8"/>
+      <c r="M102" s="8"/>
+      <c r="N102" s="6"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A103" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B103" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C103" s="13"/>
+      <c r="D103" s="13"/>
+      <c r="E103" s="13"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H103" s="13"/>
+      <c r="I103" s="13"/>
+      <c r="J103" s="6"/>
+      <c r="K103" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="L103" s="13"/>
+      <c r="M103" s="13"/>
+      <c r="N103" s="6"/>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A104" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B104" s="1">
+        <v>15.246810999999999</v>
+      </c>
+      <c r="C104" s="13">
+        <v>0.10076499999999999</v>
+      </c>
+      <c r="D104" s="13"/>
+      <c r="E104" s="13"/>
+      <c r="F104" s="6"/>
+      <c r="G104" s="13">
+        <f t="shared" ref="G104:G115" si="23">C104-B104</f>
+        <v>-15.146045999999998</v>
+      </c>
+      <c r="H104" s="13"/>
+      <c r="I104" s="13"/>
+      <c r="J104" s="6"/>
+      <c r="K104" s="14">
+        <f>G104/B104</f>
+        <v>-0.99339107699308393</v>
+      </c>
+      <c r="L104" s="14"/>
+      <c r="M104" s="14"/>
+      <c r="N104" s="6"/>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A105" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B105" s="1">
+        <v>2.0593110000000001</v>
+      </c>
+      <c r="C105" s="13">
+        <v>2.6148000000000001E-2</v>
+      </c>
+      <c r="D105" s="13"/>
+      <c r="E105" s="13"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="13">
+        <f t="shared" si="23"/>
+        <v>-2.0331630000000001</v>
+      </c>
+      <c r="H105" s="13"/>
+      <c r="I105" s="13"/>
+      <c r="J105" s="6"/>
+      <c r="K105" s="14">
+        <f t="shared" ref="K105:K115" si="24">G105/B105</f>
+        <v>-0.98730254925069594</v>
+      </c>
+      <c r="L105" s="14"/>
+      <c r="M105" s="14"/>
+      <c r="N105" s="6"/>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A106" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B106" s="1">
+        <v>2</v>
+      </c>
+      <c r="C106" s="13">
+        <v>0</v>
+      </c>
+      <c r="D106" s="13"/>
+      <c r="E106" s="13"/>
+      <c r="F106" s="6"/>
+      <c r="G106" s="13">
+        <f t="shared" si="23"/>
+        <v>-2</v>
+      </c>
+      <c r="H106" s="13"/>
+      <c r="I106" s="13"/>
+      <c r="J106" s="6"/>
+      <c r="K106" s="14">
+        <f t="shared" si="24"/>
+        <v>-1</v>
+      </c>
+      <c r="L106" s="14"/>
+      <c r="M106" s="14"/>
+      <c r="N106" s="6"/>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A107" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B107" s="1">
+        <v>-2</v>
+      </c>
+      <c r="C107" s="13">
+        <v>0</v>
+      </c>
+      <c r="D107" s="13"/>
+      <c r="E107" s="13"/>
+      <c r="F107" s="6"/>
+      <c r="G107" s="13">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+      <c r="H107" s="13"/>
+      <c r="I107" s="13"/>
+      <c r="J107" s="6"/>
+      <c r="K107" s="14">
+        <f t="shared" si="24"/>
+        <v>-1</v>
+      </c>
+      <c r="L107" s="14"/>
+      <c r="M107" s="14"/>
+      <c r="N107" s="6"/>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A108" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B108" s="1">
+        <v>-3</v>
+      </c>
+      <c r="C108" s="13">
+        <v>-2</v>
+      </c>
+      <c r="D108" s="13"/>
+      <c r="E108" s="13"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="13">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="H108" s="13"/>
+      <c r="I108" s="13"/>
+      <c r="J108" s="6"/>
+      <c r="K108" s="14">
+        <f t="shared" si="24"/>
+        <v>-0.33333333333333331</v>
+      </c>
+      <c r="L108" s="14"/>
+      <c r="M108" s="14"/>
+      <c r="N108" s="6"/>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A109" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B109" s="1">
+        <v>90</v>
+      </c>
+      <c r="C109" s="13">
+        <v>11</v>
+      </c>
+      <c r="D109" s="13"/>
+      <c r="E109" s="13"/>
+      <c r="F109" s="6"/>
+      <c r="G109" s="13">
+        <f t="shared" si="23"/>
+        <v>-79</v>
+      </c>
+      <c r="H109" s="13"/>
+      <c r="I109" s="13"/>
+      <c r="J109" s="6"/>
+      <c r="K109" s="14">
+        <f t="shared" si="24"/>
+        <v>-0.87777777777777777</v>
+      </c>
+      <c r="L109" s="14"/>
+      <c r="M109" s="14"/>
+      <c r="N109" s="6"/>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A110" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B110" s="1">
+        <v>6.7799740000000002</v>
+      </c>
+      <c r="C110" s="13">
+        <v>7.9846940000000002</v>
+      </c>
+      <c r="D110" s="13"/>
+      <c r="E110" s="13"/>
+      <c r="F110" s="6"/>
+      <c r="G110" s="13">
+        <f t="shared" si="23"/>
+        <v>1.20472</v>
+      </c>
+      <c r="H110" s="13"/>
+      <c r="I110" s="13"/>
+      <c r="J110" s="6"/>
+      <c r="K110" s="14">
+        <f t="shared" si="24"/>
+        <v>0.17768799703361693</v>
+      </c>
+      <c r="L110" s="14"/>
+      <c r="M110" s="14"/>
+      <c r="N110" s="6"/>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A111" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B111" s="1">
+        <v>7</v>
+      </c>
+      <c r="C111" s="13">
+        <v>8</v>
+      </c>
+      <c r="D111" s="13"/>
+      <c r="E111" s="13"/>
+      <c r="F111" s="6"/>
+      <c r="G111" s="13">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="H111" s="13"/>
+      <c r="I111" s="13"/>
+      <c r="J111" s="6"/>
+      <c r="K111" s="14">
+        <f t="shared" si="24"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="L111" s="14"/>
+      <c r="M111" s="14"/>
+      <c r="N111" s="6"/>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A112" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B112" s="1">
+        <v>8</v>
+      </c>
+      <c r="C112" s="13">
+        <v>8</v>
+      </c>
+      <c r="D112" s="13"/>
+      <c r="E112" s="13"/>
+      <c r="F112" s="6"/>
+      <c r="G112" s="13">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="H112" s="13"/>
+      <c r="I112" s="13"/>
+      <c r="J112" s="6"/>
+      <c r="K112" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="L112" s="14"/>
+      <c r="M112" s="14"/>
+      <c r="N112" s="6"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A113" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B113" s="1">
+        <v>3</v>
+      </c>
+      <c r="C113" s="13">
+        <v>5</v>
+      </c>
+      <c r="D113" s="13"/>
+      <c r="E113" s="13"/>
+      <c r="F113" s="6"/>
+      <c r="G113" s="13">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+      <c r="H113" s="13"/>
+      <c r="I113" s="13"/>
+      <c r="J113" s="6"/>
+      <c r="K113" s="14">
+        <f t="shared" si="24"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="L113" s="14"/>
+      <c r="M113" s="14"/>
+      <c r="N113" s="6"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A114" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B114" s="1">
+        <v>72</v>
+      </c>
+      <c r="C114" s="13">
+        <v>3094</v>
+      </c>
+      <c r="D114" s="13"/>
+      <c r="E114" s="13"/>
+      <c r="F114" s="6"/>
+      <c r="G114" s="13">
+        <f t="shared" si="23"/>
+        <v>3022</v>
+      </c>
+      <c r="H114" s="13"/>
+      <c r="I114" s="13"/>
+      <c r="J114" s="6"/>
+      <c r="K114" s="14">
+        <f t="shared" si="24"/>
+        <v>41.972222222222221</v>
+      </c>
+      <c r="L114" s="14"/>
+      <c r="M114" s="14"/>
+      <c r="N114" s="6"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A115" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B115" s="5">
+        <v>2.2959179999999999E-2</v>
+      </c>
+      <c r="C115" s="14">
+        <v>0.98660714000000005</v>
+      </c>
+      <c r="D115" s="14"/>
+      <c r="E115" s="14"/>
+      <c r="F115" s="6"/>
+      <c r="G115" s="13">
+        <f t="shared" si="23"/>
+        <v>0.96364796000000008</v>
+      </c>
+      <c r="H115" s="13"/>
+      <c r="I115" s="13"/>
+      <c r="J115" s="6"/>
+      <c r="K115" s="14">
+        <f t="shared" si="24"/>
+        <v>41.972228973334417</v>
+      </c>
+      <c r="L115" s="14"/>
+      <c r="M115" s="14"/>
+      <c r="N115" s="6"/>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A116" s="7"/>
+      <c r="B116" s="8"/>
+      <c r="C116" s="8"/>
+      <c r="D116" s="12"/>
+      <c r="E116" s="8"/>
+      <c r="F116" s="6"/>
+      <c r="G116" s="8"/>
+      <c r="H116" s="8"/>
+      <c r="I116" s="8"/>
+      <c r="J116" s="6"/>
+      <c r="K116" s="8"/>
+      <c r="L116" s="8"/>
+      <c r="M116" s="8"/>
+      <c r="N116" s="6"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A117" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B117" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C117" s="13"/>
+      <c r="D117" s="13"/>
+      <c r="E117" s="13"/>
+      <c r="F117" s="6"/>
+      <c r="G117" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H117" s="13"/>
+      <c r="I117" s="13"/>
+      <c r="J117" s="6"/>
+      <c r="K117" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="L117" s="13"/>
+      <c r="M117" s="13"/>
+      <c r="N117" s="6"/>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A118" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B118" s="1">
+        <v>0.46843099999999999</v>
+      </c>
+      <c r="C118" s="13">
+        <f t="shared" ref="C118:C129" si="25">AVERAGE(C62,C34,C90)</f>
+        <v>1.8927509999999999</v>
+      </c>
+      <c r="D118" s="13"/>
+      <c r="E118" s="13"/>
+      <c r="F118" s="6"/>
+      <c r="G118" s="13">
+        <f t="shared" ref="G118" si="26">C118-B118</f>
+        <v>1.4243199999999998</v>
+      </c>
+      <c r="H118" s="13"/>
+      <c r="I118" s="13"/>
+      <c r="J118" s="6"/>
+      <c r="K118" s="14">
+        <f>G118/B118</f>
+        <v>3.0406185756280002</v>
+      </c>
+      <c r="L118" s="14"/>
+      <c r="M118" s="14"/>
+      <c r="N118" s="6"/>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A119" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B119" s="1">
+        <v>0.34279300000000001</v>
+      </c>
+      <c r="C119" s="13">
+        <f t="shared" si="25"/>
+        <v>0.87595666666666661</v>
+      </c>
+      <c r="D119" s="13"/>
+      <c r="E119" s="13"/>
+      <c r="F119" s="6"/>
+      <c r="G119" s="13">
+        <f t="shared" ref="G119:G129" si="27">C119-B119</f>
+        <v>0.53316366666666659</v>
+      </c>
+      <c r="H119" s="13"/>
+      <c r="I119" s="13"/>
+      <c r="J119" s="6"/>
+      <c r="K119" s="14">
+        <f t="shared" ref="K119:K129" si="28">G119/B119</f>
+        <v>1.5553516748202751</v>
+      </c>
+      <c r="L119" s="14"/>
+      <c r="M119" s="14"/>
+      <c r="N119" s="6"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A120" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B120" s="1">
+        <v>0</v>
+      </c>
+      <c r="C120" s="13">
+        <f t="shared" si="25"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D120" s="13"/>
+      <c r="E120" s="13"/>
+      <c r="F120" s="6"/>
+      <c r="G120" s="13">
+        <f t="shared" si="27"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H120" s="13"/>
+      <c r="I120" s="13"/>
+      <c r="J120" s="6"/>
+      <c r="K120" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="L120" s="14"/>
+      <c r="M120" s="14"/>
+      <c r="N120" s="6"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A121" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B121" s="1">
+        <v>0</v>
+      </c>
+      <c r="C121" s="13">
+        <f t="shared" si="25"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D121" s="13"/>
+      <c r="E121" s="13"/>
+      <c r="F121" s="6"/>
+      <c r="G121" s="13">
+        <f t="shared" si="27"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H121" s="13"/>
+      <c r="I121" s="13"/>
+      <c r="J121" s="6"/>
+      <c r="K121" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="L121" s="14"/>
+      <c r="M121" s="14"/>
+      <c r="N121" s="6"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A122" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B122" s="1">
+        <v>-3</v>
+      </c>
+      <c r="C122" s="13">
+        <f t="shared" si="25"/>
+        <v>-0.33333333333333331</v>
+      </c>
+      <c r="D122" s="13"/>
+      <c r="E122" s="13"/>
+      <c r="F122" s="6"/>
+      <c r="G122" s="13">
+        <f t="shared" si="27"/>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="H122" s="13"/>
+      <c r="I122" s="13"/>
+      <c r="J122" s="6"/>
+      <c r="K122" s="14">
+        <f t="shared" si="28"/>
+        <v>-0.88888888888888884</v>
+      </c>
+      <c r="L122" s="14"/>
+      <c r="M122" s="14"/>
+      <c r="N122" s="6"/>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A123" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B123" s="1">
+        <v>1</v>
+      </c>
+      <c r="C123" s="13">
+        <f t="shared" si="25"/>
+        <v>5.333333333333333</v>
+      </c>
+      <c r="D123" s="13"/>
+      <c r="E123" s="13"/>
+      <c r="F123" s="6"/>
+      <c r="G123" s="13">
+        <f t="shared" si="27"/>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="H123" s="13"/>
+      <c r="I123" s="13"/>
+      <c r="J123" s="6"/>
+      <c r="K123" s="14">
+        <f t="shared" si="28"/>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="L123" s="14"/>
+      <c r="M123" s="14"/>
+      <c r="N123" s="6"/>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A124" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B124" s="1">
+        <v>7.5959820000000002</v>
+      </c>
+      <c r="C124" s="13">
+        <f t="shared" si="25"/>
+        <v>7.2103526666666662</v>
+      </c>
+      <c r="D124" s="13"/>
+      <c r="E124" s="13"/>
+      <c r="F124" s="6"/>
+      <c r="G124" s="13">
+        <f t="shared" si="27"/>
+        <v>-0.38562933333333405</v>
+      </c>
+      <c r="H124" s="13"/>
+      <c r="I124" s="13"/>
+      <c r="J124" s="6"/>
+      <c r="K124" s="14">
+        <f t="shared" si="28"/>
+        <v>-5.0767541752117638E-2</v>
+      </c>
+      <c r="L124" s="14"/>
+      <c r="M124" s="14"/>
+      <c r="N124" s="6"/>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A125" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B125" s="1">
+        <v>8</v>
+      </c>
+      <c r="C125" s="13">
+        <f t="shared" si="25"/>
+        <v>7.333333333333333</v>
+      </c>
+      <c r="D125" s="13"/>
+      <c r="E125" s="13"/>
+      <c r="F125" s="6"/>
+      <c r="G125" s="13">
+        <f t="shared" si="27"/>
+        <v>-0.66666666666666696</v>
+      </c>
+      <c r="H125" s="13"/>
+      <c r="I125" s="13"/>
+      <c r="J125" s="6"/>
+      <c r="K125" s="14">
+        <f t="shared" si="28"/>
+        <v>-8.333333333333337E-2</v>
+      </c>
+      <c r="L125" s="14"/>
+      <c r="M125" s="14"/>
+      <c r="N125" s="6"/>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A126" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B126" s="1">
+        <v>8</v>
+      </c>
+      <c r="C126" s="13">
+        <f t="shared" si="25"/>
+        <v>8</v>
+      </c>
+      <c r="D126" s="13"/>
+      <c r="E126" s="13"/>
+      <c r="F126" s="6"/>
+      <c r="G126" s="13">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="H126" s="13"/>
+      <c r="I126" s="13"/>
+      <c r="J126" s="6"/>
+      <c r="K126" s="14">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="L126" s="14"/>
+      <c r="M126" s="14"/>
+      <c r="N126" s="6"/>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A127" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B127" s="1">
+        <v>5</v>
+      </c>
+      <c r="C127" s="13">
+        <f t="shared" si="25"/>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="D127" s="13"/>
+      <c r="E127" s="13"/>
+      <c r="F127" s="6"/>
+      <c r="G127" s="13">
+        <f t="shared" si="27"/>
+        <v>-0.66666666666666696</v>
+      </c>
+      <c r="H127" s="13"/>
+      <c r="I127" s="13"/>
+      <c r="J127" s="6"/>
+      <c r="K127" s="14">
+        <f t="shared" si="28"/>
+        <v>-0.13333333333333339</v>
+      </c>
+      <c r="L127" s="14"/>
+      <c r="M127" s="14"/>
+      <c r="N127" s="6"/>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A128" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B128" s="1">
+        <v>2234</v>
+      </c>
+      <c r="C128" s="13">
+        <f t="shared" si="25"/>
+        <v>1430.6666666666667</v>
+      </c>
+      <c r="D128" s="13"/>
+      <c r="E128" s="13"/>
+      <c r="F128" s="6"/>
+      <c r="G128" s="13">
+        <f t="shared" si="27"/>
+        <v>-803.33333333333326</v>
+      </c>
+      <c r="H128" s="13"/>
+      <c r="I128" s="13"/>
+      <c r="J128" s="6"/>
+      <c r="K128" s="14">
+        <f t="shared" si="28"/>
+        <v>-0.35959415099970155</v>
+      </c>
+      <c r="L128" s="14"/>
+      <c r="M128" s="14"/>
+      <c r="N128" s="6"/>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A129" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B129" s="5">
+        <v>0.71237245000000005</v>
+      </c>
+      <c r="C129" s="17">
+        <f t="shared" si="25"/>
+        <v>0.45620748333333333</v>
+      </c>
+      <c r="D129" s="13"/>
+      <c r="E129" s="13"/>
+      <c r="F129" s="6"/>
+      <c r="G129" s="13">
+        <f t="shared" si="27"/>
+        <v>-0.25616496666666672</v>
+      </c>
+      <c r="H129" s="13"/>
+      <c r="I129" s="13"/>
+      <c r="J129" s="6"/>
+      <c r="K129" s="14">
+        <f t="shared" si="28"/>
+        <v>-0.35959415143955481</v>
+      </c>
+      <c r="L129" s="14"/>
+      <c r="M129" s="14"/>
+      <c r="N129" s="6"/>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A130" s="7"/>
+      <c r="B130" s="8"/>
+      <c r="C130" s="8"/>
+      <c r="D130" s="12"/>
+      <c r="E130" s="8"/>
+      <c r="F130" s="6"/>
+      <c r="G130" s="8"/>
+      <c r="H130" s="8"/>
+      <c r="I130" s="8"/>
+      <c r="J130" s="6"/>
+      <c r="K130" s="8"/>
+      <c r="L130" s="8"/>
+      <c r="M130" s="8"/>
+      <c r="N130" s="6"/>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A131" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B131" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C131" s="13"/>
+      <c r="D131" s="13"/>
+      <c r="E131" s="13"/>
+      <c r="F131" s="6"/>
+      <c r="G131" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H131" s="13"/>
+      <c r="I131" s="13"/>
+      <c r="J131" s="6"/>
+      <c r="K131" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="L131" s="13"/>
+      <c r="M131" s="13"/>
+      <c r="N131" s="6"/>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A132" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B132" s="1">
+        <v>15.246810999999999</v>
+      </c>
+      <c r="C132" s="13">
+        <f t="shared" ref="C132:C143" si="29">AVERAGE(C76,C48,C104)</f>
+        <v>1.1660286666666666</v>
+      </c>
+      <c r="D132" s="13"/>
+      <c r="E132" s="13"/>
+      <c r="F132" s="6"/>
+      <c r="G132" s="13">
+        <f t="shared" ref="G132:G143" si="30">C132-B132</f>
+        <v>-14.080782333333332</v>
+      </c>
+      <c r="H132" s="13"/>
+      <c r="I132" s="13"/>
+      <c r="J132" s="6"/>
+      <c r="K132" s="14">
+        <f>G132/B132</f>
+        <v>-0.92352311137937848</v>
+      </c>
+      <c r="L132" s="14"/>
+      <c r="M132" s="14"/>
+      <c r="N132" s="6"/>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A133" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B133" s="1">
+        <v>2.0593110000000001</v>
+      </c>
+      <c r="C133" s="13">
+        <f t="shared" si="29"/>
+        <v>0.59566333333333332</v>
+      </c>
+      <c r="D133" s="13"/>
+      <c r="E133" s="13"/>
+      <c r="F133" s="6"/>
+      <c r="G133" s="13">
+        <f t="shared" si="30"/>
+        <v>-1.4636476666666667</v>
+      </c>
+      <c r="H133" s="13"/>
+      <c r="I133" s="13"/>
+      <c r="J133" s="6"/>
+      <c r="K133" s="14">
+        <f t="shared" ref="K133:K143" si="31">G133/B133</f>
+        <v>-0.71074629653639809</v>
+      </c>
+      <c r="L133" s="14"/>
+      <c r="M133" s="14"/>
+      <c r="N133" s="6"/>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A134" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B134" s="1">
+        <v>2</v>
+      </c>
+      <c r="C134" s="13">
+        <f t="shared" si="29"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D134" s="13"/>
+      <c r="E134" s="13"/>
+      <c r="F134" s="6"/>
+      <c r="G134" s="13">
+        <f t="shared" si="30"/>
+        <v>-1.3333333333333335</v>
+      </c>
+      <c r="H134" s="13"/>
+      <c r="I134" s="13"/>
+      <c r="J134" s="6"/>
+      <c r="K134" s="14">
+        <f t="shared" si="31"/>
+        <v>-0.66666666666666674</v>
+      </c>
+      <c r="L134" s="14"/>
+      <c r="M134" s="14"/>
+      <c r="N134" s="6"/>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A135" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B135" s="1">
+        <v>-2</v>
+      </c>
+      <c r="C135" s="13">
+        <f t="shared" si="29"/>
+        <v>-0.66666666666666663</v>
+      </c>
+      <c r="D135" s="13"/>
+      <c r="E135" s="13"/>
+      <c r="F135" s="6"/>
+      <c r="G135" s="13">
+        <f t="shared" si="30"/>
+        <v>1.3333333333333335</v>
+      </c>
+      <c r="H135" s="13"/>
+      <c r="I135" s="13"/>
+      <c r="J135" s="6"/>
+      <c r="K135" s="14">
+        <f t="shared" si="31"/>
+        <v>-0.66666666666666674</v>
+      </c>
+      <c r="L135" s="14"/>
+      <c r="M135" s="14"/>
+      <c r="N135" s="6"/>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A136" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B136" s="1">
+        <v>-3</v>
+      </c>
+      <c r="C136" s="13">
+        <f t="shared" si="29"/>
+        <v>-1.6666666666666667</v>
+      </c>
+      <c r="D136" s="13"/>
+      <c r="E136" s="13"/>
+      <c r="F136" s="6"/>
+      <c r="G136" s="13">
+        <f t="shared" si="30"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="H136" s="13"/>
+      <c r="I136" s="13"/>
+      <c r="J136" s="6"/>
+      <c r="K136" s="14">
+        <f t="shared" si="31"/>
+        <v>-0.44444444444444442</v>
+      </c>
+      <c r="L136" s="14"/>
+      <c r="M136" s="14"/>
+      <c r="N136" s="6"/>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A137" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B137" s="1">
+        <v>90</v>
+      </c>
+      <c r="C137" s="13">
+        <f t="shared" si="29"/>
+        <v>7.333333333333333</v>
+      </c>
+      <c r="D137" s="13"/>
+      <c r="E137" s="13"/>
+      <c r="F137" s="6"/>
+      <c r="G137" s="13">
+        <f t="shared" si="30"/>
+        <v>-82.666666666666671</v>
+      </c>
+      <c r="H137" s="13"/>
+      <c r="I137" s="13"/>
+      <c r="J137" s="6"/>
+      <c r="K137" s="14">
+        <f t="shared" si="31"/>
+        <v>-0.91851851851851862</v>
+      </c>
+      <c r="L137" s="14"/>
+      <c r="M137" s="14"/>
+      <c r="N137" s="6"/>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A138" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B138" s="1">
+        <v>6.7799740000000002</v>
+      </c>
+      <c r="C138" s="13">
+        <f t="shared" si="29"/>
+        <v>7.3580016666666666</v>
+      </c>
+      <c r="D138" s="13"/>
+      <c r="E138" s="13"/>
+      <c r="F138" s="6"/>
+      <c r="G138" s="13">
+        <f t="shared" si="30"/>
+        <v>0.57802766666666638</v>
+      </c>
+      <c r="H138" s="13"/>
+      <c r="I138" s="13"/>
+      <c r="J138" s="6"/>
+      <c r="K138" s="14">
+        <f t="shared" si="31"/>
+        <v>8.5255145029562995E-2</v>
+      </c>
+      <c r="L138" s="14"/>
+      <c r="M138" s="14"/>
+      <c r="N138" s="6"/>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A139" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B139" s="1">
+        <v>7</v>
+      </c>
+      <c r="C139" s="13">
+        <f t="shared" si="29"/>
+        <v>7.666666666666667</v>
+      </c>
+      <c r="D139" s="13"/>
+      <c r="E139" s="13"/>
+      <c r="F139" s="6"/>
+      <c r="G139" s="13">
+        <f t="shared" si="30"/>
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="H139" s="13"/>
+      <c r="I139" s="13"/>
+      <c r="J139" s="6"/>
+      <c r="K139" s="14">
+        <f t="shared" si="31"/>
+        <v>9.5238095238095274E-2</v>
+      </c>
+      <c r="L139" s="14"/>
+      <c r="M139" s="14"/>
+      <c r="N139" s="6"/>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A140" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B140" s="1">
+        <v>8</v>
+      </c>
+      <c r="C140" s="13">
+        <f t="shared" si="29"/>
+        <v>8</v>
+      </c>
+      <c r="D140" s="13"/>
+      <c r="E140" s="13"/>
+      <c r="F140" s="6"/>
+      <c r="G140" s="13">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="H140" s="13"/>
+      <c r="I140" s="13"/>
+      <c r="J140" s="6"/>
+      <c r="K140" s="14">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="L140" s="14"/>
+      <c r="M140" s="14"/>
+      <c r="N140" s="6"/>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A141" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B141" s="1">
+        <v>3</v>
+      </c>
+      <c r="C141" s="13">
+        <f t="shared" si="29"/>
+        <v>6</v>
+      </c>
+      <c r="D141" s="13"/>
+      <c r="E141" s="13"/>
+      <c r="F141" s="6"/>
+      <c r="G141" s="13">
+        <f t="shared" si="30"/>
+        <v>3</v>
+      </c>
+      <c r="H141" s="13"/>
+      <c r="I141" s="13"/>
+      <c r="J141" s="6"/>
+      <c r="K141" s="14">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="L141" s="14"/>
+      <c r="M141" s="14"/>
+      <c r="N141" s="6"/>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A142" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B142" s="1">
+        <v>72</v>
+      </c>
+      <c r="C142" s="13">
+        <f t="shared" si="29"/>
+        <v>2107.6666666666665</v>
+      </c>
+      <c r="D142" s="13"/>
+      <c r="E142" s="13"/>
+      <c r="F142" s="6"/>
+      <c r="G142" s="13">
+        <f t="shared" si="30"/>
+        <v>2035.6666666666665</v>
+      </c>
+      <c r="H142" s="13"/>
+      <c r="I142" s="13"/>
+      <c r="J142" s="6"/>
+      <c r="K142" s="14">
+        <f t="shared" si="31"/>
+        <v>28.273148148148145</v>
+      </c>
+      <c r="L142" s="14"/>
+      <c r="M142" s="14"/>
+      <c r="N142" s="6"/>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A143" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B143" s="5">
+        <v>2.2959179999999999E-2</v>
+      </c>
+      <c r="C143" s="17">
+        <f t="shared" si="29"/>
+        <v>0.6720875833333334</v>
+      </c>
+      <c r="D143" s="13"/>
+      <c r="E143" s="13"/>
+      <c r="F143" s="6"/>
+      <c r="G143" s="13">
+        <f t="shared" si="30"/>
+        <v>0.64912840333333344</v>
+      </c>
+      <c r="H143" s="13"/>
+      <c r="I143" s="13"/>
+      <c r="J143" s="6"/>
+      <c r="K143" s="14">
+        <f t="shared" si="31"/>
+        <v>28.273152757778522</v>
+      </c>
+      <c r="L143" s="14"/>
+      <c r="M143" s="14"/>
+      <c r="N143" s="6"/>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A144" s="7"/>
+      <c r="B144" s="8"/>
+      <c r="C144" s="8"/>
+      <c r="D144" s="12"/>
+      <c r="E144" s="8"/>
+      <c r="F144" s="6"/>
+      <c r="G144" s="8"/>
+      <c r="H144" s="8"/>
+      <c r="I144" s="8"/>
+      <c r="J144" s="6"/>
+      <c r="K144" s="8"/>
+      <c r="L144" s="8"/>
+      <c r="M144" s="8"/>
+      <c r="N144" s="6"/>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A145" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B145" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C145" s="13"/>
+      <c r="D145" s="13"/>
+      <c r="E145" s="13"/>
+      <c r="F145" s="6"/>
+      <c r="G145" s="13">
+        <v>0</v>
+      </c>
+      <c r="H145" s="13"/>
+      <c r="I145" s="13"/>
+      <c r="J145" s="6"/>
+      <c r="K145" s="18">
+        <v>0</v>
+      </c>
+      <c r="L145" s="18"/>
+      <c r="M145" s="18"/>
+      <c r="N145" s="6"/>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A146" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B146" s="13">
+        <v>1</v>
+      </c>
+      <c r="C146" s="13"/>
+      <c r="D146" s="13"/>
+      <c r="E146" s="13"/>
+      <c r="F146" s="6"/>
+      <c r="G146" s="13">
+        <v>0</v>
+      </c>
+      <c r="H146" s="13"/>
+      <c r="I146" s="13"/>
+      <c r="J146" s="6"/>
+      <c r="K146" s="14">
+        <f>G146/B146</f>
+        <v>0</v>
+      </c>
+      <c r="L146" s="14"/>
+      <c r="M146" s="14"/>
+      <c r="N146" s="6"/>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A147" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B147" s="13">
+        <v>69633</v>
+      </c>
+      <c r="C147" s="13"/>
+      <c r="D147" s="13"/>
+      <c r="E147" s="13"/>
+      <c r="F147" s="6"/>
+      <c r="G147" s="13">
+        <v>0</v>
+      </c>
+      <c r="H147" s="13"/>
+      <c r="I147" s="13"/>
+      <c r="J147" s="6"/>
+      <c r="K147" s="14">
+        <f>G147/B147</f>
+        <v>0</v>
+      </c>
+      <c r="L147" s="14"/>
+      <c r="M147" s="14"/>
+      <c r="N147" s="6"/>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A148" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B148" s="13">
+        <v>70350</v>
+      </c>
+      <c r="C148" s="13"/>
+      <c r="D148" s="13"/>
+      <c r="E148" s="13"/>
+      <c r="F148" s="6"/>
+      <c r="G148" s="13">
+        <v>0</v>
+      </c>
+      <c r="H148" s="13"/>
+      <c r="I148" s="13"/>
+      <c r="J148" s="6"/>
+      <c r="K148" s="14">
+        <f>G148/B148</f>
+        <v>0</v>
+      </c>
+      <c r="L148" s="14"/>
+      <c r="M148" s="14"/>
+      <c r="N148" s="6"/>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A149" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B149" s="13">
+        <v>74925</v>
+      </c>
+      <c r="C149" s="13"/>
+      <c r="D149" s="13"/>
+      <c r="E149" s="13"/>
+      <c r="F149" s="6"/>
+      <c r="G149" s="13">
+        <v>0</v>
+      </c>
+      <c r="H149" s="13"/>
+      <c r="I149" s="13"/>
+      <c r="J149" s="6"/>
+      <c r="K149" s="14">
+        <f>G149/B149</f>
+        <v>0</v>
+      </c>
+      <c r="L149" s="14"/>
+      <c r="M149" s="14"/>
+      <c r="N149" s="6"/>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A150" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B150" s="13">
+        <f>B149-B146</f>
+        <v>74924</v>
+      </c>
+      <c r="C150" s="13"/>
+      <c r="D150" s="13"/>
+      <c r="E150" s="13"/>
+      <c r="F150" s="6"/>
+      <c r="G150" s="13">
+        <v>0</v>
+      </c>
+      <c r="H150" s="13"/>
+      <c r="I150" s="13"/>
+      <c r="J150" s="6"/>
+      <c r="K150" s="14">
+        <f>G150/B150</f>
+        <v>0</v>
+      </c>
+      <c r="L150" s="14"/>
+      <c r="M150" s="14"/>
+      <c r="N150" s="6"/>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A151" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B151" s="13">
+        <f>B150/(B3*10^3)</f>
+        <v>0.93654999999999999</v>
+      </c>
+      <c r="C151" s="13"/>
+      <c r="D151" s="13"/>
+      <c r="E151" s="1">
+        <f>B150/(E3*10^3)</f>
+        <v>0.37462000000000001</v>
+      </c>
+      <c r="F151" s="6"/>
+      <c r="G151" s="13">
+        <v>0</v>
+      </c>
+      <c r="H151" s="13"/>
+      <c r="I151" s="1">
+        <f>E151-B151</f>
+        <v>-0.56193000000000004</v>
+      </c>
+      <c r="J151" s="6"/>
+      <c r="K151" s="14">
+        <v>0</v>
+      </c>
+      <c r="L151" s="14"/>
+      <c r="M151" s="5">
+        <f>I151/B151</f>
+        <v>-0.60000000000000009</v>
+      </c>
+      <c r="N151" s="6"/>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A152" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B152" s="13">
+        <f>B149-B147</f>
+        <v>5292</v>
+      </c>
+      <c r="C152" s="13"/>
+      <c r="D152" s="13"/>
+      <c r="E152" s="13"/>
+      <c r="F152" s="6"/>
+      <c r="G152" s="13">
+        <v>0</v>
+      </c>
+      <c r="H152" s="13"/>
+      <c r="I152" s="13"/>
+      <c r="J152" s="6"/>
+      <c r="K152" s="14">
+        <f>G152/B152</f>
+        <v>0</v>
+      </c>
+      <c r="L152" s="14"/>
+      <c r="M152" s="14"/>
+      <c r="N152" s="6"/>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A153" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B153" s="13">
+        <f>B152/B3</f>
+        <v>66.150000000000006</v>
+      </c>
+      <c r="C153" s="13"/>
+      <c r="D153" s="13"/>
+      <c r="E153" s="1">
+        <f>B152/E3</f>
+        <v>26.46</v>
+      </c>
+      <c r="F153" s="6"/>
+      <c r="G153" s="13">
+        <v>0</v>
+      </c>
+      <c r="H153" s="13"/>
+      <c r="I153" s="1">
+        <f>E153-B153</f>
+        <v>-39.690000000000005</v>
+      </c>
+      <c r="J153" s="6"/>
+      <c r="K153" s="14">
+        <v>0</v>
+      </c>
+      <c r="L153" s="14"/>
+      <c r="M153" s="5">
+        <f>I153/B153</f>
+        <v>-0.6</v>
+      </c>
+      <c r="N153" s="6"/>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A154" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B154" s="1">
+        <f>B12*B151</f>
+        <v>617.04596749999996</v>
+      </c>
+      <c r="C154" s="1">
+        <f>C12*B151</f>
+        <v>596.88204600000006</v>
+      </c>
+      <c r="D154" s="11">
+        <f>D12*B151</f>
+        <v>617.60789750000004</v>
+      </c>
+      <c r="E154" s="1">
+        <f>E12*E151</f>
+        <v>379.696101</v>
+      </c>
+      <c r="F154" s="6"/>
+      <c r="G154" s="1">
+        <f>C154-B154</f>
+        <v>-20.163921499999901</v>
+      </c>
+      <c r="H154" s="1">
+        <f>D154-B154</f>
+        <v>0.56193000000007487</v>
+      </c>
+      <c r="I154" s="1">
+        <f>E154-B154</f>
+        <v>-237.34986649999996</v>
+      </c>
+      <c r="J154" s="6"/>
+      <c r="K154" s="5">
+        <f>G154/B154</f>
+        <v>-3.267815132427699E-2</v>
+      </c>
+      <c r="L154" s="5">
+        <f>H154/B154</f>
+        <v>9.1067769598555059E-4</v>
+      </c>
+      <c r="M154" s="5"/>
+      <c r="N154" s="6"/>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A155" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B69" s="15">
-        <f>1/(B65/1000)</f>
+      <c r="B155" s="13">
+        <f>1/(B151/1000)</f>
         <v>1067.7486519673269</v>
       </c>
-      <c r="C69" s="15"/>
-      <c r="D69" s="15"/>
-      <c r="E69" s="1">
-        <f>1/(E65/1000)</f>
+      <c r="C155" s="13"/>
+      <c r="D155" s="13"/>
+      <c r="E155" s="1">
+        <f>1/(E151/1000)</f>
         <v>2669.3716299183175</v>
       </c>
-      <c r="F69" s="6"/>
-      <c r="G69" s="15">
-        <v>0</v>
-      </c>
-      <c r="H69" s="15"/>
-      <c r="I69" s="1">
-        <f>E69-B69</f>
+      <c r="F155" s="6"/>
+      <c r="G155" s="13">
+        <v>0</v>
+      </c>
+      <c r="H155" s="13"/>
+      <c r="I155" s="1">
+        <f>E155-B155</f>
         <v>1601.6229779509906</v>
       </c>
-      <c r="J69" s="6"/>
-      <c r="K69" s="13">
-        <v>0</v>
-      </c>
-      <c r="L69" s="13"/>
-      <c r="M69" s="5">
-        <f>I69/B69</f>
+      <c r="J155" s="6"/>
+      <c r="K155" s="14">
+        <v>0</v>
+      </c>
+      <c r="L155" s="14"/>
+      <c r="M155" s="5">
+        <f>I155/B155</f>
         <v>1.5000000000000002</v>
       </c>
-      <c r="N69" s="6"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A70" s="7"/>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="8"/>
-      <c r="N70" s="6"/>
+      <c r="N155" s="6"/>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A156" s="7"/>
+      <c r="B156" s="8"/>
+      <c r="C156" s="8"/>
+      <c r="D156" s="12"/>
+      <c r="E156" s="8"/>
+      <c r="F156" s="6"/>
+      <c r="G156" s="8"/>
+      <c r="H156" s="8"/>
+      <c r="I156" s="8"/>
+      <c r="J156" s="6"/>
+      <c r="K156" s="8"/>
+      <c r="L156" s="8"/>
+      <c r="M156" s="8"/>
+      <c r="N156" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="113">
-    <mergeCell ref="K60:M60"/>
-    <mergeCell ref="K61:M61"/>
+  <mergeCells count="353">
+    <mergeCell ref="K155:L155"/>
+    <mergeCell ref="G141:I141"/>
+    <mergeCell ref="G142:I142"/>
+    <mergeCell ref="G143:I143"/>
+    <mergeCell ref="G145:I145"/>
+    <mergeCell ref="K146:M146"/>
+    <mergeCell ref="K147:M147"/>
+    <mergeCell ref="K148:M148"/>
+    <mergeCell ref="K149:M149"/>
+    <mergeCell ref="K150:M150"/>
+    <mergeCell ref="K145:M145"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="G153:H153"/>
+    <mergeCell ref="G151:H151"/>
+    <mergeCell ref="K141:M141"/>
+    <mergeCell ref="K142:M142"/>
+    <mergeCell ref="K143:M143"/>
+    <mergeCell ref="G146:I146"/>
+    <mergeCell ref="G147:I147"/>
+    <mergeCell ref="G148:I148"/>
+    <mergeCell ref="K152:M152"/>
+    <mergeCell ref="K151:L151"/>
+    <mergeCell ref="K153:L153"/>
+    <mergeCell ref="B153:D153"/>
+    <mergeCell ref="B155:D155"/>
+    <mergeCell ref="G117:I117"/>
+    <mergeCell ref="G119:I119"/>
+    <mergeCell ref="G120:I120"/>
+    <mergeCell ref="G121:I121"/>
+    <mergeCell ref="G122:I122"/>
+    <mergeCell ref="G123:I123"/>
+    <mergeCell ref="G124:I124"/>
+    <mergeCell ref="G125:I125"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="G127:I127"/>
+    <mergeCell ref="G128:I128"/>
+    <mergeCell ref="G129:I129"/>
+    <mergeCell ref="C124:E124"/>
+    <mergeCell ref="C125:E125"/>
+    <mergeCell ref="C126:E126"/>
+    <mergeCell ref="C127:E127"/>
+    <mergeCell ref="C128:E128"/>
+    <mergeCell ref="G155:H155"/>
+    <mergeCell ref="B152:E152"/>
+    <mergeCell ref="C141:E141"/>
+    <mergeCell ref="C142:E142"/>
+    <mergeCell ref="C143:E143"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C122:E122"/>
+    <mergeCell ref="C123:E123"/>
+    <mergeCell ref="C132:E132"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="C118:E118"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="G135:I135"/>
+    <mergeCell ref="G136:I136"/>
+    <mergeCell ref="G137:I137"/>
+    <mergeCell ref="G138:I138"/>
+    <mergeCell ref="G139:I139"/>
+    <mergeCell ref="C119:E119"/>
+    <mergeCell ref="C120:E120"/>
+    <mergeCell ref="C121:E121"/>
+    <mergeCell ref="C133:E133"/>
+    <mergeCell ref="C134:E134"/>
+    <mergeCell ref="C135:E135"/>
+    <mergeCell ref="C129:E129"/>
+    <mergeCell ref="B151:D151"/>
+    <mergeCell ref="G132:I132"/>
+    <mergeCell ref="G133:I133"/>
+    <mergeCell ref="G134:I134"/>
+    <mergeCell ref="C136:E136"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="C138:E138"/>
+    <mergeCell ref="C139:E139"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="G149:I149"/>
+    <mergeCell ref="G150:I150"/>
+    <mergeCell ref="B150:E150"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="K123:M123"/>
+    <mergeCell ref="K124:M124"/>
+    <mergeCell ref="K125:M125"/>
+    <mergeCell ref="G140:I140"/>
+    <mergeCell ref="K126:M126"/>
+    <mergeCell ref="K127:M127"/>
+    <mergeCell ref="K128:M128"/>
+    <mergeCell ref="K129:M129"/>
+    <mergeCell ref="K119:M119"/>
+    <mergeCell ref="K120:M120"/>
+    <mergeCell ref="K121:M121"/>
+    <mergeCell ref="K122:M122"/>
+    <mergeCell ref="K132:M132"/>
+    <mergeCell ref="K133:M133"/>
+    <mergeCell ref="K134:M134"/>
+    <mergeCell ref="K135:M135"/>
+    <mergeCell ref="K136:M136"/>
+    <mergeCell ref="K137:M137"/>
+    <mergeCell ref="K138:M138"/>
+    <mergeCell ref="K139:M139"/>
+    <mergeCell ref="K140:M140"/>
+    <mergeCell ref="G131:I131"/>
+    <mergeCell ref="K131:M131"/>
+    <mergeCell ref="K117:M117"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="G62:I62"/>
     <mergeCell ref="K62:M62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="G63:I63"/>
     <mergeCell ref="K63:M63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="G64:I64"/>
     <mergeCell ref="K64:M64"/>
-    <mergeCell ref="K59:M59"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="K65:M65"/>
+    <mergeCell ref="C66:E66"/>
     <mergeCell ref="G66:I66"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="K46:M46"/>
-    <mergeCell ref="K47:M47"/>
-    <mergeCell ref="K48:M48"/>
-    <mergeCell ref="K49:M49"/>
-    <mergeCell ref="K50:M50"/>
-    <mergeCell ref="K51:M51"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="K53:M53"/>
-    <mergeCell ref="K54:M54"/>
-    <mergeCell ref="K55:M55"/>
-    <mergeCell ref="K56:M56"/>
-    <mergeCell ref="K57:M57"/>
-    <mergeCell ref="G60:I60"/>
-    <mergeCell ref="G61:I61"/>
-    <mergeCell ref="G62:I62"/>
     <mergeCell ref="K66:M66"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="G55:I55"/>
-    <mergeCell ref="G56:I56"/>
-    <mergeCell ref="G57:I57"/>
-    <mergeCell ref="G59:I59"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="G53:I53"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="G41:I41"/>
-    <mergeCell ref="G42:I42"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="G44:I44"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="G63:I63"/>
-    <mergeCell ref="G64:I64"/>
-    <mergeCell ref="B64:E64"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="G67:I67"/>
     <mergeCell ref="C57:E57"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="K68:M68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="G69:I69"/>
+    <mergeCell ref="K69:M69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="G70:I70"/>
+    <mergeCell ref="K70:M70"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:M1"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="D10:E10"/>
-    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="K83:M83"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="G84:I84"/>
+    <mergeCell ref="K84:M84"/>
+    <mergeCell ref="G77:I77"/>
+    <mergeCell ref="K77:M77"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="G78:I78"/>
+    <mergeCell ref="K78:M78"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="G79:I79"/>
+    <mergeCell ref="K79:M79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="G80:I80"/>
+    <mergeCell ref="K80:M80"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="G81:I81"/>
+    <mergeCell ref="K81:M81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="G82:I82"/>
+    <mergeCell ref="K82:M82"/>
+    <mergeCell ref="G71:I71"/>
+    <mergeCell ref="K71:M71"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="G72:I72"/>
+    <mergeCell ref="K72:M72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="G73:I73"/>
+    <mergeCell ref="K73:M73"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="G76:I76"/>
+    <mergeCell ref="K76:M76"/>
+    <mergeCell ref="K67:M67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="G68:I68"/>
     <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="K35:M35"/>
     <mergeCell ref="C36:E36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="K36:M36"/>
     <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="K42:M42"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="K43:M43"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="K45:M45"/>
     <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="G46:I46"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="B47:E47"/>
     <mergeCell ref="G47:I47"/>
-    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="K47:M47"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="K49:M49"/>
     <mergeCell ref="C50:E50"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="K50:M50"/>
     <mergeCell ref="C51:E51"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="K51:M51"/>
     <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="K53:M53"/>
     <mergeCell ref="C54:E54"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="K40:M40"/>
     <mergeCell ref="G54:I54"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="K42:M42"/>
-    <mergeCell ref="K43:M43"/>
-    <mergeCell ref="K44:M44"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="K54:M54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="G55:I55"/>
+    <mergeCell ref="K55:M55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="K56:M56"/>
+    <mergeCell ref="G57:I57"/>
+    <mergeCell ref="K57:M57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="G58:I58"/>
+    <mergeCell ref="K58:M58"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="G59:I59"/>
+    <mergeCell ref="K59:M59"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="G90:I90"/>
+    <mergeCell ref="K90:M90"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="G89:I89"/>
+    <mergeCell ref="K89:M89"/>
+    <mergeCell ref="G85:I85"/>
+    <mergeCell ref="K85:M85"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="G86:I86"/>
+    <mergeCell ref="K86:M86"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="K87:M87"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="G83:I83"/>
+    <mergeCell ref="G91:I91"/>
+    <mergeCell ref="K91:M91"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="G92:I92"/>
+    <mergeCell ref="K92:M92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="G93:I93"/>
+    <mergeCell ref="K93:M93"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="G94:I94"/>
+    <mergeCell ref="K94:M94"/>
+    <mergeCell ref="G95:I95"/>
+    <mergeCell ref="K95:M95"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="G96:I96"/>
+    <mergeCell ref="K96:M96"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="G97:I97"/>
+    <mergeCell ref="K97:M97"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="G98:I98"/>
+    <mergeCell ref="K98:M98"/>
+    <mergeCell ref="G99:I99"/>
+    <mergeCell ref="K99:M99"/>
+    <mergeCell ref="C100:E100"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="K100:M100"/>
+    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="G101:I101"/>
+    <mergeCell ref="K101:M101"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="G104:I104"/>
+    <mergeCell ref="K104:M104"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="G103:I103"/>
+    <mergeCell ref="K103:M103"/>
+    <mergeCell ref="K110:M110"/>
+    <mergeCell ref="C111:E111"/>
+    <mergeCell ref="G111:I111"/>
+    <mergeCell ref="K111:M111"/>
+    <mergeCell ref="C112:E112"/>
+    <mergeCell ref="G112:I112"/>
+    <mergeCell ref="K112:M112"/>
+    <mergeCell ref="G105:I105"/>
+    <mergeCell ref="K105:M105"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="G106:I106"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="C107:E107"/>
+    <mergeCell ref="G107:I107"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="C108:E108"/>
+    <mergeCell ref="G108:I108"/>
+    <mergeCell ref="K108:M108"/>
+    <mergeCell ref="C105:E105"/>
+    <mergeCell ref="C109:E109"/>
+    <mergeCell ref="G118:I118"/>
+    <mergeCell ref="K118:M118"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="G61:I61"/>
+    <mergeCell ref="K61:M61"/>
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="G75:I75"/>
+    <mergeCell ref="K75:M75"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="G33:I33"/>
     <mergeCell ref="K33:M33"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C113:E113"/>
+    <mergeCell ref="G113:I113"/>
+    <mergeCell ref="K113:M113"/>
+    <mergeCell ref="C114:E114"/>
+    <mergeCell ref="G114:I114"/>
+    <mergeCell ref="K114:M114"/>
+    <mergeCell ref="C115:E115"/>
+    <mergeCell ref="G115:I115"/>
+    <mergeCell ref="K115:M115"/>
+    <mergeCell ref="G109:I109"/>
+    <mergeCell ref="K109:M109"/>
+    <mergeCell ref="C110:E110"/>
+    <mergeCell ref="G110:I110"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/FPGA_Performance_Comparison_Red_Small.xlsx
+++ b/FPGA_Performance_Comparison_Red_Small.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C25AD4C-C3B2-BA47-B74B-D9073EF6CA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="24100" windowHeight="26980" xr2:uid="{49DEC02E-5D37-064F-A7E8-1E1DC7B5FEA1}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="24100" windowHeight="17760" xr2:uid="{49DEC02E-5D37-064F-A7E8-1E1DC7B5FEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -374,23 +374,23 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -737,31 +737,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
+      <c r="B1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
       <c r="J1" s="6"/>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
       <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="16"/>
+      <c r="A2" s="17"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -800,19 +800,19 @@
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="14">
         <v>80</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
       <c r="E3" s="1">
         <v>200</v>
       </c>
       <c r="F3" s="6"/>
-      <c r="G3" s="13">
-        <v>0</v>
-      </c>
-      <c r="H3" s="13"/>
+      <c r="G3" s="14">
+        <v>0</v>
+      </c>
+      <c r="H3" s="14"/>
       <c r="I3" s="1">
         <f t="shared" ref="I3:I4" si="0">E3-B3</f>
         <v>120</v>
@@ -886,10 +886,10 @@
       <c r="C5" s="1">
         <v>136.59</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="17">
         <v>202.43</v>
       </c>
-      <c r="E5" s="16"/>
+      <c r="E5" s="17"/>
       <c r="F5" s="6"/>
       <c r="G5" s="1">
         <f>C5-B5</f>
@@ -944,10 +944,10 @@
       <c r="C7" s="1">
         <v>9776</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="17">
         <v>10129</v>
       </c>
-      <c r="E7" s="16"/>
+      <c r="E7" s="17"/>
       <c r="F7" s="6"/>
       <c r="G7" s="1">
         <f>C7-B7</f>
@@ -986,10 +986,10 @@
       <c r="C8" s="1">
         <v>24289</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="17">
         <v>27731</v>
       </c>
-      <c r="E8" s="16"/>
+      <c r="E8" s="17"/>
       <c r="F8" s="6"/>
       <c r="G8" s="1">
         <f>C8-B8</f>
@@ -1028,10 +1028,10 @@
       <c r="C9" s="1">
         <v>808736</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="17">
         <v>808736</v>
       </c>
-      <c r="E9" s="16"/>
+      <c r="E9" s="17"/>
       <c r="F9" s="6"/>
       <c r="G9" s="1">
         <f>C9-B9</f>
@@ -1070,10 +1070,10 @@
       <c r="C10" s="2">
         <v>12</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="17">
         <v>12</v>
       </c>
-      <c r="E10" s="16"/>
+      <c r="E10" s="17"/>
       <c r="F10" s="6"/>
       <c r="G10" s="1">
         <f>C10-B10</f>
@@ -2018,24 +2018,24 @@
       <c r="A33" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
       <c r="F33" s="6"/>
-      <c r="G33" s="13" t="s">
+      <c r="G33" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
       <c r="J33" s="6"/>
-      <c r="K33" s="13" t="s">
+      <c r="K33" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="L33" s="13"/>
-      <c r="M33" s="13"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
       <c r="N33" s="6"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
@@ -2045,25 +2045,25 @@
       <c r="B34" s="1">
         <v>0.46843099999999999</v>
       </c>
-      <c r="C34" s="13">
+      <c r="C34" s="14">
         <v>2.0848209999999998</v>
       </c>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
       <c r="F34" s="6"/>
-      <c r="G34" s="13">
+      <c r="G34" s="14">
         <f t="shared" ref="G34:G45" si="11">C34-B34</f>
         <v>1.6163899999999998</v>
       </c>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
       <c r="J34" s="6"/>
-      <c r="K34" s="14">
+      <c r="K34" s="13">
         <f>G34/B34</f>
         <v>3.4506469469356209</v>
       </c>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
       <c r="N34" s="6"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
@@ -2073,25 +2073,25 @@
       <c r="B35" s="1">
         <v>0.34279300000000001</v>
       </c>
-      <c r="C35" s="13">
+      <c r="C35" s="14">
         <v>0.91198999999999997</v>
       </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
       <c r="F35" s="6"/>
-      <c r="G35" s="13">
+      <c r="G35" s="14">
         <f t="shared" si="11"/>
         <v>0.56919699999999995</v>
       </c>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
       <c r="J35" s="6"/>
-      <c r="K35" s="14">
+      <c r="K35" s="13">
         <f t="shared" ref="K35" si="12">G35/B35</f>
         <v>1.6604685626602642</v>
       </c>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
       <c r="N35" s="6"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
@@ -2101,24 +2101,24 @@
       <c r="B36" s="1">
         <v>0</v>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="14">
         <v>1</v>
       </c>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
       <c r="F36" s="6"/>
-      <c r="G36" s="13">
+      <c r="G36" s="14">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
       <c r="J36" s="6"/>
-      <c r="K36" s="14" t="s">
+      <c r="K36" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
       <c r="N36" s="6"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
@@ -2128,24 +2128,24 @@
       <c r="B37" s="1">
         <v>0</v>
       </c>
-      <c r="C37" s="13">
+      <c r="C37" s="14">
         <v>1</v>
       </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
       <c r="F37" s="6"/>
-      <c r="G37" s="13">
+      <c r="G37" s="14">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
       <c r="J37" s="6"/>
-      <c r="K37" s="14" t="s">
+      <c r="K37" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
       <c r="N37" s="6"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
@@ -2155,25 +2155,25 @@
       <c r="B38" s="1">
         <v>-3</v>
       </c>
-      <c r="C38" s="13">
-        <v>0</v>
-      </c>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
+      <c r="C38" s="14">
+        <v>0</v>
+      </c>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
       <c r="F38" s="6"/>
-      <c r="G38" s="13">
+      <c r="G38" s="14">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
       <c r="J38" s="6"/>
-      <c r="K38" s="14">
+      <c r="K38" s="13">
         <f t="shared" ref="K38:K45" si="13">G38/B38</f>
         <v>-1</v>
       </c>
-      <c r="L38" s="14"/>
-      <c r="M38" s="14"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
       <c r="N38" s="6"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
@@ -2183,25 +2183,25 @@
       <c r="B39" s="1">
         <v>1</v>
       </c>
-      <c r="C39" s="13">
+      <c r="C39" s="14">
         <v>5</v>
       </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
       <c r="F39" s="6"/>
-      <c r="G39" s="13">
+      <c r="G39" s="14">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
       <c r="J39" s="6"/>
-      <c r="K39" s="14">
+      <c r="K39" s="13">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
-      <c r="L39" s="14"/>
-      <c r="M39" s="14"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
       <c r="N39" s="6"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
@@ -2211,25 +2211,25 @@
       <c r="B40" s="1">
         <v>7.5959820000000002</v>
       </c>
-      <c r="C40" s="13">
+      <c r="C40" s="14">
         <v>7.1970660000000004</v>
       </c>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
       <c r="F40" s="6"/>
-      <c r="G40" s="13">
+      <c r="G40" s="14">
         <f t="shared" si="11"/>
         <v>-0.39891599999999983</v>
       </c>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
       <c r="J40" s="6"/>
-      <c r="K40" s="14">
+      <c r="K40" s="13">
         <f t="shared" si="13"/>
         <v>-5.2516712124910221E-2</v>
       </c>
-      <c r="L40" s="14"/>
-      <c r="M40" s="14"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="13"/>
       <c r="N40" s="6"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
@@ -2239,25 +2239,25 @@
       <c r="B41" s="1">
         <v>8</v>
       </c>
-      <c r="C41" s="13">
+      <c r="C41" s="14">
         <v>7</v>
       </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
       <c r="F41" s="6"/>
-      <c r="G41" s="13">
+      <c r="G41" s="14">
         <f t="shared" si="11"/>
         <v>-1</v>
       </c>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
       <c r="J41" s="6"/>
-      <c r="K41" s="14">
+      <c r="K41" s="13">
         <f t="shared" si="13"/>
         <v>-0.125</v>
       </c>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
+      <c r="L41" s="13"/>
+      <c r="M41" s="13"/>
       <c r="N41" s="6"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
@@ -2267,25 +2267,25 @@
       <c r="B42" s="1">
         <v>8</v>
       </c>
-      <c r="C42" s="13">
+      <c r="C42" s="14">
         <v>8</v>
       </c>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
       <c r="F42" s="6"/>
-      <c r="G42" s="13">
+      <c r="G42" s="14">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
       <c r="J42" s="6"/>
-      <c r="K42" s="14">
+      <c r="K42" s="13">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L42" s="14"/>
-      <c r="M42" s="14"/>
+      <c r="L42" s="13"/>
+      <c r="M42" s="13"/>
       <c r="N42" s="6"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
@@ -2295,25 +2295,25 @@
       <c r="B43" s="1">
         <v>5</v>
       </c>
-      <c r="C43" s="13">
+      <c r="C43" s="14">
         <v>4</v>
       </c>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
       <c r="F43" s="6"/>
-      <c r="G43" s="13">
+      <c r="G43" s="14">
         <f t="shared" si="11"/>
         <v>-1</v>
       </c>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
       <c r="J43" s="6"/>
-      <c r="K43" s="14">
+      <c r="K43" s="13">
         <f t="shared" si="13"/>
         <v>-0.2</v>
       </c>
-      <c r="L43" s="14"/>
-      <c r="M43" s="14"/>
+      <c r="L43" s="13"/>
+      <c r="M43" s="13"/>
       <c r="N43" s="6"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
@@ -2323,25 +2323,25 @@
       <c r="B44" s="1">
         <v>2234</v>
       </c>
-      <c r="C44" s="13">
+      <c r="C44" s="14">
         <v>1454</v>
       </c>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
       <c r="F44" s="6"/>
-      <c r="G44" s="13">
+      <c r="G44" s="14">
         <f t="shared" si="11"/>
         <v>-780</v>
       </c>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
       <c r="J44" s="6"/>
-      <c r="K44" s="14">
+      <c r="K44" s="13">
         <f t="shared" si="13"/>
         <v>-0.34914950760966873</v>
       </c>
-      <c r="L44" s="14"/>
-      <c r="M44" s="14"/>
+      <c r="L44" s="13"/>
+      <c r="M44" s="13"/>
       <c r="N44" s="6"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
@@ -2351,25 +2351,25 @@
       <c r="B45" s="5">
         <v>0.71237245000000005</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="18">
         <v>0.46364796000000003</v>
       </c>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
       <c r="F45" s="6"/>
-      <c r="G45" s="13">
+      <c r="G45" s="14">
         <f t="shared" si="11"/>
         <v>-0.24872449000000002</v>
       </c>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
       <c r="J45" s="6"/>
-      <c r="K45" s="14">
+      <c r="K45" s="13">
         <f t="shared" si="13"/>
         <v>-0.34914950739602579</v>
       </c>
-      <c r="L45" s="14"/>
-      <c r="M45" s="14"/>
+      <c r="L45" s="13"/>
+      <c r="M45" s="13"/>
       <c r="N45" s="6"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
@@ -2392,24 +2392,24 @@
       <c r="A47" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
       <c r="F47" s="6"/>
-      <c r="G47" s="13" t="s">
+      <c r="G47" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H47" s="13"/>
-      <c r="I47" s="13"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
       <c r="J47" s="6"/>
-      <c r="K47" s="13" t="s">
+      <c r="K47" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="L47" s="13"/>
-      <c r="M47" s="13"/>
+      <c r="L47" s="14"/>
+      <c r="M47" s="14"/>
       <c r="N47" s="6"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
@@ -2419,25 +2419,25 @@
       <c r="B48" s="1">
         <v>15.246810999999999</v>
       </c>
-      <c r="C48" s="13">
+      <c r="C48" s="14">
         <v>3.3973209999999998</v>
       </c>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
       <c r="F48" s="6"/>
-      <c r="G48" s="13">
+      <c r="G48" s="14">
         <f t="shared" ref="G48:G59" si="14">C48-B48</f>
         <v>-11.849489999999999</v>
       </c>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
       <c r="J48" s="6"/>
-      <c r="K48" s="14">
+      <c r="K48" s="13">
         <f>G48/B48</f>
         <v>-0.77717825714505151</v>
       </c>
-      <c r="L48" s="14"/>
-      <c r="M48" s="14"/>
+      <c r="L48" s="13"/>
+      <c r="M48" s="13"/>
       <c r="N48" s="6"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
@@ -2447,25 +2447,25 @@
       <c r="B49" s="1">
         <v>2.0593110000000001</v>
       </c>
-      <c r="C49" s="13">
+      <c r="C49" s="14">
         <v>1.760842</v>
       </c>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
       <c r="F49" s="6"/>
-      <c r="G49" s="13">
+      <c r="G49" s="14">
         <f t="shared" si="14"/>
         <v>-0.2984690000000001</v>
       </c>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
       <c r="J49" s="6"/>
-      <c r="K49" s="14">
+      <c r="K49" s="13">
         <f t="shared" ref="K49:K59" si="15">G49/B49</f>
         <v>-0.14493634035849859</v>
       </c>
-      <c r="L49" s="14"/>
-      <c r="M49" s="14"/>
+      <c r="L49" s="13"/>
+      <c r="M49" s="13"/>
       <c r="N49" s="6"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
@@ -2475,25 +2475,25 @@
       <c r="B50" s="1">
         <v>2</v>
       </c>
-      <c r="C50" s="13">
+      <c r="C50" s="14">
         <v>2</v>
       </c>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
       <c r="F50" s="6"/>
-      <c r="G50" s="13">
+      <c r="G50" s="14">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
       <c r="J50" s="6"/>
-      <c r="K50" s="14">
+      <c r="K50" s="13">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L50" s="14"/>
-      <c r="M50" s="14"/>
+      <c r="L50" s="13"/>
+      <c r="M50" s="13"/>
       <c r="N50" s="6"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
@@ -2503,25 +2503,25 @@
       <c r="B51" s="1">
         <v>-2</v>
       </c>
-      <c r="C51" s="13">
+      <c r="C51" s="14">
         <v>-2</v>
       </c>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
       <c r="F51" s="6"/>
-      <c r="G51" s="13">
+      <c r="G51" s="14">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
       <c r="J51" s="6"/>
-      <c r="K51" s="14">
+      <c r="K51" s="13">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L51" s="14"/>
-      <c r="M51" s="14"/>
+      <c r="L51" s="13"/>
+      <c r="M51" s="13"/>
       <c r="N51" s="6"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
@@ -2531,25 +2531,25 @@
       <c r="B52" s="1">
         <v>-3</v>
       </c>
-      <c r="C52" s="13">
+      <c r="C52" s="14">
         <v>-3</v>
       </c>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
       <c r="F52" s="6"/>
-      <c r="G52" s="13">
+      <c r="G52" s="14">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
       <c r="J52" s="6"/>
-      <c r="K52" s="14">
+      <c r="K52" s="13">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L52" s="14"/>
-      <c r="M52" s="14"/>
+      <c r="L52" s="13"/>
+      <c r="M52" s="13"/>
       <c r="N52" s="6"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
@@ -2559,25 +2559,25 @@
       <c r="B53" s="1">
         <v>90</v>
       </c>
-      <c r="C53" s="13">
+      <c r="C53" s="14">
         <v>3</v>
       </c>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
       <c r="F53" s="6"/>
-      <c r="G53" s="13">
+      <c r="G53" s="14">
         <f t="shared" si="14"/>
         <v>-87</v>
       </c>
-      <c r="H53" s="13"/>
-      <c r="I53" s="13"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
       <c r="J53" s="6"/>
-      <c r="K53" s="14">
+      <c r="K53" s="13">
         <f t="shared" si="15"/>
         <v>-0.96666666666666667</v>
       </c>
-      <c r="L53" s="14"/>
-      <c r="M53" s="14"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="13"/>
       <c r="N53" s="6"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
@@ -2587,25 +2587,25 @@
       <c r="B54" s="1">
         <v>6.7799740000000002</v>
       </c>
-      <c r="C54" s="13">
+      <c r="C54" s="14">
         <v>6.0893110000000004</v>
       </c>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
       <c r="F54" s="6"/>
-      <c r="G54" s="13">
+      <c r="G54" s="14">
         <f t="shared" si="14"/>
         <v>-0.6906629999999998</v>
       </c>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
       <c r="J54" s="6"/>
-      <c r="K54" s="14">
+      <c r="K54" s="13">
         <f t="shared" si="15"/>
         <v>-0.10186808975963621</v>
       </c>
-      <c r="L54" s="14"/>
-      <c r="M54" s="14"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
       <c r="N54" s="6"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
@@ -2615,25 +2615,25 @@
       <c r="B55" s="1">
         <v>7</v>
       </c>
-      <c r="C55" s="13">
+      <c r="C55" s="14">
         <v>7</v>
       </c>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
       <c r="F55" s="6"/>
-      <c r="G55" s="13">
+      <c r="G55" s="14">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H55" s="13"/>
-      <c r="I55" s="13"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
       <c r="J55" s="6"/>
-      <c r="K55" s="14">
+      <c r="K55" s="13">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L55" s="14"/>
-      <c r="M55" s="14"/>
+      <c r="L55" s="13"/>
+      <c r="M55" s="13"/>
       <c r="N55" s="6"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
@@ -2643,25 +2643,25 @@
       <c r="B56" s="1">
         <v>8</v>
       </c>
-      <c r="C56" s="13">
+      <c r="C56" s="14">
         <v>8</v>
       </c>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
       <c r="F56" s="6"/>
-      <c r="G56" s="13">
+      <c r="G56" s="14">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
       <c r="J56" s="6"/>
-      <c r="K56" s="14">
+      <c r="K56" s="13">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L56" s="14"/>
-      <c r="M56" s="14"/>
+      <c r="L56" s="13"/>
+      <c r="M56" s="13"/>
       <c r="N56" s="6"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
@@ -2671,25 +2671,25 @@
       <c r="B57" s="1">
         <v>3</v>
       </c>
-      <c r="C57" s="13">
+      <c r="C57" s="14">
         <v>5</v>
       </c>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
       <c r="F57" s="6"/>
-      <c r="G57" s="13">
+      <c r="G57" s="14">
         <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
       <c r="J57" s="6"/>
-      <c r="K57" s="14">
+      <c r="K57" s="13">
         <f t="shared" si="15"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="L57" s="14"/>
-      <c r="M57" s="14"/>
+      <c r="L57" s="13"/>
+      <c r="M57" s="13"/>
       <c r="N57" s="6"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
@@ -2699,25 +2699,25 @@
       <c r="B58" s="1">
         <v>72</v>
       </c>
-      <c r="C58" s="13">
+      <c r="C58" s="14">
         <v>93</v>
       </c>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="14"/>
       <c r="F58" s="6"/>
-      <c r="G58" s="13">
+      <c r="G58" s="14">
         <f t="shared" si="14"/>
         <v>21</v>
       </c>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
       <c r="J58" s="6"/>
-      <c r="K58" s="14">
+      <c r="K58" s="13">
         <f t="shared" si="15"/>
         <v>0.29166666666666669</v>
       </c>
-      <c r="L58" s="14"/>
-      <c r="M58" s="14"/>
+      <c r="L58" s="13"/>
+      <c r="M58" s="13"/>
       <c r="N58" s="6"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
@@ -2727,25 +2727,25 @@
       <c r="B59" s="5">
         <v>2.2959179999999999E-2</v>
       </c>
-      <c r="C59" s="14">
+      <c r="C59" s="13">
         <v>2.9655609999999999E-2</v>
       </c>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
       <c r="F59" s="6"/>
-      <c r="G59" s="13">
+      <c r="G59" s="14">
         <f t="shared" si="14"/>
         <v>6.6964299999999997E-3</v>
       </c>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
       <c r="J59" s="6"/>
-      <c r="K59" s="14">
+      <c r="K59" s="13">
         <f t="shared" si="15"/>
         <v>0.29166677555557297</v>
       </c>
-      <c r="L59" s="14"/>
-      <c r="M59" s="14"/>
+      <c r="L59" s="13"/>
+      <c r="M59" s="13"/>
       <c r="N59" s="6"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
@@ -2768,24 +2768,24 @@
       <c r="A61" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B61" s="13" t="s">
+      <c r="B61" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C61" s="13"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
       <c r="F61" s="6"/>
-      <c r="G61" s="13" t="s">
+      <c r="G61" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H61" s="13"/>
-      <c r="I61" s="13"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
       <c r="J61" s="6"/>
-      <c r="K61" s="13" t="s">
+      <c r="K61" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="L61" s="13"/>
-      <c r="M61" s="13"/>
+      <c r="L61" s="14"/>
+      <c r="M61" s="14"/>
       <c r="N61" s="6"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
@@ -2795,25 +2795,25 @@
       <c r="B62" s="1">
         <v>0.46843099999999999</v>
       </c>
-      <c r="C62" s="13">
+      <c r="C62" s="14">
         <v>2.6575259999999998</v>
       </c>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="14"/>
       <c r="F62" s="6"/>
-      <c r="G62" s="13">
+      <c r="G62" s="14">
         <f t="shared" ref="G62:G73" si="16">C62-B62</f>
         <v>2.189095</v>
       </c>
-      <c r="H62" s="13"/>
-      <c r="I62" s="13"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
       <c r="J62" s="6"/>
-      <c r="K62" s="14">
+      <c r="K62" s="13">
         <f>G62/B62</f>
         <v>4.6732496354852691</v>
       </c>
-      <c r="L62" s="14"/>
-      <c r="M62" s="14"/>
+      <c r="L62" s="13"/>
+      <c r="M62" s="13"/>
       <c r="N62" s="6"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
@@ -2823,25 +2823,25 @@
       <c r="B63" s="1">
         <v>0.34279300000000001</v>
       </c>
-      <c r="C63" s="13">
+      <c r="C63" s="14">
         <v>1.2959179999999999</v>
       </c>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="14"/>
       <c r="F63" s="6"/>
-      <c r="G63" s="13">
+      <c r="G63" s="14">
         <f t="shared" si="16"/>
         <v>0.95312499999999989</v>
       </c>
-      <c r="H63" s="13"/>
-      <c r="I63" s="13"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
       <c r="J63" s="6"/>
-      <c r="K63" s="14">
+      <c r="K63" s="13">
         <f>G63/B63</f>
         <v>2.7804680959062753</v>
       </c>
-      <c r="L63" s="14"/>
-      <c r="M63" s="14"/>
+      <c r="L63" s="13"/>
+      <c r="M63" s="13"/>
       <c r="N63" s="6"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
@@ -2851,24 +2851,24 @@
       <c r="B64" s="1">
         <v>0</v>
       </c>
-      <c r="C64" s="13">
+      <c r="C64" s="14">
         <v>1</v>
       </c>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
       <c r="F64" s="6"/>
-      <c r="G64" s="13">
+      <c r="G64" s="14">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="H64" s="13"/>
-      <c r="I64" s="13"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
       <c r="J64" s="6"/>
-      <c r="K64" s="14" t="s">
+      <c r="K64" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="L64" s="14"/>
-      <c r="M64" s="14"/>
+      <c r="L64" s="13"/>
+      <c r="M64" s="13"/>
       <c r="N64" s="6"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
@@ -2878,24 +2878,24 @@
       <c r="B65" s="1">
         <v>0</v>
       </c>
-      <c r="C65" s="13">
+      <c r="C65" s="14">
         <v>1</v>
       </c>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
       <c r="F65" s="6"/>
-      <c r="G65" s="13">
+      <c r="G65" s="14">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="H65" s="13"/>
-      <c r="I65" s="13"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
       <c r="J65" s="6"/>
-      <c r="K65" s="14" t="s">
+      <c r="K65" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="L65" s="14"/>
-      <c r="M65" s="14"/>
+      <c r="L65" s="13"/>
+      <c r="M65" s="13"/>
       <c r="N65" s="6"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
@@ -2905,25 +2905,25 @@
       <c r="B66" s="1">
         <v>-3</v>
       </c>
-      <c r="C66" s="13">
+      <c r="C66" s="14">
         <v>-1</v>
       </c>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
       <c r="F66" s="6"/>
-      <c r="G66" s="13">
+      <c r="G66" s="14">
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="H66" s="13"/>
-      <c r="I66" s="13"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
       <c r="J66" s="6"/>
-      <c r="K66" s="14">
+      <c r="K66" s="13">
         <f t="shared" ref="K66:K73" si="17">G66/B66</f>
         <v>-0.66666666666666663</v>
       </c>
-      <c r="L66" s="14"/>
-      <c r="M66" s="14"/>
+      <c r="L66" s="13"/>
+      <c r="M66" s="13"/>
       <c r="N66" s="6"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
@@ -2933,25 +2933,25 @@
       <c r="B67" s="1">
         <v>1</v>
       </c>
-      <c r="C67" s="13">
+      <c r="C67" s="14">
         <v>6</v>
       </c>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
       <c r="F67" s="6"/>
-      <c r="G67" s="13">
+      <c r="G67" s="14">
         <f t="shared" si="16"/>
         <v>5</v>
       </c>
-      <c r="H67" s="13"/>
-      <c r="I67" s="13"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
       <c r="J67" s="6"/>
-      <c r="K67" s="14">
+      <c r="K67" s="13">
         <f t="shared" si="17"/>
         <v>5</v>
       </c>
-      <c r="L67" s="14"/>
-      <c r="M67" s="14"/>
+      <c r="L67" s="13"/>
+      <c r="M67" s="13"/>
       <c r="N67" s="6"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
@@ -2961,25 +2961,25 @@
       <c r="B68" s="1">
         <v>7.5959820000000002</v>
       </c>
-      <c r="C68" s="13">
+      <c r="C68" s="14">
         <v>6.7755099999999997</v>
       </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
       <c r="F68" s="6"/>
-      <c r="G68" s="13">
+      <c r="G68" s="14">
         <f t="shared" si="16"/>
         <v>-0.82047200000000053</v>
       </c>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
       <c r="J68" s="6"/>
-      <c r="K68" s="14">
+      <c r="K68" s="13">
         <f t="shared" si="17"/>
         <v>-0.10801394737375634</v>
       </c>
-      <c r="L68" s="14"/>
-      <c r="M68" s="14"/>
+      <c r="L68" s="13"/>
+      <c r="M68" s="13"/>
       <c r="N68" s="6"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
@@ -2989,25 +2989,25 @@
       <c r="B69" s="1">
         <v>8</v>
       </c>
-      <c r="C69" s="13">
+      <c r="C69" s="14">
         <v>7</v>
       </c>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
       <c r="F69" s="6"/>
-      <c r="G69" s="13">
+      <c r="G69" s="14">
         <f t="shared" si="16"/>
         <v>-1</v>
       </c>
-      <c r="H69" s="13"/>
-      <c r="I69" s="13"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
       <c r="J69" s="6"/>
-      <c r="K69" s="14">
+      <c r="K69" s="13">
         <f t="shared" si="17"/>
         <v>-0.125</v>
       </c>
-      <c r="L69" s="14"/>
-      <c r="M69" s="14"/>
+      <c r="L69" s="13"/>
+      <c r="M69" s="13"/>
       <c r="N69" s="6"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
@@ -3017,25 +3017,25 @@
       <c r="B70" s="1">
         <v>8</v>
       </c>
-      <c r="C70" s="13">
+      <c r="C70" s="14">
         <v>8</v>
       </c>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
       <c r="F70" s="6"/>
-      <c r="G70" s="13">
+      <c r="G70" s="14">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
       <c r="J70" s="6"/>
-      <c r="K70" s="14">
+      <c r="K70" s="13">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="L70" s="14"/>
-      <c r="M70" s="14"/>
+      <c r="L70" s="13"/>
+      <c r="M70" s="13"/>
       <c r="N70" s="6"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
@@ -3045,25 +3045,25 @@
       <c r="B71" s="1">
         <v>5</v>
       </c>
-      <c r="C71" s="13">
+      <c r="C71" s="14">
         <v>4</v>
       </c>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
       <c r="F71" s="6"/>
-      <c r="G71" s="13">
+      <c r="G71" s="14">
         <f t="shared" si="16"/>
         <v>-1</v>
       </c>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
       <c r="J71" s="6"/>
-      <c r="K71" s="14">
+      <c r="K71" s="13">
         <f t="shared" si="17"/>
         <v>-0.2</v>
       </c>
-      <c r="L71" s="14"/>
-      <c r="M71" s="14"/>
+      <c r="L71" s="13"/>
+      <c r="M71" s="13"/>
       <c r="N71" s="6"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
@@ -3073,25 +3073,25 @@
       <c r="B72" s="1">
         <v>2234</v>
       </c>
-      <c r="C72" s="13">
+      <c r="C72" s="14">
         <v>517</v>
       </c>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
       <c r="F72" s="6"/>
-      <c r="G72" s="13">
+      <c r="G72" s="14">
         <f t="shared" si="16"/>
         <v>-1717</v>
       </c>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
       <c r="J72" s="6"/>
-      <c r="K72" s="14">
+      <c r="K72" s="13">
         <f t="shared" si="17"/>
         <v>-0.76857654431512978</v>
       </c>
-      <c r="L72" s="14"/>
-      <c r="M72" s="14"/>
+      <c r="L72" s="13"/>
+      <c r="M72" s="13"/>
       <c r="N72" s="6"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
@@ -3101,25 +3101,25 @@
       <c r="B73" s="5">
         <v>0.71237245000000005</v>
       </c>
-      <c r="C73" s="15">
+      <c r="C73" s="18">
         <v>0.16485969</v>
       </c>
-      <c r="D73" s="15"/>
-      <c r="E73" s="15"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
       <c r="F73" s="6"/>
-      <c r="G73" s="13">
+      <c r="G73" s="14">
         <f t="shared" si="16"/>
         <v>-0.54751276000000004</v>
       </c>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
       <c r="J73" s="6"/>
-      <c r="K73" s="14">
+      <c r="K73" s="13">
         <f t="shared" si="17"/>
         <v>-0.76857655008977399</v>
       </c>
-      <c r="L73" s="14"/>
-      <c r="M73" s="14"/>
+      <c r="L73" s="13"/>
+      <c r="M73" s="13"/>
       <c r="N73" s="6"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
@@ -3142,24 +3142,24 @@
       <c r="A75" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B75" s="13" t="s">
+      <c r="B75" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C75" s="13"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
       <c r="F75" s="6"/>
-      <c r="G75" s="13" t="s">
+      <c r="G75" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H75" s="13"/>
-      <c r="I75" s="13"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
       <c r="J75" s="6"/>
-      <c r="K75" s="13" t="s">
+      <c r="K75" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="L75" s="13"/>
-      <c r="M75" s="13"/>
+      <c r="L75" s="14"/>
+      <c r="M75" s="14"/>
       <c r="N75" s="6"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
@@ -3169,25 +3169,25 @@
       <c r="B76" s="1">
         <v>15.246810999999999</v>
       </c>
-      <c r="C76" s="13">
-        <v>0</v>
-      </c>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
+      <c r="C76" s="14">
+        <v>0</v>
+      </c>
+      <c r="D76" s="14"/>
+      <c r="E76" s="14"/>
       <c r="F76" s="6"/>
-      <c r="G76" s="13">
+      <c r="G76" s="14">
         <f t="shared" ref="G76:G87" si="18">C76-B76</f>
         <v>-15.246810999999999</v>
       </c>
-      <c r="H76" s="13"/>
-      <c r="I76" s="13"/>
+      <c r="H76" s="14"/>
+      <c r="I76" s="14"/>
       <c r="J76" s="6"/>
-      <c r="K76" s="14">
+      <c r="K76" s="13">
         <f t="shared" ref="K76:K87" si="19">G76/B76</f>
         <v>-1</v>
       </c>
-      <c r="L76" s="14"/>
-      <c r="M76" s="14"/>
+      <c r="L76" s="13"/>
+      <c r="M76" s="13"/>
       <c r="N76" s="6"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
@@ -3197,25 +3197,25 @@
       <c r="B77" s="1">
         <v>2.0593110000000001</v>
       </c>
-      <c r="C77" s="13">
-        <v>0</v>
-      </c>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
+      <c r="C77" s="14">
+        <v>0</v>
+      </c>
+      <c r="D77" s="14"/>
+      <c r="E77" s="14"/>
       <c r="F77" s="6"/>
-      <c r="G77" s="13">
+      <c r="G77" s="14">
         <f t="shared" si="18"/>
         <v>-2.0593110000000001</v>
       </c>
-      <c r="H77" s="13"/>
-      <c r="I77" s="13"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
       <c r="J77" s="6"/>
-      <c r="K77" s="14">
+      <c r="K77" s="13">
         <f t="shared" si="19"/>
         <v>-1</v>
       </c>
-      <c r="L77" s="14"/>
-      <c r="M77" s="14"/>
+      <c r="L77" s="13"/>
+      <c r="M77" s="13"/>
       <c r="N77" s="6"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
@@ -3225,25 +3225,25 @@
       <c r="B78" s="1">
         <v>2</v>
       </c>
-      <c r="C78" s="13">
-        <v>0</v>
-      </c>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
+      <c r="C78" s="14">
+        <v>0</v>
+      </c>
+      <c r="D78" s="14"/>
+      <c r="E78" s="14"/>
       <c r="F78" s="6"/>
-      <c r="G78" s="13">
+      <c r="G78" s="14">
         <f t="shared" si="18"/>
         <v>-2</v>
       </c>
-      <c r="H78" s="13"/>
-      <c r="I78" s="13"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
       <c r="J78" s="6"/>
-      <c r="K78" s="14">
+      <c r="K78" s="13">
         <f t="shared" si="19"/>
         <v>-1</v>
       </c>
-      <c r="L78" s="14"/>
-      <c r="M78" s="14"/>
+      <c r="L78" s="13"/>
+      <c r="M78" s="13"/>
       <c r="N78" s="6"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
@@ -3253,25 +3253,25 @@
       <c r="B79" s="1">
         <v>-2</v>
       </c>
-      <c r="C79" s="13">
-        <v>0</v>
-      </c>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
+      <c r="C79" s="14">
+        <v>0</v>
+      </c>
+      <c r="D79" s="14"/>
+      <c r="E79" s="14"/>
       <c r="F79" s="6"/>
-      <c r="G79" s="13">
+      <c r="G79" s="14">
         <f t="shared" si="18"/>
         <v>2</v>
       </c>
-      <c r="H79" s="13"/>
-      <c r="I79" s="13"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
       <c r="J79" s="6"/>
-      <c r="K79" s="14">
+      <c r="K79" s="13">
         <f t="shared" si="19"/>
         <v>-1</v>
       </c>
-      <c r="L79" s="14"/>
-      <c r="M79" s="14"/>
+      <c r="L79" s="13"/>
+      <c r="M79" s="13"/>
       <c r="N79" s="6"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
@@ -3281,25 +3281,25 @@
       <c r="B80" s="1">
         <v>-3</v>
       </c>
-      <c r="C80" s="13">
-        <v>0</v>
-      </c>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
+      <c r="C80" s="14">
+        <v>0</v>
+      </c>
+      <c r="D80" s="14"/>
+      <c r="E80" s="14"/>
       <c r="F80" s="6"/>
-      <c r="G80" s="13">
+      <c r="G80" s="14">
         <f t="shared" si="18"/>
         <v>3</v>
       </c>
-      <c r="H80" s="13"/>
-      <c r="I80" s="13"/>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
       <c r="J80" s="6"/>
-      <c r="K80" s="14">
+      <c r="K80" s="13">
         <f t="shared" si="19"/>
         <v>-1</v>
       </c>
-      <c r="L80" s="14"/>
-      <c r="M80" s="14"/>
+      <c r="L80" s="13"/>
+      <c r="M80" s="13"/>
       <c r="N80" s="6"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
@@ -3309,25 +3309,25 @@
       <c r="B81" s="1">
         <v>90</v>
       </c>
-      <c r="C81" s="13">
+      <c r="C81" s="14">
         <v>8</v>
       </c>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="14"/>
       <c r="F81" s="6"/>
-      <c r="G81" s="13">
+      <c r="G81" s="14">
         <f t="shared" si="18"/>
         <v>-82</v>
       </c>
-      <c r="H81" s="13"/>
-      <c r="I81" s="13"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
       <c r="J81" s="6"/>
-      <c r="K81" s="14">
+      <c r="K81" s="13">
         <f t="shared" si="19"/>
         <v>-0.91111111111111109</v>
       </c>
-      <c r="L81" s="14"/>
-      <c r="M81" s="14"/>
+      <c r="L81" s="13"/>
+      <c r="M81" s="13"/>
       <c r="N81" s="6"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
@@ -3337,25 +3337,25 @@
       <c r="B82" s="1">
         <v>6.7799740000000002</v>
       </c>
-      <c r="C82" s="13">
+      <c r="C82" s="14">
         <v>8</v>
       </c>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14"/>
       <c r="F82" s="6"/>
-      <c r="G82" s="13">
+      <c r="G82" s="14">
         <f t="shared" si="18"/>
         <v>1.2200259999999998</v>
       </c>
-      <c r="H82" s="13"/>
-      <c r="I82" s="13"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
       <c r="J82" s="6"/>
-      <c r="K82" s="14">
+      <c r="K82" s="13">
         <f t="shared" si="19"/>
         <v>0.17994552781470841</v>
       </c>
-      <c r="L82" s="14"/>
-      <c r="M82" s="14"/>
+      <c r="L82" s="13"/>
+      <c r="M82" s="13"/>
       <c r="N82" s="6"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
@@ -3365,25 +3365,25 @@
       <c r="B83" s="1">
         <v>7</v>
       </c>
-      <c r="C83" s="13">
+      <c r="C83" s="14">
         <v>8</v>
       </c>
-      <c r="D83" s="13"/>
-      <c r="E83" s="13"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="14"/>
       <c r="F83" s="6"/>
-      <c r="G83" s="13">
+      <c r="G83" s="14">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="H83" s="13"/>
-      <c r="I83" s="13"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
       <c r="J83" s="6"/>
-      <c r="K83" s="14">
+      <c r="K83" s="13">
         <f t="shared" si="19"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="L83" s="14"/>
-      <c r="M83" s="14"/>
+      <c r="L83" s="13"/>
+      <c r="M83" s="13"/>
       <c r="N83" s="6"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
@@ -3393,25 +3393,25 @@
       <c r="B84" s="1">
         <v>8</v>
       </c>
-      <c r="C84" s="13">
+      <c r="C84" s="14">
         <v>8</v>
       </c>
-      <c r="D84" s="13"/>
-      <c r="E84" s="13"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="14"/>
       <c r="F84" s="6"/>
-      <c r="G84" s="13">
+      <c r="G84" s="14">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="H84" s="13"/>
-      <c r="I84" s="13"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
       <c r="J84" s="6"/>
-      <c r="K84" s="14">
+      <c r="K84" s="13">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L84" s="14"/>
-      <c r="M84" s="14"/>
+      <c r="L84" s="13"/>
+      <c r="M84" s="13"/>
       <c r="N84" s="6"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
@@ -3421,25 +3421,25 @@
       <c r="B85" s="1">
         <v>3</v>
       </c>
-      <c r="C85" s="13">
+      <c r="C85" s="14">
         <v>8</v>
       </c>
-      <c r="D85" s="13"/>
-      <c r="E85" s="13"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="14"/>
       <c r="F85" s="6"/>
-      <c r="G85" s="13">
+      <c r="G85" s="14">
         <f t="shared" si="18"/>
         <v>5</v>
       </c>
-      <c r="H85" s="13"/>
-      <c r="I85" s="13"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
       <c r="J85" s="6"/>
-      <c r="K85" s="14">
+      <c r="K85" s="13">
         <f t="shared" si="19"/>
         <v>1.6666666666666667</v>
       </c>
-      <c r="L85" s="14"/>
-      <c r="M85" s="14"/>
+      <c r="L85" s="13"/>
+      <c r="M85" s="13"/>
       <c r="N85" s="6"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
@@ -3449,25 +3449,25 @@
       <c r="B86" s="1">
         <v>72</v>
       </c>
-      <c r="C86" s="13">
+      <c r="C86" s="14">
         <v>3136</v>
       </c>
-      <c r="D86" s="13"/>
-      <c r="E86" s="13"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="14"/>
       <c r="F86" s="6"/>
-      <c r="G86" s="13">
+      <c r="G86" s="14">
         <f t="shared" si="18"/>
         <v>3064</v>
       </c>
-      <c r="H86" s="13"/>
-      <c r="I86" s="13"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
       <c r="J86" s="6"/>
-      <c r="K86" s="14">
+      <c r="K86" s="13">
         <f t="shared" si="19"/>
         <v>42.555555555555557</v>
       </c>
-      <c r="L86" s="14"/>
-      <c r="M86" s="14"/>
+      <c r="L86" s="13"/>
+      <c r="M86" s="13"/>
       <c r="N86" s="6"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
@@ -3477,25 +3477,25 @@
       <c r="B87" s="5">
         <v>2.2959179999999999E-2</v>
       </c>
-      <c r="C87" s="14">
+      <c r="C87" s="13">
         <v>1</v>
       </c>
-      <c r="D87" s="14"/>
-      <c r="E87" s="14"/>
+      <c r="D87" s="13"/>
+      <c r="E87" s="13"/>
       <c r="F87" s="6"/>
-      <c r="G87" s="13">
+      <c r="G87" s="14">
         <f t="shared" si="18"/>
         <v>0.97704082000000003</v>
       </c>
-      <c r="H87" s="13"/>
-      <c r="I87" s="13"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
       <c r="J87" s="6"/>
-      <c r="K87" s="14">
+      <c r="K87" s="13">
         <f t="shared" si="19"/>
         <v>42.555562524445563</v>
       </c>
-      <c r="L87" s="14"/>
-      <c r="M87" s="14"/>
+      <c r="L87" s="13"/>
+      <c r="M87" s="13"/>
       <c r="N87" s="6"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
@@ -3518,24 +3518,24 @@
       <c r="A89" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="B89" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C89" s="13"/>
-      <c r="D89" s="13"/>
-      <c r="E89" s="13"/>
+      <c r="C89" s="14"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="14"/>
       <c r="F89" s="6"/>
-      <c r="G89" s="13" t="s">
+      <c r="G89" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H89" s="13"/>
-      <c r="I89" s="13"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="14"/>
       <c r="J89" s="6"/>
-      <c r="K89" s="13" t="s">
+      <c r="K89" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="L89" s="13"/>
-      <c r="M89" s="13"/>
+      <c r="L89" s="14"/>
+      <c r="M89" s="14"/>
       <c r="N89" s="6"/>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
@@ -3545,25 +3545,25 @@
       <c r="B90" s="1">
         <v>0.46843099999999999</v>
       </c>
-      <c r="C90" s="13">
+      <c r="C90" s="14">
         <v>0.93590600000000002</v>
       </c>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="14"/>
       <c r="F90" s="6"/>
-      <c r="G90" s="13">
+      <c r="G90" s="14">
         <f t="shared" ref="G90:G101" si="20">C90-B90</f>
         <v>0.46747500000000003</v>
       </c>
-      <c r="H90" s="13"/>
-      <c r="I90" s="13"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
       <c r="J90" s="6"/>
-      <c r="K90" s="14">
+      <c r="K90" s="13">
         <f>G90/B90</f>
         <v>0.99795914446311207</v>
       </c>
-      <c r="L90" s="14"/>
-      <c r="M90" s="14"/>
+      <c r="L90" s="13"/>
+      <c r="M90" s="13"/>
       <c r="N90" s="6"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
@@ -3573,25 +3573,25 @@
       <c r="B91" s="1">
         <v>0.34279300000000001</v>
       </c>
-      <c r="C91" s="13">
+      <c r="C91" s="14">
         <v>0.419962</v>
       </c>
-      <c r="D91" s="13"/>
-      <c r="E91" s="13"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="14"/>
       <c r="F91" s="6"/>
-      <c r="G91" s="13">
+      <c r="G91" s="14">
         <f t="shared" si="20"/>
         <v>7.7168999999999988E-2</v>
       </c>
-      <c r="H91" s="13"/>
-      <c r="I91" s="13"/>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
       <c r="J91" s="6"/>
-      <c r="K91" s="14">
+      <c r="K91" s="13">
         <f t="shared" ref="K91" si="21">G91/B91</f>
         <v>0.22511836589428602</v>
       </c>
-      <c r="L91" s="14"/>
-      <c r="M91" s="14"/>
+      <c r="L91" s="13"/>
+      <c r="M91" s="13"/>
       <c r="N91" s="6"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
@@ -3601,24 +3601,24 @@
       <c r="B92" s="1">
         <v>0</v>
       </c>
-      <c r="C92" s="13">
-        <v>0</v>
-      </c>
-      <c r="D92" s="13"/>
-      <c r="E92" s="13"/>
+      <c r="C92" s="14">
+        <v>0</v>
+      </c>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
       <c r="F92" s="6"/>
-      <c r="G92" s="13">
+      <c r="G92" s="14">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="H92" s="13"/>
-      <c r="I92" s="13"/>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
       <c r="J92" s="6"/>
-      <c r="K92" s="14" t="s">
+      <c r="K92" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="L92" s="14"/>
-      <c r="M92" s="14"/>
+      <c r="L92" s="13"/>
+      <c r="M92" s="13"/>
       <c r="N92" s="6"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
@@ -3628,24 +3628,24 @@
       <c r="B93" s="1">
         <v>0</v>
       </c>
-      <c r="C93" s="13">
-        <v>0</v>
-      </c>
-      <c r="D93" s="13"/>
-      <c r="E93" s="13"/>
+      <c r="C93" s="14">
+        <v>0</v>
+      </c>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
       <c r="F93" s="6"/>
-      <c r="G93" s="13">
+      <c r="G93" s="14">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="H93" s="13"/>
-      <c r="I93" s="13"/>
+      <c r="H93" s="14"/>
+      <c r="I93" s="14"/>
       <c r="J93" s="6"/>
-      <c r="K93" s="14" t="s">
+      <c r="K93" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="L93" s="14"/>
-      <c r="M93" s="14"/>
+      <c r="L93" s="13"/>
+      <c r="M93" s="13"/>
       <c r="N93" s="6"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
@@ -3655,25 +3655,25 @@
       <c r="B94" s="1">
         <v>-3</v>
       </c>
-      <c r="C94" s="13">
-        <v>0</v>
-      </c>
-      <c r="D94" s="13"/>
-      <c r="E94" s="13"/>
+      <c r="C94" s="14">
+        <v>0</v>
+      </c>
+      <c r="D94" s="14"/>
+      <c r="E94" s="14"/>
       <c r="F94" s="6"/>
-      <c r="G94" s="13">
+      <c r="G94" s="14">
         <f t="shared" si="20"/>
         <v>3</v>
       </c>
-      <c r="H94" s="13"/>
-      <c r="I94" s="13"/>
+      <c r="H94" s="14"/>
+      <c r="I94" s="14"/>
       <c r="J94" s="6"/>
-      <c r="K94" s="14">
+      <c r="K94" s="13">
         <f t="shared" ref="K94:K101" si="22">G94/B94</f>
         <v>-1</v>
       </c>
-      <c r="L94" s="14"/>
-      <c r="M94" s="14"/>
+      <c r="L94" s="13"/>
+      <c r="M94" s="13"/>
       <c r="N94" s="6"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
@@ -3683,25 +3683,25 @@
       <c r="B95" s="1">
         <v>1</v>
       </c>
-      <c r="C95" s="13">
+      <c r="C95" s="14">
         <v>5</v>
       </c>
-      <c r="D95" s="13"/>
-      <c r="E95" s="13"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="14"/>
       <c r="F95" s="6"/>
-      <c r="G95" s="13">
+      <c r="G95" s="14">
         <f t="shared" si="20"/>
         <v>4</v>
       </c>
-      <c r="H95" s="13"/>
-      <c r="I95" s="13"/>
+      <c r="H95" s="14"/>
+      <c r="I95" s="14"/>
       <c r="J95" s="6"/>
-      <c r="K95" s="14">
+      <c r="K95" s="13">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="L95" s="14"/>
-      <c r="M95" s="14"/>
+      <c r="L95" s="13"/>
+      <c r="M95" s="13"/>
       <c r="N95" s="6"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
@@ -3711,25 +3711,25 @@
       <c r="B96" s="1">
         <v>7.5959820000000002</v>
       </c>
-      <c r="C96" s="13">
+      <c r="C96" s="14">
         <v>7.6584820000000002</v>
       </c>
-      <c r="D96" s="13"/>
-      <c r="E96" s="13"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="14"/>
       <c r="F96" s="6"/>
-      <c r="G96" s="13">
+      <c r="G96" s="14">
         <f t="shared" si="20"/>
         <v>6.25E-2</v>
       </c>
-      <c r="H96" s="13"/>
-      <c r="I96" s="13"/>
+      <c r="H96" s="14"/>
+      <c r="I96" s="14"/>
       <c r="J96" s="6"/>
-      <c r="K96" s="14">
+      <c r="K96" s="13">
         <f t="shared" si="22"/>
         <v>8.2280342423138968E-3</v>
       </c>
-      <c r="L96" s="14"/>
-      <c r="M96" s="14"/>
+      <c r="L96" s="13"/>
+      <c r="M96" s="13"/>
       <c r="N96" s="6"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
@@ -3739,25 +3739,25 @@
       <c r="B97" s="1">
         <v>8</v>
       </c>
-      <c r="C97" s="13">
+      <c r="C97" s="14">
         <v>8</v>
       </c>
-      <c r="D97" s="13"/>
-      <c r="E97" s="13"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
       <c r="F97" s="6"/>
-      <c r="G97" s="13">
+      <c r="G97" s="14">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="H97" s="13"/>
-      <c r="I97" s="13"/>
+      <c r="H97" s="14"/>
+      <c r="I97" s="14"/>
       <c r="J97" s="6"/>
-      <c r="K97" s="14">
+      <c r="K97" s="13">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L97" s="14"/>
-      <c r="M97" s="14"/>
+      <c r="L97" s="13"/>
+      <c r="M97" s="13"/>
       <c r="N97" s="6"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.2">
@@ -3767,25 +3767,25 @@
       <c r="B98" s="1">
         <v>8</v>
       </c>
-      <c r="C98" s="13">
+      <c r="C98" s="14">
         <v>8</v>
       </c>
-      <c r="D98" s="13"/>
-      <c r="E98" s="13"/>
+      <c r="D98" s="14"/>
+      <c r="E98" s="14"/>
       <c r="F98" s="6"/>
-      <c r="G98" s="13">
+      <c r="G98" s="14">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="H98" s="13"/>
-      <c r="I98" s="13"/>
+      <c r="H98" s="14"/>
+      <c r="I98" s="14"/>
       <c r="J98" s="6"/>
-      <c r="K98" s="14">
+      <c r="K98" s="13">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L98" s="14"/>
-      <c r="M98" s="14"/>
+      <c r="L98" s="13"/>
+      <c r="M98" s="13"/>
       <c r="N98" s="6"/>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.2">
@@ -3795,25 +3795,25 @@
       <c r="B99" s="1">
         <v>5</v>
       </c>
-      <c r="C99" s="13">
+      <c r="C99" s="14">
         <v>5</v>
       </c>
-      <c r="D99" s="13"/>
-      <c r="E99" s="13"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="14"/>
       <c r="F99" s="6"/>
-      <c r="G99" s="13">
+      <c r="G99" s="14">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="H99" s="13"/>
-      <c r="I99" s="13"/>
+      <c r="H99" s="14"/>
+      <c r="I99" s="14"/>
       <c r="J99" s="6"/>
-      <c r="K99" s="14">
+      <c r="K99" s="13">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L99" s="14"/>
-      <c r="M99" s="14"/>
+      <c r="L99" s="13"/>
+      <c r="M99" s="13"/>
       <c r="N99" s="6"/>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.2">
@@ -3823,25 +3823,25 @@
       <c r="B100" s="1">
         <v>2234</v>
       </c>
-      <c r="C100" s="13">
+      <c r="C100" s="14">
         <v>2321</v>
       </c>
-      <c r="D100" s="13"/>
-      <c r="E100" s="13"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="14"/>
       <c r="F100" s="6"/>
-      <c r="G100" s="13">
+      <c r="G100" s="14">
         <f t="shared" si="20"/>
         <v>87</v>
       </c>
-      <c r="H100" s="13"/>
-      <c r="I100" s="13"/>
+      <c r="H100" s="14"/>
+      <c r="I100" s="14"/>
       <c r="J100" s="6"/>
-      <c r="K100" s="14">
+      <c r="K100" s="13">
         <f t="shared" si="22"/>
         <v>3.8943598925693823E-2</v>
       </c>
-      <c r="L100" s="14"/>
-      <c r="M100" s="14"/>
+      <c r="L100" s="13"/>
+      <c r="M100" s="13"/>
       <c r="N100" s="6"/>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.2">
@@ -3851,25 +3851,25 @@
       <c r="B101" s="5">
         <v>0.71237245000000005</v>
       </c>
-      <c r="C101" s="15">
+      <c r="C101" s="18">
         <v>0.74011479999999996</v>
       </c>
-      <c r="D101" s="15"/>
-      <c r="E101" s="15"/>
+      <c r="D101" s="18"/>
+      <c r="E101" s="18"/>
       <c r="F101" s="6"/>
-      <c r="G101" s="13">
+      <c r="G101" s="14">
         <f t="shared" si="20"/>
         <v>2.7742349999999916E-2</v>
       </c>
-      <c r="H101" s="13"/>
-      <c r="I101" s="13"/>
+      <c r="H101" s="14"/>
+      <c r="I101" s="14"/>
       <c r="J101" s="6"/>
-      <c r="K101" s="14">
+      <c r="K101" s="13">
         <f t="shared" si="22"/>
         <v>3.8943603167135271E-2</v>
       </c>
-      <c r="L101" s="14"/>
-      <c r="M101" s="14"/>
+      <c r="L101" s="13"/>
+      <c r="M101" s="13"/>
       <c r="N101" s="6"/>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.2">
@@ -3892,24 +3892,24 @@
       <c r="A103" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B103" s="13" t="s">
+      <c r="B103" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C103" s="13"/>
-      <c r="D103" s="13"/>
-      <c r="E103" s="13"/>
+      <c r="C103" s="14"/>
+      <c r="D103" s="14"/>
+      <c r="E103" s="14"/>
       <c r="F103" s="6"/>
-      <c r="G103" s="13" t="s">
+      <c r="G103" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H103" s="13"/>
-      <c r="I103" s="13"/>
+      <c r="H103" s="14"/>
+      <c r="I103" s="14"/>
       <c r="J103" s="6"/>
-      <c r="K103" s="13" t="s">
+      <c r="K103" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="L103" s="13"/>
-      <c r="M103" s="13"/>
+      <c r="L103" s="14"/>
+      <c r="M103" s="14"/>
       <c r="N103" s="6"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.2">
@@ -3919,25 +3919,25 @@
       <c r="B104" s="1">
         <v>15.246810999999999</v>
       </c>
-      <c r="C104" s="13">
+      <c r="C104" s="14">
         <v>0.10076499999999999</v>
       </c>
-      <c r="D104" s="13"/>
-      <c r="E104" s="13"/>
+      <c r="D104" s="14"/>
+      <c r="E104" s="14"/>
       <c r="F104" s="6"/>
-      <c r="G104" s="13">
+      <c r="G104" s="14">
         <f t="shared" ref="G104:G115" si="23">C104-B104</f>
         <v>-15.146045999999998</v>
       </c>
-      <c r="H104" s="13"/>
-      <c r="I104" s="13"/>
+      <c r="H104" s="14"/>
+      <c r="I104" s="14"/>
       <c r="J104" s="6"/>
-      <c r="K104" s="14">
+      <c r="K104" s="13">
         <f>G104/B104</f>
         <v>-0.99339107699308393</v>
       </c>
-      <c r="L104" s="14"/>
-      <c r="M104" s="14"/>
+      <c r="L104" s="13"/>
+      <c r="M104" s="13"/>
       <c r="N104" s="6"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.2">
@@ -3947,25 +3947,25 @@
       <c r="B105" s="1">
         <v>2.0593110000000001</v>
       </c>
-      <c r="C105" s="13">
+      <c r="C105" s="14">
         <v>2.6148000000000001E-2</v>
       </c>
-      <c r="D105" s="13"/>
-      <c r="E105" s="13"/>
+      <c r="D105" s="14"/>
+      <c r="E105" s="14"/>
       <c r="F105" s="6"/>
-      <c r="G105" s="13">
+      <c r="G105" s="14">
         <f t="shared" si="23"/>
         <v>-2.0331630000000001</v>
       </c>
-      <c r="H105" s="13"/>
-      <c r="I105" s="13"/>
+      <c r="H105" s="14"/>
+      <c r="I105" s="14"/>
       <c r="J105" s="6"/>
-      <c r="K105" s="14">
+      <c r="K105" s="13">
         <f t="shared" ref="K105:K115" si="24">G105/B105</f>
         <v>-0.98730254925069594</v>
       </c>
-      <c r="L105" s="14"/>
-      <c r="M105" s="14"/>
+      <c r="L105" s="13"/>
+      <c r="M105" s="13"/>
       <c r="N105" s="6"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.2">
@@ -3975,25 +3975,25 @@
       <c r="B106" s="1">
         <v>2</v>
       </c>
-      <c r="C106" s="13">
-        <v>0</v>
-      </c>
-      <c r="D106" s="13"/>
-      <c r="E106" s="13"/>
+      <c r="C106" s="14">
+        <v>0</v>
+      </c>
+      <c r="D106" s="14"/>
+      <c r="E106" s="14"/>
       <c r="F106" s="6"/>
-      <c r="G106" s="13">
+      <c r="G106" s="14">
         <f t="shared" si="23"/>
         <v>-2</v>
       </c>
-      <c r="H106" s="13"/>
-      <c r="I106" s="13"/>
+      <c r="H106" s="14"/>
+      <c r="I106" s="14"/>
       <c r="J106" s="6"/>
-      <c r="K106" s="14">
+      <c r="K106" s="13">
         <f t="shared" si="24"/>
         <v>-1</v>
       </c>
-      <c r="L106" s="14"/>
-      <c r="M106" s="14"/>
+      <c r="L106" s="13"/>
+      <c r="M106" s="13"/>
       <c r="N106" s="6"/>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.2">
@@ -4003,25 +4003,25 @@
       <c r="B107" s="1">
         <v>-2</v>
       </c>
-      <c r="C107" s="13">
-        <v>0</v>
-      </c>
-      <c r="D107" s="13"/>
-      <c r="E107" s="13"/>
+      <c r="C107" s="14">
+        <v>0</v>
+      </c>
+      <c r="D107" s="14"/>
+      <c r="E107" s="14"/>
       <c r="F107" s="6"/>
-      <c r="G107" s="13">
+      <c r="G107" s="14">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
-      <c r="H107" s="13"/>
-      <c r="I107" s="13"/>
+      <c r="H107" s="14"/>
+      <c r="I107" s="14"/>
       <c r="J107" s="6"/>
-      <c r="K107" s="14">
+      <c r="K107" s="13">
         <f t="shared" si="24"/>
         <v>-1</v>
       </c>
-      <c r="L107" s="14"/>
-      <c r="M107" s="14"/>
+      <c r="L107" s="13"/>
+      <c r="M107" s="13"/>
       <c r="N107" s="6"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.2">
@@ -4031,25 +4031,25 @@
       <c r="B108" s="1">
         <v>-3</v>
       </c>
-      <c r="C108" s="13">
+      <c r="C108" s="14">
         <v>-2</v>
       </c>
-      <c r="D108" s="13"/>
-      <c r="E108" s="13"/>
+      <c r="D108" s="14"/>
+      <c r="E108" s="14"/>
       <c r="F108" s="6"/>
-      <c r="G108" s="13">
+      <c r="G108" s="14">
         <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="H108" s="13"/>
-      <c r="I108" s="13"/>
+      <c r="H108" s="14"/>
+      <c r="I108" s="14"/>
       <c r="J108" s="6"/>
-      <c r="K108" s="14">
+      <c r="K108" s="13">
         <f t="shared" si="24"/>
         <v>-0.33333333333333331</v>
       </c>
-      <c r="L108" s="14"/>
-      <c r="M108" s="14"/>
+      <c r="L108" s="13"/>
+      <c r="M108" s="13"/>
       <c r="N108" s="6"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
@@ -4059,25 +4059,25 @@
       <c r="B109" s="1">
         <v>90</v>
       </c>
-      <c r="C109" s="13">
+      <c r="C109" s="14">
         <v>11</v>
       </c>
-      <c r="D109" s="13"/>
-      <c r="E109" s="13"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="14"/>
       <c r="F109" s="6"/>
-      <c r="G109" s="13">
+      <c r="G109" s="14">
         <f t="shared" si="23"/>
         <v>-79</v>
       </c>
-      <c r="H109" s="13"/>
-      <c r="I109" s="13"/>
+      <c r="H109" s="14"/>
+      <c r="I109" s="14"/>
       <c r="J109" s="6"/>
-      <c r="K109" s="14">
+      <c r="K109" s="13">
         <f t="shared" si="24"/>
         <v>-0.87777777777777777</v>
       </c>
-      <c r="L109" s="14"/>
-      <c r="M109" s="14"/>
+      <c r="L109" s="13"/>
+      <c r="M109" s="13"/>
       <c r="N109" s="6"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.2">
@@ -4087,25 +4087,25 @@
       <c r="B110" s="1">
         <v>6.7799740000000002</v>
       </c>
-      <c r="C110" s="13">
+      <c r="C110" s="14">
         <v>7.9846940000000002</v>
       </c>
-      <c r="D110" s="13"/>
-      <c r="E110" s="13"/>
+      <c r="D110" s="14"/>
+      <c r="E110" s="14"/>
       <c r="F110" s="6"/>
-      <c r="G110" s="13">
+      <c r="G110" s="14">
         <f t="shared" si="23"/>
         <v>1.20472</v>
       </c>
-      <c r="H110" s="13"/>
-      <c r="I110" s="13"/>
+      <c r="H110" s="14"/>
+      <c r="I110" s="14"/>
       <c r="J110" s="6"/>
-      <c r="K110" s="14">
+      <c r="K110" s="13">
         <f t="shared" si="24"/>
         <v>0.17768799703361693</v>
       </c>
-      <c r="L110" s="14"/>
-      <c r="M110" s="14"/>
+      <c r="L110" s="13"/>
+      <c r="M110" s="13"/>
       <c r="N110" s="6"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.2">
@@ -4115,25 +4115,25 @@
       <c r="B111" s="1">
         <v>7</v>
       </c>
-      <c r="C111" s="13">
+      <c r="C111" s="14">
         <v>8</v>
       </c>
-      <c r="D111" s="13"/>
-      <c r="E111" s="13"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="14"/>
       <c r="F111" s="6"/>
-      <c r="G111" s="13">
+      <c r="G111" s="14">
         <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="H111" s="13"/>
-      <c r="I111" s="13"/>
+      <c r="H111" s="14"/>
+      <c r="I111" s="14"/>
       <c r="J111" s="6"/>
-      <c r="K111" s="14">
+      <c r="K111" s="13">
         <f t="shared" si="24"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="L111" s="14"/>
-      <c r="M111" s="14"/>
+      <c r="L111" s="13"/>
+      <c r="M111" s="13"/>
       <c r="N111" s="6"/>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.2">
@@ -4143,25 +4143,25 @@
       <c r="B112" s="1">
         <v>8</v>
       </c>
-      <c r="C112" s="13">
+      <c r="C112" s="14">
         <v>8</v>
       </c>
-      <c r="D112" s="13"/>
-      <c r="E112" s="13"/>
+      <c r="D112" s="14"/>
+      <c r="E112" s="14"/>
       <c r="F112" s="6"/>
-      <c r="G112" s="13">
+      <c r="G112" s="14">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="H112" s="13"/>
-      <c r="I112" s="13"/>
+      <c r="H112" s="14"/>
+      <c r="I112" s="14"/>
       <c r="J112" s="6"/>
-      <c r="K112" s="14">
+      <c r="K112" s="13">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L112" s="14"/>
-      <c r="M112" s="14"/>
+      <c r="L112" s="13"/>
+      <c r="M112" s="13"/>
       <c r="N112" s="6"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.2">
@@ -4171,25 +4171,25 @@
       <c r="B113" s="1">
         <v>3</v>
       </c>
-      <c r="C113" s="13">
+      <c r="C113" s="14">
         <v>5</v>
       </c>
-      <c r="D113" s="13"/>
-      <c r="E113" s="13"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="14"/>
       <c r="F113" s="6"/>
-      <c r="G113" s="13">
+      <c r="G113" s="14">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
-      <c r="H113" s="13"/>
-      <c r="I113" s="13"/>
+      <c r="H113" s="14"/>
+      <c r="I113" s="14"/>
       <c r="J113" s="6"/>
-      <c r="K113" s="14">
+      <c r="K113" s="13">
         <f t="shared" si="24"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="L113" s="14"/>
-      <c r="M113" s="14"/>
+      <c r="L113" s="13"/>
+      <c r="M113" s="13"/>
       <c r="N113" s="6"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.2">
@@ -4199,25 +4199,25 @@
       <c r="B114" s="1">
         <v>72</v>
       </c>
-      <c r="C114" s="13">
+      <c r="C114" s="14">
         <v>3094</v>
       </c>
-      <c r="D114" s="13"/>
-      <c r="E114" s="13"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="14"/>
       <c r="F114" s="6"/>
-      <c r="G114" s="13">
+      <c r="G114" s="14">
         <f t="shared" si="23"/>
         <v>3022</v>
       </c>
-      <c r="H114" s="13"/>
-      <c r="I114" s="13"/>
+      <c r="H114" s="14"/>
+      <c r="I114" s="14"/>
       <c r="J114" s="6"/>
-      <c r="K114" s="14">
+      <c r="K114" s="13">
         <f t="shared" si="24"/>
         <v>41.972222222222221</v>
       </c>
-      <c r="L114" s="14"/>
-      <c r="M114" s="14"/>
+      <c r="L114" s="13"/>
+      <c r="M114" s="13"/>
       <c r="N114" s="6"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.2">
@@ -4227,25 +4227,25 @@
       <c r="B115" s="5">
         <v>2.2959179999999999E-2</v>
       </c>
-      <c r="C115" s="14">
+      <c r="C115" s="13">
         <v>0.98660714000000005</v>
       </c>
-      <c r="D115" s="14"/>
-      <c r="E115" s="14"/>
+      <c r="D115" s="13"/>
+      <c r="E115" s="13"/>
       <c r="F115" s="6"/>
-      <c r="G115" s="13">
+      <c r="G115" s="14">
         <f t="shared" si="23"/>
         <v>0.96364796000000008</v>
       </c>
-      <c r="H115" s="13"/>
-      <c r="I115" s="13"/>
+      <c r="H115" s="14"/>
+      <c r="I115" s="14"/>
       <c r="J115" s="6"/>
-      <c r="K115" s="14">
+      <c r="K115" s="13">
         <f t="shared" si="24"/>
         <v>41.972228973334417</v>
       </c>
-      <c r="L115" s="14"/>
-      <c r="M115" s="14"/>
+      <c r="L115" s="13"/>
+      <c r="M115" s="13"/>
       <c r="N115" s="6"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.2">
@@ -4268,24 +4268,24 @@
       <c r="A117" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B117" s="13" t="s">
+      <c r="B117" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C117" s="13"/>
-      <c r="D117" s="13"/>
-      <c r="E117" s="13"/>
+      <c r="C117" s="14"/>
+      <c r="D117" s="14"/>
+      <c r="E117" s="14"/>
       <c r="F117" s="6"/>
-      <c r="G117" s="13" t="s">
+      <c r="G117" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H117" s="13"/>
-      <c r="I117" s="13"/>
+      <c r="H117" s="14"/>
+      <c r="I117" s="14"/>
       <c r="J117" s="6"/>
-      <c r="K117" s="13" t="s">
+      <c r="K117" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="L117" s="13"/>
-      <c r="M117" s="13"/>
+      <c r="L117" s="14"/>
+      <c r="M117" s="14"/>
       <c r="N117" s="6"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.2">
@@ -4295,26 +4295,26 @@
       <c r="B118" s="1">
         <v>0.46843099999999999</v>
       </c>
-      <c r="C118" s="13">
+      <c r="C118" s="14">
         <f t="shared" ref="C118:C129" si="25">AVERAGE(C62,C34,C90)</f>
         <v>1.8927509999999999</v>
       </c>
-      <c r="D118" s="13"/>
-      <c r="E118" s="13"/>
+      <c r="D118" s="14"/>
+      <c r="E118" s="14"/>
       <c r="F118" s="6"/>
-      <c r="G118" s="13">
+      <c r="G118" s="14">
         <f t="shared" ref="G118" si="26">C118-B118</f>
         <v>1.4243199999999998</v>
       </c>
-      <c r="H118" s="13"/>
-      <c r="I118" s="13"/>
+      <c r="H118" s="14"/>
+      <c r="I118" s="14"/>
       <c r="J118" s="6"/>
-      <c r="K118" s="14">
+      <c r="K118" s="13">
         <f>G118/B118</f>
         <v>3.0406185756280002</v>
       </c>
-      <c r="L118" s="14"/>
-      <c r="M118" s="14"/>
+      <c r="L118" s="13"/>
+      <c r="M118" s="13"/>
       <c r="N118" s="6"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.2">
@@ -4324,26 +4324,26 @@
       <c r="B119" s="1">
         <v>0.34279300000000001</v>
       </c>
-      <c r="C119" s="13">
+      <c r="C119" s="14">
         <f t="shared" si="25"/>
         <v>0.87595666666666661</v>
       </c>
-      <c r="D119" s="13"/>
-      <c r="E119" s="13"/>
+      <c r="D119" s="14"/>
+      <c r="E119" s="14"/>
       <c r="F119" s="6"/>
-      <c r="G119" s="13">
+      <c r="G119" s="14">
         <f t="shared" ref="G119:G129" si="27">C119-B119</f>
         <v>0.53316366666666659</v>
       </c>
-      <c r="H119" s="13"/>
-      <c r="I119" s="13"/>
+      <c r="H119" s="14"/>
+      <c r="I119" s="14"/>
       <c r="J119" s="6"/>
-      <c r="K119" s="14">
+      <c r="K119" s="13">
         <f t="shared" ref="K119:K129" si="28">G119/B119</f>
         <v>1.5553516748202751</v>
       </c>
-      <c r="L119" s="14"/>
-      <c r="M119" s="14"/>
+      <c r="L119" s="13"/>
+      <c r="M119" s="13"/>
       <c r="N119" s="6"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.2">
@@ -4353,25 +4353,25 @@
       <c r="B120" s="1">
         <v>0</v>
       </c>
-      <c r="C120" s="13">
+      <c r="C120" s="14">
         <f t="shared" si="25"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="D120" s="13"/>
-      <c r="E120" s="13"/>
+      <c r="D120" s="14"/>
+      <c r="E120" s="14"/>
       <c r="F120" s="6"/>
-      <c r="G120" s="13">
+      <c r="G120" s="14">
         <f t="shared" si="27"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="H120" s="13"/>
-      <c r="I120" s="13"/>
+      <c r="H120" s="14"/>
+      <c r="I120" s="14"/>
       <c r="J120" s="6"/>
-      <c r="K120" s="14" t="s">
+      <c r="K120" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="L120" s="14"/>
-      <c r="M120" s="14"/>
+      <c r="L120" s="13"/>
+      <c r="M120" s="13"/>
       <c r="N120" s="6"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.2">
@@ -4381,25 +4381,25 @@
       <c r="B121" s="1">
         <v>0</v>
       </c>
-      <c r="C121" s="13">
+      <c r="C121" s="14">
         <f t="shared" si="25"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="D121" s="13"/>
-      <c r="E121" s="13"/>
+      <c r="D121" s="14"/>
+      <c r="E121" s="14"/>
       <c r="F121" s="6"/>
-      <c r="G121" s="13">
+      <c r="G121" s="14">
         <f t="shared" si="27"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="H121" s="13"/>
-      <c r="I121" s="13"/>
+      <c r="H121" s="14"/>
+      <c r="I121" s="14"/>
       <c r="J121" s="6"/>
-      <c r="K121" s="14" t="s">
+      <c r="K121" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="L121" s="14"/>
-      <c r="M121" s="14"/>
+      <c r="L121" s="13"/>
+      <c r="M121" s="13"/>
       <c r="N121" s="6"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.2">
@@ -4409,26 +4409,26 @@
       <c r="B122" s="1">
         <v>-3</v>
       </c>
-      <c r="C122" s="13">
+      <c r="C122" s="14">
         <f t="shared" si="25"/>
         <v>-0.33333333333333331</v>
       </c>
-      <c r="D122" s="13"/>
-      <c r="E122" s="13"/>
+      <c r="D122" s="14"/>
+      <c r="E122" s="14"/>
       <c r="F122" s="6"/>
-      <c r="G122" s="13">
+      <c r="G122" s="14">
         <f t="shared" si="27"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="H122" s="13"/>
-      <c r="I122" s="13"/>
+      <c r="H122" s="14"/>
+      <c r="I122" s="14"/>
       <c r="J122" s="6"/>
-      <c r="K122" s="14">
+      <c r="K122" s="13">
         <f t="shared" si="28"/>
         <v>-0.88888888888888884</v>
       </c>
-      <c r="L122" s="14"/>
-      <c r="M122" s="14"/>
+      <c r="L122" s="13"/>
+      <c r="M122" s="13"/>
       <c r="N122" s="6"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.2">
@@ -4438,26 +4438,26 @@
       <c r="B123" s="1">
         <v>1</v>
       </c>
-      <c r="C123" s="13">
+      <c r="C123" s="14">
         <f t="shared" si="25"/>
         <v>5.333333333333333</v>
       </c>
-      <c r="D123" s="13"/>
-      <c r="E123" s="13"/>
+      <c r="D123" s="14"/>
+      <c r="E123" s="14"/>
       <c r="F123" s="6"/>
-      <c r="G123" s="13">
+      <c r="G123" s="14">
         <f t="shared" si="27"/>
         <v>4.333333333333333</v>
       </c>
-      <c r="H123" s="13"/>
-      <c r="I123" s="13"/>
+      <c r="H123" s="14"/>
+      <c r="I123" s="14"/>
       <c r="J123" s="6"/>
-      <c r="K123" s="14">
+      <c r="K123" s="13">
         <f t="shared" si="28"/>
         <v>4.333333333333333</v>
       </c>
-      <c r="L123" s="14"/>
-      <c r="M123" s="14"/>
+      <c r="L123" s="13"/>
+      <c r="M123" s="13"/>
       <c r="N123" s="6"/>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.2">
@@ -4467,26 +4467,26 @@
       <c r="B124" s="1">
         <v>7.5959820000000002</v>
       </c>
-      <c r="C124" s="13">
+      <c r="C124" s="14">
         <f t="shared" si="25"/>
         <v>7.2103526666666662</v>
       </c>
-      <c r="D124" s="13"/>
-      <c r="E124" s="13"/>
+      <c r="D124" s="14"/>
+      <c r="E124" s="14"/>
       <c r="F124" s="6"/>
-      <c r="G124" s="13">
+      <c r="G124" s="14">
         <f t="shared" si="27"/>
         <v>-0.38562933333333405</v>
       </c>
-      <c r="H124" s="13"/>
-      <c r="I124" s="13"/>
+      <c r="H124" s="14"/>
+      <c r="I124" s="14"/>
       <c r="J124" s="6"/>
-      <c r="K124" s="14">
+      <c r="K124" s="13">
         <f t="shared" si="28"/>
         <v>-5.0767541752117638E-2</v>
       </c>
-      <c r="L124" s="14"/>
-      <c r="M124" s="14"/>
+      <c r="L124" s="13"/>
+      <c r="M124" s="13"/>
       <c r="N124" s="6"/>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.2">
@@ -4496,26 +4496,26 @@
       <c r="B125" s="1">
         <v>8</v>
       </c>
-      <c r="C125" s="13">
+      <c r="C125" s="14">
         <f t="shared" si="25"/>
         <v>7.333333333333333</v>
       </c>
-      <c r="D125" s="13"/>
-      <c r="E125" s="13"/>
+      <c r="D125" s="14"/>
+      <c r="E125" s="14"/>
       <c r="F125" s="6"/>
-      <c r="G125" s="13">
+      <c r="G125" s="14">
         <f t="shared" si="27"/>
         <v>-0.66666666666666696</v>
       </c>
-      <c r="H125" s="13"/>
-      <c r="I125" s="13"/>
+      <c r="H125" s="14"/>
+      <c r="I125" s="14"/>
       <c r="J125" s="6"/>
-      <c r="K125" s="14">
+      <c r="K125" s="13">
         <f t="shared" si="28"/>
         <v>-8.333333333333337E-2</v>
       </c>
-      <c r="L125" s="14"/>
-      <c r="M125" s="14"/>
+      <c r="L125" s="13"/>
+      <c r="M125" s="13"/>
       <c r="N125" s="6"/>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.2">
@@ -4525,26 +4525,26 @@
       <c r="B126" s="1">
         <v>8</v>
       </c>
-      <c r="C126" s="13">
+      <c r="C126" s="14">
         <f t="shared" si="25"/>
         <v>8</v>
       </c>
-      <c r="D126" s="13"/>
-      <c r="E126" s="13"/>
+      <c r="D126" s="14"/>
+      <c r="E126" s="14"/>
       <c r="F126" s="6"/>
-      <c r="G126" s="13">
+      <c r="G126" s="14">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="H126" s="13"/>
-      <c r="I126" s="13"/>
+      <c r="H126" s="14"/>
+      <c r="I126" s="14"/>
       <c r="J126" s="6"/>
-      <c r="K126" s="14">
+      <c r="K126" s="13">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="L126" s="14"/>
-      <c r="M126" s="14"/>
+      <c r="L126" s="13"/>
+      <c r="M126" s="13"/>
       <c r="N126" s="6"/>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.2">
@@ -4554,26 +4554,26 @@
       <c r="B127" s="1">
         <v>5</v>
       </c>
-      <c r="C127" s="13">
+      <c r="C127" s="14">
         <f t="shared" si="25"/>
         <v>4.333333333333333</v>
       </c>
-      <c r="D127" s="13"/>
-      <c r="E127" s="13"/>
+      <c r="D127" s="14"/>
+      <c r="E127" s="14"/>
       <c r="F127" s="6"/>
-      <c r="G127" s="13">
+      <c r="G127" s="14">
         <f t="shared" si="27"/>
         <v>-0.66666666666666696</v>
       </c>
-      <c r="H127" s="13"/>
-      <c r="I127" s="13"/>
+      <c r="H127" s="14"/>
+      <c r="I127" s="14"/>
       <c r="J127" s="6"/>
-      <c r="K127" s="14">
+      <c r="K127" s="13">
         <f t="shared" si="28"/>
         <v>-0.13333333333333339</v>
       </c>
-      <c r="L127" s="14"/>
-      <c r="M127" s="14"/>
+      <c r="L127" s="13"/>
+      <c r="M127" s="13"/>
       <c r="N127" s="6"/>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.2">
@@ -4583,26 +4583,26 @@
       <c r="B128" s="1">
         <v>2234</v>
       </c>
-      <c r="C128" s="13">
+      <c r="C128" s="14">
         <f t="shared" si="25"/>
         <v>1430.6666666666667</v>
       </c>
-      <c r="D128" s="13"/>
-      <c r="E128" s="13"/>
+      <c r="D128" s="14"/>
+      <c r="E128" s="14"/>
       <c r="F128" s="6"/>
-      <c r="G128" s="13">
+      <c r="G128" s="14">
         <f t="shared" si="27"/>
         <v>-803.33333333333326</v>
       </c>
-      <c r="H128" s="13"/>
-      <c r="I128" s="13"/>
+      <c r="H128" s="14"/>
+      <c r="I128" s="14"/>
       <c r="J128" s="6"/>
-      <c r="K128" s="14">
+      <c r="K128" s="13">
         <f t="shared" si="28"/>
         <v>-0.35959415099970155</v>
       </c>
-      <c r="L128" s="14"/>
-      <c r="M128" s="14"/>
+      <c r="L128" s="13"/>
+      <c r="M128" s="13"/>
       <c r="N128" s="6"/>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
@@ -4612,26 +4612,26 @@
       <c r="B129" s="5">
         <v>0.71237245000000005</v>
       </c>
-      <c r="C129" s="17">
+      <c r="C129" s="16">
         <f t="shared" si="25"/>
         <v>0.45620748333333333</v>
       </c>
-      <c r="D129" s="13"/>
-      <c r="E129" s="13"/>
+      <c r="D129" s="14"/>
+      <c r="E129" s="14"/>
       <c r="F129" s="6"/>
-      <c r="G129" s="13">
+      <c r="G129" s="14">
         <f t="shared" si="27"/>
         <v>-0.25616496666666672</v>
       </c>
-      <c r="H129" s="13"/>
-      <c r="I129" s="13"/>
+      <c r="H129" s="14"/>
+      <c r="I129" s="14"/>
       <c r="J129" s="6"/>
-      <c r="K129" s="14">
+      <c r="K129" s="13">
         <f t="shared" si="28"/>
         <v>-0.35959415143955481</v>
       </c>
-      <c r="L129" s="14"/>
-      <c r="M129" s="14"/>
+      <c r="L129" s="13"/>
+      <c r="M129" s="13"/>
       <c r="N129" s="6"/>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.2">
@@ -4654,24 +4654,24 @@
       <c r="A131" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B131" s="13" t="s">
+      <c r="B131" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C131" s="13"/>
-      <c r="D131" s="13"/>
-      <c r="E131" s="13"/>
+      <c r="C131" s="14"/>
+      <c r="D131" s="14"/>
+      <c r="E131" s="14"/>
       <c r="F131" s="6"/>
-      <c r="G131" s="13" t="s">
+      <c r="G131" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H131" s="13"/>
-      <c r="I131" s="13"/>
+      <c r="H131" s="14"/>
+      <c r="I131" s="14"/>
       <c r="J131" s="6"/>
-      <c r="K131" s="13" t="s">
+      <c r="K131" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="L131" s="13"/>
-      <c r="M131" s="13"/>
+      <c r="L131" s="14"/>
+      <c r="M131" s="14"/>
       <c r="N131" s="6"/>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.2">
@@ -4681,26 +4681,26 @@
       <c r="B132" s="1">
         <v>15.246810999999999</v>
       </c>
-      <c r="C132" s="13">
+      <c r="C132" s="14">
         <f t="shared" ref="C132:C143" si="29">AVERAGE(C76,C48,C104)</f>
         <v>1.1660286666666666</v>
       </c>
-      <c r="D132" s="13"/>
-      <c r="E132" s="13"/>
+      <c r="D132" s="14"/>
+      <c r="E132" s="14"/>
       <c r="F132" s="6"/>
-      <c r="G132" s="13">
+      <c r="G132" s="14">
         <f t="shared" ref="G132:G143" si="30">C132-B132</f>
         <v>-14.080782333333332</v>
       </c>
-      <c r="H132" s="13"/>
-      <c r="I132" s="13"/>
+      <c r="H132" s="14"/>
+      <c r="I132" s="14"/>
       <c r="J132" s="6"/>
-      <c r="K132" s="14">
+      <c r="K132" s="13">
         <f>G132/B132</f>
         <v>-0.92352311137937848</v>
       </c>
-      <c r="L132" s="14"/>
-      <c r="M132" s="14"/>
+      <c r="L132" s="13"/>
+      <c r="M132" s="13"/>
       <c r="N132" s="6"/>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.2">
@@ -4710,26 +4710,26 @@
       <c r="B133" s="1">
         <v>2.0593110000000001</v>
       </c>
-      <c r="C133" s="13">
+      <c r="C133" s="14">
         <f t="shared" si="29"/>
         <v>0.59566333333333332</v>
       </c>
-      <c r="D133" s="13"/>
-      <c r="E133" s="13"/>
+      <c r="D133" s="14"/>
+      <c r="E133" s="14"/>
       <c r="F133" s="6"/>
-      <c r="G133" s="13">
+      <c r="G133" s="14">
         <f t="shared" si="30"/>
         <v>-1.4636476666666667</v>
       </c>
-      <c r="H133" s="13"/>
-      <c r="I133" s="13"/>
+      <c r="H133" s="14"/>
+      <c r="I133" s="14"/>
       <c r="J133" s="6"/>
-      <c r="K133" s="14">
+      <c r="K133" s="13">
         <f t="shared" ref="K133:K143" si="31">G133/B133</f>
         <v>-0.71074629653639809</v>
       </c>
-      <c r="L133" s="14"/>
-      <c r="M133" s="14"/>
+      <c r="L133" s="13"/>
+      <c r="M133" s="13"/>
       <c r="N133" s="6"/>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.2">
@@ -4739,26 +4739,26 @@
       <c r="B134" s="1">
         <v>2</v>
       </c>
-      <c r="C134" s="13">
+      <c r="C134" s="14">
         <f t="shared" si="29"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="D134" s="13"/>
-      <c r="E134" s="13"/>
+      <c r="D134" s="14"/>
+      <c r="E134" s="14"/>
       <c r="F134" s="6"/>
-      <c r="G134" s="13">
+      <c r="G134" s="14">
         <f t="shared" si="30"/>
         <v>-1.3333333333333335</v>
       </c>
-      <c r="H134" s="13"/>
-      <c r="I134" s="13"/>
+      <c r="H134" s="14"/>
+      <c r="I134" s="14"/>
       <c r="J134" s="6"/>
-      <c r="K134" s="14">
+      <c r="K134" s="13">
         <f t="shared" si="31"/>
         <v>-0.66666666666666674</v>
       </c>
-      <c r="L134" s="14"/>
-      <c r="M134" s="14"/>
+      <c r="L134" s="13"/>
+      <c r="M134" s="13"/>
       <c r="N134" s="6"/>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.2">
@@ -4768,26 +4768,26 @@
       <c r="B135" s="1">
         <v>-2</v>
       </c>
-      <c r="C135" s="13">
+      <c r="C135" s="14">
         <f t="shared" si="29"/>
         <v>-0.66666666666666663</v>
       </c>
-      <c r="D135" s="13"/>
-      <c r="E135" s="13"/>
+      <c r="D135" s="14"/>
+      <c r="E135" s="14"/>
       <c r="F135" s="6"/>
-      <c r="G135" s="13">
+      <c r="G135" s="14">
         <f t="shared" si="30"/>
         <v>1.3333333333333335</v>
       </c>
-      <c r="H135" s="13"/>
-      <c r="I135" s="13"/>
+      <c r="H135" s="14"/>
+      <c r="I135" s="14"/>
       <c r="J135" s="6"/>
-      <c r="K135" s="14">
+      <c r="K135" s="13">
         <f t="shared" si="31"/>
         <v>-0.66666666666666674</v>
       </c>
-      <c r="L135" s="14"/>
-      <c r="M135" s="14"/>
+      <c r="L135" s="13"/>
+      <c r="M135" s="13"/>
       <c r="N135" s="6"/>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.2">
@@ -4797,26 +4797,26 @@
       <c r="B136" s="1">
         <v>-3</v>
       </c>
-      <c r="C136" s="13">
+      <c r="C136" s="14">
         <f t="shared" si="29"/>
         <v>-1.6666666666666667</v>
       </c>
-      <c r="D136" s="13"/>
-      <c r="E136" s="13"/>
+      <c r="D136" s="14"/>
+      <c r="E136" s="14"/>
       <c r="F136" s="6"/>
-      <c r="G136" s="13">
+      <c r="G136" s="14">
         <f t="shared" si="30"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="H136" s="13"/>
-      <c r="I136" s="13"/>
+      <c r="H136" s="14"/>
+      <c r="I136" s="14"/>
       <c r="J136" s="6"/>
-      <c r="K136" s="14">
+      <c r="K136" s="13">
         <f t="shared" si="31"/>
         <v>-0.44444444444444442</v>
       </c>
-      <c r="L136" s="14"/>
-      <c r="M136" s="14"/>
+      <c r="L136" s="13"/>
+      <c r="M136" s="13"/>
       <c r="N136" s="6"/>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.2">
@@ -4826,26 +4826,26 @@
       <c r="B137" s="1">
         <v>90</v>
       </c>
-      <c r="C137" s="13">
+      <c r="C137" s="14">
         <f t="shared" si="29"/>
         <v>7.333333333333333</v>
       </c>
-      <c r="D137" s="13"/>
-      <c r="E137" s="13"/>
+      <c r="D137" s="14"/>
+      <c r="E137" s="14"/>
       <c r="F137" s="6"/>
-      <c r="G137" s="13">
+      <c r="G137" s="14">
         <f t="shared" si="30"/>
         <v>-82.666666666666671</v>
       </c>
-      <c r="H137" s="13"/>
-      <c r="I137" s="13"/>
+      <c r="H137" s="14"/>
+      <c r="I137" s="14"/>
       <c r="J137" s="6"/>
-      <c r="K137" s="14">
+      <c r="K137" s="13">
         <f t="shared" si="31"/>
         <v>-0.91851851851851862</v>
       </c>
-      <c r="L137" s="14"/>
-      <c r="M137" s="14"/>
+      <c r="L137" s="13"/>
+      <c r="M137" s="13"/>
       <c r="N137" s="6"/>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.2">
@@ -4855,26 +4855,26 @@
       <c r="B138" s="1">
         <v>6.7799740000000002</v>
       </c>
-      <c r="C138" s="13">
+      <c r="C138" s="14">
         <f t="shared" si="29"/>
         <v>7.3580016666666666</v>
       </c>
-      <c r="D138" s="13"/>
-      <c r="E138" s="13"/>
+      <c r="D138" s="14"/>
+      <c r="E138" s="14"/>
       <c r="F138" s="6"/>
-      <c r="G138" s="13">
+      <c r="G138" s="14">
         <f t="shared" si="30"/>
         <v>0.57802766666666638</v>
       </c>
-      <c r="H138" s="13"/>
-      <c r="I138" s="13"/>
+      <c r="H138" s="14"/>
+      <c r="I138" s="14"/>
       <c r="J138" s="6"/>
-      <c r="K138" s="14">
+      <c r="K138" s="13">
         <f t="shared" si="31"/>
         <v>8.5255145029562995E-2</v>
       </c>
-      <c r="L138" s="14"/>
-      <c r="M138" s="14"/>
+      <c r="L138" s="13"/>
+      <c r="M138" s="13"/>
       <c r="N138" s="6"/>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.2">
@@ -4884,26 +4884,26 @@
       <c r="B139" s="1">
         <v>7</v>
       </c>
-      <c r="C139" s="13">
+      <c r="C139" s="14">
         <f t="shared" si="29"/>
         <v>7.666666666666667</v>
       </c>
-      <c r="D139" s="13"/>
-      <c r="E139" s="13"/>
+      <c r="D139" s="14"/>
+      <c r="E139" s="14"/>
       <c r="F139" s="6"/>
-      <c r="G139" s="13">
+      <c r="G139" s="14">
         <f t="shared" si="30"/>
         <v>0.66666666666666696</v>
       </c>
-      <c r="H139" s="13"/>
-      <c r="I139" s="13"/>
+      <c r="H139" s="14"/>
+      <c r="I139" s="14"/>
       <c r="J139" s="6"/>
-      <c r="K139" s="14">
+      <c r="K139" s="13">
         <f t="shared" si="31"/>
         <v>9.5238095238095274E-2</v>
       </c>
-      <c r="L139" s="14"/>
-      <c r="M139" s="14"/>
+      <c r="L139" s="13"/>
+      <c r="M139" s="13"/>
       <c r="N139" s="6"/>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.2">
@@ -4913,26 +4913,26 @@
       <c r="B140" s="1">
         <v>8</v>
       </c>
-      <c r="C140" s="13">
+      <c r="C140" s="14">
         <f t="shared" si="29"/>
         <v>8</v>
       </c>
-      <c r="D140" s="13"/>
-      <c r="E140" s="13"/>
+      <c r="D140" s="14"/>
+      <c r="E140" s="14"/>
       <c r="F140" s="6"/>
-      <c r="G140" s="13">
+      <c r="G140" s="14">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="H140" s="13"/>
-      <c r="I140" s="13"/>
+      <c r="H140" s="14"/>
+      <c r="I140" s="14"/>
       <c r="J140" s="6"/>
-      <c r="K140" s="14">
+      <c r="K140" s="13">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L140" s="14"/>
-      <c r="M140" s="14"/>
+      <c r="L140" s="13"/>
+      <c r="M140" s="13"/>
       <c r="N140" s="6"/>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.2">
@@ -4942,26 +4942,26 @@
       <c r="B141" s="1">
         <v>3</v>
       </c>
-      <c r="C141" s="13">
+      <c r="C141" s="14">
         <f t="shared" si="29"/>
         <v>6</v>
       </c>
-      <c r="D141" s="13"/>
-      <c r="E141" s="13"/>
+      <c r="D141" s="14"/>
+      <c r="E141" s="14"/>
       <c r="F141" s="6"/>
-      <c r="G141" s="13">
+      <c r="G141" s="14">
         <f t="shared" si="30"/>
         <v>3</v>
       </c>
-      <c r="H141" s="13"/>
-      <c r="I141" s="13"/>
+      <c r="H141" s="14"/>
+      <c r="I141" s="14"/>
       <c r="J141" s="6"/>
-      <c r="K141" s="14">
+      <c r="K141" s="13">
         <f t="shared" si="31"/>
         <v>1</v>
       </c>
-      <c r="L141" s="14"/>
-      <c r="M141" s="14"/>
+      <c r="L141" s="13"/>
+      <c r="M141" s="13"/>
       <c r="N141" s="6"/>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.2">
@@ -4971,26 +4971,26 @@
       <c r="B142" s="1">
         <v>72</v>
       </c>
-      <c r="C142" s="13">
+      <c r="C142" s="14">
         <f t="shared" si="29"/>
         <v>2107.6666666666665</v>
       </c>
-      <c r="D142" s="13"/>
-      <c r="E142" s="13"/>
+      <c r="D142" s="14"/>
+      <c r="E142" s="14"/>
       <c r="F142" s="6"/>
-      <c r="G142" s="13">
+      <c r="G142" s="14">
         <f t="shared" si="30"/>
         <v>2035.6666666666665</v>
       </c>
-      <c r="H142" s="13"/>
-      <c r="I142" s="13"/>
+      <c r="H142" s="14"/>
+      <c r="I142" s="14"/>
       <c r="J142" s="6"/>
-      <c r="K142" s="14">
+      <c r="K142" s="13">
         <f t="shared" si="31"/>
         <v>28.273148148148145</v>
       </c>
-      <c r="L142" s="14"/>
-      <c r="M142" s="14"/>
+      <c r="L142" s="13"/>
+      <c r="M142" s="13"/>
       <c r="N142" s="6"/>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.2">
@@ -5000,26 +5000,26 @@
       <c r="B143" s="5">
         <v>2.2959179999999999E-2</v>
       </c>
-      <c r="C143" s="17">
+      <c r="C143" s="16">
         <f t="shared" si="29"/>
         <v>0.6720875833333334</v>
       </c>
-      <c r="D143" s="13"/>
-      <c r="E143" s="13"/>
+      <c r="D143" s="14"/>
+      <c r="E143" s="14"/>
       <c r="F143" s="6"/>
-      <c r="G143" s="13">
+      <c r="G143" s="14">
         <f t="shared" si="30"/>
         <v>0.64912840333333344</v>
       </c>
-      <c r="H143" s="13"/>
-      <c r="I143" s="13"/>
+      <c r="H143" s="14"/>
+      <c r="I143" s="14"/>
       <c r="J143" s="6"/>
-      <c r="K143" s="14">
+      <c r="K143" s="13">
         <f t="shared" si="31"/>
         <v>28.273152757778522</v>
       </c>
-      <c r="L143" s="14"/>
-      <c r="M143" s="14"/>
+      <c r="L143" s="13"/>
+      <c r="M143" s="13"/>
       <c r="N143" s="6"/>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.2">
@@ -5042,180 +5042,180 @@
       <c r="A145" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B145" s="13" t="s">
+      <c r="B145" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C145" s="13"/>
-      <c r="D145" s="13"/>
-      <c r="E145" s="13"/>
+      <c r="C145" s="14"/>
+      <c r="D145" s="14"/>
+      <c r="E145" s="14"/>
       <c r="F145" s="6"/>
-      <c r="G145" s="13">
-        <v>0</v>
-      </c>
-      <c r="H145" s="13"/>
-      <c r="I145" s="13"/>
+      <c r="G145" s="14">
+        <v>0</v>
+      </c>
+      <c r="H145" s="14"/>
+      <c r="I145" s="14"/>
       <c r="J145" s="6"/>
-      <c r="K145" s="18">
-        <v>0</v>
-      </c>
-      <c r="L145" s="18"/>
-      <c r="M145" s="18"/>
+      <c r="K145" s="15">
+        <v>0</v>
+      </c>
+      <c r="L145" s="15"/>
+      <c r="M145" s="15"/>
       <c r="N145" s="6"/>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B146" s="13">
+      <c r="B146" s="14">
         <v>1</v>
       </c>
-      <c r="C146" s="13"/>
-      <c r="D146" s="13"/>
-      <c r="E146" s="13"/>
+      <c r="C146" s="14"/>
+      <c r="D146" s="14"/>
+      <c r="E146" s="14"/>
       <c r="F146" s="6"/>
-      <c r="G146" s="13">
-        <v>0</v>
-      </c>
-      <c r="H146" s="13"/>
-      <c r="I146" s="13"/>
+      <c r="G146" s="14">
+        <v>0</v>
+      </c>
+      <c r="H146" s="14"/>
+      <c r="I146" s="14"/>
       <c r="J146" s="6"/>
-      <c r="K146" s="14">
+      <c r="K146" s="13">
         <f>G146/B146</f>
         <v>0</v>
       </c>
-      <c r="L146" s="14"/>
-      <c r="M146" s="14"/>
+      <c r="L146" s="13"/>
+      <c r="M146" s="13"/>
       <c r="N146" s="6"/>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B147" s="13">
+      <c r="B147" s="14">
         <v>69633</v>
       </c>
-      <c r="C147" s="13"/>
-      <c r="D147" s="13"/>
-      <c r="E147" s="13"/>
+      <c r="C147" s="14"/>
+      <c r="D147" s="14"/>
+      <c r="E147" s="14"/>
       <c r="F147" s="6"/>
-      <c r="G147" s="13">
-        <v>0</v>
-      </c>
-      <c r="H147" s="13"/>
-      <c r="I147" s="13"/>
+      <c r="G147" s="14">
+        <v>0</v>
+      </c>
+      <c r="H147" s="14"/>
+      <c r="I147" s="14"/>
       <c r="J147" s="6"/>
-      <c r="K147" s="14">
+      <c r="K147" s="13">
         <f>G147/B147</f>
         <v>0</v>
       </c>
-      <c r="L147" s="14"/>
-      <c r="M147" s="14"/>
+      <c r="L147" s="13"/>
+      <c r="M147" s="13"/>
       <c r="N147" s="6"/>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B148" s="13">
+      <c r="B148" s="14">
         <v>70350</v>
       </c>
-      <c r="C148" s="13"/>
-      <c r="D148" s="13"/>
-      <c r="E148" s="13"/>
+      <c r="C148" s="14"/>
+      <c r="D148" s="14"/>
+      <c r="E148" s="14"/>
       <c r="F148" s="6"/>
-      <c r="G148" s="13">
-        <v>0</v>
-      </c>
-      <c r="H148" s="13"/>
-      <c r="I148" s="13"/>
+      <c r="G148" s="14">
+        <v>0</v>
+      </c>
+      <c r="H148" s="14"/>
+      <c r="I148" s="14"/>
       <c r="J148" s="6"/>
-      <c r="K148" s="14">
+      <c r="K148" s="13">
         <f>G148/B148</f>
         <v>0</v>
       </c>
-      <c r="L148" s="14"/>
-      <c r="M148" s="14"/>
+      <c r="L148" s="13"/>
+      <c r="M148" s="13"/>
       <c r="N148" s="6"/>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B149" s="13">
+      <c r="B149" s="14">
         <v>74925</v>
       </c>
-      <c r="C149" s="13"/>
-      <c r="D149" s="13"/>
-      <c r="E149" s="13"/>
+      <c r="C149" s="14"/>
+      <c r="D149" s="14"/>
+      <c r="E149" s="14"/>
       <c r="F149" s="6"/>
-      <c r="G149" s="13">
-        <v>0</v>
-      </c>
-      <c r="H149" s="13"/>
-      <c r="I149" s="13"/>
+      <c r="G149" s="14">
+        <v>0</v>
+      </c>
+      <c r="H149" s="14"/>
+      <c r="I149" s="14"/>
       <c r="J149" s="6"/>
-      <c r="K149" s="14">
+      <c r="K149" s="13">
         <f>G149/B149</f>
         <v>0</v>
       </c>
-      <c r="L149" s="14"/>
-      <c r="M149" s="14"/>
+      <c r="L149" s="13"/>
+      <c r="M149" s="13"/>
       <c r="N149" s="6"/>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B150" s="13">
+      <c r="B150" s="14">
         <f>B149-B146</f>
         <v>74924</v>
       </c>
-      <c r="C150" s="13"/>
-      <c r="D150" s="13"/>
-      <c r="E150" s="13"/>
+      <c r="C150" s="14"/>
+      <c r="D150" s="14"/>
+      <c r="E150" s="14"/>
       <c r="F150" s="6"/>
-      <c r="G150" s="13">
-        <v>0</v>
-      </c>
-      <c r="H150" s="13"/>
-      <c r="I150" s="13"/>
+      <c r="G150" s="14">
+        <v>0</v>
+      </c>
+      <c r="H150" s="14"/>
+      <c r="I150" s="14"/>
       <c r="J150" s="6"/>
-      <c r="K150" s="14">
+      <c r="K150" s="13">
         <f>G150/B150</f>
         <v>0</v>
       </c>
-      <c r="L150" s="14"/>
-      <c r="M150" s="14"/>
+      <c r="L150" s="13"/>
+      <c r="M150" s="13"/>
       <c r="N150" s="6"/>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B151" s="13">
+      <c r="B151" s="14">
         <f>B150/(B3*10^3)</f>
         <v>0.93654999999999999</v>
       </c>
-      <c r="C151" s="13"/>
-      <c r="D151" s="13"/>
+      <c r="C151" s="14"/>
+      <c r="D151" s="14"/>
       <c r="E151" s="1">
         <f>B150/(E3*10^3)</f>
         <v>0.37462000000000001</v>
       </c>
       <c r="F151" s="6"/>
-      <c r="G151" s="13">
-        <v>0</v>
-      </c>
-      <c r="H151" s="13"/>
+      <c r="G151" s="14">
+        <v>0</v>
+      </c>
+      <c r="H151" s="14"/>
       <c r="I151" s="1">
         <f>E151-B151</f>
         <v>-0.56193000000000004</v>
       </c>
       <c r="J151" s="6"/>
-      <c r="K151" s="14">
-        <v>0</v>
-      </c>
-      <c r="L151" s="14"/>
+      <c r="K151" s="13">
+        <v>0</v>
+      </c>
+      <c r="L151" s="13"/>
       <c r="M151" s="5">
         <f>I151/B151</f>
         <v>-0.60000000000000009</v>
@@ -5226,56 +5226,56 @@
       <c r="A152" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B152" s="13">
+      <c r="B152" s="14">
         <f>B149-B147</f>
         <v>5292</v>
       </c>
-      <c r="C152" s="13"/>
-      <c r="D152" s="13"/>
-      <c r="E152" s="13"/>
+      <c r="C152" s="14"/>
+      <c r="D152" s="14"/>
+      <c r="E152" s="14"/>
       <c r="F152" s="6"/>
-      <c r="G152" s="13">
-        <v>0</v>
-      </c>
-      <c r="H152" s="13"/>
-      <c r="I152" s="13"/>
+      <c r="G152" s="14">
+        <v>0</v>
+      </c>
+      <c r="H152" s="14"/>
+      <c r="I152" s="14"/>
       <c r="J152" s="6"/>
-      <c r="K152" s="14">
+      <c r="K152" s="13">
         <f>G152/B152</f>
         <v>0</v>
       </c>
-      <c r="L152" s="14"/>
-      <c r="M152" s="14"/>
+      <c r="L152" s="13"/>
+      <c r="M152" s="13"/>
       <c r="N152" s="6"/>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B153" s="13">
+      <c r="B153" s="14">
         <f>B152/B3</f>
         <v>66.150000000000006</v>
       </c>
-      <c r="C153" s="13"/>
-      <c r="D153" s="13"/>
+      <c r="C153" s="14"/>
+      <c r="D153" s="14"/>
       <c r="E153" s="1">
         <f>B152/E3</f>
         <v>26.46</v>
       </c>
       <c r="F153" s="6"/>
-      <c r="G153" s="13">
-        <v>0</v>
-      </c>
-      <c r="H153" s="13"/>
+      <c r="G153" s="14">
+        <v>0</v>
+      </c>
+      <c r="H153" s="14"/>
       <c r="I153" s="1">
         <f>E153-B153</f>
         <v>-39.690000000000005</v>
       </c>
       <c r="J153" s="6"/>
-      <c r="K153" s="14">
-        <v>0</v>
-      </c>
-      <c r="L153" s="14"/>
+      <c r="K153" s="13">
+        <v>0</v>
+      </c>
+      <c r="L153" s="13"/>
       <c r="M153" s="5">
         <f>I153/B153</f>
         <v>-0.6</v>
@@ -5331,30 +5331,30 @@
       <c r="A155" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B155" s="13">
+      <c r="B155" s="14">
         <f>1/(B151/1000)</f>
         <v>1067.7486519673269</v>
       </c>
-      <c r="C155" s="13"/>
-      <c r="D155" s="13"/>
+      <c r="C155" s="14"/>
+      <c r="D155" s="14"/>
       <c r="E155" s="1">
         <f>1/(E151/1000)</f>
         <v>2669.3716299183175</v>
       </c>
       <c r="F155" s="6"/>
-      <c r="G155" s="13">
-        <v>0</v>
-      </c>
-      <c r="H155" s="13"/>
+      <c r="G155" s="14">
+        <v>0</v>
+      </c>
+      <c r="H155" s="14"/>
       <c r="I155" s="1">
         <f>E155-B155</f>
         <v>1601.6229779509906</v>
       </c>
       <c r="J155" s="6"/>
-      <c r="K155" s="14">
-        <v>0</v>
-      </c>
-      <c r="L155" s="14"/>
+      <c r="K155" s="13">
+        <v>0</v>
+      </c>
+      <c r="L155" s="13"/>
       <c r="M155" s="5">
         <f>I155/B155</f>
         <v>1.5000000000000002</v>
@@ -5379,29 +5379,312 @@
     </row>
   </sheetData>
   <mergeCells count="353">
-    <mergeCell ref="K155:L155"/>
-    <mergeCell ref="G141:I141"/>
-    <mergeCell ref="G142:I142"/>
-    <mergeCell ref="G143:I143"/>
-    <mergeCell ref="G145:I145"/>
-    <mergeCell ref="K146:M146"/>
-    <mergeCell ref="K147:M147"/>
-    <mergeCell ref="K148:M148"/>
-    <mergeCell ref="K149:M149"/>
-    <mergeCell ref="K150:M150"/>
-    <mergeCell ref="K145:M145"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="G153:H153"/>
-    <mergeCell ref="G151:H151"/>
-    <mergeCell ref="K141:M141"/>
-    <mergeCell ref="K142:M142"/>
-    <mergeCell ref="K143:M143"/>
-    <mergeCell ref="G146:I146"/>
-    <mergeCell ref="G147:I147"/>
-    <mergeCell ref="G148:I148"/>
-    <mergeCell ref="K152:M152"/>
-    <mergeCell ref="K151:L151"/>
-    <mergeCell ref="K153:L153"/>
+    <mergeCell ref="K118:M118"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="G61:I61"/>
+    <mergeCell ref="K61:M61"/>
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="G75:I75"/>
+    <mergeCell ref="K75:M75"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="K33:M33"/>
+    <mergeCell ref="C113:E113"/>
+    <mergeCell ref="G113:I113"/>
+    <mergeCell ref="K113:M113"/>
+    <mergeCell ref="C114:E114"/>
+    <mergeCell ref="G114:I114"/>
+    <mergeCell ref="K114:M114"/>
+    <mergeCell ref="C115:E115"/>
+    <mergeCell ref="G115:I115"/>
+    <mergeCell ref="K115:M115"/>
+    <mergeCell ref="G109:I109"/>
+    <mergeCell ref="K109:M109"/>
+    <mergeCell ref="C110:E110"/>
+    <mergeCell ref="G110:I110"/>
+    <mergeCell ref="K110:M110"/>
+    <mergeCell ref="C111:E111"/>
+    <mergeCell ref="G111:I111"/>
+    <mergeCell ref="K111:M111"/>
+    <mergeCell ref="C112:E112"/>
+    <mergeCell ref="G112:I112"/>
+    <mergeCell ref="K112:M112"/>
+    <mergeCell ref="G105:I105"/>
+    <mergeCell ref="K105:M105"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="G106:I106"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="C107:E107"/>
+    <mergeCell ref="G107:I107"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="C108:E108"/>
+    <mergeCell ref="G108:I108"/>
+    <mergeCell ref="K108:M108"/>
+    <mergeCell ref="C105:E105"/>
+    <mergeCell ref="C109:E109"/>
+    <mergeCell ref="G99:I99"/>
+    <mergeCell ref="K99:M99"/>
+    <mergeCell ref="C100:E100"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="K100:M100"/>
+    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="G101:I101"/>
+    <mergeCell ref="K101:M101"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="G104:I104"/>
+    <mergeCell ref="K104:M104"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="G103:I103"/>
+    <mergeCell ref="K103:M103"/>
+    <mergeCell ref="G95:I95"/>
+    <mergeCell ref="K95:M95"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="G96:I96"/>
+    <mergeCell ref="K96:M96"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="G97:I97"/>
+    <mergeCell ref="K97:M97"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="G98:I98"/>
+    <mergeCell ref="K98:M98"/>
+    <mergeCell ref="G91:I91"/>
+    <mergeCell ref="K91:M91"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="G92:I92"/>
+    <mergeCell ref="K92:M92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="G93:I93"/>
+    <mergeCell ref="K93:M93"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="G94:I94"/>
+    <mergeCell ref="K94:M94"/>
+    <mergeCell ref="G57:I57"/>
+    <mergeCell ref="K57:M57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="G58:I58"/>
+    <mergeCell ref="K58:M58"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="G59:I59"/>
+    <mergeCell ref="K59:M59"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="G90:I90"/>
+    <mergeCell ref="K90:M90"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="G89:I89"/>
+    <mergeCell ref="K89:M89"/>
+    <mergeCell ref="G85:I85"/>
+    <mergeCell ref="K85:M85"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="G86:I86"/>
+    <mergeCell ref="K86:M86"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="K87:M87"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="G83:I83"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="K53:M53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="K54:M54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="G55:I55"/>
+    <mergeCell ref="K55:M55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="K56:M56"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="K49:M49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="K50:M50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="K51:M51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="K45:M45"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="K47:M47"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="K42:M42"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="K43:M43"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="G71:I71"/>
+    <mergeCell ref="K71:M71"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="G72:I72"/>
+    <mergeCell ref="K72:M72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="G73:I73"/>
+    <mergeCell ref="K73:M73"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="G76:I76"/>
+    <mergeCell ref="K76:M76"/>
+    <mergeCell ref="K83:M83"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="G84:I84"/>
+    <mergeCell ref="K84:M84"/>
+    <mergeCell ref="G77:I77"/>
+    <mergeCell ref="K77:M77"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="G78:I78"/>
+    <mergeCell ref="K78:M78"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="G79:I79"/>
+    <mergeCell ref="K79:M79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="G80:I80"/>
+    <mergeCell ref="K80:M80"/>
+    <mergeCell ref="G81:I81"/>
+    <mergeCell ref="K81:M81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="G82:I82"/>
+    <mergeCell ref="K82:M82"/>
+    <mergeCell ref="K68:M68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="G69:I69"/>
+    <mergeCell ref="K69:M69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="G70:I70"/>
+    <mergeCell ref="K70:M70"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="K67:M67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="G68:I68"/>
+    <mergeCell ref="K117:M117"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="G62:I62"/>
+    <mergeCell ref="K62:M62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="G63:I63"/>
+    <mergeCell ref="K63:M63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="G64:I64"/>
+    <mergeCell ref="K64:M64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="K65:M65"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="G66:I66"/>
+    <mergeCell ref="K66:M66"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="G67:I67"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="K123:M123"/>
+    <mergeCell ref="K124:M124"/>
+    <mergeCell ref="K125:M125"/>
+    <mergeCell ref="G140:I140"/>
+    <mergeCell ref="K126:M126"/>
+    <mergeCell ref="K127:M127"/>
+    <mergeCell ref="K128:M128"/>
+    <mergeCell ref="K129:M129"/>
+    <mergeCell ref="K119:M119"/>
+    <mergeCell ref="K120:M120"/>
+    <mergeCell ref="K121:M121"/>
+    <mergeCell ref="K122:M122"/>
+    <mergeCell ref="K132:M132"/>
+    <mergeCell ref="K133:M133"/>
+    <mergeCell ref="K134:M134"/>
+    <mergeCell ref="K135:M135"/>
+    <mergeCell ref="K136:M136"/>
+    <mergeCell ref="K137:M137"/>
+    <mergeCell ref="K138:M138"/>
+    <mergeCell ref="K139:M139"/>
+    <mergeCell ref="K140:M140"/>
+    <mergeCell ref="G131:I131"/>
+    <mergeCell ref="K131:M131"/>
+    <mergeCell ref="B151:D151"/>
+    <mergeCell ref="G132:I132"/>
+    <mergeCell ref="G133:I133"/>
+    <mergeCell ref="G134:I134"/>
+    <mergeCell ref="C136:E136"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="C138:E138"/>
+    <mergeCell ref="C139:E139"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="G149:I149"/>
+    <mergeCell ref="G150:I150"/>
+    <mergeCell ref="B150:E150"/>
+    <mergeCell ref="C122:E122"/>
+    <mergeCell ref="C123:E123"/>
+    <mergeCell ref="C132:E132"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="C118:E118"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="G135:I135"/>
+    <mergeCell ref="G136:I136"/>
+    <mergeCell ref="G137:I137"/>
+    <mergeCell ref="G138:I138"/>
+    <mergeCell ref="G139:I139"/>
+    <mergeCell ref="C119:E119"/>
+    <mergeCell ref="C120:E120"/>
+    <mergeCell ref="C121:E121"/>
+    <mergeCell ref="C133:E133"/>
+    <mergeCell ref="C134:E134"/>
+    <mergeCell ref="C135:E135"/>
+    <mergeCell ref="C129:E129"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="G118:I118"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C44:E44"/>
     <mergeCell ref="B153:D153"/>
     <mergeCell ref="B155:D155"/>
     <mergeCell ref="G117:I117"/>
@@ -5426,312 +5709,29 @@
     <mergeCell ref="C141:E141"/>
     <mergeCell ref="C142:E142"/>
     <mergeCell ref="C143:E143"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C85:E85"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C122:E122"/>
-    <mergeCell ref="C123:E123"/>
-    <mergeCell ref="C132:E132"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="C118:E118"/>
-    <mergeCell ref="B145:E145"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="G135:I135"/>
-    <mergeCell ref="G136:I136"/>
-    <mergeCell ref="G137:I137"/>
-    <mergeCell ref="G138:I138"/>
-    <mergeCell ref="G139:I139"/>
-    <mergeCell ref="C119:E119"/>
-    <mergeCell ref="C120:E120"/>
-    <mergeCell ref="C121:E121"/>
-    <mergeCell ref="C133:E133"/>
-    <mergeCell ref="C134:E134"/>
-    <mergeCell ref="C135:E135"/>
-    <mergeCell ref="C129:E129"/>
-    <mergeCell ref="B151:D151"/>
-    <mergeCell ref="G132:I132"/>
-    <mergeCell ref="G133:I133"/>
-    <mergeCell ref="G134:I134"/>
-    <mergeCell ref="C136:E136"/>
-    <mergeCell ref="C137:E137"/>
-    <mergeCell ref="C138:E138"/>
-    <mergeCell ref="C139:E139"/>
-    <mergeCell ref="C140:E140"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="G149:I149"/>
-    <mergeCell ref="G150:I150"/>
-    <mergeCell ref="B150:E150"/>
-    <mergeCell ref="B131:E131"/>
-    <mergeCell ref="K123:M123"/>
-    <mergeCell ref="K124:M124"/>
-    <mergeCell ref="K125:M125"/>
-    <mergeCell ref="G140:I140"/>
-    <mergeCell ref="K126:M126"/>
-    <mergeCell ref="K127:M127"/>
-    <mergeCell ref="K128:M128"/>
-    <mergeCell ref="K129:M129"/>
-    <mergeCell ref="K119:M119"/>
-    <mergeCell ref="K120:M120"/>
-    <mergeCell ref="K121:M121"/>
-    <mergeCell ref="K122:M122"/>
-    <mergeCell ref="K132:M132"/>
-    <mergeCell ref="K133:M133"/>
-    <mergeCell ref="K134:M134"/>
-    <mergeCell ref="K135:M135"/>
-    <mergeCell ref="K136:M136"/>
-    <mergeCell ref="K137:M137"/>
-    <mergeCell ref="K138:M138"/>
-    <mergeCell ref="K139:M139"/>
-    <mergeCell ref="K140:M140"/>
-    <mergeCell ref="G131:I131"/>
-    <mergeCell ref="K131:M131"/>
-    <mergeCell ref="K117:M117"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="G62:I62"/>
-    <mergeCell ref="K62:M62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="G63:I63"/>
-    <mergeCell ref="K63:M63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="G64:I64"/>
-    <mergeCell ref="K64:M64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="G65:I65"/>
-    <mergeCell ref="K65:M65"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="G66:I66"/>
-    <mergeCell ref="K66:M66"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="G67:I67"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="K68:M68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="G69:I69"/>
-    <mergeCell ref="K69:M69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="G70:I70"/>
-    <mergeCell ref="K70:M70"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="K83:M83"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="G84:I84"/>
-    <mergeCell ref="K84:M84"/>
-    <mergeCell ref="G77:I77"/>
-    <mergeCell ref="K77:M77"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="G78:I78"/>
-    <mergeCell ref="K78:M78"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="G79:I79"/>
-    <mergeCell ref="K79:M79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="G80:I80"/>
-    <mergeCell ref="K80:M80"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="G81:I81"/>
-    <mergeCell ref="K81:M81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="G82:I82"/>
-    <mergeCell ref="K82:M82"/>
-    <mergeCell ref="G71:I71"/>
-    <mergeCell ref="K71:M71"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="G72:I72"/>
-    <mergeCell ref="K72:M72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="G73:I73"/>
-    <mergeCell ref="K73:M73"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="G76:I76"/>
-    <mergeCell ref="K76:M76"/>
-    <mergeCell ref="K67:M67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="G68:I68"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="G41:I41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="G42:I42"/>
-    <mergeCell ref="K42:M42"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="K43:M43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="G44:I44"/>
-    <mergeCell ref="K44:M44"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="G45:I45"/>
-    <mergeCell ref="K45:M45"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="K48:M48"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="K47:M47"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="K49:M49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="K50:M50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="K51:M51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="G53:I53"/>
-    <mergeCell ref="K53:M53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="K54:M54"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="G55:I55"/>
-    <mergeCell ref="K55:M55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="G56:I56"/>
-    <mergeCell ref="K56:M56"/>
-    <mergeCell ref="G57:I57"/>
-    <mergeCell ref="K57:M57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="G58:I58"/>
-    <mergeCell ref="K58:M58"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="G59:I59"/>
-    <mergeCell ref="K59:M59"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="G90:I90"/>
-    <mergeCell ref="K90:M90"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="G89:I89"/>
-    <mergeCell ref="K89:M89"/>
-    <mergeCell ref="G85:I85"/>
-    <mergeCell ref="K85:M85"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="G86:I86"/>
-    <mergeCell ref="K86:M86"/>
-    <mergeCell ref="C87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="K87:M87"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="G83:I83"/>
-    <mergeCell ref="G91:I91"/>
-    <mergeCell ref="K91:M91"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="G92:I92"/>
-    <mergeCell ref="K92:M92"/>
-    <mergeCell ref="C93:E93"/>
-    <mergeCell ref="G93:I93"/>
-    <mergeCell ref="K93:M93"/>
-    <mergeCell ref="C94:E94"/>
-    <mergeCell ref="G94:I94"/>
-    <mergeCell ref="K94:M94"/>
-    <mergeCell ref="G95:I95"/>
-    <mergeCell ref="K95:M95"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="G96:I96"/>
-    <mergeCell ref="K96:M96"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="G97:I97"/>
-    <mergeCell ref="K97:M97"/>
-    <mergeCell ref="C98:E98"/>
-    <mergeCell ref="G98:I98"/>
-    <mergeCell ref="K98:M98"/>
-    <mergeCell ref="G99:I99"/>
-    <mergeCell ref="K99:M99"/>
-    <mergeCell ref="C100:E100"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="K100:M100"/>
-    <mergeCell ref="C101:E101"/>
-    <mergeCell ref="G101:I101"/>
-    <mergeCell ref="K101:M101"/>
-    <mergeCell ref="C104:E104"/>
-    <mergeCell ref="G104:I104"/>
-    <mergeCell ref="K104:M104"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="G103:I103"/>
-    <mergeCell ref="K103:M103"/>
-    <mergeCell ref="K110:M110"/>
-    <mergeCell ref="C111:E111"/>
-    <mergeCell ref="G111:I111"/>
-    <mergeCell ref="K111:M111"/>
-    <mergeCell ref="C112:E112"/>
-    <mergeCell ref="G112:I112"/>
-    <mergeCell ref="K112:M112"/>
-    <mergeCell ref="G105:I105"/>
-    <mergeCell ref="K105:M105"/>
-    <mergeCell ref="C106:E106"/>
-    <mergeCell ref="G106:I106"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="C107:E107"/>
-    <mergeCell ref="G107:I107"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="C108:E108"/>
-    <mergeCell ref="G108:I108"/>
-    <mergeCell ref="K108:M108"/>
-    <mergeCell ref="C105:E105"/>
-    <mergeCell ref="C109:E109"/>
-    <mergeCell ref="G118:I118"/>
-    <mergeCell ref="K118:M118"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="G61:I61"/>
-    <mergeCell ref="K61:M61"/>
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="G75:I75"/>
-    <mergeCell ref="K75:M75"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="K33:M33"/>
-    <mergeCell ref="C113:E113"/>
-    <mergeCell ref="G113:I113"/>
-    <mergeCell ref="K113:M113"/>
-    <mergeCell ref="C114:E114"/>
-    <mergeCell ref="G114:I114"/>
-    <mergeCell ref="K114:M114"/>
-    <mergeCell ref="C115:E115"/>
-    <mergeCell ref="G115:I115"/>
-    <mergeCell ref="K115:M115"/>
-    <mergeCell ref="G109:I109"/>
-    <mergeCell ref="K109:M109"/>
-    <mergeCell ref="C110:E110"/>
-    <mergeCell ref="G110:I110"/>
+    <mergeCell ref="K155:L155"/>
+    <mergeCell ref="G141:I141"/>
+    <mergeCell ref="G142:I142"/>
+    <mergeCell ref="G143:I143"/>
+    <mergeCell ref="G145:I145"/>
+    <mergeCell ref="K146:M146"/>
+    <mergeCell ref="K147:M147"/>
+    <mergeCell ref="K148:M148"/>
+    <mergeCell ref="K149:M149"/>
+    <mergeCell ref="K150:M150"/>
+    <mergeCell ref="K145:M145"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="G153:H153"/>
+    <mergeCell ref="G151:H151"/>
+    <mergeCell ref="K141:M141"/>
+    <mergeCell ref="K142:M142"/>
+    <mergeCell ref="K143:M143"/>
+    <mergeCell ref="G146:I146"/>
+    <mergeCell ref="G147:I147"/>
+    <mergeCell ref="G148:I148"/>
+    <mergeCell ref="K152:M152"/>
+    <mergeCell ref="K151:L151"/>
+    <mergeCell ref="K153:L153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/FPGA_Performance_Comparison_Red_Small.xlsx
+++ b/FPGA_Performance_Comparison_Red_Small.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/DanielBiswas/Desktop/Documents/University/Year 5/Semester 1/AMME4112/Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C25AD4C-C3B2-BA47-B74B-D9073EF6CA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753A97B5-DF2A-B94C-A28F-9BB7C82D6327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="24100" windowHeight="17760" xr2:uid="{49DEC02E-5D37-064F-A7E8-1E1DC7B5FEA1}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="19120" windowHeight="17760" xr2:uid="{49DEC02E-5D37-064F-A7E8-1E1DC7B5FEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -380,17 +380,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -737,15 +737,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="B1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
       <c r="F1" s="6"/>
       <c r="G1" s="14" t="s">
         <v>55</v>
@@ -761,7 +761,7 @@
       <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="17"/>
+      <c r="A2" s="16"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -886,10 +886,10 @@
       <c r="C5" s="1">
         <v>136.59</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <v>202.43</v>
       </c>
-      <c r="E5" s="17"/>
+      <c r="E5" s="16"/>
       <c r="F5" s="6"/>
       <c r="G5" s="1">
         <f>C5-B5</f>
@@ -944,10 +944,10 @@
       <c r="C7" s="1">
         <v>9776</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="16">
         <v>10129</v>
       </c>
-      <c r="E7" s="17"/>
+      <c r="E7" s="16"/>
       <c r="F7" s="6"/>
       <c r="G7" s="1">
         <f>C7-B7</f>
@@ -986,10 +986,10 @@
       <c r="C8" s="1">
         <v>24289</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="16">
         <v>27731</v>
       </c>
-      <c r="E8" s="17"/>
+      <c r="E8" s="16"/>
       <c r="F8" s="6"/>
       <c r="G8" s="1">
         <f>C8-B8</f>
@@ -1028,10 +1028,10 @@
       <c r="C9" s="1">
         <v>808736</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="16">
         <v>808736</v>
       </c>
-      <c r="E9" s="17"/>
+      <c r="E9" s="16"/>
       <c r="F9" s="6"/>
       <c r="G9" s="1">
         <f>C9-B9</f>
@@ -1070,10 +1070,10 @@
       <c r="C10" s="2">
         <v>12</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="16">
         <v>12</v>
       </c>
-      <c r="E10" s="17"/>
+      <c r="E10" s="16"/>
       <c r="F10" s="6"/>
       <c r="G10" s="1">
         <f>C10-B10</f>
@@ -2351,11 +2351,11 @@
       <c r="B45" s="5">
         <v>0.71237245000000005</v>
       </c>
-      <c r="C45" s="18">
+      <c r="C45" s="15">
         <v>0.46364796000000003</v>
       </c>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
       <c r="F45" s="6"/>
       <c r="G45" s="14">
         <f t="shared" si="11"/>
@@ -2417,7 +2417,7 @@
         <v>43</v>
       </c>
       <c r="B48" s="1">
-        <v>15.246810999999999</v>
+        <v>3.6269130000000001</v>
       </c>
       <c r="C48" s="14">
         <v>3.3973209999999998</v>
@@ -2427,14 +2427,14 @@
       <c r="F48" s="6"/>
       <c r="G48" s="14">
         <f t="shared" ref="G48:G59" si="14">C48-B48</f>
-        <v>-11.849489999999999</v>
+        <v>-0.22959200000000024</v>
       </c>
       <c r="H48" s="14"/>
       <c r="I48" s="14"/>
       <c r="J48" s="6"/>
       <c r="K48" s="13">
         <f>G48/B48</f>
-        <v>-0.77717825714505151</v>
+        <v>-6.3302317976747791E-2</v>
       </c>
       <c r="L48" s="13"/>
       <c r="M48" s="13"/>
@@ -2445,7 +2445,7 @@
         <v>44</v>
       </c>
       <c r="B49" s="1">
-        <v>2.0593110000000001</v>
+        <v>1.8316330000000001</v>
       </c>
       <c r="C49" s="14">
         <v>1.760842</v>
@@ -2455,14 +2455,14 @@
       <c r="F49" s="6"/>
       <c r="G49" s="14">
         <f t="shared" si="14"/>
-        <v>-0.2984690000000001</v>
+        <v>-7.0791000000000048E-2</v>
       </c>
       <c r="H49" s="14"/>
       <c r="I49" s="14"/>
       <c r="J49" s="6"/>
       <c r="K49" s="13">
         <f t="shared" ref="K49:K59" si="15">G49/B49</f>
-        <v>-0.14493634035849859</v>
+        <v>-3.8649118027465131E-2</v>
       </c>
       <c r="L49" s="13"/>
       <c r="M49" s="13"/>
@@ -2557,7 +2557,7 @@
         <v>48</v>
       </c>
       <c r="B53" s="1">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="C53" s="14">
         <v>3</v>
@@ -2567,14 +2567,14 @@
       <c r="F53" s="6"/>
       <c r="G53" s="14">
         <f t="shared" si="14"/>
-        <v>-87</v>
+        <v>-1</v>
       </c>
       <c r="H53" s="14"/>
       <c r="I53" s="14"/>
       <c r="J53" s="6"/>
       <c r="K53" s="13">
         <f t="shared" si="15"/>
-        <v>-0.96666666666666667</v>
+        <v>-0.25</v>
       </c>
       <c r="L53" s="13"/>
       <c r="M53" s="13"/>
@@ -2585,7 +2585,7 @@
         <v>49</v>
       </c>
       <c r="B54" s="1">
-        <v>6.7799740000000002</v>
+        <v>6.7987880000000001</v>
       </c>
       <c r="C54" s="14">
         <v>6.0893110000000004</v>
@@ -2595,14 +2595,14 @@
       <c r="F54" s="6"/>
       <c r="G54" s="14">
         <f t="shared" si="14"/>
-        <v>-0.6906629999999998</v>
+        <v>-0.70947699999999969</v>
       </c>
       <c r="H54" s="14"/>
       <c r="I54" s="14"/>
       <c r="J54" s="6"/>
       <c r="K54" s="13">
         <f t="shared" si="15"/>
-        <v>-0.10186808975963621</v>
+        <v>-0.10435345240945881</v>
       </c>
       <c r="L54" s="13"/>
       <c r="M54" s="13"/>
@@ -2669,7 +2669,7 @@
         <v>52</v>
       </c>
       <c r="B57" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C57" s="14">
         <v>5</v>
@@ -2679,14 +2679,14 @@
       <c r="F57" s="6"/>
       <c r="G57" s="14">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H57" s="14"/>
       <c r="I57" s="14"/>
       <c r="J57" s="6"/>
       <c r="K57" s="13">
         <f t="shared" si="15"/>
-        <v>0.66666666666666663</v>
+        <v>0</v>
       </c>
       <c r="L57" s="13"/>
       <c r="M57" s="13"/>
@@ -2697,7 +2697,7 @@
         <v>71</v>
       </c>
       <c r="B58" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C58" s="14">
         <v>93</v>
@@ -2707,14 +2707,14 @@
       <c r="F58" s="6"/>
       <c r="G58" s="14">
         <f t="shared" si="14"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H58" s="14"/>
       <c r="I58" s="14"/>
       <c r="J58" s="6"/>
       <c r="K58" s="13">
         <f t="shared" si="15"/>
-        <v>0.29166666666666669</v>
+        <v>0.30985915492957744</v>
       </c>
       <c r="L58" s="13"/>
       <c r="M58" s="13"/>
@@ -2725,7 +2725,7 @@
         <v>53</v>
       </c>
       <c r="B59" s="5">
-        <v>2.2959179999999999E-2</v>
+        <v>2.264031E-2</v>
       </c>
       <c r="C59" s="13">
         <v>2.9655609999999999E-2</v>
@@ -2735,14 +2735,14 @@
       <c r="F59" s="6"/>
       <c r="G59" s="14">
         <f t="shared" si="14"/>
-        <v>6.6964299999999997E-3</v>
+        <v>7.0152999999999986E-3</v>
       </c>
       <c r="H59" s="14"/>
       <c r="I59" s="14"/>
       <c r="J59" s="6"/>
       <c r="K59" s="13">
         <f t="shared" si="15"/>
-        <v>0.29166677555557297</v>
+        <v>0.30985883143826204</v>
       </c>
       <c r="L59" s="13"/>
       <c r="M59" s="13"/>
@@ -2793,7 +2793,7 @@
         <v>32</v>
       </c>
       <c r="B62" s="1">
-        <v>0.46843099999999999</v>
+        <v>0.72385200000000005</v>
       </c>
       <c r="C62" s="14">
         <v>2.6575259999999998</v>
@@ -2803,14 +2803,14 @@
       <c r="F62" s="6"/>
       <c r="G62" s="14">
         <f t="shared" ref="G62:G73" si="16">C62-B62</f>
-        <v>2.189095</v>
+        <v>1.9336739999999999</v>
       </c>
       <c r="H62" s="14"/>
       <c r="I62" s="14"/>
       <c r="J62" s="6"/>
       <c r="K62" s="13">
         <f>G62/B62</f>
-        <v>4.6732496354852691</v>
+        <v>2.6713665224382881</v>
       </c>
       <c r="L62" s="13"/>
       <c r="M62" s="13"/>
@@ -2821,7 +2821,7 @@
         <v>33</v>
       </c>
       <c r="B63" s="1">
-        <v>0.34279300000000001</v>
+        <v>0.54081599999999996</v>
       </c>
       <c r="C63" s="14">
         <v>1.2959179999999999</v>
@@ -2831,14 +2831,14 @@
       <c r="F63" s="6"/>
       <c r="G63" s="14">
         <f t="shared" si="16"/>
-        <v>0.95312499999999989</v>
+        <v>0.75510199999999994</v>
       </c>
       <c r="H63" s="14"/>
       <c r="I63" s="14"/>
       <c r="J63" s="6"/>
       <c r="K63" s="13">
         <f>G63/B63</f>
-        <v>2.7804680959062753</v>
+        <v>1.3962271826277328</v>
       </c>
       <c r="L63" s="13"/>
       <c r="M63" s="13"/>
@@ -2903,7 +2903,7 @@
         <v>36</v>
       </c>
       <c r="B66" s="1">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="C66" s="14">
         <v>-1</v>
@@ -2913,14 +2913,14 @@
       <c r="F66" s="6"/>
       <c r="G66" s="14">
         <f t="shared" si="16"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" s="14"/>
       <c r="I66" s="14"/>
       <c r="J66" s="6"/>
       <c r="K66" s="13">
         <f t="shared" ref="K66:K73" si="17">G66/B66</f>
-        <v>-0.66666666666666663</v>
+        <v>-0.75</v>
       </c>
       <c r="L66" s="13"/>
       <c r="M66" s="13"/>
@@ -2959,7 +2959,7 @@
         <v>38</v>
       </c>
       <c r="B68" s="1">
-        <v>7.5959820000000002</v>
+        <v>7.3896680000000003</v>
       </c>
       <c r="C68" s="14">
         <v>6.7755099999999997</v>
@@ -2969,14 +2969,14 @@
       <c r="F68" s="6"/>
       <c r="G68" s="14">
         <f t="shared" si="16"/>
-        <v>-0.82047200000000053</v>
+        <v>-0.61415800000000065</v>
       </c>
       <c r="H68" s="14"/>
       <c r="I68" s="14"/>
       <c r="J68" s="6"/>
       <c r="K68" s="13">
         <f t="shared" si="17"/>
-        <v>-0.10801394737375634</v>
+        <v>-8.3110364362783365E-2</v>
       </c>
       <c r="L68" s="13"/>
       <c r="M68" s="13"/>
@@ -3071,7 +3071,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="1">
-        <v>2234</v>
+        <v>1687</v>
       </c>
       <c r="C72" s="14">
         <v>517</v>
@@ -3081,14 +3081,14 @@
       <c r="F72" s="6"/>
       <c r="G72" s="14">
         <f t="shared" si="16"/>
-        <v>-1717</v>
+        <v>-1170</v>
       </c>
       <c r="H72" s="14"/>
       <c r="I72" s="14"/>
       <c r="J72" s="6"/>
       <c r="K72" s="13">
         <f t="shared" si="17"/>
-        <v>-0.76857654431512978</v>
+        <v>-0.69353882631890929</v>
       </c>
       <c r="L72" s="13"/>
       <c r="M72" s="13"/>
@@ -3099,24 +3099,24 @@
         <v>42</v>
       </c>
       <c r="B73" s="5">
-        <v>0.71237245000000005</v>
-      </c>
-      <c r="C73" s="18">
+        <v>0.53794642999999998</v>
+      </c>
+      <c r="C73" s="15">
         <v>0.16485969</v>
       </c>
-      <c r="D73" s="18"/>
-      <c r="E73" s="18"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="15"/>
       <c r="F73" s="6"/>
       <c r="G73" s="14">
         <f t="shared" si="16"/>
-        <v>-0.54751276000000004</v>
+        <v>-0.37308673999999997</v>
       </c>
       <c r="H73" s="14"/>
       <c r="I73" s="14"/>
       <c r="J73" s="6"/>
       <c r="K73" s="13">
         <f t="shared" si="17"/>
-        <v>-0.76857655008977399</v>
+        <v>-0.69353883434080976</v>
       </c>
       <c r="L73" s="13"/>
       <c r="M73" s="13"/>
@@ -3167,7 +3167,7 @@
         <v>43</v>
       </c>
       <c r="B76" s="1">
-        <v>15.246810999999999</v>
+        <v>3.19E-4</v>
       </c>
       <c r="C76" s="14">
         <v>0</v>
@@ -3177,7 +3177,7 @@
       <c r="F76" s="6"/>
       <c r="G76" s="14">
         <f t="shared" ref="G76:G87" si="18">C76-B76</f>
-        <v>-15.246810999999999</v>
+        <v>-3.19E-4</v>
       </c>
       <c r="H76" s="14"/>
       <c r="I76" s="14"/>
@@ -3195,7 +3195,7 @@
         <v>44</v>
       </c>
       <c r="B77" s="1">
-        <v>2.0593110000000001</v>
+        <v>3.19E-4</v>
       </c>
       <c r="C77" s="14">
         <v>0</v>
@@ -3205,7 +3205,7 @@
       <c r="F77" s="6"/>
       <c r="G77" s="14">
         <f t="shared" si="18"/>
-        <v>-2.0593110000000001</v>
+        <v>-3.19E-4</v>
       </c>
       <c r="H77" s="14"/>
       <c r="I77" s="14"/>
@@ -3223,7 +3223,7 @@
         <v>45</v>
       </c>
       <c r="B78" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C78" s="14">
         <v>0</v>
@@ -3233,14 +3233,14 @@
       <c r="F78" s="6"/>
       <c r="G78" s="14">
         <f t="shared" si="18"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H78" s="14"/>
       <c r="I78" s="14"/>
       <c r="J78" s="6"/>
-      <c r="K78" s="13">
+      <c r="K78" s="13" t="e">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L78" s="13"/>
       <c r="M78" s="13"/>
@@ -3251,7 +3251,7 @@
         <v>46</v>
       </c>
       <c r="B79" s="1">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C79" s="14">
         <v>0</v>
@@ -3261,14 +3261,14 @@
       <c r="F79" s="6"/>
       <c r="G79" s="14">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H79" s="14"/>
       <c r="I79" s="14"/>
       <c r="J79" s="6"/>
-      <c r="K79" s="13">
+      <c r="K79" s="13" t="e">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L79" s="13"/>
       <c r="M79" s="13"/>
@@ -3279,7 +3279,7 @@
         <v>47</v>
       </c>
       <c r="B80" s="1">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C80" s="14">
         <v>0</v>
@@ -3289,14 +3289,14 @@
       <c r="F80" s="6"/>
       <c r="G80" s="14">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H80" s="14"/>
       <c r="I80" s="14"/>
       <c r="J80" s="6"/>
-      <c r="K80" s="13">
+      <c r="K80" s="13" t="e">
         <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L80" s="13"/>
       <c r="M80" s="13"/>
@@ -3307,7 +3307,7 @@
         <v>48</v>
       </c>
       <c r="B81" s="1">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="C81" s="14">
         <v>8</v>
@@ -3317,14 +3317,14 @@
       <c r="F81" s="6"/>
       <c r="G81" s="14">
         <f t="shared" si="18"/>
-        <v>-82</v>
+        <v>7</v>
       </c>
       <c r="H81" s="14"/>
       <c r="I81" s="14"/>
       <c r="J81" s="6"/>
       <c r="K81" s="13">
         <f t="shared" si="19"/>
-        <v>-0.91111111111111109</v>
+        <v>7</v>
       </c>
       <c r="L81" s="13"/>
       <c r="M81" s="13"/>
@@ -3335,7 +3335,7 @@
         <v>49</v>
       </c>
       <c r="B82" s="1">
-        <v>6.7799740000000002</v>
+        <v>7.9996809999999998</v>
       </c>
       <c r="C82" s="14">
         <v>8</v>
@@ -3345,14 +3345,14 @@
       <c r="F82" s="6"/>
       <c r="G82" s="14">
         <f t="shared" si="18"/>
-        <v>1.2200259999999998</v>
+        <v>3.1900000000018025E-4</v>
       </c>
       <c r="H82" s="14"/>
       <c r="I82" s="14"/>
       <c r="J82" s="6"/>
       <c r="K82" s="13">
         <f t="shared" si="19"/>
-        <v>0.17994552781470841</v>
+        <v>3.9876590079051935E-5</v>
       </c>
       <c r="L82" s="13"/>
       <c r="M82" s="13"/>
@@ -3363,7 +3363,7 @@
         <v>50</v>
       </c>
       <c r="B83" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C83" s="14">
         <v>8</v>
@@ -3373,14 +3373,14 @@
       <c r="F83" s="6"/>
       <c r="G83" s="14">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" s="14"/>
       <c r="I83" s="14"/>
       <c r="J83" s="6"/>
       <c r="K83" s="13">
         <f t="shared" si="19"/>
-        <v>0.14285714285714285</v>
+        <v>0</v>
       </c>
       <c r="L83" s="13"/>
       <c r="M83" s="13"/>
@@ -3419,7 +3419,7 @@
         <v>52</v>
       </c>
       <c r="B85" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C85" s="14">
         <v>8</v>
@@ -3429,14 +3429,14 @@
       <c r="F85" s="6"/>
       <c r="G85" s="14">
         <f t="shared" si="18"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H85" s="14"/>
       <c r="I85" s="14"/>
       <c r="J85" s="6"/>
       <c r="K85" s="13">
         <f t="shared" si="19"/>
-        <v>1.6666666666666667</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="L85" s="13"/>
       <c r="M85" s="13"/>
@@ -3447,7 +3447,7 @@
         <v>71</v>
       </c>
       <c r="B86" s="1">
-        <v>72</v>
+        <v>3135</v>
       </c>
       <c r="C86" s="14">
         <v>3136</v>
@@ -3457,14 +3457,14 @@
       <c r="F86" s="6"/>
       <c r="G86" s="14">
         <f t="shared" si="18"/>
-        <v>3064</v>
+        <v>1</v>
       </c>
       <c r="H86" s="14"/>
       <c r="I86" s="14"/>
       <c r="J86" s="6"/>
       <c r="K86" s="13">
         <f t="shared" si="19"/>
-        <v>42.555555555555557</v>
+        <v>3.1897926634768739E-4</v>
       </c>
       <c r="L86" s="13"/>
       <c r="M86" s="13"/>
@@ -3475,7 +3475,7 @@
         <v>53</v>
       </c>
       <c r="B87" s="5">
-        <v>2.2959179999999999E-2</v>
+        <v>0.99968111999999998</v>
       </c>
       <c r="C87" s="13">
         <v>1</v>
@@ -3485,14 +3485,14 @@
       <c r="F87" s="6"/>
       <c r="G87" s="14">
         <f t="shared" si="18"/>
-        <v>0.97704082000000003</v>
+        <v>3.1888000000002137E-4</v>
       </c>
       <c r="H87" s="14"/>
       <c r="I87" s="14"/>
       <c r="J87" s="6"/>
       <c r="K87" s="13">
         <f t="shared" si="19"/>
-        <v>42.555562524445563</v>
+        <v>3.1898171688990321E-4</v>
       </c>
       <c r="L87" s="13"/>
       <c r="M87" s="13"/>
@@ -3543,7 +3543,7 @@
         <v>32</v>
       </c>
       <c r="B90" s="1">
-        <v>0.46843099999999999</v>
+        <v>0.18909400000000001</v>
       </c>
       <c r="C90" s="14">
         <v>0.93590600000000002</v>
@@ -3553,14 +3553,14 @@
       <c r="F90" s="6"/>
       <c r="G90" s="14">
         <f t="shared" ref="G90:G101" si="20">C90-B90</f>
-        <v>0.46747500000000003</v>
+        <v>0.74681200000000003</v>
       </c>
       <c r="H90" s="14"/>
       <c r="I90" s="14"/>
       <c r="J90" s="6"/>
       <c r="K90" s="13">
         <f>G90/B90</f>
-        <v>0.99795914446311207</v>
+        <v>3.9494219806022399</v>
       </c>
       <c r="L90" s="13"/>
       <c r="M90" s="13"/>
@@ -3571,7 +3571,7 @@
         <v>33</v>
       </c>
       <c r="B91" s="1">
-        <v>0.34279300000000001</v>
+        <v>0.13361000000000001</v>
       </c>
       <c r="C91" s="14">
         <v>0.419962</v>
@@ -3581,14 +3581,14 @@
       <c r="F91" s="6"/>
       <c r="G91" s="14">
         <f t="shared" si="20"/>
-        <v>7.7168999999999988E-2</v>
+        <v>0.286352</v>
       </c>
       <c r="H91" s="14"/>
       <c r="I91" s="14"/>
       <c r="J91" s="6"/>
       <c r="K91" s="13">
         <f t="shared" ref="K91" si="21">G91/B91</f>
-        <v>0.22511836589428602</v>
+        <v>2.1431928747848215</v>
       </c>
       <c r="L91" s="13"/>
       <c r="M91" s="13"/>
@@ -3681,7 +3681,7 @@
         <v>37</v>
       </c>
       <c r="B95" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95" s="14">
         <v>5</v>
@@ -3691,14 +3691,14 @@
       <c r="F95" s="6"/>
       <c r="G95" s="14">
         <f t="shared" si="20"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H95" s="14"/>
       <c r="I95" s="14"/>
       <c r="J95" s="6"/>
       <c r="K95" s="13">
         <f t="shared" si="22"/>
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="L95" s="13"/>
       <c r="M95" s="13"/>
@@ -3709,7 +3709,7 @@
         <v>38</v>
       </c>
       <c r="B96" s="1">
-        <v>7.5959820000000002</v>
+        <v>7.8580990000000002</v>
       </c>
       <c r="C96" s="14">
         <v>7.6584820000000002</v>
@@ -3719,14 +3719,14 @@
       <c r="F96" s="6"/>
       <c r="G96" s="14">
         <f t="shared" si="20"/>
-        <v>6.25E-2</v>
+        <v>-0.19961699999999993</v>
       </c>
       <c r="H96" s="14"/>
       <c r="I96" s="14"/>
       <c r="J96" s="6"/>
       <c r="K96" s="13">
         <f t="shared" si="22"/>
-        <v>8.2280342423138968E-3</v>
+        <v>-2.5402708721282325E-2</v>
       </c>
       <c r="L96" s="13"/>
       <c r="M96" s="13"/>
@@ -3793,7 +3793,7 @@
         <v>41</v>
       </c>
       <c r="B99" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C99" s="14">
         <v>5</v>
@@ -3803,14 +3803,14 @@
       <c r="F99" s="6"/>
       <c r="G99" s="14">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H99" s="14"/>
       <c r="I99" s="14"/>
       <c r="J99" s="6"/>
       <c r="K99" s="13">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>-0.16666666666666666</v>
       </c>
       <c r="L99" s="13"/>
       <c r="M99" s="13"/>
@@ -3821,7 +3821,7 @@
         <v>70</v>
       </c>
       <c r="B100" s="1">
-        <v>2234</v>
+        <v>2792</v>
       </c>
       <c r="C100" s="14">
         <v>2321</v>
@@ -3831,14 +3831,14 @@
       <c r="F100" s="6"/>
       <c r="G100" s="14">
         <f t="shared" si="20"/>
-        <v>87</v>
+        <v>-471</v>
       </c>
       <c r="H100" s="14"/>
       <c r="I100" s="14"/>
       <c r="J100" s="6"/>
       <c r="K100" s="13">
         <f t="shared" si="22"/>
-        <v>3.8943598925693823E-2</v>
+        <v>-0.16869627507163323</v>
       </c>
       <c r="L100" s="13"/>
       <c r="M100" s="13"/>
@@ -3849,24 +3849,24 @@
         <v>42</v>
       </c>
       <c r="B101" s="5">
-        <v>0.71237245000000005</v>
-      </c>
-      <c r="C101" s="18">
+        <v>0.89030611999999998</v>
+      </c>
+      <c r="C101" s="15">
         <v>0.74011479999999996</v>
       </c>
-      <c r="D101" s="18"/>
-      <c r="E101" s="18"/>
+      <c r="D101" s="15"/>
+      <c r="E101" s="15"/>
       <c r="F101" s="6"/>
       <c r="G101" s="14">
         <f t="shared" si="20"/>
-        <v>2.7742349999999916E-2</v>
+        <v>-0.15019132000000002</v>
       </c>
       <c r="H101" s="14"/>
       <c r="I101" s="14"/>
       <c r="J101" s="6"/>
       <c r="K101" s="13">
         <f t="shared" si="22"/>
-        <v>3.8943603167135271E-2</v>
+        <v>-0.1686962682004253</v>
       </c>
       <c r="L101" s="13"/>
       <c r="M101" s="13"/>
@@ -3917,7 +3917,7 @@
         <v>43</v>
       </c>
       <c r="B104" s="1">
-        <v>15.246810999999999</v>
+        <v>1.3712E-2</v>
       </c>
       <c r="C104" s="14">
         <v>0.10076499999999999</v>
@@ -3927,14 +3927,14 @@
       <c r="F104" s="6"/>
       <c r="G104" s="14">
         <f t="shared" ref="G104:G115" si="23">C104-B104</f>
-        <v>-15.146045999999998</v>
+        <v>8.7052999999999991E-2</v>
       </c>
       <c r="H104" s="14"/>
       <c r="I104" s="14"/>
       <c r="J104" s="6"/>
       <c r="K104" s="13">
         <f>G104/B104</f>
-        <v>-0.99339107699308393</v>
+        <v>6.348672695449241</v>
       </c>
       <c r="L104" s="13"/>
       <c r="M104" s="13"/>
@@ -3945,7 +3945,7 @@
         <v>44</v>
       </c>
       <c r="B105" s="1">
-        <v>2.0593110000000001</v>
+        <v>1.1161000000000001E-2</v>
       </c>
       <c r="C105" s="14">
         <v>2.6148000000000001E-2</v>
@@ -3955,14 +3955,14 @@
       <c r="F105" s="6"/>
       <c r="G105" s="14">
         <f t="shared" si="23"/>
-        <v>-2.0331630000000001</v>
+        <v>1.4987E-2</v>
       </c>
       <c r="H105" s="14"/>
       <c r="I105" s="14"/>
       <c r="J105" s="6"/>
       <c r="K105" s="13">
         <f t="shared" ref="K105:K115" si="24">G105/B105</f>
-        <v>-0.98730254925069594</v>
+        <v>1.3428008242988978</v>
       </c>
       <c r="L105" s="13"/>
       <c r="M105" s="13"/>
@@ -3973,7 +3973,7 @@
         <v>45</v>
       </c>
       <c r="B106" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C106" s="14">
         <v>0</v>
@@ -3983,14 +3983,14 @@
       <c r="F106" s="6"/>
       <c r="G106" s="14">
         <f t="shared" si="23"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H106" s="14"/>
       <c r="I106" s="14"/>
       <c r="J106" s="6"/>
-      <c r="K106" s="13">
+      <c r="K106" s="13" t="e">
         <f t="shared" si="24"/>
-        <v>-1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L106" s="13"/>
       <c r="M106" s="13"/>
@@ -4001,7 +4001,7 @@
         <v>46</v>
       </c>
       <c r="B107" s="1">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C107" s="14">
         <v>0</v>
@@ -4011,14 +4011,14 @@
       <c r="F107" s="6"/>
       <c r="G107" s="14">
         <f t="shared" si="23"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H107" s="14"/>
       <c r="I107" s="14"/>
       <c r="J107" s="6"/>
-      <c r="K107" s="13">
+      <c r="K107" s="13" t="e">
         <f t="shared" si="24"/>
-        <v>-1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L107" s="13"/>
       <c r="M107" s="13"/>
@@ -4029,7 +4029,7 @@
         <v>47</v>
       </c>
       <c r="B108" s="1">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="C108" s="14">
         <v>-2</v>
@@ -4039,14 +4039,14 @@
       <c r="F108" s="6"/>
       <c r="G108" s="14">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108" s="14"/>
       <c r="I108" s="14"/>
       <c r="J108" s="6"/>
       <c r="K108" s="13">
         <f t="shared" si="24"/>
-        <v>-0.33333333333333331</v>
+        <v>0</v>
       </c>
       <c r="L108" s="13"/>
       <c r="M108" s="13"/>
@@ -4057,7 +4057,7 @@
         <v>48</v>
       </c>
       <c r="B109" s="1">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="C109" s="14">
         <v>11</v>
@@ -4067,14 +4067,14 @@
       <c r="F109" s="6"/>
       <c r="G109" s="14">
         <f t="shared" si="23"/>
-        <v>-79</v>
+        <v>10</v>
       </c>
       <c r="H109" s="14"/>
       <c r="I109" s="14"/>
       <c r="J109" s="6"/>
       <c r="K109" s="13">
         <f t="shared" si="24"/>
-        <v>-0.87777777777777777</v>
+        <v>10</v>
       </c>
       <c r="L109" s="13"/>
       <c r="M109" s="13"/>
@@ -4085,7 +4085,7 @@
         <v>49</v>
       </c>
       <c r="B110" s="1">
-        <v>6.7799740000000002</v>
+        <v>7.9901150000000003</v>
       </c>
       <c r="C110" s="14">
         <v>7.9846940000000002</v>
@@ -4095,14 +4095,14 @@
       <c r="F110" s="6"/>
       <c r="G110" s="14">
         <f t="shared" si="23"/>
-        <v>1.20472</v>
+        <v>-5.4210000000001202E-3</v>
       </c>
       <c r="H110" s="14"/>
       <c r="I110" s="14"/>
       <c r="J110" s="6"/>
       <c r="K110" s="13">
         <f t="shared" si="24"/>
-        <v>0.17768799703361693</v>
+        <v>-6.7846332624750961E-4</v>
       </c>
       <c r="L110" s="13"/>
       <c r="M110" s="13"/>
@@ -4113,7 +4113,7 @@
         <v>50</v>
       </c>
       <c r="B111" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C111" s="14">
         <v>8</v>
@@ -4123,14 +4123,14 @@
       <c r="F111" s="6"/>
       <c r="G111" s="14">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" s="14"/>
       <c r="I111" s="14"/>
       <c r="J111" s="6"/>
       <c r="K111" s="13">
         <f t="shared" si="24"/>
-        <v>0.14285714285714285</v>
+        <v>0</v>
       </c>
       <c r="L111" s="13"/>
       <c r="M111" s="13"/>
@@ -4169,7 +4169,7 @@
         <v>52</v>
       </c>
       <c r="B113" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C113" s="14">
         <v>5</v>
@@ -4179,14 +4179,14 @@
       <c r="F113" s="6"/>
       <c r="G113" s="14">
         <f t="shared" si="23"/>
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="H113" s="14"/>
       <c r="I113" s="14"/>
       <c r="J113" s="6"/>
       <c r="K113" s="13">
         <f t="shared" si="24"/>
-        <v>0.66666666666666663</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="L113" s="13"/>
       <c r="M113" s="13"/>
@@ -4197,7 +4197,7 @@
         <v>71</v>
       </c>
       <c r="B114" s="1">
-        <v>72</v>
+        <v>3105</v>
       </c>
       <c r="C114" s="14">
         <v>3094</v>
@@ -4207,14 +4207,14 @@
       <c r="F114" s="6"/>
       <c r="G114" s="14">
         <f t="shared" si="23"/>
-        <v>3022</v>
+        <v>-11</v>
       </c>
       <c r="H114" s="14"/>
       <c r="I114" s="14"/>
       <c r="J114" s="6"/>
       <c r="K114" s="13">
         <f t="shared" si="24"/>
-        <v>41.972222222222221</v>
+        <v>-3.5426731078904991E-3</v>
       </c>
       <c r="L114" s="13"/>
       <c r="M114" s="13"/>
@@ -4225,7 +4225,7 @@
         <v>53</v>
       </c>
       <c r="B115" s="5">
-        <v>2.2959179999999999E-2</v>
+        <v>0.99011479999999996</v>
       </c>
       <c r="C115" s="13">
         <v>0.98660714000000005</v>
@@ -4235,14 +4235,14 @@
       <c r="F115" s="6"/>
       <c r="G115" s="14">
         <f t="shared" si="23"/>
-        <v>0.96364796000000008</v>
+        <v>-3.5076599999999125E-3</v>
       </c>
       <c r="H115" s="14"/>
       <c r="I115" s="14"/>
       <c r="J115" s="6"/>
       <c r="K115" s="13">
         <f t="shared" si="24"/>
-        <v>41.972228973334417</v>
+        <v>-3.5426801013376556E-3</v>
       </c>
       <c r="L115" s="13"/>
       <c r="M115" s="13"/>
@@ -4612,7 +4612,7 @@
       <c r="B129" s="5">
         <v>0.71237245000000005</v>
       </c>
-      <c r="C129" s="16">
+      <c r="C129" s="17">
         <f t="shared" si="25"/>
         <v>0.45620748333333333</v>
       </c>
@@ -5000,7 +5000,7 @@
       <c r="B143" s="5">
         <v>2.2959179999999999E-2</v>
       </c>
-      <c r="C143" s="16">
+      <c r="C143" s="17">
         <f t="shared" si="29"/>
         <v>0.6720875833333334</v>
       </c>
@@ -5055,11 +5055,11 @@
       <c r="H145" s="14"/>
       <c r="I145" s="14"/>
       <c r="J145" s="6"/>
-      <c r="K145" s="15">
-        <v>0</v>
-      </c>
-      <c r="L145" s="15"/>
-      <c r="M145" s="15"/>
+      <c r="K145" s="18">
+        <v>0</v>
+      </c>
+      <c r="L145" s="18"/>
+      <c r="M145" s="18"/>
       <c r="N145" s="6"/>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.2">
@@ -5379,6 +5379,335 @@
     </row>
   </sheetData>
   <mergeCells count="353">
+    <mergeCell ref="K155:L155"/>
+    <mergeCell ref="G141:I141"/>
+    <mergeCell ref="G142:I142"/>
+    <mergeCell ref="G143:I143"/>
+    <mergeCell ref="G145:I145"/>
+    <mergeCell ref="K146:M146"/>
+    <mergeCell ref="K147:M147"/>
+    <mergeCell ref="K148:M148"/>
+    <mergeCell ref="K149:M149"/>
+    <mergeCell ref="K150:M150"/>
+    <mergeCell ref="K145:M145"/>
+    <mergeCell ref="G152:I152"/>
+    <mergeCell ref="G153:H153"/>
+    <mergeCell ref="G151:H151"/>
+    <mergeCell ref="K141:M141"/>
+    <mergeCell ref="K142:M142"/>
+    <mergeCell ref="K143:M143"/>
+    <mergeCell ref="G146:I146"/>
+    <mergeCell ref="G147:I147"/>
+    <mergeCell ref="G148:I148"/>
+    <mergeCell ref="K152:M152"/>
+    <mergeCell ref="K151:L151"/>
+    <mergeCell ref="K153:L153"/>
+    <mergeCell ref="B155:D155"/>
+    <mergeCell ref="G117:I117"/>
+    <mergeCell ref="G119:I119"/>
+    <mergeCell ref="G120:I120"/>
+    <mergeCell ref="G121:I121"/>
+    <mergeCell ref="G122:I122"/>
+    <mergeCell ref="G123:I123"/>
+    <mergeCell ref="G124:I124"/>
+    <mergeCell ref="G125:I125"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="G127:I127"/>
+    <mergeCell ref="G128:I128"/>
+    <mergeCell ref="G129:I129"/>
+    <mergeCell ref="C124:E124"/>
+    <mergeCell ref="C125:E125"/>
+    <mergeCell ref="C126:E126"/>
+    <mergeCell ref="C127:E127"/>
+    <mergeCell ref="C128:E128"/>
+    <mergeCell ref="G155:H155"/>
+    <mergeCell ref="B152:E152"/>
+    <mergeCell ref="C141:E141"/>
+    <mergeCell ref="C142:E142"/>
+    <mergeCell ref="C143:E143"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="B153:D153"/>
+    <mergeCell ref="C122:E122"/>
+    <mergeCell ref="C123:E123"/>
+    <mergeCell ref="C132:E132"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="C118:E118"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="G135:I135"/>
+    <mergeCell ref="G136:I136"/>
+    <mergeCell ref="G137:I137"/>
+    <mergeCell ref="G138:I138"/>
+    <mergeCell ref="G139:I139"/>
+    <mergeCell ref="C119:E119"/>
+    <mergeCell ref="C120:E120"/>
+    <mergeCell ref="C121:E121"/>
+    <mergeCell ref="C133:E133"/>
+    <mergeCell ref="C134:E134"/>
+    <mergeCell ref="C135:E135"/>
+    <mergeCell ref="C129:E129"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="G118:I118"/>
+    <mergeCell ref="B151:D151"/>
+    <mergeCell ref="G132:I132"/>
+    <mergeCell ref="G133:I133"/>
+    <mergeCell ref="G134:I134"/>
+    <mergeCell ref="C136:E136"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="C138:E138"/>
+    <mergeCell ref="C139:E139"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="G149:I149"/>
+    <mergeCell ref="G150:I150"/>
+    <mergeCell ref="B150:E150"/>
+    <mergeCell ref="K123:M123"/>
+    <mergeCell ref="K124:M124"/>
+    <mergeCell ref="K125:M125"/>
+    <mergeCell ref="G140:I140"/>
+    <mergeCell ref="K126:M126"/>
+    <mergeCell ref="K127:M127"/>
+    <mergeCell ref="K128:M128"/>
+    <mergeCell ref="K129:M129"/>
+    <mergeCell ref="K119:M119"/>
+    <mergeCell ref="K120:M120"/>
+    <mergeCell ref="K121:M121"/>
+    <mergeCell ref="K122:M122"/>
+    <mergeCell ref="K132:M132"/>
+    <mergeCell ref="K133:M133"/>
+    <mergeCell ref="K134:M134"/>
+    <mergeCell ref="K135:M135"/>
+    <mergeCell ref="K136:M136"/>
+    <mergeCell ref="K137:M137"/>
+    <mergeCell ref="K138:M138"/>
+    <mergeCell ref="K139:M139"/>
+    <mergeCell ref="K140:M140"/>
+    <mergeCell ref="G131:I131"/>
+    <mergeCell ref="K131:M131"/>
+    <mergeCell ref="K117:M117"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="G62:I62"/>
+    <mergeCell ref="K62:M62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="G63:I63"/>
+    <mergeCell ref="K63:M63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="G64:I64"/>
+    <mergeCell ref="K64:M64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="K65:M65"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="G66:I66"/>
+    <mergeCell ref="K66:M66"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="G67:I67"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="K68:M68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="G69:I69"/>
+    <mergeCell ref="K69:M69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="G70:I70"/>
+    <mergeCell ref="K70:M70"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="K67:M67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="G68:I68"/>
+    <mergeCell ref="K83:M83"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="G84:I84"/>
+    <mergeCell ref="K84:M84"/>
+    <mergeCell ref="G77:I77"/>
+    <mergeCell ref="K77:M77"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="G78:I78"/>
+    <mergeCell ref="K78:M78"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="G79:I79"/>
+    <mergeCell ref="K79:M79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="G80:I80"/>
+    <mergeCell ref="K80:M80"/>
+    <mergeCell ref="G81:I81"/>
+    <mergeCell ref="K81:M81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="G82:I82"/>
+    <mergeCell ref="K82:M82"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="G71:I71"/>
+    <mergeCell ref="K71:M71"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="G72:I72"/>
+    <mergeCell ref="K72:M72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="G73:I73"/>
+    <mergeCell ref="K73:M73"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="G76:I76"/>
+    <mergeCell ref="K76:M76"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="K42:M42"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="K43:M43"/>
+    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="K45:M45"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="K47:M47"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="K49:M49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="K50:M50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="K51:M51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="K53:M53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="K54:M54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="G55:I55"/>
+    <mergeCell ref="K55:M55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="K56:M56"/>
+    <mergeCell ref="G57:I57"/>
+    <mergeCell ref="K57:M57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="G58:I58"/>
+    <mergeCell ref="K58:M58"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="G59:I59"/>
+    <mergeCell ref="K59:M59"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="G90:I90"/>
+    <mergeCell ref="K90:M90"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="G89:I89"/>
+    <mergeCell ref="K89:M89"/>
+    <mergeCell ref="G85:I85"/>
+    <mergeCell ref="K85:M85"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="G86:I86"/>
+    <mergeCell ref="K86:M86"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="K87:M87"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="G83:I83"/>
+    <mergeCell ref="G91:I91"/>
+    <mergeCell ref="K91:M91"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="G92:I92"/>
+    <mergeCell ref="K92:M92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="G93:I93"/>
+    <mergeCell ref="K93:M93"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="G94:I94"/>
+    <mergeCell ref="K94:M94"/>
+    <mergeCell ref="G95:I95"/>
+    <mergeCell ref="K95:M95"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="G96:I96"/>
+    <mergeCell ref="K96:M96"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="G97:I97"/>
+    <mergeCell ref="K97:M97"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="G98:I98"/>
+    <mergeCell ref="K98:M98"/>
+    <mergeCell ref="G99:I99"/>
+    <mergeCell ref="K99:M99"/>
+    <mergeCell ref="C100:E100"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="K100:M100"/>
+    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="G101:I101"/>
+    <mergeCell ref="K101:M101"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="G104:I104"/>
+    <mergeCell ref="K104:M104"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="G103:I103"/>
+    <mergeCell ref="K103:M103"/>
+    <mergeCell ref="C111:E111"/>
+    <mergeCell ref="G111:I111"/>
+    <mergeCell ref="K111:M111"/>
+    <mergeCell ref="C112:E112"/>
+    <mergeCell ref="G112:I112"/>
+    <mergeCell ref="K112:M112"/>
+    <mergeCell ref="G105:I105"/>
+    <mergeCell ref="K105:M105"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="G106:I106"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="C107:E107"/>
+    <mergeCell ref="G107:I107"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="C108:E108"/>
+    <mergeCell ref="G108:I108"/>
+    <mergeCell ref="K108:M108"/>
+    <mergeCell ref="C105:E105"/>
+    <mergeCell ref="C109:E109"/>
     <mergeCell ref="K118:M118"/>
     <mergeCell ref="B61:E61"/>
     <mergeCell ref="G61:I61"/>
@@ -5403,335 +5732,6 @@
     <mergeCell ref="C110:E110"/>
     <mergeCell ref="G110:I110"/>
     <mergeCell ref="K110:M110"/>
-    <mergeCell ref="C111:E111"/>
-    <mergeCell ref="G111:I111"/>
-    <mergeCell ref="K111:M111"/>
-    <mergeCell ref="C112:E112"/>
-    <mergeCell ref="G112:I112"/>
-    <mergeCell ref="K112:M112"/>
-    <mergeCell ref="G105:I105"/>
-    <mergeCell ref="K105:M105"/>
-    <mergeCell ref="C106:E106"/>
-    <mergeCell ref="G106:I106"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="C107:E107"/>
-    <mergeCell ref="G107:I107"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="C108:E108"/>
-    <mergeCell ref="G108:I108"/>
-    <mergeCell ref="K108:M108"/>
-    <mergeCell ref="C105:E105"/>
-    <mergeCell ref="C109:E109"/>
-    <mergeCell ref="G99:I99"/>
-    <mergeCell ref="K99:M99"/>
-    <mergeCell ref="C100:E100"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="K100:M100"/>
-    <mergeCell ref="C101:E101"/>
-    <mergeCell ref="G101:I101"/>
-    <mergeCell ref="K101:M101"/>
-    <mergeCell ref="C104:E104"/>
-    <mergeCell ref="G104:I104"/>
-    <mergeCell ref="K104:M104"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="G103:I103"/>
-    <mergeCell ref="K103:M103"/>
-    <mergeCell ref="G95:I95"/>
-    <mergeCell ref="K95:M95"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="G96:I96"/>
-    <mergeCell ref="K96:M96"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="G97:I97"/>
-    <mergeCell ref="K97:M97"/>
-    <mergeCell ref="C98:E98"/>
-    <mergeCell ref="G98:I98"/>
-    <mergeCell ref="K98:M98"/>
-    <mergeCell ref="G91:I91"/>
-    <mergeCell ref="K91:M91"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="G92:I92"/>
-    <mergeCell ref="K92:M92"/>
-    <mergeCell ref="C93:E93"/>
-    <mergeCell ref="G93:I93"/>
-    <mergeCell ref="K93:M93"/>
-    <mergeCell ref="C94:E94"/>
-    <mergeCell ref="G94:I94"/>
-    <mergeCell ref="K94:M94"/>
-    <mergeCell ref="G57:I57"/>
-    <mergeCell ref="K57:M57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="G58:I58"/>
-    <mergeCell ref="K58:M58"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="G59:I59"/>
-    <mergeCell ref="K59:M59"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="G90:I90"/>
-    <mergeCell ref="K90:M90"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="G89:I89"/>
-    <mergeCell ref="K89:M89"/>
-    <mergeCell ref="G85:I85"/>
-    <mergeCell ref="K85:M85"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="G86:I86"/>
-    <mergeCell ref="K86:M86"/>
-    <mergeCell ref="C87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="K87:M87"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="G83:I83"/>
-    <mergeCell ref="G53:I53"/>
-    <mergeCell ref="K53:M53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="K54:M54"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="G55:I55"/>
-    <mergeCell ref="K55:M55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="G56:I56"/>
-    <mergeCell ref="K56:M56"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="K49:M49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="K50:M50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="K51:M51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="G44:I44"/>
-    <mergeCell ref="K44:M44"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="G45:I45"/>
-    <mergeCell ref="K45:M45"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="K48:M48"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="K47:M47"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="G41:I41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="G42:I42"/>
-    <mergeCell ref="K42:M42"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="K43:M43"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="G71:I71"/>
-    <mergeCell ref="K71:M71"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="G72:I72"/>
-    <mergeCell ref="K72:M72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="G73:I73"/>
-    <mergeCell ref="K73:M73"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="G76:I76"/>
-    <mergeCell ref="K76:M76"/>
-    <mergeCell ref="K83:M83"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="G84:I84"/>
-    <mergeCell ref="K84:M84"/>
-    <mergeCell ref="G77:I77"/>
-    <mergeCell ref="K77:M77"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="G78:I78"/>
-    <mergeCell ref="K78:M78"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="G79:I79"/>
-    <mergeCell ref="K79:M79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="G80:I80"/>
-    <mergeCell ref="K80:M80"/>
-    <mergeCell ref="G81:I81"/>
-    <mergeCell ref="K81:M81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="G82:I82"/>
-    <mergeCell ref="K82:M82"/>
-    <mergeCell ref="K68:M68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="G69:I69"/>
-    <mergeCell ref="K69:M69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="G70:I70"/>
-    <mergeCell ref="K70:M70"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="K67:M67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="G68:I68"/>
-    <mergeCell ref="K117:M117"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="G62:I62"/>
-    <mergeCell ref="K62:M62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="G63:I63"/>
-    <mergeCell ref="K63:M63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="G64:I64"/>
-    <mergeCell ref="K64:M64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="G65:I65"/>
-    <mergeCell ref="K65:M65"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="G66:I66"/>
-    <mergeCell ref="K66:M66"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="G67:I67"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="K123:M123"/>
-    <mergeCell ref="K124:M124"/>
-    <mergeCell ref="K125:M125"/>
-    <mergeCell ref="G140:I140"/>
-    <mergeCell ref="K126:M126"/>
-    <mergeCell ref="K127:M127"/>
-    <mergeCell ref="K128:M128"/>
-    <mergeCell ref="K129:M129"/>
-    <mergeCell ref="K119:M119"/>
-    <mergeCell ref="K120:M120"/>
-    <mergeCell ref="K121:M121"/>
-    <mergeCell ref="K122:M122"/>
-    <mergeCell ref="K132:M132"/>
-    <mergeCell ref="K133:M133"/>
-    <mergeCell ref="K134:M134"/>
-    <mergeCell ref="K135:M135"/>
-    <mergeCell ref="K136:M136"/>
-    <mergeCell ref="K137:M137"/>
-    <mergeCell ref="K138:M138"/>
-    <mergeCell ref="K139:M139"/>
-    <mergeCell ref="K140:M140"/>
-    <mergeCell ref="G131:I131"/>
-    <mergeCell ref="K131:M131"/>
-    <mergeCell ref="B151:D151"/>
-    <mergeCell ref="G132:I132"/>
-    <mergeCell ref="G133:I133"/>
-    <mergeCell ref="G134:I134"/>
-    <mergeCell ref="C136:E136"/>
-    <mergeCell ref="C137:E137"/>
-    <mergeCell ref="C138:E138"/>
-    <mergeCell ref="C139:E139"/>
-    <mergeCell ref="C140:E140"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="G149:I149"/>
-    <mergeCell ref="G150:I150"/>
-    <mergeCell ref="B150:E150"/>
-    <mergeCell ref="C122:E122"/>
-    <mergeCell ref="C123:E123"/>
-    <mergeCell ref="C132:E132"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="C118:E118"/>
-    <mergeCell ref="B145:E145"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="G135:I135"/>
-    <mergeCell ref="G136:I136"/>
-    <mergeCell ref="G137:I137"/>
-    <mergeCell ref="G138:I138"/>
-    <mergeCell ref="G139:I139"/>
-    <mergeCell ref="C119:E119"/>
-    <mergeCell ref="C120:E120"/>
-    <mergeCell ref="C121:E121"/>
-    <mergeCell ref="C133:E133"/>
-    <mergeCell ref="C134:E134"/>
-    <mergeCell ref="C135:E135"/>
-    <mergeCell ref="C129:E129"/>
-    <mergeCell ref="B131:E131"/>
-    <mergeCell ref="G118:I118"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C85:E85"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="B153:D153"/>
-    <mergeCell ref="B155:D155"/>
-    <mergeCell ref="G117:I117"/>
-    <mergeCell ref="G119:I119"/>
-    <mergeCell ref="G120:I120"/>
-    <mergeCell ref="G121:I121"/>
-    <mergeCell ref="G122:I122"/>
-    <mergeCell ref="G123:I123"/>
-    <mergeCell ref="G124:I124"/>
-    <mergeCell ref="G125:I125"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="G127:I127"/>
-    <mergeCell ref="G128:I128"/>
-    <mergeCell ref="G129:I129"/>
-    <mergeCell ref="C124:E124"/>
-    <mergeCell ref="C125:E125"/>
-    <mergeCell ref="C126:E126"/>
-    <mergeCell ref="C127:E127"/>
-    <mergeCell ref="C128:E128"/>
-    <mergeCell ref="G155:H155"/>
-    <mergeCell ref="B152:E152"/>
-    <mergeCell ref="C141:E141"/>
-    <mergeCell ref="C142:E142"/>
-    <mergeCell ref="C143:E143"/>
-    <mergeCell ref="K155:L155"/>
-    <mergeCell ref="G141:I141"/>
-    <mergeCell ref="G142:I142"/>
-    <mergeCell ref="G143:I143"/>
-    <mergeCell ref="G145:I145"/>
-    <mergeCell ref="K146:M146"/>
-    <mergeCell ref="K147:M147"/>
-    <mergeCell ref="K148:M148"/>
-    <mergeCell ref="K149:M149"/>
-    <mergeCell ref="K150:M150"/>
-    <mergeCell ref="K145:M145"/>
-    <mergeCell ref="G152:I152"/>
-    <mergeCell ref="G153:H153"/>
-    <mergeCell ref="G151:H151"/>
-    <mergeCell ref="K141:M141"/>
-    <mergeCell ref="K142:M142"/>
-    <mergeCell ref="K143:M143"/>
-    <mergeCell ref="G146:I146"/>
-    <mergeCell ref="G147:I147"/>
-    <mergeCell ref="G148:I148"/>
-    <mergeCell ref="K152:M152"/>
-    <mergeCell ref="K151:L151"/>
-    <mergeCell ref="K153:L153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/FPGA_Performance_Comparison_Red_Small.xlsx
+++ b/FPGA_Performance_Comparison_Red_Small.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/DanielBiswas/Desktop/Documents/University/Year 5/Semester 1/AMME4112/Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753A97B5-DF2A-B94C-A28F-9BB7C82D6327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBAAA01D-8CE4-C547-95E3-76DC7DE0CB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="19120" windowHeight="17760" xr2:uid="{49DEC02E-5D37-064F-A7E8-1E1DC7B5FEA1}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="24080" windowHeight="26900" xr2:uid="{49DEC02E-5D37-064F-A7E8-1E1DC7B5FEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2420,21 +2420,21 @@
         <v>3.6269130000000001</v>
       </c>
       <c r="C48" s="14">
-        <v>3.3973209999999998</v>
+        <v>3.3778700000000002</v>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="6"/>
       <c r="G48" s="14">
         <f t="shared" ref="G48:G59" si="14">C48-B48</f>
-        <v>-0.22959200000000024</v>
+        <v>-0.2490429999999999</v>
       </c>
       <c r="H48" s="14"/>
       <c r="I48" s="14"/>
       <c r="J48" s="6"/>
       <c r="K48" s="13">
         <f>G48/B48</f>
-        <v>-6.3302317976747791E-2</v>
+        <v>-6.866528091520252E-2</v>
       </c>
       <c r="L48" s="13"/>
       <c r="M48" s="13"/>
@@ -2448,21 +2448,21 @@
         <v>1.8316330000000001</v>
       </c>
       <c r="C49" s="14">
-        <v>1.760842</v>
+        <v>1.756696</v>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="6"/>
       <c r="G49" s="14">
         <f t="shared" si="14"/>
-        <v>-7.0791000000000048E-2</v>
+        <v>-7.4937000000000031E-2</v>
       </c>
       <c r="H49" s="14"/>
       <c r="I49" s="14"/>
       <c r="J49" s="6"/>
       <c r="K49" s="13">
         <f t="shared" ref="K49:K59" si="15">G49/B49</f>
-        <v>-3.8649118027465131E-2</v>
+        <v>-4.0912671916262716E-2</v>
       </c>
       <c r="L49" s="13"/>
       <c r="M49" s="13"/>
@@ -2588,21 +2588,21 @@
         <v>6.7987880000000001</v>
       </c>
       <c r="C54" s="14">
-        <v>6.0893110000000004</v>
+        <v>6.8118619999999996</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
       <c r="F54" s="6"/>
       <c r="G54" s="14">
         <f t="shared" si="14"/>
-        <v>-0.70947699999999969</v>
+        <v>1.3073999999999586E-2</v>
       </c>
       <c r="H54" s="14"/>
       <c r="I54" s="14"/>
       <c r="J54" s="6"/>
       <c r="K54" s="13">
         <f t="shared" si="15"/>
-        <v>-0.10435345240945881</v>
+        <v>1.9229898034766764E-3</v>
       </c>
       <c r="L54" s="13"/>
       <c r="M54" s="13"/>
@@ -3238,9 +3238,8 @@
       <c r="H78" s="14"/>
       <c r="I78" s="14"/>
       <c r="J78" s="6"/>
-      <c r="K78" s="13" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+      <c r="K78" s="13">
+        <v>0</v>
       </c>
       <c r="L78" s="13"/>
       <c r="M78" s="13"/>
@@ -3266,9 +3265,8 @@
       <c r="H79" s="14"/>
       <c r="I79" s="14"/>
       <c r="J79" s="6"/>
-      <c r="K79" s="13" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+      <c r="K79" s="13">
+        <v>0</v>
       </c>
       <c r="L79" s="13"/>
       <c r="M79" s="13"/>
@@ -3294,9 +3292,8 @@
       <c r="H80" s="14"/>
       <c r="I80" s="14"/>
       <c r="J80" s="6"/>
-      <c r="K80" s="13" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
+      <c r="K80" s="13">
+        <v>0</v>
       </c>
       <c r="L80" s="13"/>
       <c r="M80" s="13"/>
@@ -3920,21 +3917,21 @@
         <v>1.3712E-2</v>
       </c>
       <c r="C104" s="14">
-        <v>0.10076499999999999</v>
+        <v>1.3393E-2</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
       <c r="F104" s="6"/>
       <c r="G104" s="14">
         <f t="shared" ref="G104:G115" si="23">C104-B104</f>
-        <v>8.7052999999999991E-2</v>
+        <v>-3.1899999999999984E-4</v>
       </c>
       <c r="H104" s="14"/>
       <c r="I104" s="14"/>
       <c r="J104" s="6"/>
       <c r="K104" s="13">
         <f>G104/B104</f>
-        <v>6.348672695449241</v>
+        <v>-2.3264294049008157E-2</v>
       </c>
       <c r="L104" s="13"/>
       <c r="M104" s="13"/>
@@ -3948,21 +3945,21 @@
         <v>1.1161000000000001E-2</v>
       </c>
       <c r="C105" s="14">
-        <v>2.6148000000000001E-2</v>
+        <v>1.0841999999999999E-2</v>
       </c>
       <c r="D105" s="14"/>
       <c r="E105" s="14"/>
       <c r="F105" s="6"/>
       <c r="G105" s="14">
         <f t="shared" si="23"/>
-        <v>1.4987E-2</v>
+        <v>-3.1900000000000157E-4</v>
       </c>
       <c r="H105" s="14"/>
       <c r="I105" s="14"/>
       <c r="J105" s="6"/>
       <c r="K105" s="13">
         <f t="shared" ref="K105:K115" si="24">G105/B105</f>
-        <v>1.3428008242988978</v>
+        <v>-2.858166830929142E-2</v>
       </c>
       <c r="L105" s="13"/>
       <c r="M105" s="13"/>
@@ -3988,9 +3985,8 @@
       <c r="H106" s="14"/>
       <c r="I106" s="14"/>
       <c r="J106" s="6"/>
-      <c r="K106" s="13" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
+      <c r="K106" s="13">
+        <v>0</v>
       </c>
       <c r="L106" s="13"/>
       <c r="M106" s="13"/>
@@ -4016,9 +4012,8 @@
       <c r="H107" s="14"/>
       <c r="I107" s="14"/>
       <c r="J107" s="6"/>
-      <c r="K107" s="13" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
+      <c r="K107" s="13">
+        <v>0</v>
       </c>
       <c r="L107" s="13"/>
       <c r="M107" s="13"/>
@@ -4060,21 +4055,21 @@
         <v>1</v>
       </c>
       <c r="C109" s="14">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
       <c r="F109" s="6"/>
       <c r="G109" s="14">
         <f t="shared" si="23"/>
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="H109" s="14"/>
       <c r="I109" s="14"/>
       <c r="J109" s="6"/>
       <c r="K109" s="13">
         <f t="shared" si="24"/>
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="L109" s="13"/>
       <c r="M109" s="13"/>
@@ -4088,21 +4083,21 @@
         <v>7.9901150000000003</v>
       </c>
       <c r="C110" s="14">
-        <v>7.9846940000000002</v>
+        <v>7.9904339999999996</v>
       </c>
       <c r="D110" s="14"/>
       <c r="E110" s="14"/>
       <c r="F110" s="6"/>
       <c r="G110" s="14">
         <f t="shared" si="23"/>
-        <v>-5.4210000000001202E-3</v>
+        <v>3.1899999999929207E-4</v>
       </c>
       <c r="H110" s="14"/>
       <c r="I110" s="14"/>
       <c r="J110" s="6"/>
       <c r="K110" s="13">
         <f t="shared" si="24"/>
-        <v>-6.7846332624750961E-4</v>
+        <v>3.9924331502023693E-5</v>
       </c>
       <c r="L110" s="13"/>
       <c r="M110" s="13"/>
@@ -4172,21 +4167,21 @@
         <v>7</v>
       </c>
       <c r="C113" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D113" s="14"/>
       <c r="E113" s="14"/>
       <c r="F113" s="6"/>
       <c r="G113" s="14">
         <f t="shared" si="23"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H113" s="14"/>
       <c r="I113" s="14"/>
       <c r="J113" s="6"/>
       <c r="K113" s="13">
         <f t="shared" si="24"/>
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="L113" s="13"/>
       <c r="M113" s="13"/>
@@ -4200,21 +4195,21 @@
         <v>3105</v>
       </c>
       <c r="C114" s="14">
-        <v>3094</v>
+        <v>3106</v>
       </c>
       <c r="D114" s="14"/>
       <c r="E114" s="14"/>
       <c r="F114" s="6"/>
       <c r="G114" s="14">
         <f t="shared" si="23"/>
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="H114" s="14"/>
       <c r="I114" s="14"/>
       <c r="J114" s="6"/>
       <c r="K114" s="13">
         <f t="shared" si="24"/>
-        <v>-3.5426731078904991E-3</v>
+        <v>3.2206119162640903E-4</v>
       </c>
       <c r="L114" s="13"/>
       <c r="M114" s="13"/>
@@ -4228,21 +4223,21 @@
         <v>0.99011479999999996</v>
       </c>
       <c r="C115" s="13">
-        <v>0.98660714000000005</v>
+        <v>0.99043367000000004</v>
       </c>
       <c r="D115" s="13"/>
       <c r="E115" s="13"/>
       <c r="F115" s="6"/>
       <c r="G115" s="14">
         <f t="shared" si="23"/>
-        <v>-3.5076599999999125E-3</v>
+        <v>3.1887000000008214E-4</v>
       </c>
       <c r="H115" s="14"/>
       <c r="I115" s="14"/>
       <c r="J115" s="6"/>
       <c r="K115" s="13">
         <f t="shared" si="24"/>
-        <v>-3.5426801013376556E-3</v>
+        <v>3.2205356388984605E-4</v>
       </c>
       <c r="L115" s="13"/>
       <c r="M115" s="13"/>
@@ -4293,25 +4288,26 @@
         <v>32</v>
       </c>
       <c r="B118" s="1">
-        <v>0.46843099999999999</v>
+        <f>AVERAGE(B62,B34,B90)</f>
+        <v>0.46045900000000001</v>
       </c>
       <c r="C118" s="14">
-        <f t="shared" ref="C118:C129" si="25">AVERAGE(C62,C34,C90)</f>
+        <f>AVERAGE(C62,C34,C90)</f>
         <v>1.8927509999999999</v>
       </c>
       <c r="D118" s="14"/>
       <c r="E118" s="14"/>
       <c r="F118" s="6"/>
       <c r="G118" s="14">
-        <f t="shared" ref="G118" si="26">C118-B118</f>
-        <v>1.4243199999999998</v>
+        <f t="shared" ref="G118" si="25">C118-B118</f>
+        <v>1.4322919999999999</v>
       </c>
       <c r="H118" s="14"/>
       <c r="I118" s="14"/>
       <c r="J118" s="6"/>
       <c r="K118" s="13">
         <f>G118/B118</f>
-        <v>3.0406185756280002</v>
+        <v>3.110574448539392</v>
       </c>
       <c r="L118" s="13"/>
       <c r="M118" s="13"/>
@@ -4322,25 +4318,26 @@
         <v>33</v>
       </c>
       <c r="B119" s="1">
-        <v>0.34279300000000001</v>
+        <f t="shared" ref="B119:B128" si="26">AVERAGE(B63,B35,B91)</f>
+        <v>0.33907299999999996</v>
       </c>
       <c r="C119" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="C119:C129" si="27">AVERAGE(C63,C35,C91)</f>
         <v>0.87595666666666661</v>
       </c>
       <c r="D119" s="14"/>
       <c r="E119" s="14"/>
       <c r="F119" s="6"/>
       <c r="G119" s="14">
-        <f t="shared" ref="G119:G129" si="27">C119-B119</f>
-        <v>0.53316366666666659</v>
+        <f t="shared" ref="G119:G129" si="28">C119-B119</f>
+        <v>0.53688366666666665</v>
       </c>
       <c r="H119" s="14"/>
       <c r="I119" s="14"/>
       <c r="J119" s="6"/>
       <c r="K119" s="13">
-        <f t="shared" ref="K119:K129" si="28">G119/B119</f>
-        <v>1.5553516748202751</v>
+        <f t="shared" ref="K119:K129" si="29">G119/B119</f>
+        <v>1.5833866650151049</v>
       </c>
       <c r="L119" s="13"/>
       <c r="M119" s="13"/>
@@ -4351,17 +4348,18 @@
         <v>34</v>
       </c>
       <c r="B120" s="1">
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="C120" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="D120" s="14"/>
       <c r="E120" s="14"/>
       <c r="F120" s="6"/>
       <c r="G120" s="14">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="H120" s="14"/>
@@ -4379,17 +4377,18 @@
         <v>35</v>
       </c>
       <c r="B121" s="1">
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="C121" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="D121" s="14"/>
       <c r="E121" s="14"/>
       <c r="F121" s="6"/>
       <c r="G121" s="14">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="H121" s="14"/>
@@ -4407,25 +4406,26 @@
         <v>36</v>
       </c>
       <c r="B122" s="1">
-        <v>-3</v>
+        <f t="shared" si="26"/>
+        <v>-3.3333333333333335</v>
       </c>
       <c r="C122" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-0.33333333333333331</v>
       </c>
       <c r="D122" s="14"/>
       <c r="E122" s="14"/>
       <c r="F122" s="6"/>
       <c r="G122" s="14">
-        <f t="shared" si="27"/>
-        <v>2.6666666666666665</v>
+        <f t="shared" si="28"/>
+        <v>3</v>
       </c>
       <c r="H122" s="14"/>
       <c r="I122" s="14"/>
       <c r="J122" s="6"/>
       <c r="K122" s="13">
-        <f t="shared" si="28"/>
-        <v>-0.88888888888888884</v>
+        <f t="shared" si="29"/>
+        <v>-0.89999999999999991</v>
       </c>
       <c r="L122" s="13"/>
       <c r="M122" s="13"/>
@@ -4436,25 +4436,26 @@
         <v>37</v>
       </c>
       <c r="B123" s="1">
-        <v>1</v>
+        <f t="shared" si="26"/>
+        <v>1.3333333333333333</v>
       </c>
       <c r="C123" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>5.333333333333333</v>
       </c>
       <c r="D123" s="14"/>
       <c r="E123" s="14"/>
       <c r="F123" s="6"/>
       <c r="G123" s="14">
-        <f t="shared" si="27"/>
-        <v>4.333333333333333</v>
+        <f t="shared" si="28"/>
+        <v>4</v>
       </c>
       <c r="H123" s="14"/>
       <c r="I123" s="14"/>
       <c r="J123" s="6"/>
       <c r="K123" s="13">
-        <f t="shared" si="28"/>
-        <v>4.333333333333333</v>
+        <f t="shared" si="29"/>
+        <v>3</v>
       </c>
       <c r="L123" s="13"/>
       <c r="M123" s="13"/>
@@ -4465,25 +4466,26 @@
         <v>38</v>
       </c>
       <c r="B124" s="1">
-        <v>7.5959820000000002</v>
+        <f t="shared" si="26"/>
+        <v>7.6145829999999997</v>
       </c>
       <c r="C124" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>7.2103526666666662</v>
       </c>
       <c r="D124" s="14"/>
       <c r="E124" s="14"/>
       <c r="F124" s="6"/>
       <c r="G124" s="14">
-        <f t="shared" si="27"/>
-        <v>-0.38562933333333405</v>
+        <f t="shared" si="28"/>
+        <v>-0.40423033333333347</v>
       </c>
       <c r="H124" s="14"/>
       <c r="I124" s="14"/>
       <c r="J124" s="6"/>
       <c r="K124" s="13">
-        <f t="shared" si="28"/>
-        <v>-5.0767541752117638E-2</v>
+        <f t="shared" si="29"/>
+        <v>-5.3086338849196793E-2</v>
       </c>
       <c r="L124" s="13"/>
       <c r="M124" s="13"/>
@@ -4494,24 +4496,25 @@
         <v>39</v>
       </c>
       <c r="B125" s="1">
+        <f t="shared" si="26"/>
         <v>8</v>
       </c>
       <c r="C125" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>7.333333333333333</v>
       </c>
       <c r="D125" s="14"/>
       <c r="E125" s="14"/>
       <c r="F125" s="6"/>
       <c r="G125" s="14">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-0.66666666666666696</v>
       </c>
       <c r="H125" s="14"/>
       <c r="I125" s="14"/>
       <c r="J125" s="6"/>
       <c r="K125" s="13">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-8.333333333333337E-2</v>
       </c>
       <c r="L125" s="13"/>
@@ -4523,24 +4526,25 @@
         <v>40</v>
       </c>
       <c r="B126" s="1">
+        <f t="shared" si="26"/>
         <v>8</v>
       </c>
       <c r="C126" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>8</v>
       </c>
       <c r="D126" s="14"/>
       <c r="E126" s="14"/>
       <c r="F126" s="6"/>
       <c r="G126" s="14">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H126" s="14"/>
       <c r="I126" s="14"/>
       <c r="J126" s="6"/>
       <c r="K126" s="13">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L126" s="13"/>
@@ -4552,25 +4556,26 @@
         <v>41</v>
       </c>
       <c r="B127" s="1">
-        <v>5</v>
+        <f t="shared" si="26"/>
+        <v>5.333333333333333</v>
       </c>
       <c r="C127" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>4.333333333333333</v>
       </c>
       <c r="D127" s="14"/>
       <c r="E127" s="14"/>
       <c r="F127" s="6"/>
       <c r="G127" s="14">
-        <f t="shared" si="27"/>
-        <v>-0.66666666666666696</v>
+        <f t="shared" si="28"/>
+        <v>-1</v>
       </c>
       <c r="H127" s="14"/>
       <c r="I127" s="14"/>
       <c r="J127" s="6"/>
       <c r="K127" s="13">
-        <f t="shared" si="28"/>
-        <v>-0.13333333333333339</v>
+        <f t="shared" si="29"/>
+        <v>-0.1875</v>
       </c>
       <c r="L127" s="13"/>
       <c r="M127" s="13"/>
@@ -4581,25 +4586,26 @@
         <v>70</v>
       </c>
       <c r="B128" s="1">
-        <v>2234</v>
+        <f t="shared" si="26"/>
+        <v>2237.6666666666665</v>
       </c>
       <c r="C128" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1430.6666666666667</v>
       </c>
       <c r="D128" s="14"/>
       <c r="E128" s="14"/>
       <c r="F128" s="6"/>
       <c r="G128" s="14">
-        <f t="shared" si="27"/>
-        <v>-803.33333333333326</v>
+        <f t="shared" si="28"/>
+        <v>-806.99999999999977</v>
       </c>
       <c r="H128" s="14"/>
       <c r="I128" s="14"/>
       <c r="J128" s="6"/>
       <c r="K128" s="13">
-        <f t="shared" si="28"/>
-        <v>-0.35959415099970155</v>
+        <f t="shared" si="29"/>
+        <v>-0.3606435274839862</v>
       </c>
       <c r="L128" s="13"/>
       <c r="M128" s="13"/>
@@ -4610,25 +4616,26 @@
         <v>42</v>
       </c>
       <c r="B129" s="5">
-        <v>0.71237245000000005</v>
+        <f>AVERAGE(B73,B45,B101)</f>
+        <v>0.71354166666666663</v>
       </c>
       <c r="C129" s="17">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.45620748333333333</v>
       </c>
       <c r="D129" s="14"/>
       <c r="E129" s="14"/>
       <c r="F129" s="6"/>
       <c r="G129" s="14">
-        <f t="shared" si="27"/>
-        <v>-0.25616496666666672</v>
+        <f t="shared" si="28"/>
+        <v>-0.2573341833333333</v>
       </c>
       <c r="H129" s="14"/>
       <c r="I129" s="14"/>
       <c r="J129" s="6"/>
       <c r="K129" s="13">
-        <f t="shared" si="28"/>
-        <v>-0.35959415143955481</v>
+        <f t="shared" si="29"/>
+        <v>-0.36064352700729924</v>
       </c>
       <c r="L129" s="13"/>
       <c r="M129" s="13"/>
@@ -4679,25 +4686,26 @@
         <v>43</v>
       </c>
       <c r="B132" s="1">
-        <v>15.246810999999999</v>
+        <f>AVERAGE(B76,B48,B104)</f>
+        <v>1.2136480000000001</v>
       </c>
       <c r="C132" s="14">
-        <f t="shared" ref="C132:C143" si="29">AVERAGE(C76,C48,C104)</f>
-        <v>1.1660286666666666</v>
+        <f t="shared" ref="C132:C143" si="30">AVERAGE(C76,C48,C104)</f>
+        <v>1.1304210000000001</v>
       </c>
       <c r="D132" s="14"/>
       <c r="E132" s="14"/>
       <c r="F132" s="6"/>
       <c r="G132" s="14">
-        <f t="shared" ref="G132:G143" si="30">C132-B132</f>
-        <v>-14.080782333333332</v>
+        <f t="shared" ref="G132:G143" si="31">C132-B132</f>
+        <v>-8.322699999999994E-2</v>
       </c>
       <c r="H132" s="14"/>
       <c r="I132" s="14"/>
       <c r="J132" s="6"/>
       <c r="K132" s="13">
         <f>G132/B132</f>
-        <v>-0.92352311137937848</v>
+        <v>-6.8575896800390182E-2</v>
       </c>
       <c r="L132" s="13"/>
       <c r="M132" s="13"/>
@@ -4708,25 +4716,26 @@
         <v>44</v>
       </c>
       <c r="B133" s="1">
-        <v>2.0593110000000001</v>
+        <f t="shared" ref="B133:B142" si="32">AVERAGE(B77,B49,B105)</f>
+        <v>0.614371</v>
       </c>
       <c r="C133" s="14">
-        <f t="shared" si="29"/>
-        <v>0.59566333333333332</v>
+        <f t="shared" si="30"/>
+        <v>0.58917933333333339</v>
       </c>
       <c r="D133" s="14"/>
       <c r="E133" s="14"/>
       <c r="F133" s="6"/>
       <c r="G133" s="14">
-        <f t="shared" si="30"/>
-        <v>-1.4636476666666667</v>
+        <f t="shared" si="31"/>
+        <v>-2.5191666666666612E-2</v>
       </c>
       <c r="H133" s="14"/>
       <c r="I133" s="14"/>
       <c r="J133" s="6"/>
       <c r="K133" s="13">
-        <f t="shared" ref="K133:K143" si="31">G133/B133</f>
-        <v>-0.71074629653639809</v>
+        <f t="shared" ref="K133:K143" si="33">G133/B133</f>
+        <v>-4.1003997041960984E-2</v>
       </c>
       <c r="L133" s="13"/>
       <c r="M133" s="13"/>
@@ -4737,25 +4746,26 @@
         <v>45</v>
       </c>
       <c r="B134" s="1">
-        <v>2</v>
+        <f t="shared" si="32"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C134" s="14">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="D134" s="14"/>
       <c r="E134" s="14"/>
       <c r="F134" s="6"/>
       <c r="G134" s="14">
-        <f t="shared" si="30"/>
-        <v>-1.3333333333333335</v>
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="H134" s="14"/>
       <c r="I134" s="14"/>
       <c r="J134" s="6"/>
       <c r="K134" s="13">
-        <f t="shared" si="31"/>
-        <v>-0.66666666666666674</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="L134" s="13"/>
       <c r="M134" s="13"/>
@@ -4766,25 +4776,26 @@
         <v>46</v>
       </c>
       <c r="B135" s="1">
-        <v>-2</v>
+        <f t="shared" si="32"/>
+        <v>-0.66666666666666663</v>
       </c>
       <c r="C135" s="14">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-0.66666666666666663</v>
       </c>
       <c r="D135" s="14"/>
       <c r="E135" s="14"/>
       <c r="F135" s="6"/>
       <c r="G135" s="14">
-        <f t="shared" si="30"/>
-        <v>1.3333333333333335</v>
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="H135" s="14"/>
       <c r="I135" s="14"/>
       <c r="J135" s="6"/>
       <c r="K135" s="13">
-        <f t="shared" si="31"/>
-        <v>-0.66666666666666674</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="L135" s="13"/>
       <c r="M135" s="13"/>
@@ -4795,25 +4806,26 @@
         <v>47</v>
       </c>
       <c r="B136" s="1">
-        <v>-3</v>
+        <f t="shared" si="32"/>
+        <v>-1.6666666666666667</v>
       </c>
       <c r="C136" s="14">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-1.6666666666666667</v>
       </c>
       <c r="D136" s="14"/>
       <c r="E136" s="14"/>
       <c r="F136" s="6"/>
       <c r="G136" s="14">
-        <f t="shared" si="30"/>
-        <v>1.3333333333333333</v>
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="H136" s="14"/>
       <c r="I136" s="14"/>
       <c r="J136" s="6"/>
       <c r="K136" s="13">
-        <f t="shared" si="31"/>
-        <v>-0.44444444444444442</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="L136" s="13"/>
       <c r="M136" s="13"/>
@@ -4824,25 +4836,26 @@
         <v>48</v>
       </c>
       <c r="B137" s="1">
-        <v>90</v>
+        <f t="shared" si="32"/>
+        <v>2</v>
       </c>
       <c r="C137" s="14">
-        <f t="shared" si="29"/>
-        <v>7.333333333333333</v>
+        <f t="shared" si="30"/>
+        <v>3.6666666666666665</v>
       </c>
       <c r="D137" s="14"/>
       <c r="E137" s="14"/>
       <c r="F137" s="6"/>
       <c r="G137" s="14">
-        <f t="shared" si="30"/>
-        <v>-82.666666666666671</v>
+        <f t="shared" si="31"/>
+        <v>1.6666666666666665</v>
       </c>
       <c r="H137" s="14"/>
       <c r="I137" s="14"/>
       <c r="J137" s="6"/>
       <c r="K137" s="13">
-        <f t="shared" si="31"/>
-        <v>-0.91851851851851862</v>
+        <f t="shared" si="33"/>
+        <v>0.83333333333333326</v>
       </c>
       <c r="L137" s="13"/>
       <c r="M137" s="13"/>
@@ -4853,25 +4866,26 @@
         <v>49</v>
       </c>
       <c r="B138" s="1">
-        <v>6.7799740000000002</v>
+        <f t="shared" si="32"/>
+        <v>7.5961946666666664</v>
       </c>
       <c r="C138" s="14">
-        <f t="shared" si="29"/>
-        <v>7.3580016666666666</v>
+        <f t="shared" si="30"/>
+        <v>7.6007653333333325</v>
       </c>
       <c r="D138" s="14"/>
       <c r="E138" s="14"/>
       <c r="F138" s="6"/>
       <c r="G138" s="14">
-        <f t="shared" si="30"/>
-        <v>0.57802766666666638</v>
+        <f t="shared" si="31"/>
+        <v>4.5706666666660567E-3</v>
       </c>
       <c r="H138" s="14"/>
       <c r="I138" s="14"/>
       <c r="J138" s="6"/>
       <c r="K138" s="13">
-        <f t="shared" si="31"/>
-        <v>8.5255145029562995E-2</v>
+        <f t="shared" si="33"/>
+        <v>6.0170478341252669E-4</v>
       </c>
       <c r="L138" s="13"/>
       <c r="M138" s="13"/>
@@ -4882,25 +4896,26 @@
         <v>50</v>
       </c>
       <c r="B139" s="1">
-        <v>7</v>
+        <f t="shared" si="32"/>
+        <v>7.666666666666667</v>
       </c>
       <c r="C139" s="14">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>7.666666666666667</v>
       </c>
       <c r="D139" s="14"/>
       <c r="E139" s="14"/>
       <c r="F139" s="6"/>
       <c r="G139" s="14">
-        <f t="shared" si="30"/>
-        <v>0.66666666666666696</v>
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
       <c r="H139" s="14"/>
       <c r="I139" s="14"/>
       <c r="J139" s="6"/>
       <c r="K139" s="13">
-        <f t="shared" si="31"/>
-        <v>9.5238095238095274E-2</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="L139" s="13"/>
       <c r="M139" s="13"/>
@@ -4911,24 +4926,25 @@
         <v>51</v>
       </c>
       <c r="B140" s="1">
+        <f t="shared" si="32"/>
         <v>8</v>
       </c>
       <c r="C140" s="14">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>8</v>
       </c>
       <c r="D140" s="14"/>
       <c r="E140" s="14"/>
       <c r="F140" s="6"/>
       <c r="G140" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H140" s="14"/>
       <c r="I140" s="14"/>
       <c r="J140" s="6"/>
       <c r="K140" s="13">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L140" s="13"/>
@@ -4940,25 +4956,26 @@
         <v>52</v>
       </c>
       <c r="B141" s="1">
-        <v>3</v>
+        <f t="shared" si="32"/>
+        <v>6.333333333333333</v>
       </c>
       <c r="C141" s="14">
-        <f t="shared" si="29"/>
-        <v>6</v>
+        <f t="shared" si="30"/>
+        <v>6.666666666666667</v>
       </c>
       <c r="D141" s="14"/>
       <c r="E141" s="14"/>
       <c r="F141" s="6"/>
       <c r="G141" s="14">
-        <f t="shared" si="30"/>
-        <v>3</v>
+        <f t="shared" si="31"/>
+        <v>0.33333333333333393</v>
       </c>
       <c r="H141" s="14"/>
       <c r="I141" s="14"/>
       <c r="J141" s="6"/>
       <c r="K141" s="13">
-        <f t="shared" si="31"/>
-        <v>1</v>
+        <f t="shared" si="33"/>
+        <v>5.2631578947368515E-2</v>
       </c>
       <c r="L141" s="13"/>
       <c r="M141" s="13"/>
@@ -4969,25 +4986,26 @@
         <v>71</v>
       </c>
       <c r="B142" s="1">
-        <v>72</v>
+        <f t="shared" si="32"/>
+        <v>2103.6666666666665</v>
       </c>
       <c r="C142" s="14">
-        <f t="shared" si="29"/>
-        <v>2107.6666666666665</v>
+        <f t="shared" si="30"/>
+        <v>2111.6666666666665</v>
       </c>
       <c r="D142" s="14"/>
       <c r="E142" s="14"/>
       <c r="F142" s="6"/>
       <c r="G142" s="14">
-        <f t="shared" si="30"/>
-        <v>2035.6666666666665</v>
+        <f t="shared" si="31"/>
+        <v>8</v>
       </c>
       <c r="H142" s="14"/>
       <c r="I142" s="14"/>
       <c r="J142" s="6"/>
       <c r="K142" s="13">
-        <f t="shared" si="31"/>
-        <v>28.273148148148145</v>
+        <f t="shared" si="33"/>
+        <v>3.802883853588972E-3</v>
       </c>
       <c r="L142" s="13"/>
       <c r="M142" s="13"/>
@@ -4998,25 +5016,26 @@
         <v>53</v>
       </c>
       <c r="B143" s="5">
-        <v>2.2959179999999999E-2</v>
+        <f>AVERAGE(B87,B59,B115)</f>
+        <v>0.67081207666666665</v>
       </c>
       <c r="C143" s="17">
-        <f t="shared" si="29"/>
-        <v>0.6720875833333334</v>
+        <f t="shared" si="30"/>
+        <v>0.67336309333333333</v>
       </c>
       <c r="D143" s="14"/>
       <c r="E143" s="14"/>
       <c r="F143" s="6"/>
       <c r="G143" s="14">
-        <f t="shared" si="30"/>
-        <v>0.64912840333333344</v>
+        <f t="shared" si="31"/>
+        <v>2.5510166666666834E-3</v>
       </c>
       <c r="H143" s="14"/>
       <c r="I143" s="14"/>
       <c r="J143" s="6"/>
       <c r="K143" s="13">
-        <f t="shared" si="31"/>
-        <v>28.273152757778522</v>
+        <f t="shared" si="33"/>
+        <v>3.8028782656134401E-3</v>
       </c>
       <c r="L143" s="13"/>
       <c r="M143" s="13"/>
@@ -5425,6 +5444,20 @@
     <mergeCell ref="C141:E141"/>
     <mergeCell ref="C142:E142"/>
     <mergeCell ref="C143:E143"/>
+    <mergeCell ref="G135:I135"/>
+    <mergeCell ref="B153:D153"/>
+    <mergeCell ref="C122:E122"/>
+    <mergeCell ref="C123:E123"/>
+    <mergeCell ref="C132:E132"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="C118:E118"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="C111:E111"/>
+    <mergeCell ref="C134:E134"/>
+    <mergeCell ref="C135:E135"/>
+    <mergeCell ref="C129:E129"/>
+    <mergeCell ref="B131:E131"/>
     <mergeCell ref="C85:E85"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="C39:E39"/>
@@ -5433,27 +5466,6 @@
     <mergeCell ref="C53:E53"/>
     <mergeCell ref="C40:E40"/>
     <mergeCell ref="C44:E44"/>
-    <mergeCell ref="B153:D153"/>
-    <mergeCell ref="C122:E122"/>
-    <mergeCell ref="C123:E123"/>
-    <mergeCell ref="C132:E132"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="C118:E118"/>
-    <mergeCell ref="B145:E145"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="G135:I135"/>
-    <mergeCell ref="G136:I136"/>
-    <mergeCell ref="G137:I137"/>
-    <mergeCell ref="G138:I138"/>
-    <mergeCell ref="G139:I139"/>
-    <mergeCell ref="C119:E119"/>
-    <mergeCell ref="C120:E120"/>
-    <mergeCell ref="C121:E121"/>
-    <mergeCell ref="C133:E133"/>
-    <mergeCell ref="C134:E134"/>
-    <mergeCell ref="C135:E135"/>
-    <mergeCell ref="C129:E129"/>
-    <mergeCell ref="B131:E131"/>
     <mergeCell ref="G118:I118"/>
     <mergeCell ref="B151:D151"/>
     <mergeCell ref="G132:I132"/>
@@ -5470,6 +5482,14 @@
     <mergeCell ref="G149:I149"/>
     <mergeCell ref="G150:I150"/>
     <mergeCell ref="B150:E150"/>
+    <mergeCell ref="G136:I136"/>
+    <mergeCell ref="G137:I137"/>
+    <mergeCell ref="G138:I138"/>
+    <mergeCell ref="G139:I139"/>
+    <mergeCell ref="C119:E119"/>
+    <mergeCell ref="C120:E120"/>
+    <mergeCell ref="C121:E121"/>
+    <mergeCell ref="C133:E133"/>
     <mergeCell ref="K123:M123"/>
     <mergeCell ref="K124:M124"/>
     <mergeCell ref="K125:M125"/>
@@ -5689,7 +5709,6 @@
     <mergeCell ref="B103:E103"/>
     <mergeCell ref="G103:I103"/>
     <mergeCell ref="K103:M103"/>
-    <mergeCell ref="C111:E111"/>
     <mergeCell ref="G111:I111"/>
     <mergeCell ref="K111:M111"/>
     <mergeCell ref="C112:E112"/>

--- a/FPGA_Performance_Comparison_Red_Small.xlsx
+++ b/FPGA_Performance_Comparison_Red_Small.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/DanielBiswas/Desktop/Documents/University/Year 5/Semester 1/AMME4112/Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBAAA01D-8CE4-C547-95E3-76DC7DE0CB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4E4237-C34E-2243-8324-F594525AACD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="24080" windowHeight="26900" xr2:uid="{49DEC02E-5D37-064F-A7E8-1E1DC7B5FEA1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="78">
   <si>
     <t>FPGA Implementation</t>
   </si>
@@ -248,12 +248,6 @@
     <t>Bit Manipulation Throttled</t>
   </si>
   <si>
-    <t>Confidence Exact Match Pixels (Out Of 3136)</t>
-  </si>
-  <si>
-    <t>Disparity Exact Match Pixels (Out Of 3136)</t>
-  </si>
-  <si>
     <t>Dataset</t>
   </si>
   <si>
@@ -270,6 +264,12 @@
   </si>
   <si>
     <t>Average</t>
+  </si>
+  <si>
+    <t>Confidence Exact Match Pixels (Out Of 2916)</t>
+  </si>
+  <si>
+    <t>Disparity Exact Match Pixels (Out Of 2916)</t>
   </si>
 </sst>
 </file>
@@ -2016,23 +2016,23 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
       <c r="F33" s="6"/>
       <c r="G33" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H33" s="14"/>
       <c r="I33" s="14"/>
       <c r="J33" s="6"/>
       <c r="K33" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
@@ -2043,24 +2043,24 @@
         <v>32</v>
       </c>
       <c r="B34" s="1">
-        <v>0.46843099999999999</v>
+        <v>0.45678999999999997</v>
       </c>
       <c r="C34" s="14">
-        <v>2.0848209999999998</v>
+        <v>2.0373800000000002</v>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="6"/>
       <c r="G34" s="14">
         <f t="shared" ref="G34:G45" si="11">C34-B34</f>
-        <v>1.6163899999999998</v>
+        <v>1.5805900000000002</v>
       </c>
       <c r="H34" s="14"/>
       <c r="I34" s="14"/>
       <c r="J34" s="6"/>
       <c r="K34" s="13">
         <f>G34/B34</f>
-        <v>3.4506469469356209</v>
+        <v>3.4602114757328319</v>
       </c>
       <c r="L34" s="13"/>
       <c r="M34" s="13"/>
@@ -2071,24 +2071,24 @@
         <v>33</v>
       </c>
       <c r="B35" s="1">
-        <v>0.34279300000000001</v>
+        <v>0.33676299999999998</v>
       </c>
       <c r="C35" s="14">
-        <v>0.91198999999999997</v>
+        <v>0.89746199999999998</v>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="6"/>
       <c r="G35" s="14">
         <f t="shared" si="11"/>
-        <v>0.56919699999999995</v>
+        <v>0.56069900000000006</v>
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="14"/>
       <c r="J35" s="6"/>
       <c r="K35" s="13">
         <f t="shared" ref="K35" si="12">G35/B35</f>
-        <v>1.6604685626602642</v>
+        <v>1.6649661631473769</v>
       </c>
       <c r="L35" s="13"/>
       <c r="M35" s="13"/>
@@ -2209,24 +2209,24 @@
         <v>38</v>
       </c>
       <c r="B40" s="1">
-        <v>7.5959820000000002</v>
+        <v>7.5980800000000004</v>
       </c>
       <c r="C40" s="14">
-        <v>7.1970660000000004</v>
+        <v>7.2061039999999998</v>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="6"/>
       <c r="G40" s="14">
         <f t="shared" si="11"/>
-        <v>-0.39891599999999983</v>
+        <v>-0.39197600000000055</v>
       </c>
       <c r="H40" s="14"/>
       <c r="I40" s="14"/>
       <c r="J40" s="6"/>
       <c r="K40" s="13">
         <f t="shared" si="13"/>
-        <v>-5.2516712124910221E-2</v>
+        <v>-5.1588822439353171E-2</v>
       </c>
       <c r="L40" s="13"/>
       <c r="M40" s="13"/>
@@ -2318,27 +2318,27 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B44" s="1">
-        <v>2234</v>
+        <v>2087</v>
       </c>
       <c r="C44" s="14">
-        <v>1454</v>
+        <v>1368</v>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="6"/>
       <c r="G44" s="14">
         <f t="shared" si="11"/>
-        <v>-780</v>
+        <v>-719</v>
       </c>
       <c r="H44" s="14"/>
       <c r="I44" s="14"/>
       <c r="J44" s="6"/>
       <c r="K44" s="13">
         <f t="shared" si="13"/>
-        <v>-0.34914950760966873</v>
+        <v>-0.34451365596550071</v>
       </c>
       <c r="L44" s="13"/>
       <c r="M44" s="13"/>
@@ -2349,24 +2349,24 @@
         <v>42</v>
       </c>
       <c r="B45" s="5">
-        <v>0.71237245000000005</v>
+        <v>0.71570644999999999</v>
       </c>
       <c r="C45" s="15">
-        <v>0.46364796000000003</v>
+        <v>0.46913579999999999</v>
       </c>
       <c r="D45" s="15"/>
       <c r="E45" s="15"/>
       <c r="F45" s="6"/>
       <c r="G45" s="14">
         <f t="shared" si="11"/>
-        <v>-0.24872449000000002</v>
+        <v>-0.24657065</v>
       </c>
       <c r="H45" s="14"/>
       <c r="I45" s="14"/>
       <c r="J45" s="6"/>
       <c r="K45" s="13">
         <f t="shared" si="13"/>
-        <v>-0.34914950739602579</v>
+        <v>-0.34451366199089029</v>
       </c>
       <c r="L45" s="13"/>
       <c r="M45" s="13"/>
@@ -2390,23 +2390,23 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="6"/>
       <c r="G47" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H47" s="14"/>
       <c r="I47" s="14"/>
       <c r="J47" s="6"/>
       <c r="K47" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L47" s="14"/>
       <c r="M47" s="14"/>
@@ -2417,24 +2417,24 @@
         <v>43</v>
       </c>
       <c r="B48" s="1">
-        <v>3.6269130000000001</v>
+        <v>3.5994510000000002</v>
       </c>
       <c r="C48" s="14">
-        <v>3.3778700000000002</v>
+        <v>3.3590529999999998</v>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="6"/>
       <c r="G48" s="14">
         <f t="shared" ref="G48:G59" si="14">C48-B48</f>
-        <v>-0.2490429999999999</v>
+        <v>-0.24039800000000033</v>
       </c>
       <c r="H48" s="14"/>
       <c r="I48" s="14"/>
       <c r="J48" s="6"/>
       <c r="K48" s="13">
         <f>G48/B48</f>
-        <v>-6.866528091520252E-2</v>
+        <v>-6.6787407301835841E-2</v>
       </c>
       <c r="L48" s="13"/>
       <c r="M48" s="13"/>
@@ -2445,24 +2445,24 @@
         <v>44</v>
       </c>
       <c r="B49" s="1">
-        <v>1.8316330000000001</v>
+        <v>1.824417</v>
       </c>
       <c r="C49" s="14">
-        <v>1.756696</v>
+        <v>1.7520579999999999</v>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="6"/>
       <c r="G49" s="14">
         <f t="shared" si="14"/>
-        <v>-7.4937000000000031E-2</v>
+        <v>-7.2359000000000062E-2</v>
       </c>
       <c r="H49" s="14"/>
       <c r="I49" s="14"/>
       <c r="J49" s="6"/>
       <c r="K49" s="13">
         <f t="shared" ref="K49:K59" si="15">G49/B49</f>
-        <v>-4.0912671916262716E-2</v>
+        <v>-3.9661437050849707E-2</v>
       </c>
       <c r="L49" s="13"/>
       <c r="M49" s="13"/>
@@ -2585,24 +2585,24 @@
         <v>49</v>
       </c>
       <c r="B54" s="1">
-        <v>6.7987880000000001</v>
+        <v>6.8031550000000003</v>
       </c>
       <c r="C54" s="14">
-        <v>6.8118619999999996</v>
+        <v>6.8148150000000003</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
       <c r="F54" s="6"/>
       <c r="G54" s="14">
         <f t="shared" si="14"/>
-        <v>1.3073999999999586E-2</v>
+        <v>1.1660000000000004E-2</v>
       </c>
       <c r="H54" s="14"/>
       <c r="I54" s="14"/>
       <c r="J54" s="6"/>
       <c r="K54" s="13">
         <f t="shared" si="15"/>
-        <v>1.9229898034766764E-3</v>
+        <v>1.713910678207391E-3</v>
       </c>
       <c r="L54" s="13"/>
       <c r="M54" s="13"/>
@@ -2694,27 +2694,27 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B58" s="1">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C58" s="14">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D58" s="14"/>
       <c r="E58" s="14"/>
       <c r="F58" s="6"/>
       <c r="G58" s="14">
         <f t="shared" si="14"/>
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H58" s="14"/>
       <c r="I58" s="14"/>
       <c r="J58" s="6"/>
       <c r="K58" s="13">
         <f t="shared" si="15"/>
-        <v>0.30985915492957744</v>
+        <v>0.26865671641791045</v>
       </c>
       <c r="L58" s="13"/>
       <c r="M58" s="13"/>
@@ -2725,24 +2725,24 @@
         <v>53</v>
       </c>
       <c r="B59" s="5">
-        <v>2.264031E-2</v>
+        <v>2.2976679999999999E-2</v>
       </c>
       <c r="C59" s="13">
-        <v>2.9655609999999999E-2</v>
+        <v>2.9149520000000002E-2</v>
       </c>
       <c r="D59" s="13"/>
       <c r="E59" s="13"/>
       <c r="F59" s="6"/>
       <c r="G59" s="14">
         <f t="shared" si="14"/>
-        <v>7.0152999999999986E-3</v>
+        <v>6.1728400000000024E-3</v>
       </c>
       <c r="H59" s="14"/>
       <c r="I59" s="14"/>
       <c r="J59" s="6"/>
       <c r="K59" s="13">
         <f t="shared" si="15"/>
-        <v>0.30985883143826204</v>
+        <v>0.26865674240142623</v>
       </c>
       <c r="L59" s="13"/>
       <c r="M59" s="13"/>
@@ -2766,23 +2766,23 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C61" s="14"/>
       <c r="D61" s="14"/>
       <c r="E61" s="14"/>
       <c r="F61" s="6"/>
       <c r="G61" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H61" s="14"/>
       <c r="I61" s="14"/>
       <c r="J61" s="6"/>
       <c r="K61" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L61" s="14"/>
       <c r="M61" s="14"/>
@@ -2793,24 +2793,24 @@
         <v>32</v>
       </c>
       <c r="B62" s="1">
-        <v>0.72385200000000005</v>
+        <v>0.72805200000000003</v>
       </c>
       <c r="C62" s="14">
-        <v>2.6575259999999998</v>
+        <v>2.6803840000000001</v>
       </c>
       <c r="D62" s="14"/>
       <c r="E62" s="14"/>
       <c r="F62" s="6"/>
       <c r="G62" s="14">
         <f t="shared" ref="G62:G73" si="16">C62-B62</f>
-        <v>1.9336739999999999</v>
+        <v>1.9523320000000002</v>
       </c>
       <c r="H62" s="14"/>
       <c r="I62" s="14"/>
       <c r="J62" s="6"/>
       <c r="K62" s="13">
         <f>G62/B62</f>
-        <v>2.6713665224382881</v>
+        <v>2.6815831836187525</v>
       </c>
       <c r="L62" s="13"/>
       <c r="M62" s="13"/>
@@ -2821,24 +2821,24 @@
         <v>33</v>
       </c>
       <c r="B63" s="1">
-        <v>0.54081599999999996</v>
+        <v>0.54492499999999999</v>
       </c>
       <c r="C63" s="14">
-        <v>1.2959179999999999</v>
+        <v>1.303841</v>
       </c>
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
       <c r="F63" s="6"/>
       <c r="G63" s="14">
         <f t="shared" si="16"/>
-        <v>0.75510199999999994</v>
+        <v>0.75891600000000004</v>
       </c>
       <c r="H63" s="14"/>
       <c r="I63" s="14"/>
       <c r="J63" s="6"/>
       <c r="K63" s="13">
         <f>G63/B63</f>
-        <v>1.3962271826277328</v>
+        <v>1.3926980777171172</v>
       </c>
       <c r="L63" s="13"/>
       <c r="M63" s="13"/>
@@ -2959,24 +2959,24 @@
         <v>38</v>
       </c>
       <c r="B68" s="1">
-        <v>7.3896680000000003</v>
+        <v>7.3806580000000004</v>
       </c>
       <c r="C68" s="14">
-        <v>6.7755099999999997</v>
+        <v>6.7644029999999997</v>
       </c>
       <c r="D68" s="14"/>
       <c r="E68" s="14"/>
       <c r="F68" s="6"/>
       <c r="G68" s="14">
         <f t="shared" si="16"/>
-        <v>-0.61415800000000065</v>
+        <v>-0.61625500000000066</v>
       </c>
       <c r="H68" s="14"/>
       <c r="I68" s="14"/>
       <c r="J68" s="6"/>
       <c r="K68" s="13">
         <f t="shared" si="17"/>
-        <v>-8.3110364362783365E-2</v>
+        <v>-8.349594304464461E-2</v>
       </c>
       <c r="L68" s="13"/>
       <c r="M68" s="13"/>
@@ -3068,27 +3068,27 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B72" s="1">
-        <v>1687</v>
+        <v>1554</v>
       </c>
       <c r="C72" s="14">
-        <v>517</v>
+        <v>472</v>
       </c>
       <c r="D72" s="14"/>
       <c r="E72" s="14"/>
       <c r="F72" s="6"/>
       <c r="G72" s="14">
         <f t="shared" si="16"/>
-        <v>-1170</v>
+        <v>-1082</v>
       </c>
       <c r="H72" s="14"/>
       <c r="I72" s="14"/>
       <c r="J72" s="6"/>
       <c r="K72" s="13">
         <f t="shared" si="17"/>
-        <v>-0.69353882631890929</v>
+        <v>-0.69626769626769625</v>
       </c>
       <c r="L72" s="13"/>
       <c r="M72" s="13"/>
@@ -3099,24 +3099,24 @@
         <v>42</v>
       </c>
       <c r="B73" s="5">
-        <v>0.53794642999999998</v>
+        <v>0.53292181000000005</v>
       </c>
       <c r="C73" s="15">
-        <v>0.16485969</v>
+        <v>0.16186556999999999</v>
       </c>
       <c r="D73" s="15"/>
       <c r="E73" s="15"/>
       <c r="F73" s="6"/>
       <c r="G73" s="14">
         <f t="shared" si="16"/>
-        <v>-0.37308673999999997</v>
+        <v>-0.37105624000000004</v>
       </c>
       <c r="H73" s="14"/>
       <c r="I73" s="14"/>
       <c r="J73" s="6"/>
       <c r="K73" s="13">
         <f t="shared" si="17"/>
-        <v>-0.69353883434080976</v>
+        <v>-0.69626769450475301</v>
       </c>
       <c r="L73" s="13"/>
       <c r="M73" s="13"/>
@@ -3140,23 +3140,23 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C75" s="14"/>
       <c r="D75" s="14"/>
       <c r="E75" s="14"/>
       <c r="F75" s="6"/>
       <c r="G75" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H75" s="14"/>
       <c r="I75" s="14"/>
       <c r="J75" s="6"/>
       <c r="K75" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L75" s="14"/>
       <c r="M75" s="14"/>
@@ -3167,7 +3167,7 @@
         <v>43</v>
       </c>
       <c r="B76" s="1">
-        <v>3.19E-4</v>
+        <v>0</v>
       </c>
       <c r="C76" s="14">
         <v>0</v>
@@ -3177,14 +3177,13 @@
       <c r="F76" s="6"/>
       <c r="G76" s="14">
         <f t="shared" ref="G76:G87" si="18">C76-B76</f>
-        <v>-3.19E-4</v>
+        <v>0</v>
       </c>
       <c r="H76" s="14"/>
       <c r="I76" s="14"/>
       <c r="J76" s="6"/>
       <c r="K76" s="13">
-        <f t="shared" ref="K76:K87" si="19">G76/B76</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="13"/>
       <c r="M76" s="13"/>
@@ -3195,7 +3194,7 @@
         <v>44</v>
       </c>
       <c r="B77" s="1">
-        <v>3.19E-4</v>
+        <v>0</v>
       </c>
       <c r="C77" s="14">
         <v>0</v>
@@ -3205,14 +3204,13 @@
       <c r="F77" s="6"/>
       <c r="G77" s="14">
         <f t="shared" si="18"/>
-        <v>-3.19E-4</v>
+        <v>0</v>
       </c>
       <c r="H77" s="14"/>
       <c r="I77" s="14"/>
       <c r="J77" s="6"/>
       <c r="K77" s="13">
-        <f t="shared" si="19"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="13"/>
       <c r="M77" s="13"/>
@@ -3304,7 +3302,7 @@
         <v>48</v>
       </c>
       <c r="B81" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81" s="14">
         <v>8</v>
@@ -3314,14 +3312,13 @@
       <c r="F81" s="6"/>
       <c r="G81" s="14">
         <f t="shared" si="18"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H81" s="14"/>
       <c r="I81" s="14"/>
       <c r="J81" s="6"/>
       <c r="K81" s="13">
-        <f t="shared" si="19"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L81" s="13"/>
       <c r="M81" s="13"/>
@@ -3332,7 +3329,7 @@
         <v>49</v>
       </c>
       <c r="B82" s="1">
-        <v>7.9996809999999998</v>
+        <v>8</v>
       </c>
       <c r="C82" s="14">
         <v>8</v>
@@ -3342,14 +3339,14 @@
       <c r="F82" s="6"/>
       <c r="G82" s="14">
         <f t="shared" si="18"/>
-        <v>3.1900000000018025E-4</v>
+        <v>0</v>
       </c>
       <c r="H82" s="14"/>
       <c r="I82" s="14"/>
       <c r="J82" s="6"/>
       <c r="K82" s="13">
-        <f t="shared" si="19"/>
-        <v>3.9876590079051935E-5</v>
+        <f t="shared" ref="K82:K87" si="19">G82/B82</f>
+        <v>0</v>
       </c>
       <c r="L82" s="13"/>
       <c r="M82" s="13"/>
@@ -3416,7 +3413,7 @@
         <v>52</v>
       </c>
       <c r="B85" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C85" s="14">
         <v>8</v>
@@ -3426,14 +3423,14 @@
       <c r="F85" s="6"/>
       <c r="G85" s="14">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" s="14"/>
       <c r="I85" s="14"/>
       <c r="J85" s="6"/>
       <c r="K85" s="13">
         <f t="shared" si="19"/>
-        <v>0.14285714285714285</v>
+        <v>0</v>
       </c>
       <c r="L85" s="13"/>
       <c r="M85" s="13"/>
@@ -3441,27 +3438,27 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B86" s="1">
-        <v>3135</v>
+        <v>2916</v>
       </c>
       <c r="C86" s="14">
-        <v>3136</v>
+        <v>2916</v>
       </c>
       <c r="D86" s="14"/>
       <c r="E86" s="14"/>
       <c r="F86" s="6"/>
       <c r="G86" s="14">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" s="14"/>
       <c r="I86" s="14"/>
       <c r="J86" s="6"/>
       <c r="K86" s="13">
         <f t="shared" si="19"/>
-        <v>3.1897926634768739E-4</v>
+        <v>0</v>
       </c>
       <c r="L86" s="13"/>
       <c r="M86" s="13"/>
@@ -3472,7 +3469,7 @@
         <v>53</v>
       </c>
       <c r="B87" s="5">
-        <v>0.99968111999999998</v>
+        <v>1</v>
       </c>
       <c r="C87" s="13">
         <v>1</v>
@@ -3482,14 +3479,14 @@
       <c r="F87" s="6"/>
       <c r="G87" s="14">
         <f t="shared" si="18"/>
-        <v>3.1888000000002137E-4</v>
+        <v>0</v>
       </c>
       <c r="H87" s="14"/>
       <c r="I87" s="14"/>
       <c r="J87" s="6"/>
       <c r="K87" s="13">
         <f t="shared" si="19"/>
-        <v>3.1898171688990321E-4</v>
+        <v>0</v>
       </c>
       <c r="L87" s="13"/>
       <c r="M87" s="13"/>
@@ -3513,23 +3510,23 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C89" s="14"/>
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
       <c r="F89" s="6"/>
       <c r="G89" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H89" s="14"/>
       <c r="I89" s="14"/>
       <c r="J89" s="6"/>
       <c r="K89" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L89" s="14"/>
       <c r="M89" s="14"/>
@@ -3540,24 +3537,24 @@
         <v>32</v>
       </c>
       <c r="B90" s="1">
-        <v>0.18909400000000001</v>
+        <v>0.18244199999999999</v>
       </c>
       <c r="C90" s="14">
-        <v>0.93590600000000002</v>
+        <v>0.94170100000000001</v>
       </c>
       <c r="D90" s="14"/>
       <c r="E90" s="14"/>
       <c r="F90" s="6"/>
       <c r="G90" s="14">
         <f t="shared" ref="G90:G101" si="20">C90-B90</f>
-        <v>0.74681200000000003</v>
+        <v>0.75925900000000002</v>
       </c>
       <c r="H90" s="14"/>
       <c r="I90" s="14"/>
       <c r="J90" s="6"/>
       <c r="K90" s="13">
         <f>G90/B90</f>
-        <v>3.9494219806022399</v>
+        <v>4.1616458929413183</v>
       </c>
       <c r="L90" s="13"/>
       <c r="M90" s="13"/>
@@ -3568,24 +3565,24 @@
         <v>33</v>
       </c>
       <c r="B91" s="1">
-        <v>0.13361000000000001</v>
+        <v>0.12825800000000001</v>
       </c>
       <c r="C91" s="14">
-        <v>0.419962</v>
+        <v>0.42043900000000001</v>
       </c>
       <c r="D91" s="14"/>
       <c r="E91" s="14"/>
       <c r="F91" s="6"/>
       <c r="G91" s="14">
         <f t="shared" si="20"/>
-        <v>0.286352</v>
+        <v>0.29218100000000002</v>
       </c>
       <c r="H91" s="14"/>
       <c r="I91" s="14"/>
       <c r="J91" s="6"/>
       <c r="K91" s="13">
         <f t="shared" ref="K91" si="21">G91/B91</f>
-        <v>2.1431928747848215</v>
+        <v>2.2780723229740056</v>
       </c>
       <c r="L91" s="13"/>
       <c r="M91" s="13"/>
@@ -3611,8 +3608,8 @@
       <c r="H92" s="14"/>
       <c r="I92" s="14"/>
       <c r="J92" s="6"/>
-      <c r="K92" s="13" t="s">
-        <v>54</v>
+      <c r="K92" s="13">
+        <v>0</v>
       </c>
       <c r="L92" s="13"/>
       <c r="M92" s="13"/>
@@ -3638,8 +3635,8 @@
       <c r="H93" s="14"/>
       <c r="I93" s="14"/>
       <c r="J93" s="6"/>
-      <c r="K93" s="13" t="s">
-        <v>54</v>
+      <c r="K93" s="13">
+        <v>0</v>
       </c>
       <c r="L93" s="13"/>
       <c r="M93" s="13"/>
@@ -3706,24 +3703,24 @@
         <v>38</v>
       </c>
       <c r="B96" s="1">
-        <v>7.8580990000000002</v>
+        <v>7.8655689999999998</v>
       </c>
       <c r="C96" s="14">
-        <v>7.6584820000000002</v>
+        <v>7.659465</v>
       </c>
       <c r="D96" s="14"/>
       <c r="E96" s="14"/>
       <c r="F96" s="6"/>
       <c r="G96" s="14">
         <f t="shared" si="20"/>
-        <v>-0.19961699999999993</v>
+        <v>-0.20610399999999984</v>
       </c>
       <c r="H96" s="14"/>
       <c r="I96" s="14"/>
       <c r="J96" s="6"/>
       <c r="K96" s="13">
         <f t="shared" si="22"/>
-        <v>-2.5402708721282325E-2</v>
+        <v>-2.6203317267956057E-2</v>
       </c>
       <c r="L96" s="13"/>
       <c r="M96" s="13"/>
@@ -3815,27 +3812,27 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B100" s="1">
-        <v>2792</v>
+        <v>2610</v>
       </c>
       <c r="C100" s="14">
-        <v>2321</v>
+        <v>2162</v>
       </c>
       <c r="D100" s="14"/>
       <c r="E100" s="14"/>
       <c r="F100" s="6"/>
       <c r="G100" s="14">
         <f t="shared" si="20"/>
-        <v>-471</v>
+        <v>-448</v>
       </c>
       <c r="H100" s="14"/>
       <c r="I100" s="14"/>
       <c r="J100" s="6"/>
       <c r="K100" s="13">
         <f t="shared" si="22"/>
-        <v>-0.16869627507163323</v>
+        <v>-0.17164750957854405</v>
       </c>
       <c r="L100" s="13"/>
       <c r="M100" s="13"/>
@@ -3846,24 +3843,24 @@
         <v>42</v>
       </c>
       <c r="B101" s="5">
-        <v>0.89030611999999998</v>
+        <v>0.89506173</v>
       </c>
       <c r="C101" s="15">
-        <v>0.74011479999999996</v>
+        <v>0.74142660999999999</v>
       </c>
       <c r="D101" s="15"/>
       <c r="E101" s="15"/>
       <c r="F101" s="6"/>
       <c r="G101" s="14">
         <f t="shared" si="20"/>
-        <v>-0.15019132000000002</v>
+        <v>-0.15363512000000001</v>
       </c>
       <c r="H101" s="14"/>
       <c r="I101" s="14"/>
       <c r="J101" s="6"/>
       <c r="K101" s="13">
         <f t="shared" si="22"/>
-        <v>-0.1686962682004253</v>
+        <v>-0.17164751307152862</v>
       </c>
       <c r="L101" s="13"/>
       <c r="M101" s="13"/>
@@ -3887,23 +3884,23 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B103" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C103" s="14"/>
       <c r="D103" s="14"/>
       <c r="E103" s="14"/>
       <c r="F103" s="6"/>
       <c r="G103" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H103" s="14"/>
       <c r="I103" s="14"/>
       <c r="J103" s="6"/>
       <c r="K103" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L103" s="14"/>
       <c r="M103" s="14"/>
@@ -3914,24 +3911,24 @@
         <v>43</v>
       </c>
       <c r="B104" s="1">
-        <v>1.3712E-2</v>
+        <v>1.1317000000000001E-2</v>
       </c>
       <c r="C104" s="14">
-        <v>1.3393E-2</v>
+        <v>1.0973999999999999E-2</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
       <c r="F104" s="6"/>
       <c r="G104" s="14">
         <f t="shared" ref="G104:G115" si="23">C104-B104</f>
-        <v>-3.1899999999999984E-4</v>
+        <v>-3.4300000000000129E-4</v>
       </c>
       <c r="H104" s="14"/>
       <c r="I104" s="14"/>
       <c r="J104" s="6"/>
       <c r="K104" s="13">
         <f>G104/B104</f>
-        <v>-2.3264294049008157E-2</v>
+        <v>-3.0308385614562276E-2</v>
       </c>
       <c r="L104" s="13"/>
       <c r="M104" s="13"/>
@@ -3942,24 +3939,24 @@
         <v>44</v>
       </c>
       <c r="B105" s="1">
-        <v>1.1161000000000001E-2</v>
+        <v>9.2589999999999999E-3</v>
       </c>
       <c r="C105" s="14">
-        <v>1.0841999999999999E-2</v>
+        <v>8.9160000000000003E-3</v>
       </c>
       <c r="D105" s="14"/>
       <c r="E105" s="14"/>
       <c r="F105" s="6"/>
       <c r="G105" s="14">
         <f t="shared" si="23"/>
-        <v>-3.1900000000000157E-4</v>
+        <v>-3.4299999999999956E-4</v>
       </c>
       <c r="H105" s="14"/>
       <c r="I105" s="14"/>
       <c r="J105" s="6"/>
       <c r="K105" s="13">
         <f t="shared" ref="K105:K115" si="24">G105/B105</f>
-        <v>-2.858166830929142E-2</v>
+        <v>-3.7045037261043259E-2</v>
       </c>
       <c r="L105" s="13"/>
       <c r="M105" s="13"/>
@@ -4080,24 +4077,24 @@
         <v>49</v>
       </c>
       <c r="B110" s="1">
-        <v>7.9901150000000003</v>
+        <v>7.9917699999999998</v>
       </c>
       <c r="C110" s="14">
-        <v>7.9904339999999996</v>
+        <v>7.9921119999999997</v>
       </c>
       <c r="D110" s="14"/>
       <c r="E110" s="14"/>
       <c r="F110" s="6"/>
       <c r="G110" s="14">
         <f t="shared" si="23"/>
-        <v>3.1899999999929207E-4</v>
+        <v>3.4199999999984243E-4</v>
       </c>
       <c r="H110" s="14"/>
       <c r="I110" s="14"/>
       <c r="J110" s="6"/>
       <c r="K110" s="13">
         <f t="shared" si="24"/>
-        <v>3.9924331502023693E-5</v>
+        <v>4.2794024352532974E-5</v>
       </c>
       <c r="L110" s="13"/>
       <c r="M110" s="13"/>
@@ -4189,13 +4186,13 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B114" s="1">
-        <v>3105</v>
+        <v>2892</v>
       </c>
       <c r="C114" s="14">
-        <v>3106</v>
+        <v>2893</v>
       </c>
       <c r="D114" s="14"/>
       <c r="E114" s="14"/>
@@ -4209,7 +4206,7 @@
       <c r="J114" s="6"/>
       <c r="K114" s="13">
         <f t="shared" si="24"/>
-        <v>3.2206119162640903E-4</v>
+        <v>3.4578146611341634E-4</v>
       </c>
       <c r="L114" s="13"/>
       <c r="M114" s="13"/>
@@ -4220,24 +4217,24 @@
         <v>53</v>
       </c>
       <c r="B115" s="5">
-        <v>0.99011479999999996</v>
+        <v>0.99176955</v>
       </c>
       <c r="C115" s="13">
-        <v>0.99043367000000004</v>
+        <v>0.99211247999999996</v>
       </c>
       <c r="D115" s="13"/>
       <c r="E115" s="13"/>
       <c r="F115" s="6"/>
       <c r="G115" s="14">
         <f t="shared" si="23"/>
-        <v>3.1887000000008214E-4</v>
+        <v>3.4292999999996354E-4</v>
       </c>
       <c r="H115" s="14"/>
       <c r="I115" s="14"/>
       <c r="J115" s="6"/>
       <c r="K115" s="13">
         <f t="shared" si="24"/>
-        <v>3.2205356388984605E-4</v>
+        <v>3.4577589118355522E-4</v>
       </c>
       <c r="L115" s="13"/>
       <c r="M115" s="13"/>
@@ -4261,23 +4258,23 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B117" s="14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C117" s="14"/>
       <c r="D117" s="14"/>
       <c r="E117" s="14"/>
       <c r="F117" s="6"/>
       <c r="G117" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H117" s="14"/>
       <c r="I117" s="14"/>
       <c r="J117" s="6"/>
       <c r="K117" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L117" s="14"/>
       <c r="M117" s="14"/>
@@ -4289,25 +4286,25 @@
       </c>
       <c r="B118" s="1">
         <f>AVERAGE(B62,B34,B90)</f>
-        <v>0.46045900000000001</v>
+        <v>0.4557613333333333</v>
       </c>
       <c r="C118" s="14">
         <f>AVERAGE(C62,C34,C90)</f>
-        <v>1.8927509999999999</v>
+        <v>1.8864883333333335</v>
       </c>
       <c r="D118" s="14"/>
       <c r="E118" s="14"/>
       <c r="F118" s="6"/>
       <c r="G118" s="14">
         <f t="shared" ref="G118" si="25">C118-B118</f>
-        <v>1.4322919999999999</v>
+        <v>1.4307270000000003</v>
       </c>
       <c r="H118" s="14"/>
       <c r="I118" s="14"/>
       <c r="J118" s="6"/>
       <c r="K118" s="13">
         <f>G118/B118</f>
-        <v>3.110574448539392</v>
+        <v>3.139202243279378</v>
       </c>
       <c r="L118" s="13"/>
       <c r="M118" s="13"/>
@@ -4319,25 +4316,25 @@
       </c>
       <c r="B119" s="1">
         <f t="shared" ref="B119:B128" si="26">AVERAGE(B63,B35,B91)</f>
-        <v>0.33907299999999996</v>
+        <v>0.33664866666666665</v>
       </c>
       <c r="C119" s="14">
         <f t="shared" ref="C119:C129" si="27">AVERAGE(C63,C35,C91)</f>
-        <v>0.87595666666666661</v>
+        <v>0.87391400000000008</v>
       </c>
       <c r="D119" s="14"/>
       <c r="E119" s="14"/>
       <c r="F119" s="6"/>
       <c r="G119" s="14">
         <f t="shared" ref="G119:G129" si="28">C119-B119</f>
-        <v>0.53688366666666665</v>
+        <v>0.53726533333333348</v>
       </c>
       <c r="H119" s="14"/>
       <c r="I119" s="14"/>
       <c r="J119" s="6"/>
       <c r="K119" s="13">
         <f t="shared" ref="K119:K129" si="29">G119/B119</f>
-        <v>1.5833866650151049</v>
+        <v>1.5959229503359591</v>
       </c>
       <c r="L119" s="13"/>
       <c r="M119" s="13"/>
@@ -4467,25 +4464,25 @@
       </c>
       <c r="B124" s="1">
         <f t="shared" si="26"/>
-        <v>7.6145829999999997</v>
+        <v>7.6147689999999999</v>
       </c>
       <c r="C124" s="14">
         <f t="shared" si="27"/>
-        <v>7.2103526666666662</v>
+        <v>7.2099906666666662</v>
       </c>
       <c r="D124" s="14"/>
       <c r="E124" s="14"/>
       <c r="F124" s="6"/>
       <c r="G124" s="14">
         <f t="shared" si="28"/>
-        <v>-0.40423033333333347</v>
+        <v>-0.40477833333333368</v>
       </c>
       <c r="H124" s="14"/>
       <c r="I124" s="14"/>
       <c r="J124" s="6"/>
       <c r="K124" s="13">
         <f t="shared" si="29"/>
-        <v>-5.3086338849196793E-2</v>
+        <v>-5.3157007564291668E-2</v>
       </c>
       <c r="L124" s="13"/>
       <c r="M124" s="13"/>
@@ -4583,29 +4580,29 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B128" s="1">
         <f t="shared" si="26"/>
-        <v>2237.6666666666665</v>
+        <v>2083.6666666666665</v>
       </c>
       <c r="C128" s="14">
         <f t="shared" si="27"/>
-        <v>1430.6666666666667</v>
+        <v>1334</v>
       </c>
       <c r="D128" s="14"/>
       <c r="E128" s="14"/>
       <c r="F128" s="6"/>
       <c r="G128" s="14">
         <f t="shared" si="28"/>
-        <v>-806.99999999999977</v>
+        <v>-749.66666666666652</v>
       </c>
       <c r="H128" s="14"/>
       <c r="I128" s="14"/>
       <c r="J128" s="6"/>
       <c r="K128" s="13">
         <f t="shared" si="29"/>
-        <v>-0.3606435274839862</v>
+        <v>-0.35978243481043026</v>
       </c>
       <c r="L128" s="13"/>
       <c r="M128" s="13"/>
@@ -4617,25 +4614,25 @@
       </c>
       <c r="B129" s="5">
         <f>AVERAGE(B73,B45,B101)</f>
-        <v>0.71354166666666663</v>
+        <v>0.71456332999999994</v>
       </c>
       <c r="C129" s="17">
         <f t="shared" si="27"/>
-        <v>0.45620748333333333</v>
+        <v>0.45747599333333328</v>
       </c>
       <c r="D129" s="14"/>
       <c r="E129" s="14"/>
       <c r="F129" s="6"/>
       <c r="G129" s="14">
         <f t="shared" si="28"/>
-        <v>-0.2573341833333333</v>
+        <v>-0.25708733666666667</v>
       </c>
       <c r="H129" s="14"/>
       <c r="I129" s="14"/>
       <c r="J129" s="6"/>
       <c r="K129" s="13">
         <f t="shared" si="29"/>
-        <v>-0.36064352700729924</v>
+        <v>-0.3597824375715819</v>
       </c>
       <c r="L129" s="13"/>
       <c r="M129" s="13"/>
@@ -4659,23 +4656,23 @@
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B131" s="14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C131" s="14"/>
       <c r="D131" s="14"/>
       <c r="E131" s="14"/>
       <c r="F131" s="6"/>
       <c r="G131" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H131" s="14"/>
       <c r="I131" s="14"/>
       <c r="J131" s="6"/>
       <c r="K131" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L131" s="14"/>
       <c r="M131" s="14"/>
@@ -4687,25 +4684,25 @@
       </c>
       <c r="B132" s="1">
         <f>AVERAGE(B76,B48,B104)</f>
-        <v>1.2136480000000001</v>
+        <v>1.2035893333333334</v>
       </c>
       <c r="C132" s="14">
         <f t="shared" ref="C132:C143" si="30">AVERAGE(C76,C48,C104)</f>
-        <v>1.1304210000000001</v>
+        <v>1.1233423333333332</v>
       </c>
       <c r="D132" s="14"/>
       <c r="E132" s="14"/>
       <c r="F132" s="6"/>
       <c r="G132" s="14">
         <f t="shared" ref="G132:G143" si="31">C132-B132</f>
-        <v>-8.322699999999994E-2</v>
+        <v>-8.0247000000000179E-2</v>
       </c>
       <c r="H132" s="14"/>
       <c r="I132" s="14"/>
       <c r="J132" s="6"/>
       <c r="K132" s="13">
         <f>G132/B132</f>
-        <v>-6.8575896800390182E-2</v>
+        <v>-6.6673073429253979E-2</v>
       </c>
       <c r="L132" s="13"/>
       <c r="M132" s="13"/>
@@ -4717,25 +4714,25 @@
       </c>
       <c r="B133" s="1">
         <f t="shared" ref="B133:B142" si="32">AVERAGE(B77,B49,B105)</f>
-        <v>0.614371</v>
+        <v>0.61122533333333329</v>
       </c>
       <c r="C133" s="14">
         <f t="shared" si="30"/>
-        <v>0.58917933333333339</v>
+        <v>0.58699133333333331</v>
       </c>
       <c r="D133" s="14"/>
       <c r="E133" s="14"/>
       <c r="F133" s="6"/>
       <c r="G133" s="14">
         <f t="shared" si="31"/>
-        <v>-2.5191666666666612E-2</v>
+        <v>-2.4233999999999978E-2</v>
       </c>
       <c r="H133" s="14"/>
       <c r="I133" s="14"/>
       <c r="J133" s="6"/>
       <c r="K133" s="13">
         <f t="shared" ref="K133:K143" si="33">G133/B133</f>
-        <v>-4.1003997041960984E-2</v>
+        <v>-3.9648225749805276E-2</v>
       </c>
       <c r="L133" s="13"/>
       <c r="M133" s="13"/>
@@ -4837,7 +4834,7 @@
       </c>
       <c r="B137" s="1">
         <f t="shared" si="32"/>
-        <v>2</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="C137" s="14">
         <f t="shared" si="30"/>
@@ -4848,14 +4845,14 @@
       <c r="F137" s="6"/>
       <c r="G137" s="14">
         <f t="shared" si="31"/>
-        <v>1.6666666666666665</v>
+        <v>1.9999999999999998</v>
       </c>
       <c r="H137" s="14"/>
       <c r="I137" s="14"/>
       <c r="J137" s="6"/>
       <c r="K137" s="13">
         <f t="shared" si="33"/>
-        <v>0.83333333333333326</v>
+        <v>1.1999999999999997</v>
       </c>
       <c r="L137" s="13"/>
       <c r="M137" s="13"/>
@@ -4867,25 +4864,25 @@
       </c>
       <c r="B138" s="1">
         <f t="shared" si="32"/>
-        <v>7.5961946666666664</v>
+        <v>7.5983083333333328</v>
       </c>
       <c r="C138" s="14">
         <f t="shared" si="30"/>
-        <v>7.6007653333333325</v>
+        <v>7.6023089999999991</v>
       </c>
       <c r="D138" s="14"/>
       <c r="E138" s="14"/>
       <c r="F138" s="6"/>
       <c r="G138" s="14">
         <f t="shared" si="31"/>
-        <v>4.5706666666660567E-3</v>
+        <v>4.0006666666663193E-3</v>
       </c>
       <c r="H138" s="14"/>
       <c r="I138" s="14"/>
       <c r="J138" s="6"/>
       <c r="K138" s="13">
         <f t="shared" si="33"/>
-        <v>6.0170478341252669E-4</v>
+        <v>5.2652070581495482E-4</v>
       </c>
       <c r="L138" s="13"/>
       <c r="M138" s="13"/>
@@ -4957,7 +4954,7 @@
       </c>
       <c r="B141" s="1">
         <f t="shared" si="32"/>
-        <v>6.333333333333333</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="C141" s="14">
         <f t="shared" si="30"/>
@@ -4968,14 +4965,14 @@
       <c r="F141" s="6"/>
       <c r="G141" s="14">
         <f t="shared" si="31"/>
-        <v>0.33333333333333393</v>
+        <v>0</v>
       </c>
       <c r="H141" s="14"/>
       <c r="I141" s="14"/>
       <c r="J141" s="6"/>
       <c r="K141" s="13">
         <f t="shared" si="33"/>
-        <v>5.2631578947368515E-2</v>
+        <v>0</v>
       </c>
       <c r="L141" s="13"/>
       <c r="M141" s="13"/>
@@ -4983,29 +4980,29 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B142" s="1">
         <f t="shared" si="32"/>
-        <v>2103.6666666666665</v>
+        <v>1958.3333333333333</v>
       </c>
       <c r="C142" s="14">
         <f t="shared" si="30"/>
-        <v>2111.6666666666665</v>
+        <v>1964.6666666666667</v>
       </c>
       <c r="D142" s="14"/>
       <c r="E142" s="14"/>
       <c r="F142" s="6"/>
       <c r="G142" s="14">
         <f t="shared" si="31"/>
-        <v>8</v>
+        <v>6.3333333333334849</v>
       </c>
       <c r="H142" s="14"/>
       <c r="I142" s="14"/>
       <c r="J142" s="6"/>
       <c r="K142" s="13">
         <f t="shared" si="33"/>
-        <v>3.802883853588972E-3</v>
+        <v>3.2340425531915667E-3</v>
       </c>
       <c r="L142" s="13"/>
       <c r="M142" s="13"/>
@@ -5017,25 +5014,25 @@
       </c>
       <c r="B143" s="5">
         <f>AVERAGE(B87,B59,B115)</f>
-        <v>0.67081207666666665</v>
+        <v>0.67158207666666669</v>
       </c>
       <c r="C143" s="17">
         <f t="shared" si="30"/>
-        <v>0.67336309333333333</v>
+        <v>0.67375400000000008</v>
       </c>
       <c r="D143" s="14"/>
       <c r="E143" s="14"/>
       <c r="F143" s="6"/>
       <c r="G143" s="14">
         <f t="shared" si="31"/>
-        <v>2.5510166666666834E-3</v>
+        <v>2.1719233333333809E-3</v>
       </c>
       <c r="H143" s="14"/>
       <c r="I143" s="14"/>
       <c r="J143" s="6"/>
       <c r="K143" s="13">
         <f t="shared" si="33"/>
-        <v>3.8028782656134401E-3</v>
+        <v>3.2340400507909835E-3</v>
       </c>
       <c r="L143" s="13"/>
       <c r="M143" s="13"/>
@@ -5421,6 +5418,7 @@
     <mergeCell ref="K152:M152"/>
     <mergeCell ref="K151:L151"/>
     <mergeCell ref="K153:L153"/>
+    <mergeCell ref="G149:I149"/>
     <mergeCell ref="B155:D155"/>
     <mergeCell ref="G117:I117"/>
     <mergeCell ref="G119:I119"/>
@@ -5458,6 +5456,9 @@
     <mergeCell ref="C135:E135"/>
     <mergeCell ref="C129:E129"/>
     <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B151:D151"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B149:E149"/>
     <mergeCell ref="C85:E85"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="C39:E39"/>
@@ -5467,19 +5468,16 @@
     <mergeCell ref="C40:E40"/>
     <mergeCell ref="C44:E44"/>
     <mergeCell ref="G118:I118"/>
-    <mergeCell ref="B151:D151"/>
-    <mergeCell ref="G132:I132"/>
-    <mergeCell ref="G133:I133"/>
-    <mergeCell ref="G134:I134"/>
-    <mergeCell ref="C136:E136"/>
-    <mergeCell ref="C137:E137"/>
-    <mergeCell ref="C138:E138"/>
-    <mergeCell ref="C139:E139"/>
-    <mergeCell ref="C140:E140"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="G149:I149"/>
+    <mergeCell ref="G71:I71"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="G57:I57"/>
+    <mergeCell ref="G91:I91"/>
+    <mergeCell ref="G95:I95"/>
+    <mergeCell ref="G99:I99"/>
+    <mergeCell ref="G111:I111"/>
     <mergeCell ref="G150:I150"/>
     <mergeCell ref="B150:E150"/>
     <mergeCell ref="G136:I136"/>
@@ -5490,6 +5488,15 @@
     <mergeCell ref="C120:E120"/>
     <mergeCell ref="C121:E121"/>
     <mergeCell ref="C133:E133"/>
+    <mergeCell ref="G132:I132"/>
+    <mergeCell ref="G133:I133"/>
+    <mergeCell ref="G134:I134"/>
+    <mergeCell ref="C136:E136"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="C138:E138"/>
+    <mergeCell ref="C139:E139"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="B147:E147"/>
     <mergeCell ref="K123:M123"/>
     <mergeCell ref="K124:M124"/>
     <mergeCell ref="K125:M125"/>
@@ -5561,6 +5568,7 @@
     <mergeCell ref="K67:M67"/>
     <mergeCell ref="C68:E68"/>
     <mergeCell ref="G68:I68"/>
+    <mergeCell ref="C71:E71"/>
     <mergeCell ref="K83:M83"/>
     <mergeCell ref="C84:E84"/>
     <mergeCell ref="G84:I84"/>
@@ -5583,8 +5591,6 @@
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="C77:E77"/>
     <mergeCell ref="C81:E81"/>
-    <mergeCell ref="G71:I71"/>
-    <mergeCell ref="K71:M71"/>
     <mergeCell ref="C72:E72"/>
     <mergeCell ref="G72:I72"/>
     <mergeCell ref="K72:M72"/>
@@ -5594,7 +5600,6 @@
     <mergeCell ref="C76:E76"/>
     <mergeCell ref="G76:I76"/>
     <mergeCell ref="K76:M76"/>
-    <mergeCell ref="C71:E71"/>
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="G34:I34"/>
     <mergeCell ref="K34:M34"/>
@@ -5606,7 +5611,6 @@
     <mergeCell ref="C37:E37"/>
     <mergeCell ref="G37:I37"/>
     <mergeCell ref="K37:M37"/>
-    <mergeCell ref="G40:I40"/>
     <mergeCell ref="K40:M40"/>
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="G41:I41"/>
@@ -5616,7 +5620,6 @@
     <mergeCell ref="K42:M42"/>
     <mergeCell ref="G43:I43"/>
     <mergeCell ref="K43:M43"/>
-    <mergeCell ref="G44:I44"/>
     <mergeCell ref="K44:M44"/>
     <mergeCell ref="C45:E45"/>
     <mergeCell ref="G45:I45"/>
@@ -5627,7 +5630,6 @@
     <mergeCell ref="B47:E47"/>
     <mergeCell ref="G47:I47"/>
     <mergeCell ref="K47:M47"/>
-    <mergeCell ref="G49:I49"/>
     <mergeCell ref="K49:M49"/>
     <mergeCell ref="C50:E50"/>
     <mergeCell ref="G50:I50"/>
@@ -5638,7 +5640,6 @@
     <mergeCell ref="C52:E52"/>
     <mergeCell ref="G52:I52"/>
     <mergeCell ref="K52:M52"/>
-    <mergeCell ref="G53:I53"/>
     <mergeCell ref="K53:M53"/>
     <mergeCell ref="C54:E54"/>
     <mergeCell ref="G54:I54"/>
@@ -5649,7 +5650,6 @@
     <mergeCell ref="C56:E56"/>
     <mergeCell ref="G56:I56"/>
     <mergeCell ref="K56:M56"/>
-    <mergeCell ref="G57:I57"/>
     <mergeCell ref="K57:M57"/>
     <mergeCell ref="C58:E58"/>
     <mergeCell ref="G58:I58"/>
@@ -5673,7 +5673,7 @@
     <mergeCell ref="K87:M87"/>
     <mergeCell ref="C83:E83"/>
     <mergeCell ref="G83:I83"/>
-    <mergeCell ref="G91:I91"/>
+    <mergeCell ref="K71:M71"/>
     <mergeCell ref="K91:M91"/>
     <mergeCell ref="C92:E92"/>
     <mergeCell ref="G92:I92"/>
@@ -5684,7 +5684,6 @@
     <mergeCell ref="C94:E94"/>
     <mergeCell ref="G94:I94"/>
     <mergeCell ref="K94:M94"/>
-    <mergeCell ref="G95:I95"/>
     <mergeCell ref="K95:M95"/>
     <mergeCell ref="C96:E96"/>
     <mergeCell ref="G96:I96"/>
@@ -5695,7 +5694,6 @@
     <mergeCell ref="C98:E98"/>
     <mergeCell ref="G98:I98"/>
     <mergeCell ref="K98:M98"/>
-    <mergeCell ref="G99:I99"/>
     <mergeCell ref="K99:M99"/>
     <mergeCell ref="C100:E100"/>
     <mergeCell ref="G100:I100"/>
@@ -5709,7 +5707,6 @@
     <mergeCell ref="B103:E103"/>
     <mergeCell ref="G103:I103"/>
     <mergeCell ref="K103:M103"/>
-    <mergeCell ref="G111:I111"/>
     <mergeCell ref="K111:M111"/>
     <mergeCell ref="C112:E112"/>
     <mergeCell ref="G112:I112"/>

--- a/FPGA_Performance_Comparison_Red_Small.xlsx
+++ b/FPGA_Performance_Comparison_Red_Small.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/DanielBiswas/Desktop/Documents/University/Year 5/Semester 1/AMME4112/Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4E4237-C34E-2243-8324-F594525AACD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BE3258-4921-3746-9592-C2CF835A1DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="24080" windowHeight="26900" xr2:uid="{49DEC02E-5D37-064F-A7E8-1E1DC7B5FEA1}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="24080" windowHeight="17740" xr2:uid="{49DEC02E-5D37-064F-A7E8-1E1DC7B5FEA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="82">
   <si>
     <t>FPGA Implementation</t>
   </si>
@@ -270,6 +270,18 @@
   </si>
   <si>
     <t>Disparity Exact Match Pixels (Out Of 2916)</t>
+  </si>
+  <si>
+    <t>Disparity Exact Match Pixels (Out Of 8748)</t>
+  </si>
+  <si>
+    <t>Confidence Exact Match Pixels (Out Of 8748)</t>
+  </si>
+  <si>
+    <t>Confidence Exact Match Percentage</t>
+  </si>
+  <si>
+    <t>Disparity Exact Match Percentage</t>
   </si>
 </sst>
 </file>
@@ -380,17 +392,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -737,15 +749,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
+      <c r="B1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
       <c r="F1" s="6"/>
       <c r="G1" s="14" t="s">
         <v>55</v>
@@ -761,7 +773,7 @@
       <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="16"/>
+      <c r="A2" s="17"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -886,10 +898,10 @@
       <c r="C5" s="1">
         <v>136.59</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="17">
         <v>202.43</v>
       </c>
-      <c r="E5" s="16"/>
+      <c r="E5" s="17"/>
       <c r="F5" s="6"/>
       <c r="G5" s="1">
         <f>C5-B5</f>
@@ -944,10 +956,10 @@
       <c r="C7" s="1">
         <v>9776</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="17">
         <v>10129</v>
       </c>
-      <c r="E7" s="16"/>
+      <c r="E7" s="17"/>
       <c r="F7" s="6"/>
       <c r="G7" s="1">
         <f>C7-B7</f>
@@ -986,10 +998,10 @@
       <c r="C8" s="1">
         <v>24289</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="17">
         <v>27731</v>
       </c>
-      <c r="E8" s="16"/>
+      <c r="E8" s="17"/>
       <c r="F8" s="6"/>
       <c r="G8" s="1">
         <f>C8-B8</f>
@@ -1028,10 +1040,10 @@
       <c r="C9" s="1">
         <v>808736</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="17">
         <v>808736</v>
       </c>
-      <c r="E9" s="16"/>
+      <c r="E9" s="17"/>
       <c r="F9" s="6"/>
       <c r="G9" s="1">
         <f>C9-B9</f>
@@ -1070,10 +1082,10 @@
       <c r="C10" s="2">
         <v>12</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="17">
         <v>12</v>
       </c>
-      <c r="E10" s="16"/>
+      <c r="E10" s="17"/>
       <c r="F10" s="6"/>
       <c r="G10" s="1">
         <f>C10-B10</f>
@@ -2351,11 +2363,11 @@
       <c r="B45" s="5">
         <v>0.71570644999999999</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="18">
         <v>0.46913579999999999</v>
       </c>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
       <c r="F45" s="6"/>
       <c r="G45" s="14">
         <f t="shared" si="11"/>
@@ -3101,11 +3113,11 @@
       <c r="B73" s="5">
         <v>0.53292181000000005</v>
       </c>
-      <c r="C73" s="15">
+      <c r="C73" s="18">
         <v>0.16186556999999999</v>
       </c>
-      <c r="D73" s="15"/>
-      <c r="E73" s="15"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
       <c r="F73" s="6"/>
       <c r="G73" s="14">
         <f t="shared" si="16"/>
@@ -3845,11 +3857,11 @@
       <c r="B101" s="5">
         <v>0.89506173</v>
       </c>
-      <c r="C101" s="15">
+      <c r="C101" s="18">
         <v>0.74142660999999999</v>
       </c>
-      <c r="D101" s="15"/>
-      <c r="E101" s="15"/>
+      <c r="D101" s="18"/>
+      <c r="E101" s="18"/>
       <c r="F101" s="6"/>
       <c r="G101" s="14">
         <f t="shared" si="20"/>
@@ -4315,25 +4327,25 @@
         <v>33</v>
       </c>
       <c r="B119" s="1">
-        <f t="shared" ref="B119:B128" si="26">AVERAGE(B63,B35,B91)</f>
+        <f t="shared" ref="B119:C124" si="26">AVERAGE(B63,B35,B91)</f>
         <v>0.33664866666666665</v>
       </c>
       <c r="C119" s="14">
-        <f t="shared" ref="C119:C129" si="27">AVERAGE(C63,C35,C91)</f>
+        <f t="shared" si="26"/>
         <v>0.87391400000000008</v>
       </c>
       <c r="D119" s="14"/>
       <c r="E119" s="14"/>
       <c r="F119" s="6"/>
       <c r="G119" s="14">
-        <f t="shared" ref="G119:G129" si="28">C119-B119</f>
+        <f t="shared" ref="G119:G129" si="27">C119-B119</f>
         <v>0.53726533333333348</v>
       </c>
       <c r="H119" s="14"/>
       <c r="I119" s="14"/>
       <c r="J119" s="6"/>
       <c r="K119" s="13">
-        <f t="shared" ref="K119:K129" si="29">G119/B119</f>
+        <f t="shared" ref="K119:K129" si="28">G119/B119</f>
         <v>1.5959229503359591</v>
       </c>
       <c r="L119" s="13"/>
@@ -4345,19 +4357,25 @@
         <v>34</v>
       </c>
       <c r="B120" s="1">
-        <f t="shared" si="26"/>
+        <f>MEDIAN(B64,B36,B92)</f>
         <v>0</v>
       </c>
       <c r="C120" s="14">
-        <f t="shared" si="27"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D120" s="14"/>
-      <c r="E120" s="14"/>
+        <f t="shared" ref="C120:E121" si="29">MEDIAN(C64,C36,C92)</f>
+        <v>1</v>
+      </c>
+      <c r="D120" s="14" t="e">
+        <f t="shared" si="29"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="E120" s="14" t="e">
+        <f t="shared" si="29"/>
+        <v>#NUM!</v>
+      </c>
       <c r="F120" s="6"/>
       <c r="G120" s="14">
-        <f t="shared" si="28"/>
-        <v>0.66666666666666663</v>
+        <f t="shared" si="27"/>
+        <v>1</v>
       </c>
       <c r="H120" s="14"/>
       <c r="I120" s="14"/>
@@ -4374,19 +4392,25 @@
         <v>35</v>
       </c>
       <c r="B121" s="1">
-        <f t="shared" si="26"/>
+        <f>MEDIAN(B65,B37,B93)</f>
         <v>0</v>
       </c>
       <c r="C121" s="14">
-        <f t="shared" si="27"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D121" s="14"/>
-      <c r="E121" s="14"/>
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="D121" s="14" t="e">
+        <f t="shared" si="29"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="E121" s="14" t="e">
+        <f t="shared" si="29"/>
+        <v>#NUM!</v>
+      </c>
       <c r="F121" s="6"/>
       <c r="G121" s="14">
-        <f t="shared" si="28"/>
-        <v>0.66666666666666663</v>
+        <f t="shared" si="27"/>
+        <v>1</v>
       </c>
       <c r="H121" s="14"/>
       <c r="I121" s="14"/>
@@ -4403,26 +4427,26 @@
         <v>36</v>
       </c>
       <c r="B122" s="1">
-        <f t="shared" si="26"/>
-        <v>-3.3333333333333335</v>
+        <f>MIN(B66,B38,B94)</f>
+        <v>-4</v>
       </c>
       <c r="C122" s="14">
-        <f t="shared" si="27"/>
-        <v>-0.33333333333333331</v>
+        <f>MIN(C66,C38,C94)</f>
+        <v>-1</v>
       </c>
       <c r="D122" s="14"/>
       <c r="E122" s="14"/>
       <c r="F122" s="6"/>
       <c r="G122" s="14">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>3</v>
       </c>
       <c r="H122" s="14"/>
       <c r="I122" s="14"/>
       <c r="J122" s="6"/>
       <c r="K122" s="13">
-        <f t="shared" si="29"/>
-        <v>-0.89999999999999991</v>
+        <f t="shared" si="28"/>
+        <v>-0.75</v>
       </c>
       <c r="L122" s="13"/>
       <c r="M122" s="13"/>
@@ -4433,26 +4457,26 @@
         <v>37</v>
       </c>
       <c r="B123" s="1">
-        <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <f>MAX(B67,B39,B95)</f>
+        <v>2</v>
       </c>
       <c r="C123" s="14">
-        <f t="shared" si="27"/>
-        <v>5.333333333333333</v>
+        <f>MAX(C67,C39,C95)</f>
+        <v>6</v>
       </c>
       <c r="D123" s="14"/>
       <c r="E123" s="14"/>
       <c r="F123" s="6"/>
       <c r="G123" s="14">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>4</v>
       </c>
       <c r="H123" s="14"/>
       <c r="I123" s="14"/>
       <c r="J123" s="6"/>
       <c r="K123" s="13">
-        <f t="shared" si="29"/>
-        <v>3</v>
+        <f t="shared" si="28"/>
+        <v>2</v>
       </c>
       <c r="L123" s="13"/>
       <c r="M123" s="13"/>
@@ -4463,25 +4487,25 @@
         <v>38</v>
       </c>
       <c r="B124" s="1">
+        <f>AVERAGE(B68,B40,B96)</f>
+        <v>7.6147689999999999</v>
+      </c>
+      <c r="C124" s="14">
         <f t="shared" si="26"/>
-        <v>7.6147689999999999</v>
-      </c>
-      <c r="C124" s="14">
-        <f t="shared" si="27"/>
         <v>7.2099906666666662</v>
       </c>
       <c r="D124" s="14"/>
       <c r="E124" s="14"/>
       <c r="F124" s="6"/>
       <c r="G124" s="14">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>-0.40477833333333368</v>
       </c>
       <c r="H124" s="14"/>
       <c r="I124" s="14"/>
       <c r="J124" s="6"/>
       <c r="K124" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>-5.3157007564291668E-2</v>
       </c>
       <c r="L124" s="13"/>
@@ -4493,26 +4517,26 @@
         <v>39</v>
       </c>
       <c r="B125" s="1">
-        <f t="shared" si="26"/>
+        <f>MEDIAN(B69,B41,B97)</f>
         <v>8</v>
       </c>
       <c r="C125" s="14">
-        <f t="shared" si="27"/>
-        <v>7.333333333333333</v>
+        <f>MEDIAN(C69,C41,C97)</f>
+        <v>7</v>
       </c>
       <c r="D125" s="14"/>
       <c r="E125" s="14"/>
       <c r="F125" s="6"/>
       <c r="G125" s="14">
-        <f t="shared" si="28"/>
-        <v>-0.66666666666666696</v>
+        <f t="shared" si="27"/>
+        <v>-1</v>
       </c>
       <c r="H125" s="14"/>
       <c r="I125" s="14"/>
       <c r="J125" s="6"/>
       <c r="K125" s="13">
-        <f t="shared" si="29"/>
-        <v>-8.333333333333337E-2</v>
+        <f t="shared" si="28"/>
+        <v>-0.125</v>
       </c>
       <c r="L125" s="13"/>
       <c r="M125" s="13"/>
@@ -4523,25 +4547,25 @@
         <v>40</v>
       </c>
       <c r="B126" s="1">
-        <f t="shared" si="26"/>
+        <f>MAX(B70,B42,B98)</f>
         <v>8</v>
       </c>
       <c r="C126" s="14">
-        <f t="shared" si="27"/>
+        <f>MAX(C70,C42,C98)</f>
         <v>8</v>
       </c>
       <c r="D126" s="14"/>
       <c r="E126" s="14"/>
       <c r="F126" s="6"/>
       <c r="G126" s="14">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="H126" s="14"/>
       <c r="I126" s="14"/>
       <c r="J126" s="6"/>
       <c r="K126" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L126" s="13"/>
@@ -4553,26 +4577,26 @@
         <v>41</v>
       </c>
       <c r="B127" s="1">
-        <f t="shared" si="26"/>
-        <v>5.333333333333333</v>
+        <f>MIN(B71,B43,B99)</f>
+        <v>5</v>
       </c>
       <c r="C127" s="14">
-        <f t="shared" si="27"/>
-        <v>4.333333333333333</v>
+        <f>MIN(C71,C43,C99)</f>
+        <v>4</v>
       </c>
       <c r="D127" s="14"/>
       <c r="E127" s="14"/>
       <c r="F127" s="6"/>
       <c r="G127" s="14">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>-1</v>
       </c>
       <c r="H127" s="14"/>
       <c r="I127" s="14"/>
       <c r="J127" s="6"/>
       <c r="K127" s="13">
-        <f t="shared" si="29"/>
-        <v>-0.1875</v>
+        <f t="shared" si="28"/>
+        <v>-0.2</v>
       </c>
       <c r="L127" s="13"/>
       <c r="M127" s="13"/>
@@ -4580,29 +4604,29 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B128" s="1">
-        <f t="shared" si="26"/>
-        <v>2083.6666666666665</v>
+        <f>SUM(B72,B44,B100)</f>
+        <v>6251</v>
       </c>
       <c r="C128" s="14">
-        <f t="shared" si="27"/>
-        <v>1334</v>
+        <f>SUM(C72,C44,C100)</f>
+        <v>4002</v>
       </c>
       <c r="D128" s="14"/>
       <c r="E128" s="14"/>
       <c r="F128" s="6"/>
       <c r="G128" s="14">
-        <f t="shared" si="28"/>
-        <v>-749.66666666666652</v>
+        <f t="shared" si="27"/>
+        <v>-2249</v>
       </c>
       <c r="H128" s="14"/>
       <c r="I128" s="14"/>
       <c r="J128" s="6"/>
       <c r="K128" s="13">
-        <f t="shared" si="29"/>
-        <v>-0.35978243481043026</v>
+        <f t="shared" si="28"/>
+        <v>-0.35978243481043032</v>
       </c>
       <c r="L128" s="13"/>
       <c r="M128" s="13"/>
@@ -4610,29 +4634,29 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B129" s="5">
-        <f>AVERAGE(B73,B45,B101)</f>
-        <v>0.71456332999999994</v>
-      </c>
-      <c r="C129" s="17">
-        <f t="shared" si="27"/>
-        <v>0.45747599333333328</v>
+        <f>B128/8748</f>
+        <v>0.7145633287608596</v>
+      </c>
+      <c r="C129" s="16">
+        <f>C128/8748</f>
+        <v>0.45747599451303156</v>
       </c>
       <c r="D129" s="14"/>
       <c r="E129" s="14"/>
       <c r="F129" s="6"/>
       <c r="G129" s="14">
-        <f t="shared" si="28"/>
-        <v>-0.25708733666666667</v>
+        <f t="shared" si="27"/>
+        <v>-0.25708733424782804</v>
       </c>
       <c r="H129" s="14"/>
       <c r="I129" s="14"/>
       <c r="J129" s="6"/>
       <c r="K129" s="13">
-        <f t="shared" si="29"/>
-        <v>-0.3597824375715819</v>
+        <f t="shared" si="28"/>
+        <v>-0.35978243481043032</v>
       </c>
       <c r="L129" s="13"/>
       <c r="M129" s="13"/>
@@ -4687,14 +4711,14 @@
         <v>1.2035893333333334</v>
       </c>
       <c r="C132" s="14">
-        <f t="shared" ref="C132:C143" si="30">AVERAGE(C76,C48,C104)</f>
+        <f>AVERAGE(C76,C48,C104)</f>
         <v>1.1233423333333332</v>
       </c>
       <c r="D132" s="14"/>
       <c r="E132" s="14"/>
       <c r="F132" s="6"/>
       <c r="G132" s="14">
-        <f t="shared" ref="G132:G143" si="31">C132-B132</f>
+        <f t="shared" ref="G132:G143" si="30">C132-B132</f>
         <v>-8.0247000000000179E-2</v>
       </c>
       <c r="H132" s="14"/>
@@ -4713,25 +4737,25 @@
         <v>44</v>
       </c>
       <c r="B133" s="1">
-        <f t="shared" ref="B133:B142" si="32">AVERAGE(B77,B49,B105)</f>
+        <f t="shared" ref="B133:C138" si="31">AVERAGE(B77,B49,B105)</f>
         <v>0.61122533333333329</v>
       </c>
       <c r="C133" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.58699133333333331</v>
       </c>
       <c r="D133" s="14"/>
       <c r="E133" s="14"/>
       <c r="F133" s="6"/>
       <c r="G133" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>-2.4233999999999978E-2</v>
       </c>
       <c r="H133" s="14"/>
       <c r="I133" s="14"/>
       <c r="J133" s="6"/>
       <c r="K133" s="13">
-        <f t="shared" ref="K133:K143" si="33">G133/B133</f>
+        <f t="shared" ref="K133:K143" si="32">G133/B133</f>
         <v>-3.9648225749805276E-2</v>
       </c>
       <c r="L133" s="13"/>
@@ -4743,26 +4767,26 @@
         <v>45</v>
       </c>
       <c r="B134" s="1">
-        <f t="shared" si="32"/>
-        <v>0.66666666666666663</v>
+        <f>MEDIAN(B78,B50,B106)</f>
+        <v>0</v>
       </c>
       <c r="C134" s="14">
-        <f t="shared" si="30"/>
-        <v>0.66666666666666663</v>
+        <f>MEDIAN(C78,C50,C106)</f>
+        <v>0</v>
       </c>
       <c r="D134" s="14"/>
       <c r="E134" s="14"/>
       <c r="F134" s="6"/>
       <c r="G134" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H134" s="14"/>
       <c r="I134" s="14"/>
       <c r="J134" s="6"/>
-      <c r="K134" s="13">
-        <f t="shared" si="33"/>
-        <v>0</v>
+      <c r="K134" s="13" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="L134" s="13"/>
       <c r="M134" s="13"/>
@@ -4773,26 +4797,26 @@
         <v>46</v>
       </c>
       <c r="B135" s="1">
-        <f t="shared" si="32"/>
-        <v>-0.66666666666666663</v>
+        <f>MEDIAN(B79,B51,B107)</f>
+        <v>0</v>
       </c>
       <c r="C135" s="14">
-        <f t="shared" si="30"/>
-        <v>-0.66666666666666663</v>
+        <f>MEDIAN(C79,C51,C107)</f>
+        <v>0</v>
       </c>
       <c r="D135" s="14"/>
       <c r="E135" s="14"/>
       <c r="F135" s="6"/>
       <c r="G135" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H135" s="14"/>
       <c r="I135" s="14"/>
       <c r="J135" s="6"/>
-      <c r="K135" s="13">
-        <f t="shared" si="33"/>
-        <v>0</v>
+      <c r="K135" s="13" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="L135" s="13"/>
       <c r="M135" s="13"/>
@@ -4803,25 +4827,25 @@
         <v>47</v>
       </c>
       <c r="B136" s="1">
-        <f t="shared" si="32"/>
-        <v>-1.6666666666666667</v>
+        <f>MIN(B80,B52,B108)</f>
+        <v>-3</v>
       </c>
       <c r="C136" s="14">
-        <f t="shared" si="30"/>
-        <v>-1.6666666666666667</v>
+        <f>MIN(C80,C52,C108)</f>
+        <v>-3</v>
       </c>
       <c r="D136" s="14"/>
       <c r="E136" s="14"/>
       <c r="F136" s="6"/>
       <c r="G136" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H136" s="14"/>
       <c r="I136" s="14"/>
       <c r="J136" s="6"/>
       <c r="K136" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="L136" s="13"/>
@@ -4833,26 +4857,26 @@
         <v>48</v>
       </c>
       <c r="B137" s="1">
-        <f t="shared" si="32"/>
-        <v>1.6666666666666667</v>
+        <f>MAX(B81,B53,B109)</f>
+        <v>4</v>
       </c>
       <c r="C137" s="14">
-        <f t="shared" si="30"/>
-        <v>3.6666666666666665</v>
+        <f>MAX(C81,C53,C109)</f>
+        <v>8</v>
       </c>
       <c r="D137" s="14"/>
       <c r="E137" s="14"/>
       <c r="F137" s="6"/>
       <c r="G137" s="14">
-        <f t="shared" si="31"/>
-        <v>1.9999999999999998</v>
+        <f t="shared" si="30"/>
+        <v>4</v>
       </c>
       <c r="H137" s="14"/>
       <c r="I137" s="14"/>
       <c r="J137" s="6"/>
       <c r="K137" s="13">
-        <f t="shared" si="33"/>
-        <v>1.1999999999999997</v>
+        <f t="shared" si="32"/>
+        <v>1</v>
       </c>
       <c r="L137" s="13"/>
       <c r="M137" s="13"/>
@@ -4863,25 +4887,25 @@
         <v>49</v>
       </c>
       <c r="B138" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>7.5983083333333328</v>
       </c>
       <c r="C138" s="14">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>7.6023089999999991</v>
       </c>
       <c r="D138" s="14"/>
       <c r="E138" s="14"/>
       <c r="F138" s="6"/>
       <c r="G138" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>4.0006666666663193E-3</v>
       </c>
       <c r="H138" s="14"/>
       <c r="I138" s="14"/>
       <c r="J138" s="6"/>
       <c r="K138" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>5.2652070581495482E-4</v>
       </c>
       <c r="L138" s="13"/>
@@ -4893,25 +4917,25 @@
         <v>50</v>
       </c>
       <c r="B139" s="1">
-        <f t="shared" si="32"/>
-        <v>7.666666666666667</v>
+        <f>MEDIAN(B83,B55,B111)</f>
+        <v>8</v>
       </c>
       <c r="C139" s="14">
-        <f t="shared" si="30"/>
-        <v>7.666666666666667</v>
+        <f>MEDIAN(C83,C55,C111)</f>
+        <v>8</v>
       </c>
       <c r="D139" s="14"/>
       <c r="E139" s="14"/>
       <c r="F139" s="6"/>
       <c r="G139" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H139" s="14"/>
       <c r="I139" s="14"/>
       <c r="J139" s="6"/>
       <c r="K139" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="L139" s="13"/>
@@ -4923,25 +4947,25 @@
         <v>51</v>
       </c>
       <c r="B140" s="1">
-        <f t="shared" si="32"/>
+        <f>MAX(B84,B56,B112)</f>
         <v>8</v>
       </c>
       <c r="C140" s="14">
-        <f t="shared" si="30"/>
+        <f>MAX(C84,C56,C112)</f>
         <v>8</v>
       </c>
       <c r="D140" s="14"/>
       <c r="E140" s="14"/>
       <c r="F140" s="6"/>
       <c r="G140" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H140" s="14"/>
       <c r="I140" s="14"/>
       <c r="J140" s="6"/>
       <c r="K140" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="L140" s="13"/>
@@ -4953,25 +4977,25 @@
         <v>52</v>
       </c>
       <c r="B141" s="1">
-        <f t="shared" si="32"/>
-        <v>6.666666666666667</v>
+        <f>MIN(B85,B57,B113)</f>
+        <v>5</v>
       </c>
       <c r="C141" s="14">
-        <f t="shared" si="30"/>
-        <v>6.666666666666667</v>
+        <f>MIN(C85,C57,C113)</f>
+        <v>5</v>
       </c>
       <c r="D141" s="14"/>
       <c r="E141" s="14"/>
       <c r="F141" s="6"/>
       <c r="G141" s="14">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H141" s="14"/>
       <c r="I141" s="14"/>
       <c r="J141" s="6"/>
       <c r="K141" s="13">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="L141" s="13"/>
@@ -4980,29 +5004,29 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B142" s="1">
-        <f t="shared" si="32"/>
-        <v>1958.3333333333333</v>
+        <f>SUM(B86,B58,B114)</f>
+        <v>5875</v>
       </c>
       <c r="C142" s="14">
-        <f t="shared" si="30"/>
-        <v>1964.6666666666667</v>
+        <f>SUM(C86,C58,C114)</f>
+        <v>5894</v>
       </c>
       <c r="D142" s="14"/>
       <c r="E142" s="14"/>
       <c r="F142" s="6"/>
       <c r="G142" s="14">
-        <f t="shared" si="31"/>
-        <v>6.3333333333334849</v>
+        <f t="shared" si="30"/>
+        <v>19</v>
       </c>
       <c r="H142" s="14"/>
       <c r="I142" s="14"/>
       <c r="J142" s="6"/>
       <c r="K142" s="13">
-        <f t="shared" si="33"/>
-        <v>3.2340425531915667E-3</v>
+        <f t="shared" si="32"/>
+        <v>3.2340425531914895E-3</v>
       </c>
       <c r="L142" s="13"/>
       <c r="M142" s="13"/>
@@ -5010,29 +5034,29 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="B143" s="5">
-        <f>AVERAGE(B87,B59,B115)</f>
-        <v>0.67158207666666669</v>
-      </c>
-      <c r="C143" s="17">
-        <f t="shared" si="30"/>
-        <v>0.67375400000000008</v>
+        <f>B142/8748</f>
+        <v>0.67158207590306351</v>
+      </c>
+      <c r="C143" s="16">
+        <f>C142/8748</f>
+        <v>0.67375400091449478</v>
       </c>
       <c r="D143" s="14"/>
       <c r="E143" s="14"/>
       <c r="F143" s="6"/>
       <c r="G143" s="14">
-        <f t="shared" si="31"/>
-        <v>2.1719233333333809E-3</v>
+        <f t="shared" si="30"/>
+        <v>2.1719250114312638E-3</v>
       </c>
       <c r="H143" s="14"/>
       <c r="I143" s="14"/>
       <c r="J143" s="6"/>
       <c r="K143" s="13">
-        <f t="shared" si="33"/>
-        <v>3.2340400507909835E-3</v>
+        <f t="shared" si="32"/>
+        <v>3.2340425531916079E-3</v>
       </c>
       <c r="L143" s="13"/>
       <c r="M143" s="13"/>
@@ -5071,11 +5095,11 @@
       <c r="H145" s="14"/>
       <c r="I145" s="14"/>
       <c r="J145" s="6"/>
-      <c r="K145" s="18">
-        <v>0</v>
-      </c>
-      <c r="L145" s="18"/>
-      <c r="M145" s="18"/>
+      <c r="K145" s="15">
+        <v>0</v>
+      </c>
+      <c r="L145" s="15"/>
+      <c r="M145" s="15"/>
       <c r="N145" s="6"/>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.2">
@@ -5395,6 +5419,335 @@
     </row>
   </sheetData>
   <mergeCells count="353">
+    <mergeCell ref="K118:M118"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="G61:I61"/>
+    <mergeCell ref="K61:M61"/>
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="G75:I75"/>
+    <mergeCell ref="K75:M75"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="K33:M33"/>
+    <mergeCell ref="C113:E113"/>
+    <mergeCell ref="G113:I113"/>
+    <mergeCell ref="K113:M113"/>
+    <mergeCell ref="C114:E114"/>
+    <mergeCell ref="G114:I114"/>
+    <mergeCell ref="K114:M114"/>
+    <mergeCell ref="C115:E115"/>
+    <mergeCell ref="G115:I115"/>
+    <mergeCell ref="K115:M115"/>
+    <mergeCell ref="G109:I109"/>
+    <mergeCell ref="K109:M109"/>
+    <mergeCell ref="C110:E110"/>
+    <mergeCell ref="G110:I110"/>
+    <mergeCell ref="K110:M110"/>
+    <mergeCell ref="K111:M111"/>
+    <mergeCell ref="C112:E112"/>
+    <mergeCell ref="G112:I112"/>
+    <mergeCell ref="K112:M112"/>
+    <mergeCell ref="G105:I105"/>
+    <mergeCell ref="K105:M105"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="G106:I106"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="C107:E107"/>
+    <mergeCell ref="G107:I107"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="C108:E108"/>
+    <mergeCell ref="G108:I108"/>
+    <mergeCell ref="K108:M108"/>
+    <mergeCell ref="C105:E105"/>
+    <mergeCell ref="C109:E109"/>
+    <mergeCell ref="K99:M99"/>
+    <mergeCell ref="C100:E100"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="K100:M100"/>
+    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="G101:I101"/>
+    <mergeCell ref="K101:M101"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="G104:I104"/>
+    <mergeCell ref="K104:M104"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="G103:I103"/>
+    <mergeCell ref="K103:M103"/>
+    <mergeCell ref="K95:M95"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="G96:I96"/>
+    <mergeCell ref="K96:M96"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="G97:I97"/>
+    <mergeCell ref="K97:M97"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="G98:I98"/>
+    <mergeCell ref="K98:M98"/>
+    <mergeCell ref="K91:M91"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="G92:I92"/>
+    <mergeCell ref="K92:M92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="G93:I93"/>
+    <mergeCell ref="K93:M93"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="G94:I94"/>
+    <mergeCell ref="K94:M94"/>
+    <mergeCell ref="K57:M57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="G58:I58"/>
+    <mergeCell ref="K58:M58"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="G59:I59"/>
+    <mergeCell ref="K59:M59"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="G90:I90"/>
+    <mergeCell ref="K90:M90"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="G89:I89"/>
+    <mergeCell ref="K89:M89"/>
+    <mergeCell ref="G85:I85"/>
+    <mergeCell ref="K85:M85"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="G86:I86"/>
+    <mergeCell ref="K86:M86"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="K87:M87"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="G83:I83"/>
+    <mergeCell ref="K71:M71"/>
+    <mergeCell ref="K53:M53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="K54:M54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="G55:I55"/>
+    <mergeCell ref="K55:M55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="K56:M56"/>
+    <mergeCell ref="K49:M49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="K50:M50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="K51:M51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="K42:M42"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="K43:M43"/>
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="K45:M45"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="K47:M47"/>
+    <mergeCell ref="K72:M72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="G73:I73"/>
+    <mergeCell ref="K73:M73"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="G76:I76"/>
+    <mergeCell ref="K76:M76"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="K83:M83"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="G84:I84"/>
+    <mergeCell ref="K84:M84"/>
+    <mergeCell ref="G77:I77"/>
+    <mergeCell ref="K77:M77"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="G78:I78"/>
+    <mergeCell ref="K78:M78"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="G79:I79"/>
+    <mergeCell ref="K79:M79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="G80:I80"/>
+    <mergeCell ref="K80:M80"/>
+    <mergeCell ref="G81:I81"/>
+    <mergeCell ref="K81:M81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="G82:I82"/>
+    <mergeCell ref="K82:M82"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="K68:M68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="G69:I69"/>
+    <mergeCell ref="K69:M69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="G70:I70"/>
+    <mergeCell ref="K70:M70"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="K67:M67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="G68:I68"/>
+    <mergeCell ref="K117:M117"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="G62:I62"/>
+    <mergeCell ref="K62:M62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="G63:I63"/>
+    <mergeCell ref="K63:M63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="G64:I64"/>
+    <mergeCell ref="K64:M64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="K65:M65"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="G66:I66"/>
+    <mergeCell ref="K66:M66"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="G67:I67"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="K123:M123"/>
+    <mergeCell ref="K124:M124"/>
+    <mergeCell ref="K125:M125"/>
+    <mergeCell ref="G140:I140"/>
+    <mergeCell ref="K126:M126"/>
+    <mergeCell ref="K127:M127"/>
+    <mergeCell ref="K128:M128"/>
+    <mergeCell ref="K129:M129"/>
+    <mergeCell ref="K119:M119"/>
+    <mergeCell ref="K120:M120"/>
+    <mergeCell ref="K121:M121"/>
+    <mergeCell ref="K122:M122"/>
+    <mergeCell ref="K132:M132"/>
+    <mergeCell ref="K133:M133"/>
+    <mergeCell ref="K134:M134"/>
+    <mergeCell ref="K135:M135"/>
+    <mergeCell ref="K136:M136"/>
+    <mergeCell ref="K137:M137"/>
+    <mergeCell ref="K138:M138"/>
+    <mergeCell ref="K139:M139"/>
+    <mergeCell ref="K140:M140"/>
+    <mergeCell ref="G131:I131"/>
+    <mergeCell ref="K131:M131"/>
+    <mergeCell ref="G150:I150"/>
+    <mergeCell ref="B150:E150"/>
+    <mergeCell ref="G136:I136"/>
+    <mergeCell ref="G137:I137"/>
+    <mergeCell ref="G138:I138"/>
+    <mergeCell ref="G139:I139"/>
+    <mergeCell ref="C119:E119"/>
+    <mergeCell ref="C120:E120"/>
+    <mergeCell ref="C121:E121"/>
+    <mergeCell ref="C133:E133"/>
+    <mergeCell ref="G132:I132"/>
+    <mergeCell ref="G133:I133"/>
+    <mergeCell ref="G134:I134"/>
+    <mergeCell ref="C136:E136"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="C138:E138"/>
+    <mergeCell ref="C139:E139"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="G118:I118"/>
+    <mergeCell ref="G71:I71"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="G57:I57"/>
+    <mergeCell ref="G91:I91"/>
+    <mergeCell ref="G95:I95"/>
+    <mergeCell ref="G99:I99"/>
+    <mergeCell ref="G111:I111"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="G72:I72"/>
+    <mergeCell ref="B153:D153"/>
+    <mergeCell ref="C122:E122"/>
+    <mergeCell ref="C123:E123"/>
+    <mergeCell ref="C132:E132"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="C118:E118"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="C111:E111"/>
+    <mergeCell ref="C134:E134"/>
+    <mergeCell ref="C135:E135"/>
+    <mergeCell ref="C129:E129"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B151:D151"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="B155:D155"/>
+    <mergeCell ref="G117:I117"/>
+    <mergeCell ref="G119:I119"/>
+    <mergeCell ref="G120:I120"/>
+    <mergeCell ref="G121:I121"/>
+    <mergeCell ref="G122:I122"/>
+    <mergeCell ref="G123:I123"/>
+    <mergeCell ref="G124:I124"/>
+    <mergeCell ref="G125:I125"/>
+    <mergeCell ref="G126:I126"/>
+    <mergeCell ref="G127:I127"/>
+    <mergeCell ref="G128:I128"/>
+    <mergeCell ref="G129:I129"/>
+    <mergeCell ref="C124:E124"/>
+    <mergeCell ref="C125:E125"/>
+    <mergeCell ref="C126:E126"/>
+    <mergeCell ref="C127:E127"/>
+    <mergeCell ref="C128:E128"/>
+    <mergeCell ref="G155:H155"/>
+    <mergeCell ref="B152:E152"/>
+    <mergeCell ref="C141:E141"/>
+    <mergeCell ref="C142:E142"/>
+    <mergeCell ref="C143:E143"/>
+    <mergeCell ref="G135:I135"/>
     <mergeCell ref="K155:L155"/>
     <mergeCell ref="G141:I141"/>
     <mergeCell ref="G142:I142"/>
@@ -5419,335 +5772,6 @@
     <mergeCell ref="K151:L151"/>
     <mergeCell ref="K153:L153"/>
     <mergeCell ref="G149:I149"/>
-    <mergeCell ref="B155:D155"/>
-    <mergeCell ref="G117:I117"/>
-    <mergeCell ref="G119:I119"/>
-    <mergeCell ref="G120:I120"/>
-    <mergeCell ref="G121:I121"/>
-    <mergeCell ref="G122:I122"/>
-    <mergeCell ref="G123:I123"/>
-    <mergeCell ref="G124:I124"/>
-    <mergeCell ref="G125:I125"/>
-    <mergeCell ref="G126:I126"/>
-    <mergeCell ref="G127:I127"/>
-    <mergeCell ref="G128:I128"/>
-    <mergeCell ref="G129:I129"/>
-    <mergeCell ref="C124:E124"/>
-    <mergeCell ref="C125:E125"/>
-    <mergeCell ref="C126:E126"/>
-    <mergeCell ref="C127:E127"/>
-    <mergeCell ref="C128:E128"/>
-    <mergeCell ref="G155:H155"/>
-    <mergeCell ref="B152:E152"/>
-    <mergeCell ref="C141:E141"/>
-    <mergeCell ref="C142:E142"/>
-    <mergeCell ref="C143:E143"/>
-    <mergeCell ref="G135:I135"/>
-    <mergeCell ref="B153:D153"/>
-    <mergeCell ref="C122:E122"/>
-    <mergeCell ref="C123:E123"/>
-    <mergeCell ref="C132:E132"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="C118:E118"/>
-    <mergeCell ref="B145:E145"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="C111:E111"/>
-    <mergeCell ref="C134:E134"/>
-    <mergeCell ref="C135:E135"/>
-    <mergeCell ref="C129:E129"/>
-    <mergeCell ref="B131:E131"/>
-    <mergeCell ref="B151:D151"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="C85:E85"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="G118:I118"/>
-    <mergeCell ref="G71:I71"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="G44:I44"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="G53:I53"/>
-    <mergeCell ref="G57:I57"/>
-    <mergeCell ref="G91:I91"/>
-    <mergeCell ref="G95:I95"/>
-    <mergeCell ref="G99:I99"/>
-    <mergeCell ref="G111:I111"/>
-    <mergeCell ref="G150:I150"/>
-    <mergeCell ref="B150:E150"/>
-    <mergeCell ref="G136:I136"/>
-    <mergeCell ref="G137:I137"/>
-    <mergeCell ref="G138:I138"/>
-    <mergeCell ref="G139:I139"/>
-    <mergeCell ref="C119:E119"/>
-    <mergeCell ref="C120:E120"/>
-    <mergeCell ref="C121:E121"/>
-    <mergeCell ref="C133:E133"/>
-    <mergeCell ref="G132:I132"/>
-    <mergeCell ref="G133:I133"/>
-    <mergeCell ref="G134:I134"/>
-    <mergeCell ref="C136:E136"/>
-    <mergeCell ref="C137:E137"/>
-    <mergeCell ref="C138:E138"/>
-    <mergeCell ref="C139:E139"/>
-    <mergeCell ref="C140:E140"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="K123:M123"/>
-    <mergeCell ref="K124:M124"/>
-    <mergeCell ref="K125:M125"/>
-    <mergeCell ref="G140:I140"/>
-    <mergeCell ref="K126:M126"/>
-    <mergeCell ref="K127:M127"/>
-    <mergeCell ref="K128:M128"/>
-    <mergeCell ref="K129:M129"/>
-    <mergeCell ref="K119:M119"/>
-    <mergeCell ref="K120:M120"/>
-    <mergeCell ref="K121:M121"/>
-    <mergeCell ref="K122:M122"/>
-    <mergeCell ref="K132:M132"/>
-    <mergeCell ref="K133:M133"/>
-    <mergeCell ref="K134:M134"/>
-    <mergeCell ref="K135:M135"/>
-    <mergeCell ref="K136:M136"/>
-    <mergeCell ref="K137:M137"/>
-    <mergeCell ref="K138:M138"/>
-    <mergeCell ref="K139:M139"/>
-    <mergeCell ref="K140:M140"/>
-    <mergeCell ref="G131:I131"/>
-    <mergeCell ref="K131:M131"/>
-    <mergeCell ref="K117:M117"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="G62:I62"/>
-    <mergeCell ref="K62:M62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="G63:I63"/>
-    <mergeCell ref="K63:M63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="G64:I64"/>
-    <mergeCell ref="K64:M64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="G65:I65"/>
-    <mergeCell ref="K65:M65"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="G66:I66"/>
-    <mergeCell ref="K66:M66"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="G67:I67"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="K68:M68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="G69:I69"/>
-    <mergeCell ref="K69:M69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="G70:I70"/>
-    <mergeCell ref="K70:M70"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="K67:M67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="G68:I68"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="K83:M83"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="G84:I84"/>
-    <mergeCell ref="K84:M84"/>
-    <mergeCell ref="G77:I77"/>
-    <mergeCell ref="K77:M77"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="G78:I78"/>
-    <mergeCell ref="K78:M78"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="G79:I79"/>
-    <mergeCell ref="K79:M79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="G80:I80"/>
-    <mergeCell ref="K80:M80"/>
-    <mergeCell ref="G81:I81"/>
-    <mergeCell ref="K81:M81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="G82:I82"/>
-    <mergeCell ref="K82:M82"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="G72:I72"/>
-    <mergeCell ref="K72:M72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="G73:I73"/>
-    <mergeCell ref="K73:M73"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="G76:I76"/>
-    <mergeCell ref="K76:M76"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="K37:M37"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="G41:I41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="G42:I42"/>
-    <mergeCell ref="K42:M42"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="K43:M43"/>
-    <mergeCell ref="K44:M44"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="G45:I45"/>
-    <mergeCell ref="K45:M45"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="K48:M48"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="K47:M47"/>
-    <mergeCell ref="K49:M49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="K50:M50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="K51:M51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="K53:M53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="K54:M54"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="G55:I55"/>
-    <mergeCell ref="K55:M55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="G56:I56"/>
-    <mergeCell ref="K56:M56"/>
-    <mergeCell ref="K57:M57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="G58:I58"/>
-    <mergeCell ref="K58:M58"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="G59:I59"/>
-    <mergeCell ref="K59:M59"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="G90:I90"/>
-    <mergeCell ref="K90:M90"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="G89:I89"/>
-    <mergeCell ref="K89:M89"/>
-    <mergeCell ref="G85:I85"/>
-    <mergeCell ref="K85:M85"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="G86:I86"/>
-    <mergeCell ref="K86:M86"/>
-    <mergeCell ref="C87:E87"/>
-    <mergeCell ref="G87:I87"/>
-    <mergeCell ref="K87:M87"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="G83:I83"/>
-    <mergeCell ref="K71:M71"/>
-    <mergeCell ref="K91:M91"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="G92:I92"/>
-    <mergeCell ref="K92:M92"/>
-    <mergeCell ref="C93:E93"/>
-    <mergeCell ref="G93:I93"/>
-    <mergeCell ref="K93:M93"/>
-    <mergeCell ref="C94:E94"/>
-    <mergeCell ref="G94:I94"/>
-    <mergeCell ref="K94:M94"/>
-    <mergeCell ref="K95:M95"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="G96:I96"/>
-    <mergeCell ref="K96:M96"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="G97:I97"/>
-    <mergeCell ref="K97:M97"/>
-    <mergeCell ref="C98:E98"/>
-    <mergeCell ref="G98:I98"/>
-    <mergeCell ref="K98:M98"/>
-    <mergeCell ref="K99:M99"/>
-    <mergeCell ref="C100:E100"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="K100:M100"/>
-    <mergeCell ref="C101:E101"/>
-    <mergeCell ref="G101:I101"/>
-    <mergeCell ref="K101:M101"/>
-    <mergeCell ref="C104:E104"/>
-    <mergeCell ref="G104:I104"/>
-    <mergeCell ref="K104:M104"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="G103:I103"/>
-    <mergeCell ref="K103:M103"/>
-    <mergeCell ref="K111:M111"/>
-    <mergeCell ref="C112:E112"/>
-    <mergeCell ref="G112:I112"/>
-    <mergeCell ref="K112:M112"/>
-    <mergeCell ref="G105:I105"/>
-    <mergeCell ref="K105:M105"/>
-    <mergeCell ref="C106:E106"/>
-    <mergeCell ref="G106:I106"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="C107:E107"/>
-    <mergeCell ref="G107:I107"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="C108:E108"/>
-    <mergeCell ref="G108:I108"/>
-    <mergeCell ref="K108:M108"/>
-    <mergeCell ref="C105:E105"/>
-    <mergeCell ref="C109:E109"/>
-    <mergeCell ref="K118:M118"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="G61:I61"/>
-    <mergeCell ref="K61:M61"/>
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="G75:I75"/>
-    <mergeCell ref="K75:M75"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="K33:M33"/>
-    <mergeCell ref="C113:E113"/>
-    <mergeCell ref="G113:I113"/>
-    <mergeCell ref="K113:M113"/>
-    <mergeCell ref="C114:E114"/>
-    <mergeCell ref="G114:I114"/>
-    <mergeCell ref="K114:M114"/>
-    <mergeCell ref="C115:E115"/>
-    <mergeCell ref="G115:I115"/>
-    <mergeCell ref="K115:M115"/>
-    <mergeCell ref="G109:I109"/>
-    <mergeCell ref="K109:M109"/>
-    <mergeCell ref="C110:E110"/>
-    <mergeCell ref="G110:I110"/>
-    <mergeCell ref="K110:M110"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
